--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7561FC-557B-4F41-A002-78F16E2CF6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3777A24-5516-4F92-B1E5-8B2E37F67EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5327" uniqueCount="1937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5327" uniqueCount="1938">
   <si>
     <t>Prénom</t>
   </si>
@@ -4534,18 +4534,12 @@
     <t>"Le Rêve de l'Architecte"</t>
   </si>
   <si>
-    <t>"L'Oxbow</t>
-  </si>
-  <si>
     <t>Série allégorique de quatre tableaux</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/c/c6/Cole_Thomas_The_Architect-s_Dream_1840.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/a3/Thomas_Cole%2C_The_Oxbow.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
     <t>213,6 cm</t>
   </si>
   <si>
@@ -5831,6 +5825,15 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/08/Dante_Gabriel_Rossetti_-_Ecce_Ancilla_Domini%21_-_Google_Art_Project.jpg/960px-Dante_Gabriel_Rossetti_-_Ecce_Ancilla_Domini%21_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>"Le Départ"</t>
+  </si>
+  <si>
+    <t>161,6 cm</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Thomas_Cole%2C_The_Departure%2C_1837%2C_NGA_166439.jpg/1280px-Thomas_Cole%2C_The_Departure%2C_1837%2C_NGA_166439.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -10232,7 +10235,7 @@
       <c r="M86" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="N86" s="7" t="s">
+      <c r="N86" s="8" t="s">
         <v>347</v>
       </c>
       <c r="S86" s="1" t="s">
@@ -10276,11 +10279,11 @@
       <c r="M87" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="N87" s="7" t="s">
+      <c r="N87" s="8" t="s">
         <v>352</v>
       </c>
       <c r="O87" s="7" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="S87" s="1" t="s">
         <v>32</v>
@@ -10324,16 +10327,16 @@
         <v>1503</v>
       </c>
       <c r="N88" s="8" t="s">
+        <v>1505</v>
+      </c>
+      <c r="S88" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T88" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="U88" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="S88" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T88" s="1" t="s">
-        <v>1509</v>
-      </c>
-      <c r="U88" s="1" t="s">
-        <v>1508</v>
       </c>
       <c r="W88" s="1" t="s">
         <v>103</v>
@@ -10356,28 +10359,28 @@
         <v>210</v>
       </c>
       <c r="H89" s="11">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>80</v>
+        <v>242</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>1504</v>
+        <v>1935</v>
       </c>
       <c r="N89" s="8" t="s">
-        <v>1507</v>
+        <v>1937</v>
       </c>
       <c r="S89" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T89" s="1" t="s">
-        <v>348</v>
+        <v>250</v>
       </c>
       <c r="U89" s="1" t="s">
-        <v>349</v>
+        <v>1936</v>
       </c>
       <c r="W89" s="1" t="s">
         <v>103</v>
@@ -10497,10 +10500,10 @@
         <v>366</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="N92" s="8" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="S92" s="1" t="s">
         <v>32</v>
@@ -10509,7 +10512,7 @@
         <v>678</v>
       </c>
       <c r="U92" s="1" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="W92" s="1" t="s">
         <v>122</v>
@@ -10541,16 +10544,16 @@
         <v>360</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="N93" s="8" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="S93" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T93" s="1" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="U93" s="1" t="s">
         <v>945</v>
@@ -10796,7 +10799,7 @@
         <v>211</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>66</v>
@@ -10805,16 +10808,16 @@
         <v>316</v>
       </c>
       <c r="M99" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="N99" s="8" t="s">
+        <v>1520</v>
+      </c>
+      <c r="S99" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T99" s="1" t="s">
         <v>1516</v>
-      </c>
-      <c r="N99" s="8" t="s">
-        <v>1522</v>
-      </c>
-      <c r="S99" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T99" s="1" t="s">
-        <v>1518</v>
       </c>
       <c r="U99" s="1" t="s">
         <v>262</v>
@@ -10849,16 +10852,16 @@
         <v>316</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="N100" s="8" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="S100" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T100" s="1" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="U100" s="1" t="s">
         <v>980</v>
@@ -10893,10 +10896,10 @@
         <v>316</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="N101" s="8" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="S101" s="1" t="s">
         <v>32</v>
@@ -11547,16 +11550,16 @@
         <v>1864</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="J116" s="1" t="s">
         <v>566</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="N116" s="8" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="S116" s="1" t="s">
         <v>32</v>
@@ -11565,7 +11568,7 @@
         <v>1205</v>
       </c>
       <c r="U116" s="1" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="W116" s="1" t="s">
         <v>72</v>
@@ -11588,28 +11591,28 @@
         <v>178</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="J117" s="1" t="s">
         <v>1097</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="N117" s="8" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="S117" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T117" s="1" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="U117" s="1" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="W117" s="1" t="s">
         <v>72</v>
@@ -11858,19 +11861,19 @@
         <v>466</v>
       </c>
       <c r="M123" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="N123" s="8" t="s">
+        <v>1540</v>
+      </c>
+      <c r="S123" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T123" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="U123" s="1" t="s">
         <v>1534</v>
-      </c>
-      <c r="N123" s="8" t="s">
-        <v>1542</v>
-      </c>
-      <c r="S123" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T123" s="1" t="s">
-        <v>1535</v>
-      </c>
-      <c r="U123" s="1" t="s">
-        <v>1536</v>
       </c>
       <c r="W123" s="1" t="s">
         <v>72</v>
@@ -11902,19 +11905,19 @@
         <v>1480</v>
       </c>
       <c r="M124" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="N124" s="8" t="s">
+        <v>1541</v>
+      </c>
+      <c r="S124" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T124" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="U124" s="1" t="s">
         <v>1537</v>
-      </c>
-      <c r="N124" s="8" t="s">
-        <v>1543</v>
-      </c>
-      <c r="S124" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T124" s="1" t="s">
-        <v>1538</v>
-      </c>
-      <c r="U124" s="1" t="s">
-        <v>1539</v>
       </c>
       <c r="W124" s="1" t="s">
         <v>72</v>
@@ -11946,10 +11949,10 @@
         <v>297</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="N125" s="8" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="S125" s="1" t="s">
         <v>32</v>
@@ -11958,7 +11961,7 @@
         <v>177</v>
       </c>
       <c r="U125" s="1" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="W125" s="1" t="s">
         <v>72</v>
@@ -12439,10 +12442,10 @@
         <v>67</v>
       </c>
       <c r="M136" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="N136" s="8" t="s">
         <v>1545</v>
-      </c>
-      <c r="N136" s="8" t="s">
-        <v>1547</v>
       </c>
       <c r="S136" s="1" t="s">
         <v>168</v>
@@ -12483,10 +12486,10 @@
         <v>67</v>
       </c>
       <c r="M137" s="2" t="s">
+        <v>1544</v>
+      </c>
+      <c r="N137" s="8" t="s">
         <v>1546</v>
-      </c>
-      <c r="N137" s="8" t="s">
-        <v>1548</v>
       </c>
       <c r="S137" s="1" t="s">
         <v>168</v>
@@ -13011,16 +13014,16 @@
         <v>67</v>
       </c>
       <c r="M149" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="N149" s="8" t="s">
         <v>1549</v>
       </c>
-      <c r="N149" s="8" t="s">
-        <v>1551</v>
-      </c>
       <c r="S149" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T149" s="1" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="U149" s="1" t="s">
         <v>267</v>
@@ -13701,10 +13704,10 @@
         <v>67</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="N164" s="8" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="S164" s="1" t="s">
         <v>32</v>
@@ -13713,7 +13716,7 @@
         <v>319</v>
       </c>
       <c r="U164" s="1" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="W164" s="1" t="s">
         <v>72</v>
@@ -13745,19 +13748,19 @@
         <v>674</v>
       </c>
       <c r="M165" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="N165" s="8" t="s">
+        <v>1553</v>
+      </c>
+      <c r="S165" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T165" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="U165" s="1" t="s">
         <v>1552</v>
-      </c>
-      <c r="N165" s="8" t="s">
-        <v>1555</v>
-      </c>
-      <c r="S165" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T165" s="1" t="s">
-        <v>1553</v>
-      </c>
-      <c r="U165" s="1" t="s">
-        <v>1554</v>
       </c>
       <c r="W165" s="1" t="s">
         <v>72</v>
@@ -13868,22 +13871,22 @@
         <v>684</v>
       </c>
       <c r="I168" s="1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="J168" s="1" t="s">
+        <v>1562</v>
+      </c>
+      <c r="M168" s="2" t="s">
+        <v>1557</v>
+      </c>
+      <c r="N168" s="8" t="s">
+        <v>1564</v>
+      </c>
+      <c r="S168" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T168" s="1" t="s">
         <v>1563</v>
-      </c>
-      <c r="J168" s="1" t="s">
-        <v>1564</v>
-      </c>
-      <c r="M168" s="2" t="s">
-        <v>1559</v>
-      </c>
-      <c r="N168" s="8" t="s">
-        <v>1566</v>
-      </c>
-      <c r="S168" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T168" s="1" t="s">
-        <v>1565</v>
       </c>
       <c r="U168" s="1" t="s">
         <v>93</v>
@@ -13918,19 +13921,19 @@
         <v>686</v>
       </c>
       <c r="M169" s="2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="N169" s="8" t="s">
+        <v>1565</v>
+      </c>
+      <c r="S169" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T169" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="U169" s="1" t="s">
         <v>1560</v>
-      </c>
-      <c r="N169" s="8" t="s">
-        <v>1567</v>
-      </c>
-      <c r="S169" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T169" s="1" t="s">
-        <v>1561</v>
-      </c>
-      <c r="U169" s="1" t="s">
-        <v>1562</v>
       </c>
       <c r="W169" s="1" t="s">
         <v>103</v>
@@ -14050,10 +14053,10 @@
         <v>481</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="N172" s="8" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="S172" s="1" t="s">
         <v>32</v>
@@ -14088,16 +14091,16 @@
         <v>1899</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="J173" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="M173" s="2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="N173" s="8" t="s">
         <v>1571</v>
-      </c>
-      <c r="M173" s="2" t="s">
-        <v>1569</v>
-      </c>
-      <c r="N173" s="8" t="s">
-        <v>1573</v>
       </c>
       <c r="S173" s="1" t="s">
         <v>32</v>
@@ -14226,16 +14229,16 @@
         <v>719</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="N176" s="8" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="S176" s="1" t="s">
         <v>142</v>
       </c>
       <c r="T176" s="1" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="U176" s="1" t="s">
         <v>861</v>
@@ -14267,19 +14270,19 @@
         <v>1385</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="N177" s="8" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="S177" s="1" t="s">
         <v>142</v>
       </c>
       <c r="T177" s="1" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="U177" s="1" t="s">
         <v>207</v>
@@ -14393,7 +14396,7 @@
         <v>650</v>
       </c>
       <c r="H180" s="11" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>132</v>
@@ -14402,10 +14405,10 @@
         <v>139</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="N180" s="8" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="S180" s="1" t="s">
         <v>32</v>
@@ -14440,16 +14443,16 @@
         <v>1818</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="J181" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="M181" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="N181" s="8" t="s">
         <v>1585</v>
-      </c>
-      <c r="M181" s="2" t="s">
-        <v>1583</v>
-      </c>
-      <c r="N181" s="8" t="s">
-        <v>1587</v>
       </c>
       <c r="S181" s="1" t="s">
         <v>32</v>
@@ -14751,13 +14754,13 @@
         <v>336</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="N188" s="8" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="S188" s="1" t="s">
         <v>32</v>
@@ -14795,13 +14798,13 @@
         <v>480</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="M189" s="2" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="N189" s="8" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="S189" s="1" t="s">
         <v>32</v>
@@ -14842,10 +14845,10 @@
         <v>67</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="N190" s="8" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="S190" s="1" t="s">
         <v>32</v>
@@ -14886,19 +14889,19 @@
         <v>81</v>
       </c>
       <c r="M191" s="2" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="N191" s="8" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="S191" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T191" s="1" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="U191" s="1" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="W191" s="1" t="s">
         <v>72</v>
@@ -14927,19 +14930,19 @@
         <v>1425</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="M192" s="2" t="s">
+        <v>1592</v>
+      </c>
+      <c r="N192" s="8" t="s">
+        <v>1604</v>
+      </c>
+      <c r="S192" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T192" s="1" t="s">
         <v>1594</v>
-      </c>
-      <c r="N192" s="8" t="s">
-        <v>1606</v>
-      </c>
-      <c r="S192" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T192" s="1" t="s">
-        <v>1596</v>
       </c>
       <c r="U192" s="1" t="s">
         <v>587</v>
@@ -14971,22 +14974,22 @@
         <v>228</v>
       </c>
       <c r="J193" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="M193" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="N193" s="8" t="s">
+        <v>1605</v>
+      </c>
+      <c r="S193" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T193" s="1" t="s">
         <v>1598</v>
       </c>
-      <c r="M193" s="2" t="s">
+      <c r="U193" s="1" t="s">
         <v>1597</v>
-      </c>
-      <c r="N193" s="8" t="s">
-        <v>1607</v>
-      </c>
-      <c r="S193" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T193" s="1" t="s">
-        <v>1600</v>
-      </c>
-      <c r="U193" s="1" t="s">
-        <v>1599</v>
       </c>
       <c r="W193" s="1" t="s">
         <v>72</v>
@@ -15156,7 +15159,7 @@
         <v>785</v>
       </c>
       <c r="O197" s="7" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="S197" s="1" t="s">
         <v>32</v>
@@ -15232,22 +15235,22 @@
         <v>479</v>
       </c>
       <c r="H199" s="11" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="M199" s="2" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="N199" s="8" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="O199" s="7" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="S199" s="1" t="s">
         <v>32</v>
@@ -15279,7 +15282,7 @@
         <v>479</v>
       </c>
       <c r="H200" s="11" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>116</v>
@@ -15288,19 +15291,19 @@
         <v>366</v>
       </c>
       <c r="M200" s="2" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="N200" s="8" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="S200" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T200" s="1" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="U200" s="1" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="W200" s="1" t="s">
         <v>72</v>
@@ -15323,25 +15326,25 @@
         <v>479</v>
       </c>
       <c r="H201" s="11" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="M201" s="2" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="N201" s="8" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="S201" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T201" s="1" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="U201" s="1" t="s">
         <v>137</v>
@@ -15458,25 +15461,25 @@
         <v>1872</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="M204" s="2" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="N204" s="8" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="S204" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T204" s="1" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="U204" s="1" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="W204" s="1" t="s">
         <v>72</v>
@@ -15502,22 +15505,22 @@
         <v>1879</v>
       </c>
       <c r="I205" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="J205" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="M205" s="2" t="s">
         <v>1611</v>
       </c>
-      <c r="J205" s="1" t="s">
+      <c r="N205" s="8" t="s">
+        <v>1616</v>
+      </c>
+      <c r="S205" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T205" s="1" t="s">
         <v>1612</v>
-      </c>
-      <c r="M205" s="2" t="s">
-        <v>1613</v>
-      </c>
-      <c r="N205" s="8" t="s">
-        <v>1618</v>
-      </c>
-      <c r="S205" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T205" s="1" t="s">
-        <v>1614</v>
       </c>
       <c r="U205" s="1" t="s">
         <v>204</v>
@@ -15637,25 +15640,25 @@
         <v>1823</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="M208" s="2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="N208" s="8" t="s">
+        <v>1640</v>
+      </c>
+      <c r="S208" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T208" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="U208" s="1" t="s">
         <v>1634</v>
-      </c>
-      <c r="N208" s="8" t="s">
-        <v>1642</v>
-      </c>
-      <c r="S208" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T208" s="1" t="s">
-        <v>1635</v>
-      </c>
-      <c r="U208" s="1" t="s">
-        <v>1636</v>
       </c>
       <c r="W208" s="1" t="s">
         <v>718</v>
@@ -15684,13 +15687,13 @@
         <v>1391</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="M209" s="2" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="N209" s="8" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="S209" s="1" t="s">
         <v>32</v>
@@ -15699,7 +15702,7 @@
         <v>1381</v>
       </c>
       <c r="U209" s="1" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="W209" s="1" t="s">
         <v>718</v>
@@ -15819,10 +15822,10 @@
         <v>67</v>
       </c>
       <c r="M212" s="2" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="N212" s="8" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="S212" s="1" t="s">
         <v>32</v>
@@ -15863,10 +15866,10 @@
         <v>818</v>
       </c>
       <c r="M213" s="2" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="N213" s="8" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="S213" s="1" t="s">
         <v>32</v>
@@ -15951,19 +15954,19 @@
         <v>454</v>
       </c>
       <c r="M215" s="2" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N215" s="8" t="s">
+        <v>1655</v>
+      </c>
+      <c r="S215" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="T215" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="U215" s="1" t="s">
         <v>1648</v>
-      </c>
-      <c r="N215" s="8" t="s">
-        <v>1657</v>
-      </c>
-      <c r="S215" s="1" t="s">
-        <v>1652</v>
-      </c>
-      <c r="T215" s="1" t="s">
-        <v>1649</v>
-      </c>
-      <c r="U215" s="1" t="s">
-        <v>1650</v>
       </c>
       <c r="W215" s="1" t="s">
         <v>138</v>
@@ -15995,19 +15998,19 @@
         <v>1426</v>
       </c>
       <c r="M216" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="N216" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="S216" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="T216" s="1" t="s">
         <v>1651</v>
       </c>
-      <c r="N216" s="8" t="s">
-        <v>1658</v>
-      </c>
-      <c r="S216" s="1" t="s">
+      <c r="U216" s="1" t="s">
         <v>1652</v>
-      </c>
-      <c r="T216" s="1" t="s">
-        <v>1653</v>
-      </c>
-      <c r="U216" s="1" t="s">
-        <v>1654</v>
       </c>
       <c r="W216" s="1" t="s">
         <v>138</v>
@@ -16039,16 +16042,16 @@
         <v>1426</v>
       </c>
       <c r="M217" s="2" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="N217" s="8" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="S217" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T217" s="1" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="U217" s="1" t="s">
         <v>677</v>
@@ -16165,19 +16168,19 @@
         <v>1849</v>
       </c>
       <c r="I220" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="J220" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="M220" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="N220" s="8" t="s">
         <v>1665</v>
       </c>
-      <c r="J220" s="1" t="s">
-        <v>1666</v>
-      </c>
-      <c r="M220" s="2" t="s">
-        <v>1660</v>
-      </c>
-      <c r="N220" s="8" t="s">
-        <v>1667</v>
-      </c>
       <c r="S220" s="1" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="T220" s="1" t="s">
         <v>1276</v>
@@ -16209,25 +16212,25 @@
         <v>1848</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="M221" s="2" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="N221" s="8" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="S221" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="T221" s="1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="U221" s="1" t="s">
         <v>1662</v>
-      </c>
-      <c r="T221" s="1" t="s">
-        <v>1663</v>
-      </c>
-      <c r="U221" s="1" t="s">
-        <v>1664</v>
       </c>
       <c r="W221" s="1" t="s">
         <v>847</v>
@@ -16347,16 +16350,16 @@
         <v>243</v>
       </c>
       <c r="M224" s="2" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="N224" s="8" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="S224" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T224" s="1" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="U224" s="1" t="s">
         <v>677</v>
@@ -16388,19 +16391,19 @@
         <v>685</v>
       </c>
       <c r="J225" s="1" t="s">
+        <v>1673</v>
+      </c>
+      <c r="M225" s="2" t="s">
+        <v>1672</v>
+      </c>
+      <c r="N225" s="8" t="s">
         <v>1675</v>
       </c>
-      <c r="M225" s="2" t="s">
-        <v>1674</v>
-      </c>
-      <c r="N225" s="8" t="s">
-        <v>1677</v>
-      </c>
       <c r="S225" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T225" s="1" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="U225" s="1" t="s">
         <v>435</v>
@@ -16655,10 +16658,10 @@
         <v>67</v>
       </c>
       <c r="M231" s="2" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="N231" s="8" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="S231" s="1" t="s">
         <v>886</v>
@@ -16699,16 +16702,16 @@
         <v>316</v>
       </c>
       <c r="M232" s="2" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="N232" s="8" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="S232" s="1" t="s">
         <v>886</v>
       </c>
       <c r="T232" s="1" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="U232" s="1" t="s">
         <v>677</v>
@@ -16737,25 +16740,25 @@
         <v>1824</v>
       </c>
       <c r="I233" s="1" t="s">
+        <v>1678</v>
+      </c>
+      <c r="J233" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="M233" s="2" t="s">
         <v>1680</v>
       </c>
-      <c r="J233" s="1" t="s">
-        <v>1681</v>
-      </c>
-      <c r="M233" s="2" t="s">
-        <v>1682</v>
-      </c>
       <c r="N233" s="8" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="S233" s="1" t="s">
         <v>886</v>
       </c>
       <c r="T233" s="1" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="U233" s="1" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="W233" s="1" t="s">
         <v>72</v>
@@ -16787,19 +16790,19 @@
         <v>316</v>
       </c>
       <c r="M234" s="2" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="N234" s="8" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="S234" s="1" t="s">
         <v>886</v>
       </c>
       <c r="T234" s="1" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="U234" s="1" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="W234" s="1" t="s">
         <v>72</v>
@@ -16825,22 +16828,22 @@
         <v>1811</v>
       </c>
       <c r="I235" s="1" t="s">
+        <v>1683</v>
+      </c>
+      <c r="J235" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="M235" s="2" t="s">
         <v>1685</v>
       </c>
-      <c r="J235" s="1" t="s">
-        <v>1686</v>
-      </c>
-      <c r="M235" s="2" t="s">
-        <v>1687</v>
-      </c>
       <c r="N235" s="8" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="S235" s="1" t="s">
         <v>886</v>
       </c>
       <c r="T235" s="1" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="U235" s="1" t="s">
         <v>628</v>
@@ -16875,10 +16878,10 @@
         <v>316</v>
       </c>
       <c r="M236" s="2" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="N236" s="8" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="S236" s="1" t="s">
         <v>886</v>
@@ -16887,7 +16890,7 @@
         <v>536</v>
       </c>
       <c r="U236" s="1" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="W236" s="1" t="s">
         <v>72</v>
@@ -16919,19 +16922,19 @@
         <v>316</v>
       </c>
       <c r="M237" s="2" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="N237" s="8" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="S237" s="1" t="s">
         <v>886</v>
       </c>
       <c r="T237" s="1" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="U237" s="1" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="W237" s="1" t="s">
         <v>72</v>
@@ -17048,18 +17051,18 @@
         <v>1876</v>
       </c>
       <c r="I240" s="4" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="J240" s="4" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="K240" s="4"/>
       <c r="L240" s="4"/>
       <c r="M240" s="5" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="N240" s="10" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="O240" s="9"/>
       <c r="P240" s="4"/>
@@ -17069,7 +17072,7 @@
         <v>32</v>
       </c>
       <c r="T240" s="4" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="U240" s="4" t="s">
         <v>861</v>
@@ -17105,15 +17108,15 @@
         <v>491</v>
       </c>
       <c r="J241" s="4" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="K241" s="4"/>
       <c r="L241" s="4"/>
       <c r="M241" s="5" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="N241" s="10" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="O241" s="9"/>
       <c r="P241" s="4"/>
@@ -17123,10 +17126,10 @@
         <v>32</v>
       </c>
       <c r="T241" s="4" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="U241" s="4" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="V241" s="4"/>
       <c r="W241" s="4" t="s">
@@ -17599,10 +17602,10 @@
         <v>67</v>
       </c>
       <c r="M252" s="2" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="N252" s="8" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="S252" s="1" t="s">
         <v>32</v>
@@ -17611,7 +17614,7 @@
         <v>959</v>
       </c>
       <c r="U252" s="1" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="W252" s="1" t="s">
         <v>72</v>
@@ -17643,10 +17646,10 @@
         <v>67</v>
       </c>
       <c r="M253" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="N253" s="8" t="s">
         <v>1715</v>
-      </c>
-      <c r="N253" s="8" t="s">
-        <v>1717</v>
       </c>
       <c r="S253" s="1" t="s">
         <v>32</v>
@@ -17769,16 +17772,16 @@
         <v>1856</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="J256" s="1" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="M256" s="2" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="N256" s="8" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="S256" s="1" t="s">
         <v>32</v>
@@ -17787,7 +17790,7 @@
         <v>951</v>
       </c>
       <c r="U256" s="1" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="W256" s="1" t="s">
         <v>122</v>
@@ -17816,22 +17819,22 @@
         <v>1444</v>
       </c>
       <c r="J257" s="1" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M257" s="2" t="s">
+        <v>1720</v>
+      </c>
+      <c r="N257" s="8" t="s">
+        <v>1725</v>
+      </c>
+      <c r="S257" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T257" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="U257" s="1" t="s">
         <v>1723</v>
-      </c>
-      <c r="M257" s="2" t="s">
-        <v>1722</v>
-      </c>
-      <c r="N257" s="8" t="s">
-        <v>1727</v>
-      </c>
-      <c r="S257" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T257" s="1" t="s">
-        <v>1724</v>
-      </c>
-      <c r="U257" s="1" t="s">
-        <v>1725</v>
       </c>
       <c r="W257" s="1" t="s">
         <v>122</v>
@@ -17995,7 +17998,7 @@
         <v>67</v>
       </c>
       <c r="M261" s="2" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="N261" s="7" t="s">
         <v>960</v>
@@ -18083,10 +18086,10 @@
         <v>67</v>
       </c>
       <c r="M263" s="2" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="N263" s="8" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="S263" s="1" t="s">
         <v>32</v>
@@ -18118,7 +18121,7 @@
         <v>211</v>
       </c>
       <c r="H264" s="11" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>66</v>
@@ -18127,10 +18130,10 @@
         <v>67</v>
       </c>
       <c r="M264" s="2" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="N264" s="8" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="S264" s="1" t="s">
         <v>32</v>
@@ -18171,16 +18174,16 @@
         <v>67</v>
       </c>
       <c r="M265" s="2" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="N265" s="8" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="S265" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T265" s="1" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="U265" s="1" t="s">
         <v>295</v>
@@ -18699,10 +18702,10 @@
         <v>67</v>
       </c>
       <c r="M277" s="2" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="N277" s="8" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="S277" s="1" t="s">
         <v>32</v>
@@ -18831,19 +18834,19 @@
         <v>81</v>
       </c>
       <c r="M280" s="2" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="N280" s="8" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="S280" s="1" t="s">
         <v>142</v>
       </c>
       <c r="T280" s="1" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="U280" s="1" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="W280" s="1" t="s">
         <v>72</v>
@@ -18866,19 +18869,19 @@
         <v>78</v>
       </c>
       <c r="H281" s="11" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>66</v>
       </c>
       <c r="J281" s="1" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="M281" s="2" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="N281" s="8" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="S281" s="1" t="s">
         <v>142</v>
@@ -18887,7 +18890,7 @@
         <v>1335</v>
       </c>
       <c r="U281" s="1" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="W281" s="1" t="s">
         <v>72</v>
@@ -19136,16 +19139,16 @@
         <v>67</v>
       </c>
       <c r="M287" s="2" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="N287" s="8" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="S287" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T287" s="1" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="U287" s="1" t="s">
         <v>397</v>
@@ -19174,10 +19177,10 @@
         <v>48</v>
       </c>
       <c r="M288" s="2" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="N288" s="8" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="S288" s="1" t="s">
         <v>32</v>
@@ -19215,10 +19218,10 @@
         <v>975</v>
       </c>
       <c r="M289" s="2" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="N289" s="8" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="S289" s="1" t="s">
         <v>32</v>
@@ -19265,7 +19268,7 @@
         <v>1026</v>
       </c>
       <c r="S290" s="1" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="T290" s="1" t="s">
         <v>1027</v>
@@ -19297,25 +19300,25 @@
         <v>1899</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="J291" s="1" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="M291" s="2" t="s">
         <v>403</v>
       </c>
       <c r="N291" s="8" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="S291" s="1" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="T291" s="1" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="U291" s="1" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="W291" s="1" t="s">
         <v>1029</v>
@@ -19341,19 +19344,19 @@
         <v>1896</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="J292" s="1" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="M292" s="2" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="N292" s="8" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="S292" s="1" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="T292" s="1" t="s">
         <v>1276</v>
@@ -19385,19 +19388,19 @@
         <v>1896</v>
       </c>
       <c r="I293" s="1" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="J293" s="1" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="M293" s="2" t="s">
         <v>57</v>
       </c>
       <c r="N293" s="8" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="S293" s="1" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="T293" s="1" t="s">
         <v>1276</v>
@@ -19520,16 +19523,16 @@
         <v>1034</v>
       </c>
       <c r="M296" s="2" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="N296" s="8" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="S296" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T296" s="1" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="U296" s="1" t="s">
         <v>1347</v>
@@ -19552,7 +19555,7 @@
         <v>1032</v>
       </c>
       <c r="H297" s="11" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>1033</v>
@@ -19561,19 +19564,19 @@
         <v>1034</v>
       </c>
       <c r="M297" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="N297" s="8" t="s">
+        <v>1847</v>
+      </c>
+      <c r="S297" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T297" s="1" t="s">
         <v>1844</v>
       </c>
-      <c r="N297" s="8" t="s">
-        <v>1849</v>
-      </c>
-      <c r="S297" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T297" s="1" t="s">
-        <v>1846</v>
-      </c>
       <c r="U297" s="1" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="W297" s="1" t="s">
         <v>1038</v>
@@ -19822,25 +19825,25 @@
         <v>1898</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="J303" s="1" t="s">
         <v>566</v>
       </c>
       <c r="M303" s="2" t="s">
+        <v>1888</v>
+      </c>
+      <c r="N303" s="8" t="s">
+        <v>1894</v>
+      </c>
+      <c r="S303" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T303" s="1" t="s">
         <v>1890</v>
       </c>
-      <c r="N303" s="8" t="s">
-        <v>1896</v>
-      </c>
-      <c r="S303" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T303" s="1" t="s">
-        <v>1892</v>
-      </c>
       <c r="U303" s="1" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="W303" s="1" t="s">
         <v>72</v>
@@ -19869,13 +19872,13 @@
         <v>80</v>
       </c>
       <c r="J304" s="1" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="M304" s="2" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="N304" s="8" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="S304" s="1" t="s">
         <v>32</v>
@@ -19910,25 +19913,25 @@
         <v>1896</v>
       </c>
       <c r="I305" s="1" t="s">
+        <v>1897</v>
+      </c>
+      <c r="J305" s="1" t="s">
+        <v>1898</v>
+      </c>
+      <c r="M305" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="N305" s="8" t="s">
         <v>1899</v>
       </c>
-      <c r="J305" s="1" t="s">
+      <c r="S305" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T305" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="U305" s="1" t="s">
         <v>1900</v>
-      </c>
-      <c r="M305" s="2" t="s">
-        <v>1895</v>
-      </c>
-      <c r="N305" s="8" t="s">
-        <v>1901</v>
-      </c>
-      <c r="S305" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T305" s="1" t="s">
-        <v>1741</v>
-      </c>
-      <c r="U305" s="1" t="s">
-        <v>1902</v>
       </c>
       <c r="W305" s="1" t="s">
         <v>72</v>
@@ -20048,19 +20051,19 @@
         <v>67</v>
       </c>
       <c r="M308" s="2" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="N308" s="8" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="S308" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T308" s="1" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="U308" s="1" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="W308" s="1" t="s">
         <v>72</v>
@@ -20083,7 +20086,7 @@
         <v>78</v>
       </c>
       <c r="H309" s="11" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>782</v>
@@ -20092,19 +20095,19 @@
         <v>566</v>
       </c>
       <c r="M309" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="N309" s="8" t="s">
+        <v>1917</v>
+      </c>
+      <c r="S309" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T309" s="1" t="s">
         <v>1914</v>
       </c>
-      <c r="N309" s="8" t="s">
-        <v>1919</v>
-      </c>
-      <c r="S309" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T309" s="1" t="s">
-        <v>1916</v>
-      </c>
       <c r="U309" s="1" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="W309" s="1" t="s">
         <v>72</v>
@@ -20221,19 +20224,19 @@
         <v>412</v>
       </c>
       <c r="J312" s="1" t="s">
+        <v>1848</v>
+      </c>
+      <c r="M312" s="2" t="s">
         <v>1850</v>
       </c>
-      <c r="M312" s="2" t="s">
-        <v>1852</v>
-      </c>
       <c r="N312" s="8" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="S312" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T312" s="1" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="U312" s="1" t="s">
         <v>169</v>
@@ -20268,16 +20271,16 @@
         <v>243</v>
       </c>
       <c r="M313" s="2" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="N313" s="8" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="S313" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T313" s="1" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="W313" s="1" t="s">
         <v>72</v>
@@ -20799,19 +20802,19 @@
         <v>81</v>
       </c>
       <c r="M325" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="N325" s="8" t="s">
+        <v>1921</v>
+      </c>
+      <c r="S325" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T325" s="1" t="s">
+        <v>1919</v>
+      </c>
+      <c r="U325" s="1" t="s">
         <v>1920</v>
-      </c>
-      <c r="N325" s="8" t="s">
-        <v>1923</v>
-      </c>
-      <c r="S325" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T325" s="1" t="s">
-        <v>1921</v>
-      </c>
-      <c r="U325" s="1" t="s">
-        <v>1922</v>
       </c>
       <c r="W325" s="1" t="s">
         <v>72</v>
@@ -20928,7 +20931,7 @@
         <v>1119</v>
       </c>
       <c r="H328" s="11" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>37</v>
@@ -20937,10 +20940,10 @@
         <v>38</v>
       </c>
       <c r="M328" s="2" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="N328" s="8" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="S328" s="1" t="s">
         <v>32</v>
@@ -20972,7 +20975,7 @@
         <v>1119</v>
       </c>
       <c r="H329" s="11" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>37</v>
@@ -20981,10 +20984,10 @@
         <v>38</v>
       </c>
       <c r="M329" s="2" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="N329" s="8" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="S329" s="1" t="s">
         <v>32</v>
@@ -20993,7 +20996,7 @@
         <v>445</v>
       </c>
       <c r="U329" s="1" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="W329" s="1" t="s">
         <v>35</v>
@@ -21104,7 +21107,7 @@
         <v>801</v>
       </c>
       <c r="H332" s="11" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>116</v>
@@ -21113,10 +21116,10 @@
         <v>117</v>
       </c>
       <c r="M332" s="2" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="N332" s="8" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="S332" s="1" t="s">
         <v>32</v>
@@ -21157,10 +21160,10 @@
         <v>117</v>
       </c>
       <c r="M333" s="2" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="N333" s="8" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="S333" s="1" t="s">
         <v>32</v>
@@ -21169,7 +21172,7 @@
         <v>1257</v>
       </c>
       <c r="U333" s="1" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="W333" s="1" t="s">
         <v>122</v>
@@ -21280,7 +21283,7 @@
         <v>163</v>
       </c>
       <c r="H336" s="11" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>66</v>
@@ -21289,16 +21292,16 @@
         <v>316</v>
       </c>
       <c r="M336" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="N336" s="8" t="s">
+        <v>1907</v>
+      </c>
+      <c r="S336" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T336" s="1" t="s">
         <v>1903</v>
-      </c>
-      <c r="N336" s="8" t="s">
-        <v>1909</v>
-      </c>
-      <c r="S336" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T336" s="1" t="s">
-        <v>1905</v>
       </c>
       <c r="U336" s="1" t="s">
         <v>693</v>
@@ -21324,7 +21327,7 @@
         <v>163</v>
       </c>
       <c r="H337" s="11" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>66</v>
@@ -21333,19 +21336,19 @@
         <v>316</v>
       </c>
       <c r="M337" s="2" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="N337" s="8" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="S337" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T337" s="1" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="U337" s="1" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="W337" s="1" t="s">
         <v>72</v>
@@ -21462,19 +21465,19 @@
         <v>761</v>
       </c>
       <c r="M340" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="N340" s="8" t="s">
+        <v>1860</v>
+      </c>
+      <c r="S340" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T340" s="1" t="s">
+        <v>1856</v>
+      </c>
+      <c r="U340" s="1" t="s">
         <v>1857</v>
-      </c>
-      <c r="N340" s="8" t="s">
-        <v>1862</v>
-      </c>
-      <c r="S340" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T340" s="1" t="s">
-        <v>1858</v>
-      </c>
-      <c r="U340" s="1" t="s">
-        <v>1859</v>
       </c>
       <c r="W340" s="1" t="s">
         <v>103</v>
@@ -21503,13 +21506,13 @@
         <v>760</v>
       </c>
       <c r="J341" s="1" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="M341" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="N341" s="8" t="s">
         <v>1861</v>
-      </c>
-      <c r="N341" s="8" t="s">
-        <v>1863</v>
       </c>
       <c r="S341" s="1" t="s">
         <v>32</v>
@@ -21629,25 +21632,25 @@
         <v>1157</v>
       </c>
       <c r="H344" s="11" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="I344" s="1" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="J344" s="1" t="s">
         <v>566</v>
       </c>
       <c r="M344" s="2" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="N344" s="8" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="S344" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T344" s="1" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="U344" s="1" t="s">
         <v>301</v>
@@ -21682,10 +21685,10 @@
         <v>67</v>
       </c>
       <c r="M345" s="2" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="N345" s="8" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="S345" s="1" t="s">
         <v>32</v>
@@ -21931,19 +21934,19 @@
         <v>165</v>
       </c>
       <c r="H351" s="11" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>685</v>
       </c>
       <c r="J351" s="1" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="M351" s="2" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="N351" s="8" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="S351" s="1" t="s">
         <v>32</v>
@@ -21972,7 +21975,7 @@
         <v>165</v>
       </c>
       <c r="H352" s="11" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>80</v>
@@ -21981,16 +21984,16 @@
         <v>81</v>
       </c>
       <c r="M352" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="N352" s="8" t="s">
+        <v>1830</v>
+      </c>
+      <c r="S352" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T352" s="1" t="s">
         <v>1826</v>
-      </c>
-      <c r="N352" s="8" t="s">
-        <v>1832</v>
-      </c>
-      <c r="S352" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T352" s="1" t="s">
-        <v>1828</v>
       </c>
       <c r="U352" s="1" t="s">
         <v>806</v>
@@ -22022,10 +22025,10 @@
         <v>1186</v>
       </c>
       <c r="M353" s="2" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="N353" s="8" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="S353" s="1" t="s">
         <v>32</v>
@@ -22034,7 +22037,7 @@
         <v>1205</v>
       </c>
       <c r="U353" s="1" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="W353" s="1" t="s">
         <v>72</v>
@@ -22154,10 +22157,10 @@
         <v>67</v>
       </c>
       <c r="M356" s="2" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="N356" s="8" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="S356" s="1" t="s">
         <v>32</v>
@@ -22198,16 +22201,16 @@
         <v>67</v>
       </c>
       <c r="M357" s="2" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="N357" s="8" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="S357" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T357" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="W357" s="1" t="s">
         <v>72</v>
@@ -22456,16 +22459,16 @@
         <v>81</v>
       </c>
       <c r="M363" s="2" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="N363" s="8" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="S363" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T363" s="1" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="U363" s="1" t="s">
         <v>1205</v>
@@ -22497,10 +22500,10 @@
         <v>67</v>
       </c>
       <c r="M364" s="2" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="N364" s="8" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="S364" s="1" t="s">
         <v>32</v>
@@ -22529,7 +22532,7 @@
         <v>148</v>
       </c>
       <c r="H365" s="11" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="I365" s="1" t="s">
         <v>66</v>
@@ -22538,10 +22541,10 @@
         <v>67</v>
       </c>
       <c r="M365" s="2" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="N365" s="8" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="S365" s="1" t="s">
         <v>32</v>
@@ -22667,13 +22670,13 @@
         <v>116</v>
       </c>
       <c r="J368" s="1" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="M368" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="N368" s="8" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="S368" s="1" t="s">
         <v>32</v>
@@ -22682,7 +22685,7 @@
         <v>1272</v>
       </c>
       <c r="U368" s="1" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="W368" s="1" t="s">
         <v>72</v>
@@ -22714,19 +22717,19 @@
         <v>117</v>
       </c>
       <c r="M369" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="N369" s="8" t="s">
+        <v>1807</v>
+      </c>
+      <c r="S369" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T369" s="1" t="s">
+        <v>1804</v>
+      </c>
+      <c r="U369" s="1" t="s">
         <v>1805</v>
-      </c>
-      <c r="N369" s="8" t="s">
-        <v>1809</v>
-      </c>
-      <c r="S369" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T369" s="1" t="s">
-        <v>1806</v>
-      </c>
-      <c r="U369" s="1" t="s">
-        <v>1807</v>
       </c>
       <c r="W369" s="1" t="s">
         <v>72</v>
@@ -23022,10 +23025,10 @@
         <v>366</v>
       </c>
       <c r="M376" s="2" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="N376" s="8" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="S376" s="1" t="s">
         <v>32</v>
@@ -23066,19 +23069,19 @@
         <v>366</v>
       </c>
       <c r="M377" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="N377" s="8" t="s">
+        <v>1799</v>
+      </c>
+      <c r="S377" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T377" s="1" t="s">
+        <v>1796</v>
+      </c>
+      <c r="U377" s="1" t="s">
         <v>1797</v>
-      </c>
-      <c r="N377" s="8" t="s">
-        <v>1801</v>
-      </c>
-      <c r="S377" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T377" s="1" t="s">
-        <v>1798</v>
-      </c>
-      <c r="U377" s="1" t="s">
-        <v>1799</v>
       </c>
       <c r="W377" s="1" t="s">
         <v>122</v>
@@ -23192,16 +23195,16 @@
         <v>1893</v>
       </c>
       <c r="I380" s="1" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="J380" s="1" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="M380" s="2" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="N380" s="8" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="S380" s="1" t="s">
         <v>32</v>
@@ -23245,16 +23248,16 @@
         <v>1245</v>
       </c>
       <c r="N381" s="8" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="S381" s="1" t="s">
+        <v>1785</v>
+      </c>
+      <c r="T381" s="1" t="s">
+        <v>1786</v>
+      </c>
+      <c r="U381" s="1" t="s">
         <v>1787</v>
-      </c>
-      <c r="T381" s="1" t="s">
-        <v>1788</v>
-      </c>
-      <c r="U381" s="1" t="s">
-        <v>1789</v>
       </c>
       <c r="W381" s="1" t="s">
         <v>138</v>
@@ -23726,10 +23729,10 @@
         <v>1250</v>
       </c>
       <c r="M392" s="2" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="N392" s="8" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="S392" s="1" t="s">
         <v>32</v>
@@ -23767,10 +23770,10 @@
         <v>67</v>
       </c>
       <c r="M393" s="2" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="N393" s="8" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="S393" s="1" t="s">
         <v>32</v>
@@ -23896,13 +23899,13 @@
         <v>1177</v>
       </c>
       <c r="J396" s="1" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="M396" s="2" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="N396" s="8" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="S396" s="1" t="s">
         <v>32</v>
@@ -23911,7 +23914,7 @@
         <v>544</v>
       </c>
       <c r="U396" s="1" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="W396" s="1" t="s">
         <v>703</v>
@@ -23940,13 +23943,13 @@
         <v>116</v>
       </c>
       <c r="J397" s="1" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="M397" s="2" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="N397" s="8" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="S397" s="1" t="s">
         <v>32</v>
@@ -24081,19 +24084,19 @@
         <v>38</v>
       </c>
       <c r="M400" s="2" t="s">
+        <v>1756</v>
+      </c>
+      <c r="N400" s="8" t="s">
+        <v>1762</v>
+      </c>
+      <c r="S400" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T400" s="1" t="s">
         <v>1758</v>
       </c>
-      <c r="N400" s="8" t="s">
-        <v>1764</v>
-      </c>
-      <c r="S400" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T400" s="1" t="s">
-        <v>1760</v>
-      </c>
       <c r="U400" s="1" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="W400" s="1" t="s">
         <v>35</v>
@@ -24125,19 +24128,19 @@
         <v>38</v>
       </c>
       <c r="M401" s="2" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="N401" s="8" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="S401" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T401" s="1" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="U401" s="1" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="W401" s="1" t="s">
         <v>35</v>
@@ -24389,13 +24392,13 @@
         <v>67</v>
       </c>
       <c r="M407" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="N407" s="8" t="s">
         <v>1747</v>
       </c>
-      <c r="N407" s="8" t="s">
-        <v>1749</v>
-      </c>
       <c r="S407" s="1" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="T407" s="1" t="s">
         <v>92</v>
@@ -24433,10 +24436,10 @@
         <v>67</v>
       </c>
       <c r="M408" s="2" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="N408" s="8" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="S408" s="1" t="s">
         <v>168</v>
@@ -24445,7 +24448,7 @@
         <v>1078</v>
       </c>
       <c r="U408" s="1" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="W408" s="1" t="s">
         <v>72</v>
@@ -24474,22 +24477,22 @@
         <v>80</v>
       </c>
       <c r="J409" s="1" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="M409" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="N409" s="8" t="s">
         <v>1754</v>
       </c>
-      <c r="N409" s="8" t="s">
-        <v>1756</v>
-      </c>
       <c r="S409" s="1" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="T409" s="1" t="s">
         <v>852</v>
       </c>
       <c r="U409" s="1" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="W409" s="1" t="s">
         <v>72</v>
@@ -24609,16 +24612,16 @@
         <v>943</v>
       </c>
       <c r="N412" s="8" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="S412" s="1" t="s">
         <v>32</v>
       </c>
       <c r="T412" s="1" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="U412" s="1" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="W412" s="1" t="s">
         <v>122</v>
@@ -24647,19 +24650,19 @@
         <v>48</v>
       </c>
       <c r="M413" s="2" t="s">
+        <v>1740</v>
+      </c>
+      <c r="N413" s="8" t="s">
+        <v>1744</v>
+      </c>
+      <c r="S413" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T413" s="1" t="s">
+        <v>1741</v>
+      </c>
+      <c r="U413" s="1" t="s">
         <v>1742</v>
-      </c>
-      <c r="N413" s="8" t="s">
-        <v>1746</v>
-      </c>
-      <c r="S413" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T413" s="1" t="s">
-        <v>1743</v>
-      </c>
-      <c r="U413" s="1" t="s">
-        <v>1744</v>
       </c>
       <c r="W413" s="1" t="s">
         <v>122</v>
@@ -24735,7 +24738,7 @@
         <v>67</v>
       </c>
       <c r="M415" s="2" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="N415" s="7" t="s">
         <v>1337</v>
@@ -24776,19 +24779,19 @@
         <v>1498</v>
       </c>
       <c r="J416" s="1" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="M416" s="2" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="N416" s="8" t="s">
+        <v>1734</v>
+      </c>
+      <c r="S416" s="1" t="s">
         <v>1736</v>
       </c>
-      <c r="S416" s="1" t="s">
-        <v>1738</v>
-      </c>
       <c r="T416" s="1" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="U416" s="1">
         <v>46.7</v>
@@ -24814,19 +24817,19 @@
         <v>740</v>
       </c>
       <c r="H417" s="11" t="s">
+        <v>1733</v>
+      </c>
+      <c r="I417" s="1" t="s">
+        <v>1732</v>
+      </c>
+      <c r="J417" s="1" t="s">
+        <v>1731</v>
+      </c>
+      <c r="M417" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="N417" s="8" t="s">
         <v>1735</v>
-      </c>
-      <c r="I417" s="1" t="s">
-        <v>1734</v>
-      </c>
-      <c r="J417" s="1" t="s">
-        <v>1733</v>
-      </c>
-      <c r="M417" s="2" t="s">
-        <v>1732</v>
-      </c>
-      <c r="N417" s="8" t="s">
-        <v>1737</v>
       </c>
       <c r="S417" s="1" t="s">
         <v>32</v>
@@ -24901,126 +24904,128 @@
     <hyperlink ref="N84" r:id="rId52" xr:uid="{A9342BBA-0845-424E-B2B5-289429CB1616}"/>
     <hyperlink ref="N85" r:id="rId53" xr:uid="{880990DF-2955-42FC-947A-009DB9BB415F}"/>
     <hyperlink ref="N88" r:id="rId54" xr:uid="{2A96C005-7149-4AC6-8403-A0B2442960AD}"/>
-    <hyperlink ref="N89" r:id="rId55" xr:uid="{04E598F9-5E01-44E9-B4EE-F33C90D585CE}"/>
-    <hyperlink ref="N92" r:id="rId56" xr:uid="{A613982D-4B46-4374-ABCB-BF1147E04070}"/>
-    <hyperlink ref="N93" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/22/John_Constable_-_Salisbury_Cathedral_from_the_Bishop%27s_Grounds.jpg/1280px-John_Constable_-_Salisbury_Cathedral_from_the_Bishop%27s_Grounds.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{660778C8-21D7-41DF-B43E-6AB9477E3041}"/>
-    <hyperlink ref="N99" r:id="rId58" xr:uid="{C48A7729-30CF-4FE9-8F28-02F8DA31A683}"/>
-    <hyperlink ref="N100" r:id="rId59" xr:uid="{4355C2FD-1FAD-43D0-B9B7-5E0F150A552F}"/>
-    <hyperlink ref="N101" r:id="rId60" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/La_Dame_en_bleu_-_Jean-Baptiste_Camille_Corot_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2056.jpg/960px-La_Dame_en_bleu_-_Jean-Baptiste_Camille_Corot_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2056.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C304865E-4701-43BB-A315-1F54723C4241}"/>
-    <hyperlink ref="N116" r:id="rId61" xr:uid="{71C6818B-3187-42E8-8DA0-B7A822A5161E}"/>
-    <hyperlink ref="N117" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/55/Honor%C3%A9_Daumier_-_The_Uprising_%28L%27Emeute%29_-_Google_Art_Project.jpg/1280px-Honor%C3%A9_Daumier_-_The_Uprising_%28L%27Emeute%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2207849A-0FD5-454F-9F02-BAFFE2A6CDBE}"/>
-    <hyperlink ref="N123" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b0/Jacques_Louis_David-Serment_de_l%27arm%C3%A9e_fait_%C3%A0_l%27Empereur_apr%C3%A8s_la_distribution_des_aigles%2C_5_d%C3%A9cembre_1804.jpg/1280px-Jacques_Louis_David-Serment_de_l%27arm%C3%A9e_fait_%C3%A0_l%27Empereur_apr%C3%A8s_la_distribution_des_aigles%2C_5_d%C3%A9cembre_1804.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FF061AFF-C251-448E-9092-2C0E0595BD0F}"/>
-    <hyperlink ref="N124" r:id="rId64" xr:uid="{20150DC0-5C76-48C1-8808-A0D4060073A6}"/>
-    <hyperlink ref="N125" r:id="rId65" xr:uid="{468650D3-BAF1-4E97-8F04-8619CF1DA868}"/>
-    <hyperlink ref="N136" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/55/%28Albi%29_Rousse_%28La_Toilette%29_-_1889_-_Henri_de_Toulouse-Lautrec_-_Mus%C3%A9e_d%27Orsay%2C_Paris.jpg/960px-%28Albi%29_Rousse_%28La_Toilette%29_-_1889_-_Henri_de_Toulouse-Lautrec_-_Mus%C3%A9e_d%27Orsay%2C_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{804889E5-620C-4811-B6FA-11BE07AA7B60}"/>
-    <hyperlink ref="N137" r:id="rId67" xr:uid="{58C2DEE8-3184-4821-A01F-DCE034EEF75D}"/>
-    <hyperlink ref="N149" r:id="rId68" xr:uid="{DE98B191-43F3-4002-A4F9-65E9FCE87D17}"/>
-    <hyperlink ref="N165" r:id="rId69" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/Saint-Germain-en-Laye_%28Yvelines%29_-_Mus%C3%A9e_d%C3%A9partemental_Maurice-Denis_%C2%AB_Le_Prieur%C3%A9_%C2%BB_-_%22L%27%C3%A9chelle_dans_le_feuillage%22_%28Maurice_Denis%2C_1870-1943%29_%2848287824526%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{E6A7C1F6-A887-4899-B0AA-F6F162C706B7}"/>
-    <hyperlink ref="N164" r:id="rId70" xr:uid="{B444480C-FE46-4D42-A99D-37429BE0A5C1}"/>
-    <hyperlink ref="N168" r:id="rId71" xr:uid="{82F22ECA-6133-47C7-9F70-67330F9C864F}"/>
-    <hyperlink ref="N169" r:id="rId72" xr:uid="{81BF6C34-FD61-4BC2-9A73-40BAE8E04824}"/>
-    <hyperlink ref="N172" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/09/James_Ensor_%281891%29_-_Geraamten_twistend_om_een_gehangene_001.jpg/1280px-James_Ensor_%281891%29_-_Geraamten_twistend_om_een_gehangene_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E01C2438-10A1-4097-99F6-6760F1D8DD7B}"/>
-    <hyperlink ref="N173" r:id="rId74" xr:uid="{4F111A99-5D9C-4573-9817-9976166F9483}"/>
-    <hyperlink ref="N176" r:id="rId75" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/On_the_lookout_%28The_white_wall%29_%281872%29%2C_by_Giovanni_Fattori.jpg/1280px-On_the_lookout_%28The_white_wall%29_%281872%29%2C_by_Giovanni_Fattori.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7164BD98-294C-4BC4-867D-7C529084065C}"/>
-    <hyperlink ref="N177" r:id="rId76" xr:uid="{784C806F-BF54-44EB-B9B9-69E21EF04D71}"/>
-    <hyperlink ref="N180" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Friedrich%2C_Caspar_David_-_M%C3%B6nch_am_Meer_-_Alte_Nationalgalerie_in_Berlin.jpg/1280px-Friedrich%2C_Caspar_David_-_M%C3%B6nch_am_Meer_-_Alte_Nationalgalerie_in_Berlin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{936C1E04-B264-4501-8EA0-0E2C488110F6}"/>
-    <hyperlink ref="N181" r:id="rId78" xr:uid="{2ED30E2A-A679-4FCB-8484-14A9E011F084}"/>
-    <hyperlink ref="N188" r:id="rId79" xr:uid="{79787671-35C1-4B84-876B-A82D17EFAB7E}"/>
-    <hyperlink ref="N189" r:id="rId80" xr:uid="{64EA1C71-990E-448A-99B5-3E5600421DBC}"/>
-    <hyperlink ref="N190" r:id="rId81" xr:uid="{BD69ED86-B038-46CD-9EF3-71128AE3BE92}"/>
-    <hyperlink ref="N191" r:id="rId82" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Paul_Gauguin_Ia_Orana_Maria_%28Hail_Mary%29_The_Metropolitan_Museum_of_Art1.jpg/960px-Paul_Gauguin_Ia_Orana_Maria_%28Hail_Mary%29_The_Metropolitan_Museum_of_Art1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BC19CAAD-1CF7-4574-BC0B-D6B8AD503766}"/>
-    <hyperlink ref="N192" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bd/Paul_Gauguin%2C_Nafea_Faa_Ipoipo%3F_%28When_Will_You_Marry%3F%29_1892%2C_oil_on_canvas%2C_101_x_77_cm.jpg/960px-Paul_Gauguin%2C_Nafea_Faa_Ipoipo%3F_%28When_Will_You_Marry%3F%29_1892%2C_oil_on_canvas%2C_101_x_77_cm.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{86BFA8A3-05C5-400B-B6D8-D5597C9A9CA1}"/>
-    <hyperlink ref="N193" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Paul_Gauguin_-_Mahana_no_atua_%28Day_of_the_God%29_-_1926.198_-_Art_Institute_of_Chicago.jpg/1280px-Paul_Gauguin_-_Mahana_no_atua_%28Day_of_the_God%29_-_1926.198_-_Art_Institute_of_Chicago.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C9FEA22A-DF23-46B5-85CD-37650AA49FA0}"/>
-    <hyperlink ref="N204" r:id="rId85" xr:uid="{76214D94-66A9-4BE5-84AA-4CF9FE4120DB}"/>
-    <hyperlink ref="N205" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a9/Jean-L%C3%A9on_G%C3%A9r%C3%B4me_-_Le_charmeur_de_serpents.jpg/1280px-Jean-L%C3%A9on_G%C3%A9r%C3%B4me_-_Le_charmeur_de_serpents.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D037830-A93D-453A-B01B-BE50323ABFE0}"/>
-    <hyperlink ref="N199" r:id="rId87" xr:uid="{76F9296C-85C4-4A4C-835B-18E125C9EED3}"/>
-    <hyperlink ref="N200" r:id="rId88" xr:uid="{DCE4207A-DAB3-440F-8D82-D3B5EDAC8D4B}"/>
-    <hyperlink ref="N201" r:id="rId89" xr:uid="{A1835D70-5A3C-4E41-A85A-31232D6D7B3F}"/>
-    <hyperlink ref="N208" r:id="rId90" xr:uid="{F5572090-998E-4BF4-A715-EF255ECCEF21}"/>
-    <hyperlink ref="N209" r:id="rId91" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e2/Francesco_Hayez_-_Distruzione_des_tempio_di_Gerusalemme.jpg/1280px-Francesco_Hayez_-_Distruzione_des_tempio_di_Gerusalemme.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F4D2961A-398D-462E-BC0F-AA9C52FB41CC}"/>
-    <hyperlink ref="N212" r:id="rId92" xr:uid="{F2644B0B-A243-49CE-8AB7-5CA7AB3544D2}"/>
-    <hyperlink ref="N213" r:id="rId93" xr:uid="{E6DE9528-18E1-4B93-9909-7FE7B5915738}"/>
-    <hyperlink ref="N215" r:id="rId94" xr:uid="{54418522-D935-41FF-8DCE-42FE2321CC7F}"/>
-    <hyperlink ref="N216" r:id="rId95" xr:uid="{7392222B-02FE-4A19-A5EE-B1CD7D91681C}"/>
-    <hyperlink ref="N217" r:id="rId96" xr:uid="{1961306B-75F0-41CC-BEA9-EB01815AD97B}"/>
-    <hyperlink ref="N220" r:id="rId97" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/48/Katsushika_Hokusai%2C_drago_che_vola_sul_monte_fuji%2C_pittura_su_seta%2C_1849%2C_02.jpg/500px-Katsushika_Hokusai%2C_drago_che_vola_sul_monte_fuji%2C_pittura_su_seta%2C_1849%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AC945414-55C6-4873-AD5B-8CE95A1AA6CA}"/>
-    <hyperlink ref="N221" r:id="rId98" xr:uid="{61CA0861-4A90-44E8-87E5-4C9DC527A23D}"/>
-    <hyperlink ref="N224" r:id="rId99" xr:uid="{E1045DCA-3462-4144-BC63-B713FBE9D4F5}"/>
-    <hyperlink ref="N225" r:id="rId100" xr:uid="{D4D57138-87CD-4408-8975-AA87499F756A}"/>
-    <hyperlink ref="N231" r:id="rId101" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/46/Jean_Auguste_Dominique_Ingres_-_The_Spring_-_Google_Art_Project_2.jpg/960px-Jean_Auguste_Dominique_Ingres_-_The_Spring_-_Google_Art_Project_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A693F64E-53D5-4410-B881-34D855875369}"/>
-    <hyperlink ref="N232" r:id="rId102" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/44/Jean-Auguste-Dominique_Ingres_-_La_Baigneuse_Valpin%C3%A7on.jpg/960px-Jean-Auguste-Dominique_Ingres_-_La_Baigneuse_Valpin%C3%A7on.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D1938B45-011F-414F-87DA-4FC0E8D2AE2F}"/>
-    <hyperlink ref="N233" r:id="rId103" xr:uid="{D0C8F28C-F2C6-49C0-9CD4-0D598E1A180E}"/>
-    <hyperlink ref="N234" r:id="rId104" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Hom%C3%A8re_d%C3%A9ifi%C3%A9%2C_dit_aussi_L%27apoth%C3%A9ose_d%27Hom%C3%A8re_-_Jean-Auguste_Dominique_Ingres_-_Mus%C3%A9e_du_Louvre_Peintures_INV_5417_%3B_C_196.jpg/1280px-Hom%C3%A8re_d%C3%A9ifi%C3%A9%2C_dit_aussi_L%27apoth%C3%A9ose_d%27Hom%C3%A8re_-_Jean-Auguste_Dominique_Ingres_-_Mus%C3%A9e_du_Louvre_Peintures_INV_5417_%3B_C_196.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BB2F7B03-FF62-4F35-8281-56DF3CE982B5}"/>
-    <hyperlink ref="N235" r:id="rId105" xr:uid="{E2FE698E-035E-4186-8C9F-DDFD51D4D1CB}"/>
-    <hyperlink ref="N236" r:id="rId106" xr:uid="{ED1DD965-7C21-4DD7-A91A-87D77F90CA3D}"/>
-    <hyperlink ref="N237" r:id="rId107" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/%C5%92dipe_explique_l%27%C3%A9nigme_du_sphinx_-_Jean-Auguste_Dominique_Ingres_-_Mus%C3%A9e_du_Louvre_Peintures_RF_218.jpg/960px-%C5%92dipe_explique_l%27%C3%A9nigme_du_sphinx_-_Jean-Auguste_Dominique_Ingres_-_Mus%C3%A9e_du_Louvre_Peintures_RF_218.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F85C5582-6667-468A-888A-F96346A9F70C}"/>
-    <hyperlink ref="N241" r:id="rId108" xr:uid="{80F05F13-B8A9-4854-BBC4-97713609CE55}"/>
-    <hyperlink ref="N240" r:id="rId109" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Jongkind_The_Church_of_St._-M%C3%A9dard_on_the_Rue_Mouffetard.png/1280px-Jongkind_The_Church_of_St._-M%C3%A9dard_on_the_Rue_Mouffetard.png?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D318E97A-60C3-4ED8-A330-A050814C061E}"/>
-    <hyperlink ref="N252" r:id="rId110" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Edouard_Manet_-_Berthe_Morisot_With_a_Bouquet_of_Violets_-_Google_Art_Project.jpg/1920px-Edouard_Manet_-_Berthe_Morisot_With_a_Bouquet_of_Violets_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8C937D96-E75E-43EA-9D2B-789AD29346E7}"/>
-    <hyperlink ref="N253" r:id="rId111" xr:uid="{6EC144FB-DA52-4EC7-8CDE-265B928359ED}"/>
-    <hyperlink ref="N256" r:id="rId112" xr:uid="{21B4DF45-B86D-4E4B-8079-A7D5DFE136BA}"/>
-    <hyperlink ref="N257" r:id="rId113" xr:uid="{D98C0F42-EB5A-4AA3-BBF3-20A9670248AC}"/>
-    <hyperlink ref="N416" r:id="rId114" xr:uid="{E3389331-0D52-4A47-897F-64A681B3D28E}"/>
-    <hyperlink ref="N417" r:id="rId115" xr:uid="{BAA0F219-AB77-49BB-94B1-4FD97CBDFE59}"/>
-    <hyperlink ref="N412" r:id="rId116" xr:uid="{4608A50E-2C37-4FB4-B64F-77495BC756C3}"/>
-    <hyperlink ref="N413" r:id="rId117" xr:uid="{19E7B006-0390-4004-83FF-861BB79A0766}"/>
-    <hyperlink ref="N407" r:id="rId118" xr:uid="{5B11A8F3-5B7A-4ED7-8693-8A188273DB8A}"/>
-    <hyperlink ref="N408" r:id="rId119" xr:uid="{598B9595-608C-43B0-B701-CE61322F3A18}"/>
-    <hyperlink ref="N409" r:id="rId120" xr:uid="{F0B20B8C-84CC-47B9-A783-80F80AEF8C1F}"/>
-    <hyperlink ref="N400" r:id="rId121" xr:uid="{BEF9C22C-2034-41C2-A40B-D047266179FF}"/>
-    <hyperlink ref="N401" r:id="rId122" xr:uid="{C63B34B5-0284-4C9E-868F-FE18453F0DDB}"/>
-    <hyperlink ref="N396" r:id="rId123" xr:uid="{99B32D0E-B115-4463-9369-F646863F2620}"/>
-    <hyperlink ref="N397" r:id="rId124" xr:uid="{9A8A5AE7-4BDC-4395-A702-A2210C5D205A}"/>
-    <hyperlink ref="N291" r:id="rId125" xr:uid="{19A60C58-34F0-41D9-9C86-8B03D65386E5}"/>
-    <hyperlink ref="N293" r:id="rId126" xr:uid="{FC449AFA-82CA-44FC-B5A5-2FFF7D75D6BA}"/>
-    <hyperlink ref="N292" r:id="rId127" xr:uid="{8FD57115-A880-412C-B0E9-4D02ACC5D655}"/>
-    <hyperlink ref="N380" r:id="rId128" xr:uid="{51BF2C03-8845-437E-8FC8-11DBB0895200}"/>
-    <hyperlink ref="N381" r:id="rId129" xr:uid="{2D41CF16-D658-4AE1-B0E0-3FBFEEC5D632}"/>
-    <hyperlink ref="N392" r:id="rId130" xr:uid="{D06E67B7-CD04-42A8-8860-9C9CCD8081FE}"/>
-    <hyperlink ref="N393" r:id="rId131" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/df/Vincent_van_Gogh_-_The_siesta_%28after_Millet%29_-_Google_Art_Project.jpg/1280px-Vincent_van_Gogh_-_The_siesta_%28after_Millet%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{16B07E33-CCA7-4F67-876E-D8BB2BD29546}"/>
-    <hyperlink ref="N376" r:id="rId132" xr:uid="{27BED2DB-F6C4-4150-95B4-C9108126E570}"/>
-    <hyperlink ref="N377" r:id="rId133" display="https://upload.wikimedia.org/wikipedia/commons/7/77/Joseph_Mallord_William_Turner_%281775-1851%29_-_The_Decline_of_the_Carthaginian_Empire_..._-_N00499_-_National_Gallery.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{9D6556D4-6148-4CCD-86AE-A6B5FBE9D50E}"/>
-    <hyperlink ref="N368" r:id="rId134" xr:uid="{005D9B4C-17EB-403D-B6DD-09878FBDE2F1}"/>
-    <hyperlink ref="N369" r:id="rId135" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/19/James_Tissot_-_The_Gallery_of_HMS_Calcutta_%28Portsmouth%29.jpg/1280px-James_Tissot_-_The_Gallery_of_HMS_Calcutta_%28Portsmouth%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{10CCD7EE-99E6-459D-B550-85413C45C147}"/>
-    <hyperlink ref="N359" r:id="rId136" xr:uid="{F733DDEE-6357-4F18-9F20-968ED933E864}"/>
-    <hyperlink ref="N361" r:id="rId137" xr:uid="{A6CFDCA6-16CB-49B8-B807-95DDEAD46170}"/>
-    <hyperlink ref="N363" r:id="rId138" xr:uid="{8F4BA8B8-227C-46A7-8A7D-54AA77B7DFE8}"/>
-    <hyperlink ref="N364" r:id="rId139" xr:uid="{122411B4-5D1A-40C7-9595-833A421BB315}"/>
-    <hyperlink ref="N365" r:id="rId140" xr:uid="{59AF839D-63A1-49B1-ACF6-A31703A595B4}"/>
-    <hyperlink ref="N356" r:id="rId141" xr:uid="{97CFB5A1-2F11-47B9-97A9-FBFCF35DB072}"/>
-    <hyperlink ref="N357" r:id="rId142" xr:uid="{9484D7F3-1D81-48E1-B23D-A81433DE18F7}"/>
-    <hyperlink ref="N351" r:id="rId143" xr:uid="{78DF006F-D22E-46EB-88E8-6E9C6107B1F0}"/>
-    <hyperlink ref="N352" r:id="rId144" xr:uid="{D6B0ED16-112A-4C05-99CB-8EEF6772A0B6}"/>
-    <hyperlink ref="N353" r:id="rId145" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/48/Georges-Pierre_Seurat_-_The_Channel_at_Gravelines%2C_Evening_-_Google_Art_Project.jpg/1280px-Georges-Pierre_Seurat_-_The_Channel_at_Gravelines%2C_Evening_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{44E7F09D-BA5B-4B30-9966-F38F4FE62864}"/>
-    <hyperlink ref="N287" r:id="rId146" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/23/Berthe_Morisot_-_Young_Girl_in_a_Ball_Gown_-_Google_Art_Project.jpg/960px-Berthe_Morisot_-_Young_Girl_in_a_Ball_Gown_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{6CE40D0A-56D4-476F-B9B5-21DBD67B01ED}"/>
-    <hyperlink ref="N288" r:id="rId147" xr:uid="{E94A27FC-A5CF-4035-B509-4B11E64DE7E4}"/>
-    <hyperlink ref="N289" r:id="rId148" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Berthe_Morisot_-_Le_Cerisier_-_Mus%C3%A9e_Marmottan-Monet.jpg/960px-Berthe_Morisot_-_Le_Cerisier_-_Mus%C3%A9e_Marmottan-Monet.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D233A10A-695E-4FA0-A0B2-0C7EF6A8BA78}"/>
-    <hyperlink ref="N296" r:id="rId149" xr:uid="{825E3E84-D8AF-4AF8-96FC-01C5D22B9B33}"/>
-    <hyperlink ref="N297" r:id="rId150" xr:uid="{57980F99-8278-47B3-AE8A-D68D2C074813}"/>
-    <hyperlink ref="N312" r:id="rId151" xr:uid="{04534A08-444E-46DD-AB77-ED5C5FDDBB0F}"/>
-    <hyperlink ref="N313" r:id="rId152" xr:uid="{EBC20411-FBFB-4A55-8825-3966C870B423}"/>
-    <hyperlink ref="N340" r:id="rId153" xr:uid="{46CA573F-B5AF-41A7-BA97-A158F1E7658A}"/>
-    <hyperlink ref="N341" r:id="rId154" xr:uid="{F65D3E21-52EC-497C-970D-7CEB078EA87A}"/>
-    <hyperlink ref="N344" r:id="rId155" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/L%27Incantation_ou_Le_Bois_sacr%C3%A9%2C_par_Paul_S%C3%A9rusier.jpg/960px-L%27Incantation_ou_Le_Bois_sacr%C3%A9%2C_par_Paul_S%C3%A9rusier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C5C4347F-C474-438C-AA0D-79EFEFF8E5C8}"/>
-    <hyperlink ref="N345" r:id="rId156" xr:uid="{1F200118-43D5-41AE-B380-8B89ACF96DC3}"/>
-    <hyperlink ref="N263" r:id="rId157" xr:uid="{6751F152-C2D4-42C8-AFCD-C6DA60282F11}"/>
-    <hyperlink ref="N264" r:id="rId158" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Jean-Fran%C3%A7ois_Millet%2C_L%27Eglise_de_Gr%C3%A9ville.jpg/1280px-Jean-Fran%C3%A7ois_Millet%2C_L%27Eglise_de_Gr%C3%A9ville.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E4EE9526-6116-4054-9420-8DCDEA59AF51}"/>
-    <hyperlink ref="N265" r:id="rId159" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Jean-Fran%C3%A7ois_Millet%2C_Le_parc_%C3%A0_moutons%2C_clair_de_lune.jpg/1280px-Jean-Fran%C3%A7ois_Millet%2C_Le_parc_%C3%A0_moutons%2C_clair_de_lune.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{037C5127-6F76-4488-9B09-463C9B17BC05}"/>
-    <hyperlink ref="N277" r:id="rId160" xr:uid="{E7D56AE3-C8D7-482A-BD82-7B3904A63564}"/>
-    <hyperlink ref="N280" r:id="rId161" xr:uid="{ADFDD23B-6EE8-414C-AB2F-6DD4E0E894B9}"/>
-    <hyperlink ref="N281" r:id="rId162" xr:uid="{D4610BD7-9DAC-4C36-8E24-7B4369AA09D8}"/>
-    <hyperlink ref="N303" r:id="rId163" xr:uid="{1E08B277-C603-4895-BB4C-19035EF34B4F}"/>
-    <hyperlink ref="N304" r:id="rId164" xr:uid="{B40C45C7-5FFB-4790-B211-95958CA32D3D}"/>
-    <hyperlink ref="N305" r:id="rId165" xr:uid="{44D04354-741B-4AD9-ABDA-23137640984D}"/>
-    <hyperlink ref="N336" r:id="rId166" xr:uid="{26A69729-DD97-48BF-9506-F65687236C3A}"/>
-    <hyperlink ref="N337" r:id="rId167" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Th%C3%A9odore_rousseau%2C_il_viale_dei_castagni_%28al_castello_di_souliers%2C_in_piccardia%29%2C_1837.jpg/1280px-Th%C3%A9odore_rousseau%2C_il_viale_dei_castagni_%28al_castello_di_souliers%2C_in_piccardia%29%2C_1837.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1C46117D-D180-4C9C-82F6-AAFC16A3108B}"/>
-    <hyperlink ref="N308" r:id="rId168" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cc/Jeunes_filles_au_bord_de_la_mer-Puvis_de_Chavannes-Orsay-RF_2015.jpg/960px-Jeunes_filles_au_bord_de_la_mer-Puvis_de_Chavannes-Orsay-RF_2015.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B4454A13-7486-4594-AA23-6355C64E43B0}"/>
-    <hyperlink ref="N309" r:id="rId169" xr:uid="{19CF765A-7B83-4601-A434-FB927C6341BE}"/>
-    <hyperlink ref="N325" r:id="rId170" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Eug%C3%A8ne_Murer_%28Hyacinthe-Eug%C3%A8ne_Meunier%2C_1841%E2%80%931906%29_MET_DT1882.jpg/960px-Eug%C3%A8ne_Murer_%28Hyacinthe-Eug%C3%A8ne_Meunier%2C_1841%E2%80%931906%29_MET_DT1882.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{72C16458-F46D-4DDC-9F44-6CDD6AC8CC19}"/>
-    <hyperlink ref="N328" r:id="rId171" xr:uid="{33847253-E337-4888-A830-ECCA93B5FF16}"/>
-    <hyperlink ref="N329" r:id="rId172" xr:uid="{90B77712-EA1D-49A3-8687-58344CAEC6EF}"/>
-    <hyperlink ref="N332" r:id="rId173" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Dante_Gabriel_Rossetti_-_Beata_Beatrix_-_Google_Art_Project.jpg/1920px-Dante_Gabriel_Rossetti_-_Beata_Beatrix_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3091A622-97BA-4DCF-A8D2-5E70F36372BD}"/>
-    <hyperlink ref="N333" r:id="rId174" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/08/Dante_Gabriel_Rossetti_-_Ecce_Ancilla_Domini%21_-_Google_Art_Project.jpg/960px-Dante_Gabriel_Rossetti_-_Ecce_Ancilla_Domini%21_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{ADD15DEB-95A1-4276-9AA8-34E32EFC00A0}"/>
+    <hyperlink ref="N92" r:id="rId55" xr:uid="{A613982D-4B46-4374-ABCB-BF1147E04070}"/>
+    <hyperlink ref="N93" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/22/John_Constable_-_Salisbury_Cathedral_from_the_Bishop%27s_Grounds.jpg/1280px-John_Constable_-_Salisbury_Cathedral_from_the_Bishop%27s_Grounds.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{660778C8-21D7-41DF-B43E-6AB9477E3041}"/>
+    <hyperlink ref="N99" r:id="rId57" xr:uid="{C48A7729-30CF-4FE9-8F28-02F8DA31A683}"/>
+    <hyperlink ref="N100" r:id="rId58" xr:uid="{4355C2FD-1FAD-43D0-B9B7-5E0F150A552F}"/>
+    <hyperlink ref="N101" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/La_Dame_en_bleu_-_Jean-Baptiste_Camille_Corot_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2056.jpg/960px-La_Dame_en_bleu_-_Jean-Baptiste_Camille_Corot_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2056.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C304865E-4701-43BB-A315-1F54723C4241}"/>
+    <hyperlink ref="N116" r:id="rId60" xr:uid="{71C6818B-3187-42E8-8DA0-B7A822A5161E}"/>
+    <hyperlink ref="N117" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/55/Honor%C3%A9_Daumier_-_The_Uprising_%28L%27Emeute%29_-_Google_Art_Project.jpg/1280px-Honor%C3%A9_Daumier_-_The_Uprising_%28L%27Emeute%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2207849A-0FD5-454F-9F02-BAFFE2A6CDBE}"/>
+    <hyperlink ref="N123" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b0/Jacques_Louis_David-Serment_de_l%27arm%C3%A9e_fait_%C3%A0_l%27Empereur_apr%C3%A8s_la_distribution_des_aigles%2C_5_d%C3%A9cembre_1804.jpg/1280px-Jacques_Louis_David-Serment_de_l%27arm%C3%A9e_fait_%C3%A0_l%27Empereur_apr%C3%A8s_la_distribution_des_aigles%2C_5_d%C3%A9cembre_1804.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FF061AFF-C251-448E-9092-2C0E0595BD0F}"/>
+    <hyperlink ref="N124" r:id="rId63" xr:uid="{20150DC0-5C76-48C1-8808-A0D4060073A6}"/>
+    <hyperlink ref="N125" r:id="rId64" xr:uid="{468650D3-BAF1-4E97-8F04-8619CF1DA868}"/>
+    <hyperlink ref="N136" r:id="rId65" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/55/%28Albi%29_Rousse_%28La_Toilette%29_-_1889_-_Henri_de_Toulouse-Lautrec_-_Mus%C3%A9e_d%27Orsay%2C_Paris.jpg/960px-%28Albi%29_Rousse_%28La_Toilette%29_-_1889_-_Henri_de_Toulouse-Lautrec_-_Mus%C3%A9e_d%27Orsay%2C_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{804889E5-620C-4811-B6FA-11BE07AA7B60}"/>
+    <hyperlink ref="N137" r:id="rId66" xr:uid="{58C2DEE8-3184-4821-A01F-DCE034EEF75D}"/>
+    <hyperlink ref="N149" r:id="rId67" xr:uid="{DE98B191-43F3-4002-A4F9-65E9FCE87D17}"/>
+    <hyperlink ref="N165" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/Saint-Germain-en-Laye_%28Yvelines%29_-_Mus%C3%A9e_d%C3%A9partemental_Maurice-Denis_%C2%AB_Le_Prieur%C3%A9_%C2%BB_-_%22L%27%C3%A9chelle_dans_le_feuillage%22_%28Maurice_Denis%2C_1870-1943%29_%2848287824526%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{E6A7C1F6-A887-4899-B0AA-F6F162C706B7}"/>
+    <hyperlink ref="N164" r:id="rId69" xr:uid="{B444480C-FE46-4D42-A99D-37429BE0A5C1}"/>
+    <hyperlink ref="N168" r:id="rId70" xr:uid="{82F22ECA-6133-47C7-9F70-67330F9C864F}"/>
+    <hyperlink ref="N169" r:id="rId71" xr:uid="{81BF6C34-FD61-4BC2-9A73-40BAE8E04824}"/>
+    <hyperlink ref="N172" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/09/James_Ensor_%281891%29_-_Geraamten_twistend_om_een_gehangene_001.jpg/1280px-James_Ensor_%281891%29_-_Geraamten_twistend_om_een_gehangene_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E01C2438-10A1-4097-99F6-6760F1D8DD7B}"/>
+    <hyperlink ref="N173" r:id="rId73" xr:uid="{4F111A99-5D9C-4573-9817-9976166F9483}"/>
+    <hyperlink ref="N176" r:id="rId74" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/On_the_lookout_%28The_white_wall%29_%281872%29%2C_by_Giovanni_Fattori.jpg/1280px-On_the_lookout_%28The_white_wall%29_%281872%29%2C_by_Giovanni_Fattori.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7164BD98-294C-4BC4-867D-7C529084065C}"/>
+    <hyperlink ref="N177" r:id="rId75" xr:uid="{784C806F-BF54-44EB-B9B9-69E21EF04D71}"/>
+    <hyperlink ref="N180" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Friedrich%2C_Caspar_David_-_M%C3%B6nch_am_Meer_-_Alte_Nationalgalerie_in_Berlin.jpg/1280px-Friedrich%2C_Caspar_David_-_M%C3%B6nch_am_Meer_-_Alte_Nationalgalerie_in_Berlin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{936C1E04-B264-4501-8EA0-0E2C488110F6}"/>
+    <hyperlink ref="N181" r:id="rId77" xr:uid="{2ED30E2A-A679-4FCB-8484-14A9E011F084}"/>
+    <hyperlink ref="N188" r:id="rId78" xr:uid="{79787671-35C1-4B84-876B-A82D17EFAB7E}"/>
+    <hyperlink ref="N189" r:id="rId79" xr:uid="{64EA1C71-990E-448A-99B5-3E5600421DBC}"/>
+    <hyperlink ref="N190" r:id="rId80" xr:uid="{BD69ED86-B038-46CD-9EF3-71128AE3BE92}"/>
+    <hyperlink ref="N191" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Paul_Gauguin_Ia_Orana_Maria_%28Hail_Mary%29_The_Metropolitan_Museum_of_Art1.jpg/960px-Paul_Gauguin_Ia_Orana_Maria_%28Hail_Mary%29_The_Metropolitan_Museum_of_Art1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BC19CAAD-1CF7-4574-BC0B-D6B8AD503766}"/>
+    <hyperlink ref="N192" r:id="rId82" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bd/Paul_Gauguin%2C_Nafea_Faa_Ipoipo%3F_%28When_Will_You_Marry%3F%29_1892%2C_oil_on_canvas%2C_101_x_77_cm.jpg/960px-Paul_Gauguin%2C_Nafea_Faa_Ipoipo%3F_%28When_Will_You_Marry%3F%29_1892%2C_oil_on_canvas%2C_101_x_77_cm.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{86BFA8A3-05C5-400B-B6D8-D5597C9A9CA1}"/>
+    <hyperlink ref="N193" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Paul_Gauguin_-_Mahana_no_atua_%28Day_of_the_God%29_-_1926.198_-_Art_Institute_of_Chicago.jpg/1280px-Paul_Gauguin_-_Mahana_no_atua_%28Day_of_the_God%29_-_1926.198_-_Art_Institute_of_Chicago.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C9FEA22A-DF23-46B5-85CD-37650AA49FA0}"/>
+    <hyperlink ref="N204" r:id="rId84" xr:uid="{76214D94-66A9-4BE5-84AA-4CF9FE4120DB}"/>
+    <hyperlink ref="N205" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a9/Jean-L%C3%A9on_G%C3%A9r%C3%B4me_-_Le_charmeur_de_serpents.jpg/1280px-Jean-L%C3%A9on_G%C3%A9r%C3%B4me_-_Le_charmeur_de_serpents.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D037830-A93D-453A-B01B-BE50323ABFE0}"/>
+    <hyperlink ref="N199" r:id="rId86" xr:uid="{76F9296C-85C4-4A4C-835B-18E125C9EED3}"/>
+    <hyperlink ref="N200" r:id="rId87" xr:uid="{DCE4207A-DAB3-440F-8D82-D3B5EDAC8D4B}"/>
+    <hyperlink ref="N201" r:id="rId88" xr:uid="{A1835D70-5A3C-4E41-A85A-31232D6D7B3F}"/>
+    <hyperlink ref="N208" r:id="rId89" xr:uid="{F5572090-998E-4BF4-A715-EF255ECCEF21}"/>
+    <hyperlink ref="N209" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e2/Francesco_Hayez_-_Distruzione_des_tempio_di_Gerusalemme.jpg/1280px-Francesco_Hayez_-_Distruzione_des_tempio_di_Gerusalemme.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F4D2961A-398D-462E-BC0F-AA9C52FB41CC}"/>
+    <hyperlink ref="N212" r:id="rId91" xr:uid="{F2644B0B-A243-49CE-8AB7-5CA7AB3544D2}"/>
+    <hyperlink ref="N213" r:id="rId92" xr:uid="{E6DE9528-18E1-4B93-9909-7FE7B5915738}"/>
+    <hyperlink ref="N215" r:id="rId93" xr:uid="{54418522-D935-41FF-8DCE-42FE2321CC7F}"/>
+    <hyperlink ref="N216" r:id="rId94" xr:uid="{7392222B-02FE-4A19-A5EE-B1CD7D91681C}"/>
+    <hyperlink ref="N217" r:id="rId95" xr:uid="{1961306B-75F0-41CC-BEA9-EB01815AD97B}"/>
+    <hyperlink ref="N220" r:id="rId96" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/48/Katsushika_Hokusai%2C_drago_che_vola_sul_monte_fuji%2C_pittura_su_seta%2C_1849%2C_02.jpg/500px-Katsushika_Hokusai%2C_drago_che_vola_sul_monte_fuji%2C_pittura_su_seta%2C_1849%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AC945414-55C6-4873-AD5B-8CE95A1AA6CA}"/>
+    <hyperlink ref="N221" r:id="rId97" xr:uid="{61CA0861-4A90-44E8-87E5-4C9DC527A23D}"/>
+    <hyperlink ref="N224" r:id="rId98" xr:uid="{E1045DCA-3462-4144-BC63-B713FBE9D4F5}"/>
+    <hyperlink ref="N225" r:id="rId99" xr:uid="{D4D57138-87CD-4408-8975-AA87499F756A}"/>
+    <hyperlink ref="N231" r:id="rId100" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/46/Jean_Auguste_Dominique_Ingres_-_The_Spring_-_Google_Art_Project_2.jpg/960px-Jean_Auguste_Dominique_Ingres_-_The_Spring_-_Google_Art_Project_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A693F64E-53D5-4410-B881-34D855875369}"/>
+    <hyperlink ref="N232" r:id="rId101" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/44/Jean-Auguste-Dominique_Ingres_-_La_Baigneuse_Valpin%C3%A7on.jpg/960px-Jean-Auguste-Dominique_Ingres_-_La_Baigneuse_Valpin%C3%A7on.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D1938B45-011F-414F-87DA-4FC0E8D2AE2F}"/>
+    <hyperlink ref="N233" r:id="rId102" xr:uid="{D0C8F28C-F2C6-49C0-9CD4-0D598E1A180E}"/>
+    <hyperlink ref="N234" r:id="rId103" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Hom%C3%A8re_d%C3%A9ifi%C3%A9%2C_dit_aussi_L%27apoth%C3%A9ose_d%27Hom%C3%A8re_-_Jean-Auguste_Dominique_Ingres_-_Mus%C3%A9e_du_Louvre_Peintures_INV_5417_%3B_C_196.jpg/1280px-Hom%C3%A8re_d%C3%A9ifi%C3%A9%2C_dit_aussi_L%27apoth%C3%A9ose_d%27Hom%C3%A8re_-_Jean-Auguste_Dominique_Ingres_-_Mus%C3%A9e_du_Louvre_Peintures_INV_5417_%3B_C_196.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BB2F7B03-FF62-4F35-8281-56DF3CE982B5}"/>
+    <hyperlink ref="N235" r:id="rId104" xr:uid="{E2FE698E-035E-4186-8C9F-DDFD51D4D1CB}"/>
+    <hyperlink ref="N236" r:id="rId105" xr:uid="{ED1DD965-7C21-4DD7-A91A-87D77F90CA3D}"/>
+    <hyperlink ref="N237" r:id="rId106" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/%C5%92dipe_explique_l%27%C3%A9nigme_du_sphinx_-_Jean-Auguste_Dominique_Ingres_-_Mus%C3%A9e_du_Louvre_Peintures_RF_218.jpg/960px-%C5%92dipe_explique_l%27%C3%A9nigme_du_sphinx_-_Jean-Auguste_Dominique_Ingres_-_Mus%C3%A9e_du_Louvre_Peintures_RF_218.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F85C5582-6667-468A-888A-F96346A9F70C}"/>
+    <hyperlink ref="N241" r:id="rId107" xr:uid="{80F05F13-B8A9-4854-BBC4-97713609CE55}"/>
+    <hyperlink ref="N240" r:id="rId108" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Jongkind_The_Church_of_St._-M%C3%A9dard_on_the_Rue_Mouffetard.png/1280px-Jongkind_The_Church_of_St._-M%C3%A9dard_on_the_Rue_Mouffetard.png?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D318E97A-60C3-4ED8-A330-A050814C061E}"/>
+    <hyperlink ref="N252" r:id="rId109" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Edouard_Manet_-_Berthe_Morisot_With_a_Bouquet_of_Violets_-_Google_Art_Project.jpg/1920px-Edouard_Manet_-_Berthe_Morisot_With_a_Bouquet_of_Violets_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8C937D96-E75E-43EA-9D2B-789AD29346E7}"/>
+    <hyperlink ref="N253" r:id="rId110" xr:uid="{6EC144FB-DA52-4EC7-8CDE-265B928359ED}"/>
+    <hyperlink ref="N256" r:id="rId111" xr:uid="{21B4DF45-B86D-4E4B-8079-A7D5DFE136BA}"/>
+    <hyperlink ref="N257" r:id="rId112" xr:uid="{D98C0F42-EB5A-4AA3-BBF3-20A9670248AC}"/>
+    <hyperlink ref="N416" r:id="rId113" xr:uid="{E3389331-0D52-4A47-897F-64A681B3D28E}"/>
+    <hyperlink ref="N417" r:id="rId114" xr:uid="{BAA0F219-AB77-49BB-94B1-4FD97CBDFE59}"/>
+    <hyperlink ref="N412" r:id="rId115" xr:uid="{4608A50E-2C37-4FB4-B64F-77495BC756C3}"/>
+    <hyperlink ref="N413" r:id="rId116" xr:uid="{19E7B006-0390-4004-83FF-861BB79A0766}"/>
+    <hyperlink ref="N407" r:id="rId117" xr:uid="{5B11A8F3-5B7A-4ED7-8693-8A188273DB8A}"/>
+    <hyperlink ref="N408" r:id="rId118" xr:uid="{598B9595-608C-43B0-B701-CE61322F3A18}"/>
+    <hyperlink ref="N409" r:id="rId119" xr:uid="{F0B20B8C-84CC-47B9-A783-80F80AEF8C1F}"/>
+    <hyperlink ref="N400" r:id="rId120" xr:uid="{BEF9C22C-2034-41C2-A40B-D047266179FF}"/>
+    <hyperlink ref="N401" r:id="rId121" xr:uid="{C63B34B5-0284-4C9E-868F-FE18453F0DDB}"/>
+    <hyperlink ref="N396" r:id="rId122" xr:uid="{99B32D0E-B115-4463-9369-F646863F2620}"/>
+    <hyperlink ref="N397" r:id="rId123" xr:uid="{9A8A5AE7-4BDC-4395-A702-A2210C5D205A}"/>
+    <hyperlink ref="N291" r:id="rId124" xr:uid="{19A60C58-34F0-41D9-9C86-8B03D65386E5}"/>
+    <hyperlink ref="N293" r:id="rId125" xr:uid="{FC449AFA-82CA-44FC-B5A5-2FFF7D75D6BA}"/>
+    <hyperlink ref="N292" r:id="rId126" xr:uid="{8FD57115-A880-412C-B0E9-4D02ACC5D655}"/>
+    <hyperlink ref="N380" r:id="rId127" xr:uid="{51BF2C03-8845-437E-8FC8-11DBB0895200}"/>
+    <hyperlink ref="N381" r:id="rId128" xr:uid="{2D41CF16-D658-4AE1-B0E0-3FBFEEC5D632}"/>
+    <hyperlink ref="N392" r:id="rId129" xr:uid="{D06E67B7-CD04-42A8-8860-9C9CCD8081FE}"/>
+    <hyperlink ref="N393" r:id="rId130" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/df/Vincent_van_Gogh_-_The_siesta_%28after_Millet%29_-_Google_Art_Project.jpg/1280px-Vincent_van_Gogh_-_The_siesta_%28after_Millet%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{16B07E33-CCA7-4F67-876E-D8BB2BD29546}"/>
+    <hyperlink ref="N376" r:id="rId131" xr:uid="{27BED2DB-F6C4-4150-95B4-C9108126E570}"/>
+    <hyperlink ref="N377" r:id="rId132" display="https://upload.wikimedia.org/wikipedia/commons/7/77/Joseph_Mallord_William_Turner_%281775-1851%29_-_The_Decline_of_the_Carthaginian_Empire_..._-_N00499_-_National_Gallery.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{9D6556D4-6148-4CCD-86AE-A6B5FBE9D50E}"/>
+    <hyperlink ref="N368" r:id="rId133" xr:uid="{005D9B4C-17EB-403D-B6DD-09878FBDE2F1}"/>
+    <hyperlink ref="N369" r:id="rId134" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/19/James_Tissot_-_The_Gallery_of_HMS_Calcutta_%28Portsmouth%29.jpg/1280px-James_Tissot_-_The_Gallery_of_HMS_Calcutta_%28Portsmouth%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{10CCD7EE-99E6-459D-B550-85413C45C147}"/>
+    <hyperlink ref="N359" r:id="rId135" xr:uid="{F733DDEE-6357-4F18-9F20-968ED933E864}"/>
+    <hyperlink ref="N361" r:id="rId136" xr:uid="{A6CFDCA6-16CB-49B8-B807-95DDEAD46170}"/>
+    <hyperlink ref="N363" r:id="rId137" xr:uid="{8F4BA8B8-227C-46A7-8A7D-54AA77B7DFE8}"/>
+    <hyperlink ref="N364" r:id="rId138" xr:uid="{122411B4-5D1A-40C7-9595-833A421BB315}"/>
+    <hyperlink ref="N365" r:id="rId139" xr:uid="{59AF839D-63A1-49B1-ACF6-A31703A595B4}"/>
+    <hyperlink ref="N356" r:id="rId140" xr:uid="{97CFB5A1-2F11-47B9-97A9-FBFCF35DB072}"/>
+    <hyperlink ref="N357" r:id="rId141" xr:uid="{9484D7F3-1D81-48E1-B23D-A81433DE18F7}"/>
+    <hyperlink ref="N351" r:id="rId142" xr:uid="{78DF006F-D22E-46EB-88E8-6E9C6107B1F0}"/>
+    <hyperlink ref="N352" r:id="rId143" xr:uid="{D6B0ED16-112A-4C05-99CB-8EEF6772A0B6}"/>
+    <hyperlink ref="N353" r:id="rId144" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/48/Georges-Pierre_Seurat_-_The_Channel_at_Gravelines%2C_Evening_-_Google_Art_Project.jpg/1280px-Georges-Pierre_Seurat_-_The_Channel_at_Gravelines%2C_Evening_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{44E7F09D-BA5B-4B30-9966-F38F4FE62864}"/>
+    <hyperlink ref="N287" r:id="rId145" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/23/Berthe_Morisot_-_Young_Girl_in_a_Ball_Gown_-_Google_Art_Project.jpg/960px-Berthe_Morisot_-_Young_Girl_in_a_Ball_Gown_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{6CE40D0A-56D4-476F-B9B5-21DBD67B01ED}"/>
+    <hyperlink ref="N288" r:id="rId146" xr:uid="{E94A27FC-A5CF-4035-B509-4B11E64DE7E4}"/>
+    <hyperlink ref="N289" r:id="rId147" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Berthe_Morisot_-_Le_Cerisier_-_Mus%C3%A9e_Marmottan-Monet.jpg/960px-Berthe_Morisot_-_Le_Cerisier_-_Mus%C3%A9e_Marmottan-Monet.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D233A10A-695E-4FA0-A0B2-0C7EF6A8BA78}"/>
+    <hyperlink ref="N296" r:id="rId148" xr:uid="{825E3E84-D8AF-4AF8-96FC-01C5D22B9B33}"/>
+    <hyperlink ref="N297" r:id="rId149" xr:uid="{57980F99-8278-47B3-AE8A-D68D2C074813}"/>
+    <hyperlink ref="N312" r:id="rId150" xr:uid="{04534A08-444E-46DD-AB77-ED5C5FDDBB0F}"/>
+    <hyperlink ref="N313" r:id="rId151" xr:uid="{EBC20411-FBFB-4A55-8825-3966C870B423}"/>
+    <hyperlink ref="N340" r:id="rId152" xr:uid="{46CA573F-B5AF-41A7-BA97-A158F1E7658A}"/>
+    <hyperlink ref="N341" r:id="rId153" xr:uid="{F65D3E21-52EC-497C-970D-7CEB078EA87A}"/>
+    <hyperlink ref="N344" r:id="rId154" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/L%27Incantation_ou_Le_Bois_sacr%C3%A9%2C_par_Paul_S%C3%A9rusier.jpg/960px-L%27Incantation_ou_Le_Bois_sacr%C3%A9%2C_par_Paul_S%C3%A9rusier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C5C4347F-C474-438C-AA0D-79EFEFF8E5C8}"/>
+    <hyperlink ref="N345" r:id="rId155" xr:uid="{1F200118-43D5-41AE-B380-8B89ACF96DC3}"/>
+    <hyperlink ref="N263" r:id="rId156" xr:uid="{6751F152-C2D4-42C8-AFCD-C6DA60282F11}"/>
+    <hyperlink ref="N264" r:id="rId157" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Jean-Fran%C3%A7ois_Millet%2C_L%27Eglise_de_Gr%C3%A9ville.jpg/1280px-Jean-Fran%C3%A7ois_Millet%2C_L%27Eglise_de_Gr%C3%A9ville.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E4EE9526-6116-4054-9420-8DCDEA59AF51}"/>
+    <hyperlink ref="N265" r:id="rId158" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Jean-Fran%C3%A7ois_Millet%2C_Le_parc_%C3%A0_moutons%2C_clair_de_lune.jpg/1280px-Jean-Fran%C3%A7ois_Millet%2C_Le_parc_%C3%A0_moutons%2C_clair_de_lune.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{037C5127-6F76-4488-9B09-463C9B17BC05}"/>
+    <hyperlink ref="N277" r:id="rId159" xr:uid="{E7D56AE3-C8D7-482A-BD82-7B3904A63564}"/>
+    <hyperlink ref="N280" r:id="rId160" xr:uid="{ADFDD23B-6EE8-414C-AB2F-6DD4E0E894B9}"/>
+    <hyperlink ref="N281" r:id="rId161" xr:uid="{D4610BD7-9DAC-4C36-8E24-7B4369AA09D8}"/>
+    <hyperlink ref="N303" r:id="rId162" xr:uid="{1E08B277-C603-4895-BB4C-19035EF34B4F}"/>
+    <hyperlink ref="N304" r:id="rId163" xr:uid="{B40C45C7-5FFB-4790-B211-95958CA32D3D}"/>
+    <hyperlink ref="N305" r:id="rId164" xr:uid="{44D04354-741B-4AD9-ABDA-23137640984D}"/>
+    <hyperlink ref="N336" r:id="rId165" xr:uid="{26A69729-DD97-48BF-9506-F65687236C3A}"/>
+    <hyperlink ref="N337" r:id="rId166" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Th%C3%A9odore_rousseau%2C_il_viale_dei_castagni_%28al_castello_di_souliers%2C_in_piccardia%29%2C_1837.jpg/1280px-Th%C3%A9odore_rousseau%2C_il_viale_dei_castagni_%28al_castello_di_souliers%2C_in_piccardia%29%2C_1837.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1C46117D-D180-4C9C-82F6-AAFC16A3108B}"/>
+    <hyperlink ref="N308" r:id="rId167" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cc/Jeunes_filles_au_bord_de_la_mer-Puvis_de_Chavannes-Orsay-RF_2015.jpg/960px-Jeunes_filles_au_bord_de_la_mer-Puvis_de_Chavannes-Orsay-RF_2015.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B4454A13-7486-4594-AA23-6355C64E43B0}"/>
+    <hyperlink ref="N309" r:id="rId168" xr:uid="{19CF765A-7B83-4601-A434-FB927C6341BE}"/>
+    <hyperlink ref="N325" r:id="rId169" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Eug%C3%A8ne_Murer_%28Hyacinthe-Eug%C3%A8ne_Meunier%2C_1841%E2%80%931906%29_MET_DT1882.jpg/960px-Eug%C3%A8ne_Murer_%28Hyacinthe-Eug%C3%A8ne_Meunier%2C_1841%E2%80%931906%29_MET_DT1882.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{72C16458-F46D-4DDC-9F44-6CDD6AC8CC19}"/>
+    <hyperlink ref="N328" r:id="rId170" xr:uid="{33847253-E337-4888-A830-ECCA93B5FF16}"/>
+    <hyperlink ref="N329" r:id="rId171" xr:uid="{90B77712-EA1D-49A3-8687-58344CAEC6EF}"/>
+    <hyperlink ref="N332" r:id="rId172" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Dante_Gabriel_Rossetti_-_Beata_Beatrix_-_Google_Art_Project.jpg/1920px-Dante_Gabriel_Rossetti_-_Beata_Beatrix_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3091A622-97BA-4DCF-A8D2-5E70F36372BD}"/>
+    <hyperlink ref="N333" r:id="rId173" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/08/Dante_Gabriel_Rossetti_-_Ecce_Ancilla_Domini%21_-_Google_Art_Project.jpg/960px-Dante_Gabriel_Rossetti_-_Ecce_Ancilla_Domini%21_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{ADD15DEB-95A1-4276-9AA8-34E32EFC00A0}"/>
+    <hyperlink ref="N87" r:id="rId174" xr:uid="{B392E652-0869-4DE7-AAFE-854E4DA84395}"/>
+    <hyperlink ref="N86" r:id="rId175" xr:uid="{68353DC3-A384-413D-94FD-D8CE88022F6B}"/>
+    <hyperlink ref="N89" r:id="rId176" xr:uid="{05C638B7-FFFA-4FF0-9EC0-36027CBA2BC9}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296DFD84-F173-4525-B4AF-04E572A2290C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD00E8B-11F2-4388-BADE-72521F859817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5692,10 +5692,10 @@
     <t>"Femme au collier de perles dans une loge"</t>
   </si>
   <si>
-    <t>3150 cm</t>
-  </si>
-  <si>
     <t>6680 cm</t>
+  </si>
+  <si>
+    <t>315 cm</t>
   </si>
 </sst>
 </file>
@@ -10935,10 +10935,10 @@
         <v>33</v>
       </c>
       <c r="T105" s="1" t="s">
+        <v>1891</v>
+      </c>
+      <c r="U105" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="U105" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="W105" s="1" t="s">
         <v>95</v>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD00E8B-11F2-4388-BADE-72521F859817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA25D82-0101-4A84-A283-846023C2958D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5692,10 +5692,10 @@
     <t>"Femme au collier de perles dans une loge"</t>
   </si>
   <si>
-    <t>6680 cm</t>
-  </si>
-  <si>
     <t>315 cm</t>
+  </si>
+  <si>
+    <t>668 cm</t>
   </si>
 </sst>
 </file>
@@ -10935,10 +10935,10 @@
         <v>33</v>
       </c>
       <c r="T105" s="1" t="s">
+        <v>1890</v>
+      </c>
+      <c r="U105" s="1" t="s">
         <v>1891</v>
-      </c>
-      <c r="U105" s="1" t="s">
-        <v>1890</v>
       </c>
       <c r="W105" s="1" t="s">
         <v>95</v>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feuil1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -32,12 +32,17 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2A8"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,20 +61,21 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC6E0B4"/>
-          <bgColor rgb="FFC6E0B4"/>
+          <fgColor rgb="FFF4B183"/>
+          <bgColor rgb="FFF4B183"/>
         </patternFill>
       </fill>
     </dxf>
@@ -84,8 +90,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF4B183"/>
-          <bgColor rgb="FFF4B183"/>
+          <fgColor rgb="FFC6E0B4"/>
+          <bgColor rgb="FFC6E0B4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -452,7 +458,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:V413"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -602,6 +608,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/54/Aivazovsky%2C_Ivan_-_The_Ninth_Wave.jpg/1280px-Aivazovsky%2C_Ivan_-_The_Ninth_Wave.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -657,6 +668,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f6/Aivazovsky_-_The_Black_Sea.jpg/1280px-Aivazovsky_-_The_Black_Sea.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -710,6 +726,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/21/Museum_Y1A2487_Aivazovsky_%2821596201195%29.jpg/1280px-Museum_Y1A2487_Aivazovsky_%2821596201195%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -763,6 +784,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/63/Aivazovsky_Chaos_1841.jpg/960px-Aivazovsky_Chaos_1841.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>Huile sur papier</t>
@@ -813,6 +839,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cd/Alma-Tadema_-_The_Roses_of_Heliogabalus.jpg/1280px-Alma-Tadema_-_The_Roses_of_Heliogabalus.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -868,6 +899,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/47/Alma_Tadema_Spring.jpg/1280px-Alma_Tadema_Spring.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -916,6 +952,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/14/1904_Lawrence_Alma-Tadema_-_The_Finding_of_Moses.jpg/1280px-1904_Lawrence_Alma-Tadema_-_The_Finding_of_Moses.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -969,6 +1010,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f5/Sir_Lawrence_Alma-Tadema%2C_English_%28born_Netherlands%29_-_A_Reading_from_Homer_-_Google_Art_Project.jpg/1280px-Sir_Lawrence_Alma-Tadema%2C_English_%28born_Netherlands%29_-_A_Reading_from_Homer_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1024,6 +1070,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/9/91/R%C3%A9union_de_famille_-_Fr%C3%A9d%C3%A9ric_Bazille_-_mus%C3%A9e_d%27Orsay_RF_2749.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1079,6 +1130,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/8b/Fr%C3%A9d%C3%A9ric_Bazille_-_Bazille%27s_Studio_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1127,6 +1183,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bazille%2C_Fr%C3%A9d%C3%A9ric_~_Summer_Scene%2C_1869%2C_Oil_on_canvas_Fogg_Art_Museum%2C_Cambridge%2C_Massachusetts.jpg/1280px-Bazille%2C_Fr%C3%A9d%C3%A9ric_~_Summer_Scene%2C_1869%2C_Oil_on_canvas_Fogg_Art_Museum%2C_Cambridge%2C_Massachusetts.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1180,6 +1241,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0b/Fr%C3%A9d%C3%A9ric_Bazille_-_The_Pink_Dress_-_Google_Art_Project.jpg/960px-Fr%C3%A9d%C3%A9ric_Bazille_-_The_Pink_Dress_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1233,6 +1299,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d8/Fr%C3%A9d%C3%A9ric_Bazille_-_Self-Portrait_-_1962.336_-_Art_Institute_of_Chicago.jpg/960px-Fr%C3%A9d%C3%A9ric_Bazille_-_Self-Portrait_-_1962.336_-_Art_Institute_of_Chicago.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1286,6 +1357,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/09/Fr%C3%A9d%C3%A9ric_Bazille_%E2%80%93_La_T%C3%A9rasse_de_M%C3%A9ric.jpg/1280px-Fr%C3%A9d%C3%A9ric_Bazille_%E2%80%93_La_T%C3%A9rasse_de_M%C3%A9ric.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1339,6 +1415,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7e/The_Ramparts_at_Aigues-Mortes_A29987.jpg/1280px-The_Ramparts_at_Aigues-Mortes_A29987.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1392,6 +1473,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9e/Bazille_-_Vue_de_village%2C_1868%2C_898.5.1.jpg/960px-Bazille_-_Vue_de_village%2C_1868%2C_898.5.1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1447,6 +1533,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/5/55/%C3%89mile_Bernard_-_Madeleine_au_Bois_d%27Amour_%281888%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1502,6 +1593,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/b4/%C3%89mile_Bernard_-_The_Pardon_%28Le_Pardon%29_1888.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1555,6 +1651,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Zelfportret_Rijksmuseum_SK-A-3263.jpeg/960px-Zelfportret_Rijksmuseum_SK-A-3263.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1608,6 +1709,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/4/48/Bernard_-_Quai_de_Clichy_sur_la_Seine%2C_1887.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1663,6 +1769,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/Albert_Bierstadt_-_The_Rocky_Mountains%2C_Lander%27s_Peak.jpg/1280px-Albert_Bierstadt_-_The_Rocky_Mountains%2C_Lander%27s_Peak.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1718,6 +1829,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c6/Albert_Bierstadt_-_Yosemite_Valley_%281866%29.jpg/1280px-Albert_Bierstadt_-_Yosemite_Valley_%281866%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1771,6 +1887,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/The_Last_of_the_Buffalo.jpg/1280px-The_Last_of_the_Buffalo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1824,6 +1945,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Albert_Bierstadt%2C_Among_the_Sierra_Nevada_Mountains.jpg/1280px-Albert_Bierstadt%2C_Among_the_Sierra_Nevada_Mountains.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -1884,6 +2010,11 @@
           <t>Les peintures du Grand Dragon Rouge</t>
         </is>
       </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>Aquarelle</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>Aquarelle, graphite et encre</t>
@@ -1939,6 +2070,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/93/William_Blake_-_The_Ghost_of_a_Flea_-_Google_Art_Project.jpg/960px-William_Blake_-_The_Ghost_of_a_Flea_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>Tempera et or sur bois</t>
@@ -1997,6 +2133,11 @@
           <t>Les peintures du Grand Dragon Rouge</t>
         </is>
       </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Aquarelle</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
           <t>Aquarelle, graphite et encre</t>
@@ -2055,6 +2196,11 @@
           <t>Les peintures du Grand Dragon Rouge</t>
         </is>
       </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Aquarelle</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>Aquarelle, graphite et encre</t>
@@ -2110,6 +2256,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/db/Arnold_Boecklin-fiedelnder_Tod.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -2165,6 +2316,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/6/65/Arnold_B%C3%B6cklin_-_Die_Toteninsel_III_%28Alte_Nationalgalerie%2C_Berlin%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
           <t>Huile sur bois</t>
@@ -2218,6 +2374,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/ba/Arnold_B%C3%B6cklin_-_Die_Pest.jpg/960px-Arnold_B%C3%B6cklin_-_Die_Pest.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr">
         <is>
           <t>Tempera sur bois de sapin</t>
@@ -2271,6 +2432,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Sacred_Grove_%281882%29_-_Arnold_B%C3%B6cklin_%28Kunstmuseum_Basel%29.jpg/1280px-Sacred_Grove_%281882%29_-_Arnold_B%C3%B6cklin_%28Kunstmuseum_Basel%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
           <t>Huile sur bois</t>
@@ -2326,6 +2492,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/c6/Rosa_Bonheur%2C_The_Horse_Fair%2C_1852%E2%80%9355.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -2381,6 +2552,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/2/2b/Rosa_Bonheur_-_Portrait_de_Col._William_F._CodyFXD.jpg</t>
         </is>
       </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -2434,6 +2610,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Mus%C3%A9e_d%27Orsay_-_Rosa_Bonheur_-_Labourage_nivernais_-_001.jpg/1280px-Mus%C3%A9e_d%27Orsay_-_Rosa_Bonheur_-_Labourage_nivernais_-_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -2482,6 +2663,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/5/56/La_fenaison%2C_Rosa_Bonheur.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -2537,6 +2723,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/df/Pierre_Bonnard_-_Panneaux_d%C3%A9coratifs_-_Femmes_au_jardin_-_1982-0024.a-d_-_Kunsthaus_Z%C3%BCrich.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr</t>
         </is>
       </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
           <t>Peinture à la colle sur papier marouflé sur toile</t>
@@ -2590,6 +2781,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/2/2a/Pierre_Bonnard_The_Croquet_Game.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -2643,6 +2839,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/de/Pierre_Bonnard_The_Dressing_Gown.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -2696,6 +2897,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b8/Pierre_Bonnard_The_Large_Garden.jpg/1280px-Pierre_Bonnard_The_Large_Garden.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -2751,6 +2957,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/2/27/William_Bouguereau_-_Dante_and_Virgile_-_Google_Art_Project_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -2806,6 +3017,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/ed/William-Adolphe_Bouguereau_%281825-1905%29_-_The_Birth_of_Venus_%281879%29FXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -2859,6 +3075,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/99/William-Adolphe_Bouguereau_%281825-1905%29_-_The_Dance_%281856%29.jpg/960px-William-Adolphe_Bouguereau_%281825-1905%29_-_The_Dance_%281856%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr">
         <is>
           <t>Huile encaustiquée sur toile</t>
@@ -2919,6 +3140,11 @@
           <t>Ensemble de six œuvres peintes pour La Cathédrale Saint-Louis, dont cinq compositions de plafond</t>
         </is>
       </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr">
         <is>
           <t>Huile encaustiquée sur toile</t>
@@ -2974,6 +3200,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/b7/Edward_Burne-Jones_Le_Chant_d_Amour_%28Song_of_Love%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3027,6 +3258,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Edward_Burne-Jones_The_Golden_Stairs.jpg/500px-Edward_Burne-Jones_The_Golden_Stairs.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3080,6 +3316,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Beguiling_of_Merlin.jpg/960px-Beguiling_of_Merlin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3135,6 +3376,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/e2/Edward_Burne-Jones_-_King_Cophetua_and_the_Beggar_Maid_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3190,6 +3436,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/Fallen_Angel_%28Alexandre_Cabanel%29.jpg/1280px-Fallen_Angel_%28Alexandre_Cabanel%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3243,6 +3494,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Alexandre_Cabanel_Ph%C3%A8dre.jpg/1280px-Alexandre_Cabanel_Ph%C3%A8dre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3296,6 +3552,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e7/Alexandre_Cabanel_-_Cl%C3%A9opatre_essayant_des_poisons_sur_des_condamn%C3%A9s_%C3%A0_mort.jpg/1280px-Alexandre_Cabanel_-_Cl%C3%A9opatre_essayant_des_poisons_sur_des_condamn%C3%A9s_%C3%A0_mort.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R52" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3351,6 +3612,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f6/1863_Alexandre_Cabanel_-_The_Birth_of_Venus.jpg/1280px-1863_Alexandre_Cabanel_-_The_Birth_of_Venus.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R53" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3406,6 +3672,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/c0/Gustave_Caillebotte_-_The_Floor_Planers_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R54" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3461,6 +3732,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/c3/Gustave_Caillebotte_-_Jeune_homme_%C3%A0_sa_fen%C3%AAtre_%28B_32%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R55" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3516,6 +3792,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/f/fe/G._Caillebotte_-_Le_pont_de_l%27Europe.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3571,6 +3852,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Gustave%20Caillebotte%20-%20Paris%20Street%3B%20Rainy%20Day%20-%20Google%20Art%20Project.jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3624,6 +3910,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/f/fc/G._Caillebotte_-_La_Partie_de_B%C3%A2teau.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R58" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3672,6 +3963,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/5/53/Caillebotte%2C_L%27Homme_au_balcon%2C_boulevard_Haussmann_-_Christie%27s.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R59" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3725,6 +4021,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/39/Les_P%C3%A9rissoires_by_Gustave_Caillebotte.JPG/960px-Les_P%C3%A9rissoires_by_Gustave_Caillebotte.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R60" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3778,6 +4079,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/75/Gustave_Caillebotte_-_Rooftops_in_the_Snow_%28snow_effect%29_-_Google_Art_Project.jpg/1280px-Gustave_Caillebotte_-_Rooftops_in_the_Snow_%28snow_effect%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R61" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3833,6 +4139,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/9/9c/Cassat_-_Blue_Armchair_NGA.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R62" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3888,6 +4199,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Mary%20Cassatt%20-%20The%20Child's%20Bath%20-%20Google%20Art%20Project.jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R63" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3941,6 +4257,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Mary_Stevenson_Cassatt%2C_American_-_Woman_with_a_Pearl_Necklace_in_a_Loge_-_Google_Art_Project.jpg/960px-Mary_Stevenson_Cassatt%2C_American_-_Woman_with_a_Pearl_Necklace_in_a_Loge_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R64" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -3996,6 +4317,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d8/Mary_Cassatt_-_The_Boating_Party_-_Google_Art_Project.jpg/1280px-Mary_Cassatt_-_The_Boating_Party_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R65" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4051,6 +4377,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6c/Paul_c%C3%A9zanne%2C_pastorale_%28idillio%29%2C_1870%2C_02.JPG/1280px-Paul_c%C3%A9zanne%2C_pastorale_%28idillio%29%2C_1870%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R66" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4106,6 +4437,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7c/La_Maison_du_pendu%2C_Auvers-sur-Oise%2C_par_Paul_C%C3%A9zanne%2C_FWN_81.jpg/1280px-La_Maison_du_pendu%2C_Auvers-sur-Oise%2C_par_Paul_C%C3%A9zanne%2C_FWN_81.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R67" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4161,6 +4497,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f3/Paul_C%C3%A9zanne_-_The_Buffet_-_Google_Art_Project.jpg/1280px-Paul_C%C3%A9zanne_-_The_Buffet_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R68" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4216,6 +4557,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/89/Compotier%2C_verre_et_pommes%2C_par_Paul_C%C3%A9zanne.jpg</t>
         </is>
       </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R69" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4271,6 +4617,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/09/Pont_de_Maincy%2C_par_Paul_C%C3%A9zanne.jpg/1280px-Pont_de_Maincy%2C_par_Paul_C%C3%A9zanne.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R70" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4326,6 +4677,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/db/Paul_Cezanne%2C_The_Gulf_of_Marseilles_Seen_from_L%27Estaque%2C_c1885.jpg/1280px-Paul_Cezanne%2C_The_Gulf_of_Marseilles_Seen_from_L%27Estaque%2C_c1885.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R71" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4381,6 +4737,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/9/92/Mont_Sainte-Victoire_with_Large_Pine%2C_by_Paul_C%C3%A9zanne.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R72" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4436,6 +4797,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2b/Paul_C%C3%A9zanne_-_Le_Gar%C3%A7on_au_gilet_rouge_-_B%C3%BChrle.jpg/1280px-Paul_C%C3%A9zanne_-_Le_Gar%C3%A7on_au_gilet_rouge_-_B%C3%BChrle.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R73" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4491,6 +4857,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/0/08/The_Card_Players_MET_DP231550.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R74" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4546,6 +4917,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/ca/Homme_%C3%A0_la_pipe%2C_par_Paul_C%C3%A9zanne%2C_Mus%C3%A9e_de_l'Ermitage.jpg</t>
         </is>
       </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R75" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4601,6 +4977,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Paul_c%C3%A9zanne%2C_mele_e_arance%2C_1899_ca._01.JPG/1280px-Paul_c%C3%A9zanne%2C_mele_e_arance%2C_1899_ca._01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R76" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4656,6 +5037,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/f/fe/Paul_C%C3%A9zanne_-_Bathers_(Les_Grandes_Baigneuses)_-_Google_Art_Project.jpg</t>
         </is>
       </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R77" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4711,6 +5097,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9b/Th%C3%A9odore_Chass%C3%A9riau_-_The_Artist%27s_Sisters_-_WGA4808.jpg/1280px-Th%C3%A9odore_Chass%C3%A9riau_-_The_Artist%27s_Sisters_-_WGA4808.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R78" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4766,6 +5157,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Th%C3%A9odore_Chass%C3%A9riau_-_Tepidarium_-_Google_Art_Project.jpg/1280px-Th%C3%A9odore_Chass%C3%A9riau_-_Tepidarium_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R79" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4819,6 +5215,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/La_Toilette_d%27Esther.jpg/960px-La_Toilette_d%27Esther.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R80" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4872,6 +5273,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/96/Th%C3%A9odore_Chass%C3%A9riau_-_Portrait_de_l%27artiste.jpg/960px-Th%C3%A9odore_Chass%C3%A9riau_-_Portrait_de_l%27artiste.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R81" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4927,6 +5333,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/b9/The_Icebergs_%28Frederic_Edwin_Church%29%2C_1861_%28color%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R82" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -4982,6 +5393,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/f/fb/Frederic_Edwin_Church_-_Niagara_Falls%2C_from_the_American_Side_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R83" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5035,6 +5451,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/78/Church_Heart_of_the_Andes.jpg/1280px-Church_Heart_of_the_Andes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R84" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5088,6 +5509,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Cotopaxi_church.jpg/1280px-Cotopaxi_church.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R85" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5143,6 +5569,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/b1/Cole_Thomas_The_Oxbow_%28The_Connecticut_River_near_Northampton_1836%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R86" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5203,6 +5634,11 @@
           <t>Série allégorique de quatre tableaux</t>
         </is>
       </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R87" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5256,6 +5692,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/c6/Cole_Thomas_The_Architect-s_Dream_1840.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R88" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5309,6 +5750,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Thomas_Cole%2C_The_Departure%2C_1837%2C_NGA_166439.jpg/1280px-Thomas_Cole%2C_The_Departure%2C_1837%2C_NGA_166439.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R89" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5364,6 +5810,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/9/97/John_Constable_-_The_Vale_of_Dedham_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R90" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5419,6 +5870,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/John%20Constable%20-%20The%20Hay%20Wain%20(1821).jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R91" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5472,6 +5928,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/3a/Constable_-_The_Cornfield.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R92" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5525,6 +5986,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/22/John_Constable_-_Salisbury_Cathedral_from_the_Bishop%27s_Grounds.jpg/1280px-John_Constable_-_Salisbury_Cathedral_from_the_Bishop%27s_Grounds.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R93" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5580,6 +6046,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/33/Le_pont_de_Narni_-_Jean-Baptiste_Camille_Corot_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1613.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R94" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5635,6 +6106,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/a/aa/Camille_corot%2C_la_cattedrale_di_chartres%2C_1830_poi_1872.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R95" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5690,6 +6166,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/2/21/Corot-_La_Vire_%C3%A0_Saint-L%C3%B4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R96" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5745,6 +6226,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/1/13/Camille_Corot_-_A_Morning._The_Dance_of_the_Nymphs_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R97" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5800,6 +6286,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/2/2c/J-B_Camille_Corot_-_Mortefontaine.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R98" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5855,6 +6346,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/Femme_a_la_perle_-_Jean_Baptiste_Camille_Corot.jpg/960px-Femme_a_la_perle_-_Jean_Baptiste_Camille_Corot.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R99" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5908,6 +6404,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/0/03/Jean-Baptiste-Camille_Corot_-_The_Forum_Seen_from_the_Farnese_Gardens_-_WGA05281.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R100" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -5961,6 +6462,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/La_Dame_en_bleu_-_Jean-Baptiste_Camille_Corot_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2056.jpg/960px-La_Dame_en_bleu_-_Jean-Baptiste_Camille_Corot_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2056.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R101" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6011,6 +6517,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/8f/Gustave_Courbet_-_Le_D%C3%A9sesp%C3%A9r%C3%A9_%281843%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R102" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6066,6 +6577,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e4/The_Wounded_Man.jpg/1280px-The_Wounded_Man.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R103" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6121,6 +6637,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/35/Courbet_Autoportrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R104" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6176,6 +6697,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/eb/Courbet%2C_Un_enterrement_%C3%A0_Ornans.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R105" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6231,6 +6757,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/87/Gustave_Courbet_-_After_Dinner_at_Ornans_-_WGA05456.jpg/1280px-Gustave_Courbet_-_After_Dinner_at_Ornans_-_WGA05456.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R106" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6286,6 +6817,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/95/Gustave_Courbet_-_The_Sleeping_Spinner_-_WGA05461.jpg/1280px-Gustave_Courbet_-_The_Sleeping_Spinner_-_WGA05461.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R107" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6341,6 +6877,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Courbet_LAtelier_du_peintre.jpg/1280px-Courbet_LAtelier_du_peintre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R108" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6396,6 +6937,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/c5/Gustave_Courbet_-_The_Meeting_or_Bonjour_Monsieur_Courbet_-_WGA05463.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R109" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6451,6 +6997,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/28/Gustave_Courbet_027.jpg/1280px-Gustave_Courbet_027.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R110" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6506,6 +7057,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/3f/Origin-of-the-World.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R111" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6561,6 +7117,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6c/Gustave_Courbet_-_Le_Sommeil_%281866%29%2C_Paris%2C_Petit_Palais.jpg/1280px-Gustave_Courbet_-_Le_Sommeil_%281866%29%2C_Paris%2C_Petit_Palais.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R112" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6621,6 +7182,11 @@
           <t>Cycle des Vagues</t>
         </is>
       </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R113" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6676,6 +7242,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/39/Honor%C3%A9_Daumier_-_Crispin_and_Scapin_-_WGA05960.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R114" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6731,6 +7302,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/a/ac/Honor%C3%A9_Daumier_017_%28Don_Quixote%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R115" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6784,6 +7360,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2e/Honor%C3%A9_Daumier_034.jpg/1280px-Honor%C3%A9_Daumier_034.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R116" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6839,6 +7420,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/55/Honor%C3%A9_Daumier_-_The_Uprising_%28L%27Emeute%29_-_Google_Art_Project.jpg/1280px-Honor%C3%A9_Daumier_-_The_Uprising_%28L%27Emeute%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R117" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6894,6 +7480,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/a/a8/Jacques-Louis_David_-_Madame_R%C3%A9camier_-_WGA6082.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R118" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6944,6 +7535,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/e3/Jacques_Louis_David_-_Bonaparte_franchissant_le_Grand_Saint-Bernard%2C_20_mai_1800_-_Google_Art_ProjectFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R119" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -6999,6 +7595,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/b8/Le_Sacre_de_Napol%C3%A9on%2C_David%2C_1804.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R120" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -7052,6 +7653,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/96/Jacques-Louis_David_004.jpg/1280px-Jacques-Louis_David_004.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R121" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -7107,6 +7713,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/d7/Jacques-Louis_David_-_Mars_desarme_par_Venus.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R122" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -7155,6 +7766,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b0/Jacques_Louis_David-Serment_de_l%27arm%C3%A9e_fait_%C3%A0_l%27Empereur_apr%C3%A8s_la_distribution_des_aigles%2C_5_d%C3%A9cembre_1804.jpg/1280px-Jacques_Louis_David-Serment_de_l%27arm%C3%A9e_fait_%C3%A0_l%27Empereur_apr%C3%A8s_la_distribution_des_aigles%2C_5_d%C3%A9cembre_1804.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R123" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -7208,6 +7824,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/ba/Clevelandart_1962.37.jpg/1280px-Clevelandart_1962.37.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R124" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -7261,6 +7882,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fc/Sappho-and-phaon.jpg/1280px-Sappho-and-phaon.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R125" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -7316,6 +7942,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/4/4c/Goya_Maja_naga2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R126" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -7371,6 +8002,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/89/La_familia_de_Carlos_IV%2C_Francisco_de_Goya.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R127" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -7426,6 +8062,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/a/a6/Goya_Maja_ubrana2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R128" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -7481,6 +8122,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/3f/Francisco_de_Goya_y_Lucientes_-_Los_fusilamientos_del_tres_de_mayo_-_1814.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R129" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -7536,6 +8182,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/82/Francisco_de_Goya%2C_Saturno_devorando_a_su_hijo_%281819-1823%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Fresque</t>
+        </is>
+      </c>
       <c r="R130" t="inlineStr">
         <is>
           <t>Peinture murale transposée sur toile</t>
@@ -7591,6 +8242,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/17/Lautrec_moulin_rouge%2C_la_goulue_%28poster%29_1891.jpg/1280px-Lautrec_moulin_rouge%2C_la_goulue_%28poster%29_1891.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>Estampe</t>
+        </is>
+      </c>
       <c r="R131" t="inlineStr">
         <is>
           <t>Lithographie</t>
@@ -7646,6 +8302,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/0/0b/Henri_de_Toulouse-Lautrec_-_Jane_Avril_Dancing_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R132" t="inlineStr">
         <is>
           <t>Huile sur carton</t>
@@ -7701,6 +8362,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Toulouse-Lautrec_-_Ambassadeurs_Aristide_Bruant%2C_1948.450.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>Estampe</t>
+        </is>
+      </c>
       <c r="R133" t="inlineStr">
         <is>
           <t xml:space="preserve">Lithographie </t>
@@ -7756,6 +8422,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/6/60/%28Albi%29_Au_Salon_de_la_rue_des_Moulins_-_Henri_de_Toulouse-Lautrec_1894_MTL.inv181.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R134" t="inlineStr">
         <is>
           <t>Peinture à la colle sur toile</t>
@@ -7811,6 +8482,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Henri_de_toulouse-laurtrec%2C_ballo_al_moulin_rouge_%28la_goulue_e_valentin_il_disossato%29%2C_1895%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R135" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -7864,6 +8540,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/55/%28Albi%29_Rousse_%28La_Toilette%29_-_1889_-_Henri_de_Toulouse-Lautrec_-_Mus%C3%A9e_d%27Orsay%2C_Paris.jpg/960px-%28Albi%29_Rousse_%28La_Toilette%29_-_1889_-_Henri_de_Toulouse-Lautrec_-_Mus%C3%A9e_d%27Orsay%2C_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R136" t="inlineStr">
         <is>
           <t>Huile sur carton</t>
@@ -7917,6 +8598,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/8a/Lautrec_the_clownesse_cha-u-kao_at_the_moulin_rouge_1895.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R137" t="inlineStr">
         <is>
           <t>Huile sur carton</t>
@@ -7972,6 +8658,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/f/ff/Edgar_Degas_-_The_Bellelli_Family_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R138" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8027,6 +8718,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/d2/Edgar_Degas_-_The_Orchestra_at_the_Opera_-_Google_Art_Project_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R139" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8082,6 +8778,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Edgar%20Degas%20-%20The%20Ballet%20Class%20-%20Google%20Art%20Project.jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R140" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8137,6 +8838,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/80/Cottonexchange1873-Degas.jpg/1280px-Cottonexchange1873-Degas.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R141" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8153,7 +8859,7 @@
         </is>
       </c>
       <c r="V141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -8192,6 +8898,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/c9/Edgar_Degas_-_Ballet_Rehearsal_on_Stage_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R142" t="inlineStr">
         <is>
           <t>Peinture à l'essence sur toile</t>
@@ -8247,6 +8958,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/e8/Edgar_Degas_-_In_a_Caf%C3%A9_-_Google_Art_Project_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R143" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8302,6 +9018,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/ec/Edgar_Degas_-_Ballet_%28L%27%C3%89toile%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R144" t="inlineStr">
         <is>
           <t>Pastel sur monotype</t>
@@ -8357,6 +9078,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ef/Edgar_Degas%2C_Miss_La_La_at_the_Cirque_Fernando%2C_1879.jpg/1280px-Edgar_Degas%2C_Miss_La_La_at_the_Cirque_Fernando%2C_1879.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R145" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8373,7 +9099,7 @@
         </is>
       </c>
       <c r="V145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -8412,6 +9138,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Edgar_Degas_-_The_Millinery_Shop_-_Google_Art_Project.jpg/1280px-Edgar_Degas_-_The_Millinery_Shop_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R146" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8428,7 +9159,7 @@
         </is>
       </c>
       <c r="V146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -8467,6 +9198,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Edgar_Degas%2C_1886_-_The_Tub.jpg/1280px-Edgar_Degas%2C_1886_-_The_Tub.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R147" t="inlineStr">
         <is>
           <t>Pastel sur carton</t>
@@ -8483,7 +9219,7 @@
         </is>
       </c>
       <c r="V147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -8522,6 +9258,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Edgar_Germain_Hilaire_Degas_076.jpg/1280px-Edgar_Germain_Hilaire_Degas_076.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R148" t="inlineStr">
         <is>
           <t>Pastel sur papier</t>
@@ -8538,7 +9279,7 @@
         </is>
       </c>
       <c r="V148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -8577,6 +9318,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/9/97/Edgar_Germain_Hilaire_Degas_084.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R149" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8593,7 +9339,7 @@
         </is>
       </c>
       <c r="V149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -8632,6 +9378,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/9/9f/La_Barque_de_Dante_%28Delacroix_3820%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R150" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8687,6 +9438,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/74/Jeune_Orpheline_au_cimeti%C3%A8re_-_Eug%C3%A8ne_Delacroix_-_Muse_du_Louvre_Peintures_RF_1652_-_photo_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R151" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8742,6 +9498,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/6/66/Eug%C3%A8ne_Delacroix_-_Le_Massacre_de_Scio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R152" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8797,6 +9558,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/0/03/Death_of_Sardanapalus_by_Eug%C3%A8ne_Delacroix.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original&amp;uselang=fr</t>
         </is>
       </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R153" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8852,6 +9618,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Eug%C3%A8ne%20Delacroix%20-%20La%20libert%C3%A9%20guidant%20le%20peuple.jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R154" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8907,6 +9678,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/54/Delacroix-Bataille-de-Nancy_cropped.jpg/1280px-Delacroix-Bataille-de-Nancy_cropped.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R155" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -8923,7 +9699,7 @@
         </is>
       </c>
       <c r="V155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -8962,6 +9738,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/74/Femmes_d%27Alger_dans_leur_appartement%2C_Eug%C3%A8ne_Delacroix_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3824.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R156" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9017,6 +9798,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/9/9d/Eugene_delacroix.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R157" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9067,6 +9853,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/57/The_Battle_of_Taillebourg%2C_21st_July_1242FXD.jpg/1280px-The_Battle_of_Taillebourg%2C_21st_July_1242FXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R158" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9083,7 +9874,7 @@
         </is>
       </c>
       <c r="V158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -9122,6 +9913,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e4/Prise_de_Constantinople_par_les_Crois%C3%A9s_%2812_avril_1204%29_-_Eug%C3%A8ne_Delacroix_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1659.jpg/1280px-Prise_de_Constantinople_par_les_Crois%C3%A9s_%2812_avril_1204%29_-_Eug%C3%A8ne_Delacroix_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1659.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R159" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9138,7 +9934,7 @@
         </is>
       </c>
       <c r="V159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -9177,6 +9973,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2f/Delacroix_-_Femmes_d%27Alger_dans_leur_int%C3%A9rieur%2C_1849.jpg/1280px-Delacroix_-_Femmes_d%27Alger_dans_leur_int%C3%A9rieur%2C_1849.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R160" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9237,6 +10038,11 @@
           <t>Cycle de la chapelle des Saints-Anges</t>
         </is>
       </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R161" t="inlineStr">
         <is>
           <t>Peinture à la cire et à l'huile sur mur</t>
@@ -9253,7 +10059,7 @@
         </is>
       </c>
       <c r="V161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -9292,6 +10098,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/4/4d/MauriceDenis-LeMystereCatholique.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R162" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9347,6 +10158,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/ee/Les_Muses%2C_par_Maurice_Denis.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R163" t="inlineStr">
         <is>
           <t>Huile sur carton</t>
@@ -9400,6 +10216,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/23/Maurice_Denis_Homage_to_Cezanne_1900.jpg/1280px-Maurice_Denis_Homage_to_Cezanne_1900.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R164" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9453,6 +10274,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/Saint-Germain-en-Laye_%28Yvelines%29_-_Mus%C3%A9e_d%C3%A9partemental_Maurice-Denis_%C2%AB_Le_Prieur%C3%A9_%C2%BB_-_%22L%27%C3%A9chelle_dans_le_feuillage%22_%28Maurice_Denis%2C_1870-1943%29_%2848287824526%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R165" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9508,6 +10334,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/8f/The_pair-oared_shell_thomas_eakins.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R166" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9563,6 +10394,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/be/The_gross_clinic_thomas_eakins.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R167" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9618,6 +10454,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/50/Swimming_hole.jpg/1280px-Swimming_hole.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R168" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9671,6 +10512,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/Thomas_Eakins_-_Between_Rounds_%281890s%29.jpg/960px-Thomas_Eakins_-_Between_Rounds_%281890s%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R169" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9726,6 +10572,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/James%20Ensor%20-%20Christ's%20Entry%20into%20Brussels%20in%201889.jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R170" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9781,6 +10632,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/c3/L%27Intrigue_%28James_Ensor%2C_1890%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R171" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9834,6 +10690,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/09/James_Ensor_%281891%29_-_Geraamten_twistend_om_een_gehangene_001.jpg/1280px-James_Ensor_%281891%29_-_Geraamten_twistend_om_een_gehangene_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R172" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9887,6 +10748,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/5/59/James_Ensor_-_Ensor_with_Masks.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R173" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9942,6 +10808,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/Giovanni_Fattori%2C_Battle_of_Magenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R174" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -9997,6 +10868,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/6/69/The_Palmieri_Baths_Roundabout_in_Livorno_%281866%29%2C_by_Giovanni_Fattori.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R175" t="inlineStr">
         <is>
           <t>Huile sur bois</t>
@@ -10050,6 +10926,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/On_the_lookout_%28The_white_wall%29_%281872%29%2C_by_Giovanni_Fattori.jpg/1280px-On_the_lookout_%28The_white_wall%29_%281872%29%2C_by_Giovanni_Fattori.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R176" t="inlineStr">
         <is>
           <t>Huile sur bois</t>
@@ -10103,6 +10984,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Giovanni_Fattori_023.jpg/1280px-Giovanni_Fattori_023.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R177" t="inlineStr">
         <is>
           <t>Huile sur bois</t>
@@ -10158,6 +11044,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/a/a6/Ueber-die-sammlung-19-jahrhundert-caspar-david-friedrich-wanderer-ueber-dem-nebelmeer.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R178" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10213,6 +11104,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/77/Friedrich%2C_Caspar_David_-_Eismeer.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R179" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10268,6 +11164,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Friedrich%2C_Caspar_David_-_M%C3%B6nch_am_Meer_-_Alte_Nationalgalerie_in_Berlin.jpg/1280px-Friedrich%2C_Caspar_David_-_M%C3%B6nch_am_Meer_-_Alte_Nationalgalerie_in_Berlin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R180" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10321,6 +11222,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/79/Friedrich%2C_Caspar_David_-_Kreidefelsen_auf_R%C3%BCgen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R181" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10376,6 +11282,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/6/64/Paul_Gauguin_-_Self-Portrait_with_Halo_and_Snake.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R182" t="inlineStr">
         <is>
           <t>Huile sur bois</t>
@@ -10431,6 +11342,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/5/54/Paul_Gauguin_-_The_Yellow_Christ_%28Le_Christ_jaune%29_1889.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R183" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10486,6 +11402,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/73/Paul_Gauguin_056.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R184" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10541,6 +11462,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/dc/Arearea%2C_by_Paul_Gauguin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R185" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10596,6 +11522,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/d0/Gauguin%2C_Paul_-_Woman_Holding_a_Fruit_%28Eu_haere_ia_oe%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R186" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10651,6 +11582,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/e5/Paul_Gauguin_-_D%27ou_venons-nous.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R187" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10704,6 +11640,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/56/La_vision_apr%C3%A8s_le_sermon_%28Paul_Gauguin%29.jpg/1280px-La_vision_apr%C3%A8s_le_sermon_%28Paul_Gauguin%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R188" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10757,6 +11698,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Paul_Gauguin_-_The_Green_Christ_%281889%29.jpg/960px-Paul_Gauguin_-_The_Green_Christ_%281889%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R189" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10810,6 +11756,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Paul_Gauguin_085.jpg/960px-Paul_Gauguin_085.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R190" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10863,6 +11814,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Paul_Gauguin_Ia_Orana_Maria_%28Hail_Mary%29_The_Metropolitan_Museum_of_Art1.jpg/960px-Paul_Gauguin_Ia_Orana_Maria_%28Hail_Mary%29_The_Metropolitan_Museum_of_Art1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R191" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10916,6 +11872,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bd/Paul_Gauguin%2C_Nafea_Faa_Ipoipo%3F_%28When_Will_You_Marry%3F%29_1892%2C_oil_on_canvas%2C_101_x_77_cm.jpg/960px-Paul_Gauguin%2C_Nafea_Faa_Ipoipo%3F_%28When_Will_You_Marry%3F%29_1892%2C_oil_on_canvas%2C_101_x_77_cm.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R192" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -10969,6 +11930,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Paul_Gauguin_-_Mahana_no_atua_%28Day_of_the_God%29_-_1926.198_-_Art_Institute_of_Chicago.jpg/1280px-Paul_Gauguin_-_Mahana_no_atua_%28Day_of_the_God%29_-_1926.198_-_Art_Institute_of_Chicago.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R193" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11024,6 +11990,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/7e/GericaultHorseman.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original&amp;uselang=fr</t>
         </is>
       </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R194" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11079,6 +12050,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cc/G%C3%A9ricault_-_Course_de_chevaux_libres_%C3%A0_Rome%2C_1817.jpg/1280px-G%C3%A9ricault_-_Course_de_chevaux_libres_%C3%A0_Rome%2C_1817.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R195" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11134,6 +12110,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/6/69/Th%C3%A9odore_G%C3%A9ricault_-_Le_Radeau_de_la_M%C3%A9duse.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R196" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11194,6 +12175,11 @@
           <t>Série médicale de dix portraits d'aliénés commandés par le psychiatre Etienne-Jean Georget (cinq tableaux ont survécu)</t>
         </is>
       </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R197" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11249,6 +12235,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/0/03/Le_Derby_de_1821_%C3%A0_Epsom_-_Th%C3%A9odore_G%C3%A9ricault_-_Mus%C3%A9e_du_Louvre_Peintures_MI_708_-_photo_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R198" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11309,6 +12300,11 @@
           <t>Série médicale de dix portraits d'aliénés commandés par le psychiatre Etienne-Jean Georget (cinq tableaux ont survécu)</t>
         </is>
       </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R199" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11364,6 +12360,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/39/Jean_Louis_Th%C3%A9odore_G%C3%A9ricault_011.jpg/1280px-Jean_Louis_Th%C3%A9odore_G%C3%A9ricault_011.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R200" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11419,6 +12420,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/79/Th%C3%A9odore_G%C3%A9ricault_-_T%C3%AAtes_coup%C3%A9es.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R201" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11474,6 +12480,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Jean-L%C3%A9on_G%C3%A9r%C3%B4me_-_Jeunes_Grecs_faisant_battre_des_coqs%2C_1846.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R202" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11529,6 +12540,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/d8/Jean-L%C3%A9on_G%C3%A9r%C3%B4me%2C_Phryne_revealed_before_the_Areopagus_%281861%29_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R203" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11582,6 +12598,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Jean-Leon_Gerome_Pollice_Verso.jpg/1280px-Jean-Leon_Gerome_Pollice_Verso.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R204" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11635,6 +12656,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a9/Jean-L%C3%A9on_G%C3%A9r%C3%B4me_-_Le_charmeur_de_serpents.jpg/1280px-Jean-L%C3%A9on_G%C3%A9r%C3%B4me_-_Le_charmeur_de_serpents.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R205" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11690,6 +12716,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/2/29/Bathsheba_%28c.1827%29%2C_by_Francesco_Hayez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R206" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11745,6 +12776,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/c6/El_Beso_%28Pinacoteca_de_Brera%2C_Mil%C3%A1n%2C_1859%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=origina</t>
         </is>
       </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R207" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11798,6 +12834,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/4/48/Hayez%2C_L%27ultimo_addio_di_Giulietta_a_Romeo%2C_1823.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R208" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11851,6 +12892,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e2/Francesco_Hayez_-_Distruzione_des_tempio_di_Gerusalemme.jpg/1280px-Francesco_Hayez_-_Distruzione_des_tempio_di_Gerusalemme.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R209" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11906,6 +12952,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/1/1d/L%27Alsace_Elle_attend_Mus%C3%A9e_JJ_Henner.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R210" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -11961,6 +13012,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Jean-Jacques_Henner_Fabiola.jpg/1280px-Jean-Jacques_Henner_Fabiola.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R211" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -12014,6 +13070,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ec/Liseuse-Henner-Orsay.jpg/1280px-Liseuse-Henner-Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R212" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -12067,6 +13128,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/2/2e/Saint_S%C3%A9bastien%2C_par_Jean-Jacques_Henner.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R213" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -12122,6 +13188,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Ferdinand_Hodler_-_Die_Nacht_%281889-90%29.jpg/1280px-Ferdinand_Hodler_-_Die_Nacht_%281889-90%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R214" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -12175,6 +13246,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3d/Ferdinand_Hodler_Die_Lebensm%C3%BCden.jpg/1280px-Ferdinand_Hodler_Die_Lebensm%C3%BCden.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R215" t="inlineStr">
         <is>
           <t>Huile et tempera sur toile</t>
@@ -12230,6 +13306,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bf/Ferdinand_hodler%2C_l%27eletto%2C_1893-94.JPG/1280px-Ferdinand_hodler%2C_l%27eletto%2C_1893-94.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R216" t="inlineStr">
         <is>
           <t>Huile et tempera sur toile</t>
@@ -12283,6 +13364,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e7/Hodler_Aufgehen_im_All_1892.jpg/960px-Hodler_Aufgehen_im_All_1892.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R217" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -12338,6 +13424,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fb/Winslow_Homer_-_Snap_the_Whip_%28Butler_Institute_of_American_Art%29.jpg/1280px-Winslow_Homer_-_Snap_the_Whip_%28Butler_Institute_of_American_Art%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R218" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -12354,7 +13445,7 @@
         </is>
       </c>
       <c r="V218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219">
@@ -12393,6 +13484,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b5/Winslow_Homer_-_The_Gulf_Stream.jpg/1280px-Winslow_Homer_-_The_Gulf_Stream.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R219" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -12448,6 +13544,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d7/Winslow_Homer_-_Breezing_Up_%28A_Fair_Wind%29.jpg/1280px-Winslow_Homer_-_Breezing_Up_%28A_Fair_Wind%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R220" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -12501,6 +13602,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/Fox_Hunt_1893_Winslow_Homer.jpg/1280px-Fox_Hunt_1893_Winslow_Homer.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R221" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -12556,6 +13662,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/8b/Jean_Auguste_Dominique_Ingres_017.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R222" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -12572,7 +13683,7 @@
         </is>
       </c>
       <c r="V222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -12611,6 +13722,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/df/La_grande_odalisque_-_Jean-Auguste_Dominique_Ingres_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1158.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R223" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -12666,6 +13782,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/de/Jean_Auguste_Dominique_Ingres_-_Monsieur_Bertin_-_WGA11850.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R224" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -12721,6 +13842,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/80/Jean-Auguste-Dominique_Ingres_-_Comtesse_d%27Haussonville_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R225" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -12776,6 +13902,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/9/9c/Le_Bain_Turc%2C_by_Jean_Auguste_Dominique_Ingres%2C_from_C2RMFFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R226" t="inlineStr">
         <is>
           <t>Huile sur toile marouflée sur bois (tondo)</t>
@@ -12829,6 +13960,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/46/Jean_Auguste_Dominique_Ingres_-_The_Spring_-_Google_Art_Project_2.jpg/960px-Jean_Auguste_Dominique_Ingres_-_The_Spring_-_Google_Art_Project_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R227" t="inlineStr">
         <is>
           <t xml:space="preserve">Huile sur toile </t>
@@ -12882,6 +14018,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/44/Jean-Auguste-Dominique_Ingres_-_La_Baigneuse_Valpin%C3%A7on.jpg/960px-Jean-Auguste-Dominique_Ingres_-_La_Baigneuse_Valpin%C3%A7on.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R228" t="inlineStr">
         <is>
           <t xml:space="preserve">Huile sur toile </t>
@@ -12935,6 +14076,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/f/f6/Le_Voeu_de_Louis_XIII.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R229" t="inlineStr">
         <is>
           <t>Huile sur toile )</t>
@@ -12988,6 +14134,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Hom%C3%A8re_d%C3%A9ifi%C3%A9%2C_dit_aussi_L%27apoth%C3%A9ose_d%27Hom%C3%A8re_-_Jean-Auguste_Dominique_Ingres_-_Mus%C3%A9e_du_Louvre_Peintures_INV_5417_%3B_C_196.jpg/1280px-Hom%C3%A8re_d%C3%A9ifi%C3%A9%2C_dit_aussi_L%27apoth%C3%A9ose_d%27Hom%C3%A8re_-_Jean-Auguste_Dominique_Ingres_-_Mus%C3%A9e_du_Louvre_Peintures_INV_5417_%3B_C_196.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R230" t="inlineStr">
         <is>
           <t xml:space="preserve">Huile sur toile </t>
@@ -13041,6 +14192,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/08/J%C3%BApiter_y_Tetis%2C_por_Dominique_Ingres.jpg/960px-J%C3%BApiter_y_Tetis%2C_por_Dominique_Ingres.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R231" t="inlineStr">
         <is>
           <t xml:space="preserve">Huile sur toile </t>
@@ -13094,6 +14250,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Jean_Auguste_Dominique_Ingres_-_Mademoiselle_Riviere.jpg/960px-Jean_Auguste_Dominique_Ingres_-_Mademoiselle_Riviere.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R232" t="inlineStr">
         <is>
           <t xml:space="preserve">Huile sur toile </t>
@@ -13147,6 +14308,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/%C5%92dipe_explique_l%27%C3%A9nigme_du_sphinx_-_Jean-Auguste_Dominique_Ingres_-_Mus%C3%A9e_du_Louvre_Peintures_RF_218.jpg/960px-%C5%92dipe_explique_l%27%C3%A9nigme_du_sphinx_-_Jean-Auguste_Dominique_Ingres_-_Mus%C3%A9e_du_Louvre_Peintures_RF_218.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R233" t="inlineStr">
         <is>
           <t xml:space="preserve">Huile sur toile </t>
@@ -13202,6 +14368,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/bb/Johan_Barthold_Jongkind%2C_The_Pont_Neuf%2C_ca._1849%E2%80%9350.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R234" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13257,6 +14428,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/5/57/Johan_Barthold_Jongkind_The_Seine_and_Notre-Dame_in_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R235" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13310,6 +14486,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Jongkind_The_Church_of_St._-M%C3%A9dard_on_the_Rue_Mouffetard.png/1280px-Jongkind_The_Church_of_St._-M%C3%A9dard_on_the_Rue_Mouffetard.png?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R236" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13363,6 +14544,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/78/Johan_Barthold_Jongkind_-_Jaagpad_bij_Overschie.jpg/1280px-Johan_Barthold_Jongkind_-_Jaagpad_bij_Overschie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R237" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13418,6 +14604,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/MANET_-_M%C3%BAsica_en_las_Tuller%C3%ADas_%28National_Gallery%2C_Londres%2C_1862%29.jpg/1280px-MANET_-_M%C3%BAsica_en_las_Tuller%C3%ADas_%28National_Gallery%2C_Londres%2C_1862%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R238" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13473,6 +14664,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/5/5c/Edouard_Manet_-_Olympia_-_Google_Art_Project_3.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R239" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13528,6 +14724,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/f/fc/%C3%89douard_Manet_-_Le_D%C3%A9jeuner_sur_l%27herbe.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R240" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13583,6 +14784,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/a/a2/Manet%2C_Edouard_-_Young_Flautist%2C_or_The_Fifer%2C_1866_%282%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R241" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13638,6 +14844,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/a/ad/Edouard_Manet_-_The_Balcony_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R242" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13693,6 +14904,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/ec/Edouard_Manet.-_Monet_peignant_sur_son_atelier-b%C3%A2teau.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R243" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13748,6 +14964,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Edouard_Manet_003.jpg/960px-Edouard_Manet_003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R244" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13803,6 +15024,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9e/1877_Manet_Nana_anagoria.jpg/1280px-1877_Manet_Nana_anagoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R245" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13858,6 +15084,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/In_the_Conservatory.jpg/1280px-In_the_Conservatory.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R246" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13913,6 +15144,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/0/0d/Edouard_Manet%2C_A_Bar_at_the_Folies-Berg%C3%A8re.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R247" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -13966,6 +15202,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Edouard_Manet_-_Berthe_Morisot_With_a_Bouquet_of_Violets_-_Google_Art_Project.jpg/1920px-Edouard_Manet_-_Berthe_Morisot_With_a_Bouquet_of_Violets_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R248" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14019,6 +15260,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Edouard_Manet_049.jpg/960px-Edouard_Manet_049.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R249" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14074,6 +15320,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/7b/John_Everett_Millais_-_Christ_in_the_House_of_His_Parents_%28%60The_Carpenter%27s_Shop%27%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R250" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14129,6 +15380,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/John%20Everett%20Millais%20-%20Ophelia%20-%20Google%20Art%20Project.jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R251" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14182,6 +15438,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/John_Everett_Millais_-_The_Blind_Girl%2C_1854-56.jpg/960px-John_Everett_Millais_-_The_Blind_Girl%2C_1854-56.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R252" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14235,6 +15496,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Bubbles_-_Sir_John_Everett_Millais.png/960px-Bubbles_-_Sir_John_Everett_Millais.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R253" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14288,6 +15554,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/40/Jean-Fran%C3%A7ois_Millet_-_Le_Semeur.jpg/960px-Jean-Fran%C3%A7ois_Millet_-_Le_Semeur.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R254" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14343,6 +15614,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Jean-Fran%C3%A7ois%20Millet%20-%20Gleaners%20-%20Google%20Art%20Project%202.jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R255" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14359,7 +15635,7 @@
         </is>
       </c>
       <c r="V255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -14398,6 +15674,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/c4/Jean-fran%C3%A7ois_millet%2C_l%27angelus%2C_1857-59_%28parigi%2C_orsay%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R256" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14414,7 +15695,7 @@
         </is>
       </c>
       <c r="V256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -14451,6 +15732,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a1/Jean-Fran%C3%A7ois_Millet_%28II%29_007.jpg/1280px-Jean-Fran%C3%A7ois_Millet_%28II%29_007.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R257" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14506,6 +15792,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/5/52/Jean-Fran%C3%A7ois_Millet_%28II%29_-_Spring_-_WGA15693.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R258" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14559,6 +15850,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/9/9d/Jean-Fran%C3%A7ois_Millet_%28II%29_-_Un_vanneur.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R259" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14614,6 +15910,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Jean-Fran%C3%A7ois_Millet%2C_L%27Eglise_de_Gr%C3%A9ville.jpg/1280px-Jean-Fran%C3%A7ois_Millet%2C_L%27Eglise_de_Gr%C3%A9ville.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R260" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14667,6 +15968,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Jean-Fran%C3%A7ois_Millet%2C_Le_parc_%C3%A0_moutons%2C_clair_de_lune.jpg/1280px-Jean-Fran%C3%A7ois_Millet%2C_Le_parc_%C3%A0_moutons%2C_clair_de_lune.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R261" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14722,6 +16028,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/6/6a/Claude_Monet%2C_1867%2C_Regatta_at_Sainte-Adresse%2C_Metropolitan_Museum_of_Art.jpg</t>
         </is>
       </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R262" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14777,6 +16088,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/0/0e/Claude_Monet_022.jpg</t>
         </is>
       </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R263" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14832,6 +16148,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/6/61/Claude_Monet_-_Regattas_at_Argenteuil_-_Google_Art_Project.jpg</t>
         </is>
       </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R264" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14887,6 +16208,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Claude%20Monet%2C%20Impression%2C%20soleil%20levant.jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R265" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14942,6 +16268,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/89/Claude_Monet_-_Poppy_Field_-_Google_Art_Project.jpg</t>
         </is>
       </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R266" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -14997,6 +16328,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Claude_Monet_-_The_Rue_Montorgueil_in_Paris._Celebration_of_June_30%2C_1878_-_Google_Art_Project.jpg/1280px-Claude_Monet_-_The_Rue_Montorgueil_in_Paris._Celebration_of_June_30%2C_1878_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R267" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15052,6 +16388,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/bf/Femme_%C3%A0_l'ombrelle_tourn%C3%A9e_vers_la_droite_-_Claude_Monnet_-_Mus%C3%A9e_d'Orsay_RF_2620.jpg</t>
         </is>
       </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R268" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15107,6 +16448,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/5/5a/Monet%2C_Claude_-_Haystack_at_Giverny.jpg</t>
         </is>
       </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R269" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15162,6 +16508,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/30/Claude_Monet_-_Poplars_(Wind_effect).JPG</t>
         </is>
       </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R270" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15217,6 +16568,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/8c/Claude_Monet_-_Rouen_Cathedral_in_the_evening_(1894)_-_Pushkin_Museum_%D0%96-3312.jpg</t>
         </is>
       </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R271" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15272,6 +16628,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/a/ad/Claude_Monet_-_Water_Lilies_and_Japanese_Bridge.jpg</t>
         </is>
       </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R272" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15325,6 +16686,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/La_Pie_de_Monet.jpg/1280px-La_Pie_de_Monet.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R273" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15380,6 +16746,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/9/93/Gustave_Moreau_-_Orpheus_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R274" t="inlineStr">
         <is>
           <t>Huile sur bois</t>
@@ -15435,6 +16806,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/2/23/Gustave_Moreau_-_The_Apparition_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>Aquarelle</t>
+        </is>
+      </c>
       <c r="R275" t="inlineStr">
         <is>
           <t>Aquarelle</t>
@@ -15451,7 +16827,7 @@
         </is>
       </c>
       <c r="V275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276">
@@ -15488,6 +16864,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Oedipus_and_the_Sphinx_MET_DP-14201-023.jpg/500px-Oedipus_and_the_Sphinx_MET_DP-14201-023.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R276" t="inlineStr">
         <is>
           <t>Huile sur bois</t>
@@ -15504,7 +16885,7 @@
         </is>
       </c>
       <c r="V276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -15543,6 +16924,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Jupiter_and_Semele_by_Gustave_Moreau.jpg/960px-Jupiter_and_Semele_by_Gustave_Moreau.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R277" t="inlineStr">
         <is>
           <t>Huile sur bois</t>
@@ -15559,7 +16945,7 @@
         </is>
       </c>
       <c r="V277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278">
@@ -15598,6 +16984,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Berthe%20Morisot%20-%20The%20Cradle%20-%20Google%20Art%20Project.jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R278" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15653,6 +17044,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/1/16/Berthe_Morisot_Chasse_aux_papillons.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R279" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15708,6 +17104,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/cd/Berthe_Morisot_-_Eug%C3%A8ne_Manet_%C3%A0_l%27%C3%AEle_de_Wight.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R280" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15763,6 +17164,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9b/Berthe_Morisot_-_Woman_at_Her_Toilette_-_1924.127_-_Art_Institute_of_Chicago.jpg/1280px-Berthe_Morisot_-_Woman_at_Her_Toilette_-_1924.127_-_Art_Institute_of_Chicago.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R281" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15818,6 +17224,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Berthe_Morisot_-_Jour_d%27%C3%A9t%C3%A9%2C_1879.jpg/1280px-Berthe_Morisot_-_Jour_d%27%C3%A9t%C3%A9%2C_1879.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R282" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15871,6 +17282,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/23/Berthe_Morisot_-_Young_Girl_in_a_Ball_Gown_-_Google_Art_Project.jpg/960px-Berthe_Morisot_-_Young_Girl_in_a_Ball_Gown_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R283" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15919,6 +17335,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/63/Berthe_morisot_Apr%C3%A8s_le_d%C3%A9jeuner.jpg/1280px-Berthe_morisot_Apr%C3%A8s_le_d%C3%A9jeuner.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R284" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -15972,6 +17393,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Berthe_Morisot_-_Le_Cerisier_-_Mus%C3%A9e_Marmottan-Monet.jpg/960px-Berthe_Morisot_-_Le_Cerisier_-_Mus%C3%A9e_Marmottan-Monet.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R285" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16022,6 +17448,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2f/Alfons_Mucha_-_1894_-_Gismonda.jpg/1280px-Alfons_Mucha_-_1894_-_Gismonda.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q286" s="2" t="inlineStr">
+        <is>
+          <t>Aquarelle</t>
+        </is>
+      </c>
       <c r="R286" t="inlineStr">
         <is>
           <t xml:space="preserve">Aquarelle et gouache </t>
@@ -16075,6 +17506,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/AlfonsSelf.jpg/960px-AlfonsSelf.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R287" t="inlineStr">
         <is>
           <t>Huile sur panneau</t>
@@ -16128,6 +17564,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/87/Alfons_Mucha_-_1896_-_Summer.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R288" t="inlineStr">
         <is>
           <t>Huile sur panneau</t>
@@ -16176,6 +17617,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/Le_printemps%2C_Mucha.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R289" t="inlineStr">
         <is>
           <t>Huile sur panneau</t>
@@ -16231,6 +17677,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Edvard%20Munch%20-%20The%20Scream%20-%20Google%20Art%20Project.jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R290" t="inlineStr">
         <is>
           <t>Huile, tempera et pastel sur carton</t>
@@ -16286,6 +17737,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/5/5f/Edvard_Munch_-_Madonna_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R291" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16302,7 +17758,7 @@
         </is>
       </c>
       <c r="V291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292">
@@ -16339,6 +17795,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Puberty_%281894-95%29_by_Edvard_Munch.jpg/960px-Puberty_%281894-95%29_by_Edvard_Munch.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R292" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16355,7 +17816,7 @@
         </is>
       </c>
       <c r="V292" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
@@ -16394,6 +17855,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c2/Munch_Det_Syke_Barn_1885-86.jpg/1280px-Munch_Det_Syke_Barn_1885-86.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R293" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16410,7 +17876,7 @@
         </is>
       </c>
       <c r="V293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -16447,6 +17913,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Camille_Pissarro_-_La_C%C3%B4te_du_Jallais%2C_Pontoise_-_1867.jpg/1280px-Camille_Pissarro_-_La_C%C3%B4te_du_Jallais%2C_Pontoise_-_1867.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R294" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16502,6 +17973,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/85/Camille_Pissarro%2C_Gelee_blanche_%28Hoarfrost%29%2C_1873.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R295" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16557,6 +18033,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/d6/Camille_Pissarro_-_Red_roofs%2C_corner_of_a_village%2C_winter_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R296" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16612,6 +18093,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/7f/Pissarro%2C_Camille_-_La_Berg%C3%A8re.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R297" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16667,6 +18153,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/82/Camille_Pissarro%2C_The_Boulevard_Montmartre_at_Night%2C_1897.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R298" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16720,6 +18211,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/0/0c/Camille_Pissarro_-_Avenue_de_l%27Opera_-_Mus%C3%A9e_des_Beaux-Arts_Reims.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R299" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16773,6 +18269,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Pissarro_L%27Hermitage_%C3%A0_Pontoise%2C1867.jpg/1280px-Pissarro_L%27Hermitage_%C3%A0_Pontoise%2C1867.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R300" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16821,6 +18322,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/3b/Pissarro_-_Pont_Boieldieu_in_Rouen%2C_Rainy_Weather.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R301" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16876,6 +18382,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Le_Pauvre_Pecheur-Pierre_Puvis_de_Chavannes-IMG_8268.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R302" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16931,6 +18442,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Le_Reve-Puvis_de_Chavannes-Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R303" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -16984,6 +18500,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cc/Jeunes_filles_au_bord_de_la_mer-Puvis_de_Chavannes-Orsay-RF_2015.jpg/960px-Jeunes_filles_au_bord_de_la_mer-Puvis_de_Chavannes-Orsay-RF_2015.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R304" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17039,6 +18560,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/4/48/Arts_and_the_Muses_by_Pierre_Puvis_de_Chavannes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R305" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17094,6 +18620,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/cc/Odilon_Redon_-_Caliban_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R306" t="inlineStr">
         <is>
           <t>Huile sur carton</t>
@@ -17149,6 +18680,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/f/fb/Redon.yeux-clos.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R307" t="inlineStr">
         <is>
           <t>Huile sur carton</t>
@@ -17202,6 +18738,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Lille_PdBA_redon_regard.JPG/1280px-Lille_PdBA_redon_regard.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R308" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17255,6 +18796,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Breton_Village_A21237.jpg/1280px-Breton_Village_A21237.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R309" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17310,6 +18856,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/La_Loge_Pierre-Auguste_Renoir_1874.jpg/1280px-La_Loge_Pierre-Auguste_Renoir_1874.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R310" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17365,6 +18916,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Pierre-Auguste%20Renoir%2C%20Le%20Moulin%20de%20la%20Galette.jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R311" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17420,6 +18976,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/1/10/Pierre-Auguste_Renoir_006.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R312" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17475,6 +19036,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/a/a8/Torso_Effect_of_Sunlight_Renoir_1876.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R313" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17530,6 +19096,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d2/Renoir_-_Madame_Georges_Charpentier_et_ses_enfants.jpg/1280px-Renoir_-_Madame_Georges_Charpentier_et_ses_enfants.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R314" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17546,7 +19117,7 @@
         </is>
       </c>
       <c r="V314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
@@ -17585,6 +19156,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/8d/Pierre-Auguste_Renoir_-_Luncheon_of_the_Boating_Party_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R315" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17640,6 +19216,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/Renoir_-_The_Two_Sisters%2C_On_the_Terrace.jpg/1280px-Renoir_-_The_Two_Sisters%2C_On_the_Terrace.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R316" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17700,6 +19281,11 @@
           <t>Cycle des Danses (Pendant avec Danse à la campagne)</t>
         </is>
       </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R317" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17760,6 +19346,11 @@
           <t>Cycle des Danses (Pendant avec Danse à la ville)</t>
         </is>
       </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R318" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17815,6 +19406,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/d4/Pierre-Auguste_Renoir%2C_French_-_The_Large_Bathers_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R319" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17870,6 +19466,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/73/Auguste_Renoir_-_Young_Girls_at_the_Piano_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R320" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17923,6 +19524,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Eug%C3%A8ne_Murer_%28Hyacinthe-Eug%C3%A8ne_Meunier%2C_1841%E2%80%931906%29_MET_DT1882.jpg/960px-Eug%C3%A8ne_Murer_%28Hyacinthe-Eug%C3%A8ne_Meunier%2C_1841%E2%80%931906%29_MET_DT1882.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R321" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -17978,6 +19584,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/7a/Ilya_Repin_-_Barge_Haulers_on_the_Volga_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R322" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18033,6 +19644,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/73/Repin_Cossacks.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R323" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18088,6 +19704,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9f/1880-3_Repin_Religioese_Prozession_in_Kursk_anagoria.JPG/1280px-1880-3_Repin_Religioese_Prozession_in_Kursk_anagoria.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R324" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18143,6 +19764,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/Ilya_Repin_Unexpected_visitors.jpg/1280px-Ilya_Repin_Unexpected_visitors.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R325" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18198,6 +19824,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/ed/Dante_gabriel_rossetti%2C_l%27amata_%28la_sposa%29%2C_1865-66FXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R326" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18253,6 +19884,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/6/68/Dante_Gabriel_Rossetti_-_Proserpine.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R327" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18308,6 +19944,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Dante_Gabriel_Rossetti_-_Beata_Beatrix_-_Google_Art_Project.jpg/1920px-Dante_Gabriel_Rossetti_-_Beata_Beatrix_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R328" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18363,6 +20004,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/08/Dante_Gabriel_Rossetti_-_Ecce_Ancilla_Domini%21_-_Google_Art_Project.jpg/960px-Dante_Gabriel_Rossetti_-_Ecce_Ancilla_Domini%21_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R329" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18418,6 +20064,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/3f/Ch%C3%AAnes_Apremont_by_Rousseau_Louvre_RF1447_n1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R330" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18473,6 +20124,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/4/45/A_Mash_in_the_Landes%2C_1852%2C_Th%C3%A9odore_Rousseau.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R331" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18528,6 +20184,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/9/90/Th%C3%A9odore_Rousseau_-_Edge_of_the_Forest_at_Fontainebleau%2C_Setting_Sun_-_WGA20162.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R332" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18583,6 +20244,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Th%C3%A9odore_rousseau%2C_il_viale_dei_castagni_%28al_castello_di_souliers%2C_in_piccardia%29%2C_1837.jpg/1280px-Th%C3%A9odore_rousseau%2C_il_viale_dei_castagni_%28al_castello_di_souliers%2C_in_piccardia%29%2C_1837.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R333" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18638,6 +20304,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/77/Madame_X_%28Madame_Pierre_Gautreau%29%2C_John_Singer_Sargent%2C_1884_-_detail_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R334" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18693,6 +20364,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/ed/John_Singer_Sargent_-_Carnation%2C_Lily%2C_Lily%2C_Rose_-_Google_Art_Project.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R335" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18746,6 +20422,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/John_Singer_Sargent_001.jpg/1280px-John_Singer_Sargent_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R336" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18799,6 +20480,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/EL_JALEO-SINGER.jpg/1280px-EL_JALEO-SINGER.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R337" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18854,6 +20540,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/2/20/Serusier_-_the_talisman.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R338" t="inlineStr">
         <is>
           <t>Huile sur bois</t>
@@ -18909,6 +20600,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/a/a2/La_barri%C3%A8re_fleurie%2C_Le_Pouldu_1889_Paul_Serusier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R339" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -18964,6 +20660,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/L%27Incantation_ou_Le_Bois_sacr%C3%A9%2C_par_Paul_S%C3%A9rusier.jpg/960px-L%27Incantation_ou_Le_Bois_sacr%C3%A9%2C_par_Paul_S%C3%A9rusier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R340" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19017,6 +20718,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Paul_Serusier_-_Les_Laveuses_A_La_Laita.jpg/1280px-Paul_Serusier_-_Les_Laveuses_A_La_Laita.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R341" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19072,6 +20778,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/5/5d/Georges_seurat%2C_bagnanti_ad_asni%C3%A8res%2C_1884%2C_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R342" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19127,6 +20838,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/A%20Sunday%20on%20La%20Grande%20Jatte%2C%20Georges%20Seurat%2C%201884.jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R343" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19182,6 +20898,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/4/4f/Die_Frau_mit_der_Puderquaste_-_Georges_Seurat_%28Courtauld_Institute_of_Art%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R344" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19237,6 +20958,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/84/Georges_Seurat_-_Le_Chahut_-_Google_Art_Project.jpg/1280px-Georges_Seurat_-_Le_Chahut_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R345" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19292,6 +21018,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/ea/Georges_seurat%2C_circo%2C_1891%2C_06.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R346" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19347,6 +21078,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/39/Georges_Seurat_-_Models_%28Poseuses%29_-_BF811_-_Barnes_Foundation.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R347" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19402,6 +21138,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Georges_Seurat_066.jpg/1280px-Georges_Seurat_066.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R348" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19455,6 +21196,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/48/Georges-Pierre_Seurat_-_The_Channel_at_Gravelines%2C_Evening_-_Google_Art_Project.jpg/1280px-Georges-Pierre_Seurat_-_The_Channel_at_Gravelines%2C_Evening_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R349" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19510,6 +21256,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/3a/Signac_-_Portrait_de_F%C3%A9lix_F%C3%A9n%C3%A9on.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R350" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19565,6 +21316,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Paul_Signac_Port_de_Saint-Tropez.jpg/1280px-Paul_Signac_Port_de_Saint-Tropez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R351" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19618,6 +21374,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ec/Paul_Signac_Femmes_au_puits_1892.jpg/960px-Paul_Signac_Femmes_au_puits_1892.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R352" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19671,6 +21432,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Paul_Signac_La_bouee_rouge.jpg/960px-Paul_Signac_La_bouee_rouge.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R353" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19726,6 +21492,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/3b/Alfred_Sisley%2C_La_Neige_%C3%A0_Louveciennes_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R354" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19781,6 +21552,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/4/44/Alfred_Sisley_062.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R355" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19836,6 +21612,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/34/Alfred_Sisley_018.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R356" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19891,6 +21672,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/The_Flood_at_Port-Marly_-_1876_-_Alfred_Sisley.jpg/1280px-The_Flood_at_Port-Marly_-_1876_-_Alfred_Sisley.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R357" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19946,6 +21732,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/e2/All%C3%A9e_de_peupliers_aux_environs_de_Moret-sur-Loing.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R358" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -19999,6 +21790,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Sisley-Bridge_at_Villeneuve-la-Garenne.jpg/1280px-Sisley-Bridge_at_Villeneuve-la-Garenne.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R359" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20052,6 +21848,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/04/Alfred_Sisley_001.jpg/1280px-Alfred_Sisley_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R360" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20107,6 +21908,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/54/Alfred_Sisley_071.jpg/1280px-Alfred_Sisley_071.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R361" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20162,6 +21968,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0f/James_Tissot_%281836-1902%29_-_The_Ball_on_Shipboard_-_N04892_-_National_Gallery.jpg/1280px-James_Tissot_%281836-1902%29_-_The_Ball_on_Shipboard_-_N04892_-_National_Gallery.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R362" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20217,6 +22028,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/86/James_Tissot_-_October.jpg/1280px-James_Tissot_-_October.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R363" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20270,6 +22086,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/be/James_Tissot_-_Too_Early.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr</t>
         </is>
       </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R364" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20323,6 +22144,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/19/James_Tissot_-_The_Gallery_of_HMS_Calcutta_%28Portsmouth%29.jpg/1280px-James_Tissot_-_The_Gallery_of_HMS_Calcutta_%28Portsmouth%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R365" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20378,6 +22204,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/de/Turner_-_Ulysses_deriding_Polyphemus_1829.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R366" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20433,6 +22264,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/30/The_Fighting_Temeraire%2C_JMW_Turner%2C_National_Gallery.jpg/1280px-The_Fighting_Temeraire%2C_JMW_Turner%2C_National_Gallery.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R367" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20486,6 +22322,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Joseph_Mallord_William_Turner_-_Ancient_Rome%3B_Agrippina_Landing_with_the_Ashes_of_Germanicus_-_Google_Art_Project.jpg/1280px-Joseph_Mallord_William_Turner_-_Ancient_Rome%3B_Agrippina_Landing_with_the_Ashes_of_Germanicus_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R368" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20541,6 +22382,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/J.M.W._Turner_Slave_Ship_%28_Slavers_Throwing_Overboard_the_Dead_and_Dying%2C_Typhoon_Coming_On%29._1840.png/1280px-J.M.W._Turner_Slave_Ship_%28_Slavers_Throwing_Overboard_the_Dead_and_Dying%2C_Typhoon_Coming_On%29._1840.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R369" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20596,6 +22442,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/30/Joseph_Mallord_William_Turner_-_Snow_Storm_-_Steam-Boat_off_a_Harbour%27s_Mouth_-_WGA23178.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R370" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20651,6 +22502,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/9/96/Turner_-_Rain%2C_Steam_and_Speed_-_National_Gallery_file.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R371" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20704,6 +22560,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/f/f4/Turner_Dido_Building_Carthage.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R372" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20757,6 +22618,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/77/Joseph_Mallord_William_Turner_%281775-1851%29_-_The_Decline_of_the_Carthaginian_Empire_..._-_N00499_-_National_Gallery.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R373" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20812,6 +22678,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5a/Vallotton_Das_Bad_Sommerabend_1892.jpg/1280px-Vallotton_Das_Bad_Sommerabend_1892.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R374" t="inlineStr">
         <is>
           <t>Détrempe sur toile</t>
@@ -20867,6 +22738,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/be/Le_Ballon_Valloton_Orsay.jpg/1280px-Le_Ballon_Valloton_Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R375" t="inlineStr">
         <is>
           <t>Détrempe sur carton</t>
@@ -20920,6 +22796,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9e/F%C3%A9lix_Vallotton%2C_1893_-_La_Valse.jpg/960px-F%C3%A9lix_Vallotton%2C_1893_-_La_Valse.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R376" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -20973,6 +22854,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/F%C3%A9lix_Vallotton_-_The_Ball_-_Google_Art_Project.jpg/1280px-F%C3%A9lix_Vallotton_-_The_Ball_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R377" t="inlineStr">
         <is>
           <t>Huile sur carton marouflé sur bois</t>
@@ -21028,6 +22914,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/c6/De_aardappeleters_-_s0005V1962_-_Van_Gogh_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R378" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21083,6 +22974,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/3b/Vincent_Van_Gogh_0011.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R379" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21138,6 +23034,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/0/0c/Vincent_Van_Gogh_0010.jpg</t>
         </is>
       </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R380" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21193,6 +23094,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5e/Vincent_Willem_van_Gogh_076.jpg/1280px-Vincent_Willem_van_Gogh_076.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R381" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21248,6 +23154,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ea/Van_Gogh_-_Starry_Night_-_Google_Art_Project.jpg/1280px-Van_Gogh_-_Starry_Night_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R382" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21303,6 +23214,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/f/f0/VanGogh-self-portrait-with_bandaged_ear.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R383" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21358,6 +23274,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c8/Vincent_van_Gogh_-_Irises_%281889%29.jpg/1280px-Vincent_van_Gogh_-_Irises_%281889%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R384" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21413,6 +23334,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d3/Vincent_Van_Gogh_-_Wheatfield_with_Crows.jpg/1280px-Vincent_Van_Gogh_-_Wheatfield_with_Crows.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R385" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21468,6 +23394,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ad/Vincent_van_Gogh_-_The_Church_in_Auvers-sur-Oise%2C_View_from_the_Chevet_-_Google_Art_Project.jpg/1280px-Vincent_van_Gogh_-_The_Church_in_Auvers-sur-Oise%2C_View_from_the_Chevet_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R386" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21523,6 +23454,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/3c/Vincent_van_Gogh_-_Dr_Paul_Gachet_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R387" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21576,6 +23512,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/a/ab/Amandelbloesem.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R388" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21631,6 +23572,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/df/Vincent_van_Gogh_-_The_siesta_%28after_Millet%29_-_Google_Art_Project.jpg/1280px-Vincent_van_Gogh_-_The_siesta_%28after_Millet%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R389" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21686,6 +23632,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/f/f1/Th%C3%A9o_van_Rysselberghe_-_Portrait_d%27Irma_S%C3%A8the.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R390" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21741,6 +23692,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/e/e9/Van_Rysselberghe_femme_et_enfant.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R391" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21794,6 +23750,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Rysselberghe_anagoria.JPG/1280px-Rysselberghe_anagoria.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R392" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21847,6 +23808,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Th%C3%A9o_van_Rysselberghe_%281862-1926%29_-_Coastal_Scene_-_NG6582_-_National_Gallery.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R393" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21902,6 +23868,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/9/9f/Vrubel_Demon.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R394" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -21957,6 +23928,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/d4/Mikhail_Vrubel_-_%D0%9F%D1%80%D0%B8%D0%BD%D1%86%D0%B5%D1%81%D1%81%D0%B0_%D0%93%D1%80%D1%91%D0%B7%D0%B0_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R395" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -22010,6 +23986,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c8/Michail_Alexandrowitsch_Wrubel_001.jpg/960px-Michail_Alexandrowitsch_Wrubel_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R396" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -22063,6 +24044,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e3/Vrubel_pan.jpg/960px-Vrubel_pan.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R397" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -22118,6 +24104,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/d/d4/Vuillard-Deux_femmes_sous_la_lampe-Mus%C3%A9e_de_l'Annonciade.jpg</t>
         </is>
       </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R398" t="inlineStr">
         <is>
           <t>Huile sur carton</t>
@@ -22173,6 +24164,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/b1/Int%C3%A9rieur%2C_m%C3%A8re_et_s%C5%93ur_de_l'artiste%2C_par_%C3%89douard_Vuillard.jpg</t>
         </is>
       </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R399" t="inlineStr">
         <is>
           <t>Huile sur carton</t>
@@ -22228,6 +24224,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/5/58/%C3%89douard_vuillard%2C_giardini_pubblici%2C_ragazzine_che_giocano%2C_1894%2C_ripreso_nel_1936.JPG</t>
         </is>
       </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R400" t="inlineStr">
         <is>
           <t>Peinture à la colle sur toile</t>
@@ -22283,6 +24284,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/5/5b/Edouard_Vuillard_-_Public_Gardens_-_Google_Art_Project.jpg</t>
         </is>
       </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R401" t="inlineStr">
         <is>
           <t>Peinture à la colle sur toile</t>
@@ -22338,6 +24344,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/2/23/%C3%89douard_vuillard%2C_giardini_pubblici%2C_l'interrogatorio%2C_1894%2C_ripreso_nel_1936.JPG</t>
         </is>
       </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R402" t="inlineStr">
         <is>
           <t>Peinture à la colle sur toile</t>
@@ -22391,6 +24402,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Edouard_Vuillard_-_In_Bed_-_Google_Art_Project.jpg/1280px-Edouard_Vuillard_-_In_Bed_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R403" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -22444,6 +24460,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/b8/Vuillard_-_Salomon_and_Cogeval%2C_II-025.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R404" t="inlineStr">
         <is>
           <t>Huile sur carton</t>
@@ -22497,6 +24518,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/Misia_at_the_Piano_MET_DT3150.jpg/1280px-Misia_at_the_Piano_MET_DT3150.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R405" t="inlineStr">
         <is>
           <t>Peinture à la colle sur carton</t>
@@ -22552,6 +24578,11 @@
           <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/John%20William%20Waterhouse%20-%20The%20Lady%20of%20Shalott%20-%20Google%20Art%20Project.jpg?width=1200</t>
         </is>
       </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R406" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -22607,6 +24638,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/b/bd/Waterhouse_Hylas_and_the_Nymphs_Manchester_Art_Gallery_1896.15.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R407" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -22655,6 +24691,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/John_William_Waterhouse_-_Ophelia_%281894%29.jpg/960px-John_William_Waterhouse_-_Ophelia_%281894%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R408" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -22703,6 +24744,11 @@
           <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bd/Waterhouse%2C_John_William_-_Saint_Cecilia_-_1895.jpg/1280px-Waterhouse%2C_John_William_-_Saint_Cecilia_-_1895.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R409" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -22758,6 +24804,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/3/3f/Whistler_James_Symphony_in_White_no_1_%28The_White_Girl%29_1862.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R410" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -22813,6 +24864,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/1/1b/Whistlers_Mother_high_res.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R411" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -22866,6 +24922,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/1/1c/Whistler_James_Nocturne_in_Black_and_Gold_The_Falling_Rocket_1875.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R412" t="inlineStr">
         <is>
           <t>Huile sur panneau</t>
@@ -22921,6 +24982,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/c/cf/Whistler_James_Arrangement_in_Gray_and_Black_No2_1873.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
       <c r="R413" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
@@ -22942,13 +25008,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:V413">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="2">
       <formula>IFERROR(--$V2,0)=1</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>IFERROR(--$V2,0)=2</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="0">
       <formula>IFERROR(--$V2,0)=3</formula>
     </cfRule>
   </conditionalFormatting>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B28A6E-6B7E-4432-9987-00CA287C3FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CAAA75-66DD-45A6-8741-16098E957EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="345" windowWidth="16275" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4405" uniqueCount="1613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4405" uniqueCount="1612">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -3990,9 +3990,6 @@
   </si>
   <si>
     <t>176 cm</t>
-  </si>
-  <si>
-    <t>Art Institute of Chicago</t>
   </si>
   <si>
     <t>"Les Deux Sœurs"</t>
@@ -8673,10 +8670,10 @@
         <v>441</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="L90" s="4" t="s">
         <v>474</v>
@@ -17249,13 +17246,13 @@
         <v>101</v>
       </c>
       <c r="F316" t="s">
+        <v>712</v>
+      </c>
+      <c r="J316" t="s">
         <v>1319</v>
       </c>
-      <c r="J316" t="s">
+      <c r="L316" s="1" t="s">
         <v>1320</v>
-      </c>
-      <c r="L316" s="1" t="s">
-        <v>1321</v>
       </c>
       <c r="R316" t="s">
         <v>30</v>
@@ -17290,13 +17287,13 @@
         <v>82</v>
       </c>
       <c r="J317" t="s">
+        <v>1321</v>
+      </c>
+      <c r="L317" s="1" t="s">
         <v>1322</v>
       </c>
-      <c r="L317" s="1" t="s">
+      <c r="M317" t="s">
         <v>1323</v>
-      </c>
-      <c r="M317" t="s">
-        <v>1324</v>
       </c>
       <c r="R317" t="s">
         <v>30</v>
@@ -17331,13 +17328,13 @@
         <v>82</v>
       </c>
       <c r="J318" t="s">
+        <v>1324</v>
+      </c>
+      <c r="L318" s="1" t="s">
         <v>1325</v>
       </c>
-      <c r="L318" s="1" t="s">
+      <c r="M318" t="s">
         <v>1326</v>
-      </c>
-      <c r="M318" t="s">
-        <v>1327</v>
       </c>
       <c r="R318" t="s">
         <v>30</v>
@@ -17363,19 +17360,19 @@
         <v>1303</v>
       </c>
       <c r="D319" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="E319" t="s">
         <v>72</v>
       </c>
       <c r="F319" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="J319" t="s">
         <v>410</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="R319" t="s">
         <v>30</v>
@@ -17410,10 +17407,10 @@
         <v>82</v>
       </c>
       <c r="J320" t="s">
+        <v>1330</v>
+      </c>
+      <c r="L320" s="1" t="s">
         <v>1331</v>
-      </c>
-      <c r="L320" s="1" t="s">
-        <v>1332</v>
       </c>
       <c r="R320" t="s">
         <v>30</v>
@@ -17448,10 +17445,10 @@
         <v>146</v>
       </c>
       <c r="J321" t="s">
+        <v>1332</v>
+      </c>
+      <c r="L321" s="1" t="s">
         <v>1333</v>
-      </c>
-      <c r="L321" s="1" t="s">
-        <v>1334</v>
       </c>
       <c r="R321" t="s">
         <v>30</v>
@@ -17471,13 +17468,13 @@
     </row>
     <row r="322" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B322" t="s">
         <v>1335</v>
       </c>
-      <c r="B322" t="s">
+      <c r="D322" t="s">
         <v>1336</v>
-      </c>
-      <c r="D322" t="s">
-        <v>1337</v>
       </c>
       <c r="E322" t="s">
         <v>26</v>
@@ -17486,10 +17483,10 @@
         <v>41</v>
       </c>
       <c r="J322" t="s">
+        <v>1337</v>
+      </c>
+      <c r="L322" s="1" t="s">
         <v>1338</v>
-      </c>
-      <c r="L322" s="1" t="s">
-        <v>1339</v>
       </c>
       <c r="R322" t="s">
         <v>30</v>
@@ -17509,13 +17506,13 @@
     </row>
     <row r="323" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B323" t="s">
         <v>1335</v>
       </c>
-      <c r="B323" t="s">
-        <v>1336</v>
-      </c>
       <c r="D323" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="E323" t="s">
         <v>26</v>
@@ -17524,22 +17521,22 @@
         <v>41</v>
       </c>
       <c r="J323" t="s">
+        <v>1340</v>
+      </c>
+      <c r="L323" s="1" t="s">
         <v>1341</v>
       </c>
-      <c r="L323" s="1" t="s">
+      <c r="R323" t="s">
+        <v>30</v>
+      </c>
+      <c r="S323" t="s">
+        <v>31</v>
+      </c>
+      <c r="T323" t="s">
         <v>1342</v>
       </c>
-      <c r="R323" t="s">
-        <v>30</v>
-      </c>
-      <c r="S323" t="s">
-        <v>31</v>
-      </c>
-      <c r="T323" t="s">
+      <c r="U323" t="s">
         <v>1343</v>
-      </c>
-      <c r="U323" t="s">
-        <v>1344</v>
       </c>
       <c r="W323">
         <v>3</v>
@@ -17547,13 +17544,13 @@
     </row>
     <row r="324" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B324" t="s">
         <v>1335</v>
       </c>
-      <c r="B324" t="s">
-        <v>1336</v>
-      </c>
       <c r="D324" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="E324" t="s">
         <v>35</v>
@@ -17562,10 +17559,10 @@
         <v>36</v>
       </c>
       <c r="J324" t="s">
+        <v>1345</v>
+      </c>
+      <c r="L324" s="1" t="s">
         <v>1346</v>
-      </c>
-      <c r="L324" s="1" t="s">
-        <v>1347</v>
       </c>
       <c r="R324" t="s">
         <v>30</v>
@@ -17585,13 +17582,13 @@
     </row>
     <row r="325" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B325" t="s">
         <v>1335</v>
       </c>
-      <c r="B325" t="s">
-        <v>1336</v>
-      </c>
       <c r="D325" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="E325" t="s">
         <v>35</v>
@@ -17600,10 +17597,10 @@
         <v>36</v>
       </c>
       <c r="J325" t="s">
+        <v>1348</v>
+      </c>
+      <c r="L325" s="1" t="s">
         <v>1349</v>
-      </c>
-      <c r="L325" s="1" t="s">
-        <v>1350</v>
       </c>
       <c r="R325" t="s">
         <v>30</v>
@@ -17623,13 +17620,13 @@
     </row>
     <row r="326" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B326" t="s">
         <v>1351</v>
       </c>
-      <c r="B326" t="s">
+      <c r="D326" t="s">
         <v>1352</v>
-      </c>
-      <c r="D326" t="s">
-        <v>1353</v>
       </c>
       <c r="E326" t="s">
         <v>178</v>
@@ -17638,10 +17635,10 @@
         <v>179</v>
       </c>
       <c r="J326" t="s">
+        <v>1353</v>
+      </c>
+      <c r="L326" s="1" t="s">
         <v>1354</v>
-      </c>
-      <c r="L326" s="1" t="s">
-        <v>1355</v>
       </c>
       <c r="R326" t="s">
         <v>30</v>
@@ -17661,10 +17658,10 @@
     </row>
     <row r="327" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B327" t="s">
         <v>1351</v>
-      </c>
-      <c r="B327" t="s">
-        <v>1352</v>
       </c>
       <c r="D327" t="s">
         <v>695</v>
@@ -17676,10 +17673,10 @@
         <v>179</v>
       </c>
       <c r="J327" t="s">
+        <v>1355</v>
+      </c>
+      <c r="L327" s="1" t="s">
         <v>1356</v>
-      </c>
-      <c r="L327" s="1" t="s">
-        <v>1357</v>
       </c>
       <c r="R327" t="s">
         <v>30</v>
@@ -17699,13 +17696,13 @@
     </row>
     <row r="328" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B328" t="s">
         <v>1351</v>
       </c>
-      <c r="B328" t="s">
-        <v>1352</v>
-      </c>
       <c r="D328" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="E328" t="s">
         <v>178</v>
@@ -17714,10 +17711,10 @@
         <v>179</v>
       </c>
       <c r="J328" t="s">
+        <v>1358</v>
+      </c>
+      <c r="L328" s="1" t="s">
         <v>1359</v>
-      </c>
-      <c r="L328" s="1" t="s">
-        <v>1360</v>
       </c>
       <c r="R328" t="s">
         <v>30</v>
@@ -17737,10 +17734,10 @@
     </row>
     <row r="329" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B329" t="s">
         <v>1351</v>
-      </c>
-      <c r="B329" t="s">
-        <v>1352</v>
       </c>
       <c r="D329" t="s">
         <v>526</v>
@@ -17752,10 +17749,10 @@
         <v>179</v>
       </c>
       <c r="J329" t="s">
+        <v>1360</v>
+      </c>
+      <c r="L329" s="1" t="s">
         <v>1361</v>
-      </c>
-      <c r="L329" s="1" t="s">
-        <v>1362</v>
       </c>
       <c r="R329" t="s">
         <v>30</v>
@@ -17778,10 +17775,10 @@
         <v>414</v>
       </c>
       <c r="B330" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D330" t="s">
         <v>1363</v>
-      </c>
-      <c r="D330" t="s">
-        <v>1364</v>
       </c>
       <c r="E330" t="s">
         <v>81</v>
@@ -17790,10 +17787,10 @@
         <v>417</v>
       </c>
       <c r="J330" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L330" s="1" t="s">
         <v>1365</v>
-      </c>
-      <c r="L330" s="1" t="s">
-        <v>1366</v>
       </c>
       <c r="R330" t="s">
         <v>30</v>
@@ -17816,7 +17813,7 @@
         <v>414</v>
       </c>
       <c r="B331" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D331" t="s">
         <v>537</v>
@@ -17828,10 +17825,10 @@
         <v>417</v>
       </c>
       <c r="J331" t="s">
+        <v>1366</v>
+      </c>
+      <c r="L331" s="1" t="s">
         <v>1367</v>
-      </c>
-      <c r="L331" s="1" t="s">
-        <v>1368</v>
       </c>
       <c r="R331" t="s">
         <v>30</v>
@@ -17854,10 +17851,10 @@
         <v>414</v>
       </c>
       <c r="B332" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D332" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E332" t="s">
         <v>81</v>
@@ -17866,19 +17863,19 @@
         <v>417</v>
       </c>
       <c r="J332" t="s">
+        <v>1369</v>
+      </c>
+      <c r="L332" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="L332" s="1" t="s">
+      <c r="R332" t="s">
+        <v>30</v>
+      </c>
+      <c r="S332" t="s">
+        <v>31</v>
+      </c>
+      <c r="T332" t="s">
         <v>1371</v>
-      </c>
-      <c r="R332" t="s">
-        <v>30</v>
-      </c>
-      <c r="S332" t="s">
-        <v>31</v>
-      </c>
-      <c r="T332" t="s">
-        <v>1372</v>
       </c>
       <c r="U332" t="s">
         <v>805</v>
@@ -17892,10 +17889,10 @@
         <v>414</v>
       </c>
       <c r="B333" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D333" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="E333" t="s">
         <v>81</v>
@@ -17904,10 +17901,10 @@
         <v>417</v>
       </c>
       <c r="J333" t="s">
+        <v>1373</v>
+      </c>
+      <c r="L333" s="1" t="s">
         <v>1374</v>
-      </c>
-      <c r="L333" s="1" t="s">
-        <v>1375</v>
       </c>
       <c r="R333" t="s">
         <v>30</v>
@@ -17927,13 +17924,13 @@
     </row>
     <row r="334" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B334" t="s">
         <v>1376</v>
       </c>
-      <c r="B334" t="s">
+      <c r="D334" t="s">
         <v>1377</v>
-      </c>
-      <c r="D334" t="s">
-        <v>1378</v>
       </c>
       <c r="E334" t="s">
         <v>145</v>
@@ -17942,19 +17939,19 @@
         <v>146</v>
       </c>
       <c r="J334" t="s">
+        <v>1378</v>
+      </c>
+      <c r="L334" s="1" t="s">
         <v>1379</v>
       </c>
-      <c r="L334" s="1" t="s">
+      <c r="R334" t="s">
+        <v>30</v>
+      </c>
+      <c r="S334" t="s">
+        <v>31</v>
+      </c>
+      <c r="T334" t="s">
         <v>1380</v>
-      </c>
-      <c r="R334" t="s">
-        <v>30</v>
-      </c>
-      <c r="S334" t="s">
-        <v>31</v>
-      </c>
-      <c r="T334" t="s">
-        <v>1381</v>
       </c>
       <c r="U334" t="s">
         <v>100</v>
@@ -17965,10 +17962,10 @@
     </row>
     <row r="335" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B335" t="s">
         <v>1376</v>
-      </c>
-      <c r="B335" t="s">
-        <v>1377</v>
       </c>
       <c r="D335" t="s">
         <v>382</v>
@@ -17980,10 +17977,10 @@
         <v>179</v>
       </c>
       <c r="J335" t="s">
+        <v>1381</v>
+      </c>
+      <c r="L335" s="1" t="s">
         <v>1382</v>
-      </c>
-      <c r="L335" s="1" t="s">
-        <v>1383</v>
       </c>
       <c r="R335" t="s">
         <v>30</v>
@@ -18003,10 +18000,10 @@
     </row>
     <row r="336" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B336" t="s">
         <v>1376</v>
-      </c>
-      <c r="B336" t="s">
-        <v>1377</v>
       </c>
       <c r="D336">
         <v>1882</v>
@@ -18018,22 +18015,22 @@
         <v>882</v>
       </c>
       <c r="J336" t="s">
+        <v>1383</v>
+      </c>
+      <c r="L336" s="1" t="s">
         <v>1384</v>
       </c>
-      <c r="L336" s="1" t="s">
+      <c r="R336" t="s">
+        <v>30</v>
+      </c>
+      <c r="S336" t="s">
+        <v>31</v>
+      </c>
+      <c r="T336" t="s">
         <v>1385</v>
       </c>
-      <c r="R336" t="s">
-        <v>30</v>
-      </c>
-      <c r="S336" t="s">
-        <v>31</v>
-      </c>
-      <c r="T336" t="s">
+      <c r="U336" t="s">
         <v>1386</v>
-      </c>
-      <c r="U336" t="s">
-        <v>1387</v>
       </c>
       <c r="W336">
         <v>3</v>
@@ -18041,10 +18038,10 @@
     </row>
     <row r="337" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B337" t="s">
         <v>1376</v>
-      </c>
-      <c r="B337" t="s">
-        <v>1377</v>
       </c>
       <c r="D337">
         <v>1882</v>
@@ -18053,13 +18050,13 @@
         <v>881</v>
       </c>
       <c r="F337" t="s">
+        <v>1387</v>
+      </c>
+      <c r="J337" t="s">
         <v>1388</v>
       </c>
-      <c r="J337" t="s">
+      <c r="L337" s="1" t="s">
         <v>1389</v>
-      </c>
-      <c r="L337" s="1" t="s">
-        <v>1390</v>
       </c>
       <c r="R337" t="s">
         <v>30</v>
@@ -18082,7 +18079,7 @@
         <v>365</v>
       </c>
       <c r="B338" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D338" t="s">
         <v>55</v>
@@ -18094,10 +18091,10 @@
         <v>82</v>
       </c>
       <c r="J338" t="s">
+        <v>1391</v>
+      </c>
+      <c r="L338" s="1" t="s">
         <v>1392</v>
-      </c>
-      <c r="L338" s="1" t="s">
-        <v>1393</v>
       </c>
       <c r="R338" t="s">
         <v>30</v>
@@ -18120,7 +18117,7 @@
         <v>365</v>
       </c>
       <c r="B339" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D339" t="s">
         <v>225</v>
@@ -18132,10 +18129,10 @@
         <v>82</v>
       </c>
       <c r="J339" t="s">
+        <v>1393</v>
+      </c>
+      <c r="L339" s="1" t="s">
         <v>1394</v>
-      </c>
-      <c r="L339" s="1" t="s">
-        <v>1395</v>
       </c>
       <c r="R339" t="s">
         <v>30</v>
@@ -18158,22 +18155,22 @@
         <v>365</v>
       </c>
       <c r="B340" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D340" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E340" t="s">
         <v>1396</v>
-      </c>
-      <c r="E340" t="s">
-        <v>1397</v>
       </c>
       <c r="F340" t="s">
         <v>346</v>
       </c>
       <c r="J340" t="s">
+        <v>1397</v>
+      </c>
+      <c r="L340" s="1" t="s">
         <v>1398</v>
-      </c>
-      <c r="L340" s="1" t="s">
-        <v>1399</v>
       </c>
       <c r="R340" t="s">
         <v>30</v>
@@ -18196,7 +18193,7 @@
         <v>365</v>
       </c>
       <c r="B341" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D341">
         <v>1892</v>
@@ -18208,10 +18205,10 @@
         <v>82</v>
       </c>
       <c r="J341" t="s">
+        <v>1399</v>
+      </c>
+      <c r="L341" s="1" t="s">
         <v>1400</v>
-      </c>
-      <c r="L341" s="1" t="s">
-        <v>1401</v>
       </c>
       <c r="R341" t="s">
         <v>30</v>
@@ -18231,10 +18228,10 @@
     </row>
     <row r="342" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B342" t="s">
         <v>1402</v>
-      </c>
-      <c r="B342" t="s">
-        <v>1403</v>
       </c>
       <c r="D342" t="s">
         <v>296</v>
@@ -18246,19 +18243,19 @@
         <v>477</v>
       </c>
       <c r="J342" t="s">
+        <v>1403</v>
+      </c>
+      <c r="L342" s="1" t="s">
         <v>1404</v>
       </c>
-      <c r="L342" s="1" t="s">
+      <c r="R342" t="s">
+        <v>30</v>
+      </c>
+      <c r="S342" t="s">
+        <v>31</v>
+      </c>
+      <c r="T342" t="s">
         <v>1405</v>
-      </c>
-      <c r="R342" t="s">
-        <v>30</v>
-      </c>
-      <c r="S342" t="s">
-        <v>31</v>
-      </c>
-      <c r="T342" t="s">
-        <v>1406</v>
       </c>
       <c r="U342" t="s">
         <v>265</v>
@@ -18269,10 +18266,10 @@
     </row>
     <row r="343" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B343" t="s">
         <v>1402</v>
-      </c>
-      <c r="B343" t="s">
-        <v>1403</v>
       </c>
       <c r="D343" t="s">
         <v>725</v>
@@ -18284,10 +18281,10 @@
         <v>335</v>
       </c>
       <c r="J343" t="s">
+        <v>1406</v>
+      </c>
+      <c r="L343" s="1" t="s">
         <v>1407</v>
-      </c>
-      <c r="L343" s="1" t="s">
-        <v>1408</v>
       </c>
       <c r="R343" t="s">
         <v>30</v>
@@ -18307,10 +18304,10 @@
     </row>
     <row r="344" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B344" t="s">
         <v>1402</v>
-      </c>
-      <c r="B344" t="s">
-        <v>1403</v>
       </c>
       <c r="D344" t="s">
         <v>990</v>
@@ -18319,13 +18316,13 @@
         <v>178</v>
       </c>
       <c r="F344" t="s">
+        <v>1408</v>
+      </c>
+      <c r="J344" t="s">
         <v>1409</v>
       </c>
-      <c r="J344" t="s">
+      <c r="L344" s="1" t="s">
         <v>1410</v>
-      </c>
-      <c r="L344" s="1" t="s">
-        <v>1411</v>
       </c>
       <c r="R344" t="s">
         <v>30</v>
@@ -18345,25 +18342,25 @@
     </row>
     <row r="345" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B345" t="s">
         <v>1402</v>
-      </c>
-      <c r="B345" t="s">
-        <v>1403</v>
       </c>
       <c r="D345" t="s">
         <v>990</v>
       </c>
       <c r="E345" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F345" t="s">
         <v>1412</v>
       </c>
-      <c r="F345" t="s">
+      <c r="J345" t="s">
         <v>1413</v>
       </c>
-      <c r="J345" t="s">
+      <c r="L345" s="1" t="s">
         <v>1414</v>
-      </c>
-      <c r="L345" s="1" t="s">
-        <v>1415</v>
       </c>
       <c r="R345" t="s">
         <v>30</v>
@@ -18383,10 +18380,10 @@
     </row>
     <row r="346" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B346" t="s">
         <v>1402</v>
-      </c>
-      <c r="B346" t="s">
-        <v>1403</v>
       </c>
       <c r="D346" t="s">
         <v>240</v>
@@ -18398,10 +18395,10 @@
         <v>82</v>
       </c>
       <c r="J346" t="s">
+        <v>1415</v>
+      </c>
+      <c r="L346" s="1" t="s">
         <v>1416</v>
-      </c>
-      <c r="L346" s="1" t="s">
-        <v>1417</v>
       </c>
       <c r="R346" t="s">
         <v>30</v>
@@ -18421,25 +18418,25 @@
     </row>
     <row r="347" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B347" t="s">
         <v>1402</v>
       </c>
-      <c r="B347" t="s">
-        <v>1403</v>
-      </c>
       <c r="D347" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="E347" t="s">
         <v>72</v>
       </c>
       <c r="F347" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J347" t="s">
         <v>1419</v>
       </c>
-      <c r="J347" t="s">
+      <c r="L347" s="1" t="s">
         <v>1420</v>
-      </c>
-      <c r="L347" s="1" t="s">
-        <v>1421</v>
       </c>
       <c r="R347" t="s">
         <v>30</v>
@@ -18459,13 +18456,13 @@
     </row>
     <row r="348" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B348" t="s">
         <v>1402</v>
       </c>
-      <c r="B348" t="s">
-        <v>1403</v>
-      </c>
       <c r="D348" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="E348" t="s">
         <v>145</v>
@@ -18474,10 +18471,10 @@
         <v>146</v>
       </c>
       <c r="J348" t="s">
+        <v>1422</v>
+      </c>
+      <c r="L348" s="1" t="s">
         <v>1423</v>
-      </c>
-      <c r="L348" s="1" t="s">
-        <v>1424</v>
       </c>
       <c r="R348" t="s">
         <v>30</v>
@@ -18497,10 +18494,10 @@
     </row>
     <row r="349" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B349" t="s">
         <v>1402</v>
-      </c>
-      <c r="B349" t="s">
-        <v>1403</v>
       </c>
       <c r="D349">
         <v>1890</v>
@@ -18509,13 +18506,13 @@
         <v>145</v>
       </c>
       <c r="F349" t="s">
+        <v>1424</v>
+      </c>
+      <c r="J349" t="s">
         <v>1425</v>
       </c>
-      <c r="J349" t="s">
+      <c r="L349" s="1" t="s">
         <v>1426</v>
-      </c>
-      <c r="L349" s="1" t="s">
-        <v>1427</v>
       </c>
       <c r="R349" t="s">
         <v>30</v>
@@ -18538,7 +18535,7 @@
         <v>365</v>
       </c>
       <c r="B350" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D350" t="s">
         <v>786</v>
@@ -18547,13 +18544,13 @@
         <v>145</v>
       </c>
       <c r="F350" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="J350" t="s">
+        <v>1428</v>
+      </c>
+      <c r="L350" s="1" t="s">
         <v>1429</v>
-      </c>
-      <c r="L350" s="1" t="s">
-        <v>1430</v>
       </c>
       <c r="R350" t="s">
         <v>30</v>
@@ -18576,22 +18573,22 @@
         <v>365</v>
       </c>
       <c r="B351" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D351" t="s">
         <v>1012</v>
       </c>
       <c r="E351" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F351" t="s">
         <v>1431</v>
       </c>
-      <c r="F351" t="s">
+      <c r="J351" t="s">
         <v>1432</v>
       </c>
-      <c r="J351" t="s">
+      <c r="L351" s="1" t="s">
         <v>1433</v>
-      </c>
-      <c r="L351" s="1" t="s">
-        <v>1434</v>
       </c>
       <c r="R351" t="s">
         <v>30</v>
@@ -18614,7 +18611,7 @@
         <v>365</v>
       </c>
       <c r="B352" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D352">
         <v>1892</v>
@@ -18626,10 +18623,10 @@
         <v>82</v>
       </c>
       <c r="J352" t="s">
+        <v>1434</v>
+      </c>
+      <c r="L352" s="1" t="s">
         <v>1435</v>
-      </c>
-      <c r="L352" s="1" t="s">
-        <v>1436</v>
       </c>
       <c r="R352" t="s">
         <v>30</v>
@@ -18652,7 +18649,7 @@
         <v>365</v>
       </c>
       <c r="B353" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D353">
         <v>1895</v>
@@ -18664,10 +18661,10 @@
         <v>82</v>
       </c>
       <c r="J353" t="s">
+        <v>1436</v>
+      </c>
+      <c r="L353" s="1" t="s">
         <v>1437</v>
-      </c>
-      <c r="L353" s="1" t="s">
-        <v>1438</v>
       </c>
       <c r="R353" t="s">
         <v>30</v>
@@ -18687,10 +18684,10 @@
     </row>
     <row r="354" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B354" t="s">
         <v>1439</v>
-      </c>
-      <c r="B354" t="s">
-        <v>1440</v>
       </c>
       <c r="D354" t="s">
         <v>321</v>
@@ -18702,10 +18699,10 @@
         <v>82</v>
       </c>
       <c r="J354" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L354" s="1" t="s">
         <v>1441</v>
-      </c>
-      <c r="L354" s="1" t="s">
-        <v>1442</v>
       </c>
       <c r="R354" t="s">
         <v>30</v>
@@ -18725,25 +18722,25 @@
     </row>
     <row r="355" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B355" t="s">
         <v>1439</v>
-      </c>
-      <c r="B355" t="s">
-        <v>1440</v>
       </c>
       <c r="D355" t="s">
         <v>325</v>
       </c>
       <c r="E355" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="F355" t="s">
         <v>346</v>
       </c>
       <c r="J355" t="s">
+        <v>1443</v>
+      </c>
+      <c r="L355" s="1" t="s">
         <v>1444</v>
-      </c>
-      <c r="L355" s="1" t="s">
-        <v>1445</v>
       </c>
       <c r="R355" t="s">
         <v>30</v>
@@ -18763,10 +18760,10 @@
     </row>
     <row r="356" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B356" t="s">
         <v>1439</v>
-      </c>
-      <c r="B356" t="s">
-        <v>1440</v>
       </c>
       <c r="D356" t="s">
         <v>325</v>
@@ -18778,10 +18775,10 @@
         <v>146</v>
       </c>
       <c r="J356" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L356" s="1" t="s">
         <v>1446</v>
-      </c>
-      <c r="L356" s="1" t="s">
-        <v>1447</v>
       </c>
       <c r="R356" t="s">
         <v>30</v>
@@ -18801,10 +18798,10 @@
     </row>
     <row r="357" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B357" t="s">
         <v>1439</v>
-      </c>
-      <c r="B357" t="s">
-        <v>1440</v>
       </c>
       <c r="D357" t="s">
         <v>325</v>
@@ -18816,10 +18813,10 @@
         <v>82</v>
       </c>
       <c r="J357" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="L357" s="1" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="R357" t="s">
         <v>30</v>
@@ -18839,10 +18836,10 @@
     </row>
     <row r="358" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B358" t="s">
         <v>1439</v>
-      </c>
-      <c r="B358" t="s">
-        <v>1440</v>
       </c>
       <c r="D358" t="s">
         <v>786</v>
@@ -18854,10 +18851,10 @@
         <v>82</v>
       </c>
       <c r="J358" t="s">
+        <v>1448</v>
+      </c>
+      <c r="L358" s="1" t="s">
         <v>1449</v>
-      </c>
-      <c r="L358" s="1" t="s">
-        <v>1450</v>
       </c>
       <c r="R358" t="s">
         <v>30</v>
@@ -18877,10 +18874,10 @@
     </row>
     <row r="359" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B359" t="s">
         <v>1439</v>
-      </c>
-      <c r="B359" t="s">
-        <v>1440</v>
       </c>
       <c r="D359">
         <v>1872</v>
@@ -18892,10 +18889,10 @@
         <v>146</v>
       </c>
       <c r="J359" t="s">
+        <v>1450</v>
+      </c>
+      <c r="L359" s="1" t="s">
         <v>1451</v>
-      </c>
-      <c r="L359" s="1" t="s">
-        <v>1452</v>
       </c>
       <c r="R359" t="s">
         <v>30</v>
@@ -18915,10 +18912,10 @@
     </row>
     <row r="360" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B360" t="s">
         <v>1439</v>
-      </c>
-      <c r="B360" t="s">
-        <v>1440</v>
       </c>
       <c r="D360">
         <v>1870</v>
@@ -18930,10 +18927,10 @@
         <v>82</v>
       </c>
       <c r="J360" t="s">
+        <v>1452</v>
+      </c>
+      <c r="L360" s="1" t="s">
         <v>1453</v>
-      </c>
-      <c r="L360" s="1" t="s">
-        <v>1454</v>
       </c>
       <c r="R360" t="s">
         <v>30</v>
@@ -18953,10 +18950,10 @@
     </row>
     <row r="361" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B361" t="s">
         <v>1439</v>
-      </c>
-      <c r="B361" t="s">
-        <v>1440</v>
       </c>
       <c r="D361">
         <v>1873</v>
@@ -18968,10 +18965,10 @@
         <v>82</v>
       </c>
       <c r="J361" t="s">
+        <v>1454</v>
+      </c>
+      <c r="L361" s="1" t="s">
         <v>1455</v>
-      </c>
-      <c r="L361" s="1" t="s">
-        <v>1456</v>
       </c>
       <c r="R361" t="s">
         <v>30</v>
@@ -18994,7 +18991,7 @@
         <v>814</v>
       </c>
       <c r="B362" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D362" t="s">
         <v>695</v>
@@ -19006,10 +19003,10 @@
         <v>179</v>
       </c>
       <c r="J362" t="s">
+        <v>1457</v>
+      </c>
+      <c r="L362" s="1" t="s">
         <v>1458</v>
-      </c>
-      <c r="L362" s="1" t="s">
-        <v>1459</v>
       </c>
       <c r="R362" t="s">
         <v>30</v>
@@ -19032,22 +19029,22 @@
         <v>814</v>
       </c>
       <c r="B363" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D363" t="s">
         <v>334</v>
       </c>
       <c r="E363" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F363" t="s">
         <v>1460</v>
       </c>
-      <c r="F363" t="s">
+      <c r="J363" t="s">
         <v>1461</v>
       </c>
-      <c r="J363" t="s">
+      <c r="L363" s="1" t="s">
         <v>1462</v>
-      </c>
-      <c r="L363" s="1" t="s">
-        <v>1463</v>
       </c>
       <c r="R363" t="s">
         <v>30</v>
@@ -19070,7 +19067,7 @@
         <v>814</v>
       </c>
       <c r="B364" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D364">
         <v>1873</v>
@@ -19079,13 +19076,13 @@
         <v>178</v>
       </c>
       <c r="F364" t="s">
+        <v>1463</v>
+      </c>
+      <c r="J364" t="s">
         <v>1464</v>
       </c>
-      <c r="J364" t="s">
+      <c r="L364" s="1" t="s">
         <v>1465</v>
-      </c>
-      <c r="L364" s="1" t="s">
-        <v>1466</v>
       </c>
       <c r="R364" t="s">
         <v>30</v>
@@ -19097,7 +19094,7 @@
         <v>106</v>
       </c>
       <c r="U364" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="W364">
         <v>2</v>
@@ -19108,7 +19105,7 @@
         <v>814</v>
       </c>
       <c r="B365" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D365">
         <v>1876</v>
@@ -19120,10 +19117,10 @@
         <v>179</v>
       </c>
       <c r="J365" t="s">
+        <v>1467</v>
+      </c>
+      <c r="L365" s="1" t="s">
         <v>1468</v>
-      </c>
-      <c r="L365" s="1" t="s">
-        <v>1469</v>
       </c>
       <c r="R365" t="s">
         <v>30</v>
@@ -19143,10 +19140,10 @@
     </row>
     <row r="366" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B366" t="s">
         <v>1470</v>
-      </c>
-      <c r="B366" t="s">
-        <v>1471</v>
       </c>
       <c r="D366" t="s">
         <v>743</v>
@@ -19158,10 +19155,10 @@
         <v>477</v>
       </c>
       <c r="J366" t="s">
+        <v>1471</v>
+      </c>
+      <c r="L366" s="1" t="s">
         <v>1472</v>
-      </c>
-      <c r="L366" s="1" t="s">
-        <v>1473</v>
       </c>
       <c r="R366" t="s">
         <v>30</v>
@@ -19173,7 +19170,7 @@
         <v>59</v>
       </c>
       <c r="U366" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="W366">
         <v>2</v>
@@ -19181,13 +19178,13 @@
     </row>
     <row r="367" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B367" t="s">
         <v>1470</v>
       </c>
-      <c r="B367" t="s">
-        <v>1471</v>
-      </c>
       <c r="D367" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="E367" t="s">
         <v>178</v>
@@ -19196,10 +19193,10 @@
         <v>477</v>
       </c>
       <c r="J367" t="s">
+        <v>1474</v>
+      </c>
+      <c r="L367" s="1" t="s">
         <v>1475</v>
-      </c>
-      <c r="L367" s="1" t="s">
-        <v>1476</v>
       </c>
       <c r="R367" t="s">
         <v>30</v>
@@ -19219,10 +19216,10 @@
     </row>
     <row r="368" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B368" t="s">
         <v>1470</v>
-      </c>
-      <c r="B368" t="s">
-        <v>1471</v>
       </c>
       <c r="D368">
         <v>1837</v>
@@ -19234,10 +19231,10 @@
         <v>179</v>
       </c>
       <c r="J368" t="s">
+        <v>1476</v>
+      </c>
+      <c r="L368" s="1" t="s">
         <v>1477</v>
-      </c>
-      <c r="L368" s="1" t="s">
-        <v>1478</v>
       </c>
       <c r="R368" t="s">
         <v>30</v>
@@ -19257,10 +19254,10 @@
     </row>
     <row r="369" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B369" t="s">
         <v>1470</v>
-      </c>
-      <c r="B369" t="s">
-        <v>1471</v>
       </c>
       <c r="D369" t="s">
         <v>769</v>
@@ -19272,10 +19269,10 @@
         <v>882</v>
       </c>
       <c r="J369" t="s">
+        <v>1478</v>
+      </c>
+      <c r="L369" s="1" t="s">
         <v>1479</v>
-      </c>
-      <c r="L369" s="1" t="s">
-        <v>1480</v>
       </c>
       <c r="R369" t="s">
         <v>30</v>
@@ -19295,10 +19292,10 @@
     </row>
     <row r="370" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B370" t="s">
         <v>1470</v>
-      </c>
-      <c r="B370" t="s">
-        <v>1471</v>
       </c>
       <c r="D370" t="s">
         <v>459</v>
@@ -19310,10 +19307,10 @@
         <v>179</v>
       </c>
       <c r="J370" t="s">
+        <v>1480</v>
+      </c>
+      <c r="L370" s="1" t="s">
         <v>1481</v>
-      </c>
-      <c r="L370" s="1" t="s">
-        <v>1482</v>
       </c>
       <c r="R370" t="s">
         <v>30</v>
@@ -19333,10 +19330,10 @@
     </row>
     <row r="371" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B371" t="s">
         <v>1470</v>
-      </c>
-      <c r="B371" t="s">
-        <v>1471</v>
       </c>
       <c r="D371" t="s">
         <v>416</v>
@@ -19348,10 +19345,10 @@
         <v>477</v>
       </c>
       <c r="J371" t="s">
+        <v>1482</v>
+      </c>
+      <c r="L371" s="1" t="s">
         <v>1483</v>
-      </c>
-      <c r="L371" s="1" t="s">
-        <v>1484</v>
       </c>
       <c r="R371" t="s">
         <v>30</v>
@@ -19371,10 +19368,10 @@
     </row>
     <row r="372" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B372" t="s">
         <v>1470</v>
-      </c>
-      <c r="B372" t="s">
-        <v>1471</v>
       </c>
       <c r="D372">
         <v>1815</v>
@@ -19386,10 +19383,10 @@
         <v>477</v>
       </c>
       <c r="J372" t="s">
+        <v>1484</v>
+      </c>
+      <c r="L372" s="1" t="s">
         <v>1485</v>
-      </c>
-      <c r="L372" s="1" t="s">
-        <v>1486</v>
       </c>
       <c r="R372" t="s">
         <v>30</v>
@@ -19409,10 +19406,10 @@
     </row>
     <row r="373" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B373" t="s">
         <v>1470</v>
-      </c>
-      <c r="B373" t="s">
-        <v>1471</v>
       </c>
       <c r="D373">
         <v>1817</v>
@@ -19424,10 +19421,10 @@
         <v>477</v>
       </c>
       <c r="J373" t="s">
+        <v>1486</v>
+      </c>
+      <c r="L373" s="1" t="s">
         <v>1487</v>
-      </c>
-      <c r="L373" s="1" t="s">
-        <v>1488</v>
       </c>
       <c r="R373" t="s">
         <v>30</v>
@@ -19447,31 +19444,31 @@
     </row>
     <row r="374" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B374" t="s">
         <v>1489</v>
-      </c>
-      <c r="B374" t="s">
-        <v>1490</v>
       </c>
       <c r="D374" t="s">
         <v>655</v>
       </c>
       <c r="E374" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F374" t="s">
         <v>1491</v>
       </c>
-      <c r="F374" t="s">
+      <c r="J374" t="s">
         <v>1492</v>
       </c>
-      <c r="J374" t="s">
+      <c r="L374" s="1" t="s">
         <v>1493</v>
       </c>
-      <c r="L374" s="1" t="s">
+      <c r="R374" t="s">
+        <v>30</v>
+      </c>
+      <c r="S374" t="s">
         <v>1494</v>
-      </c>
-      <c r="R374" t="s">
-        <v>30</v>
-      </c>
-      <c r="S374" t="s">
-        <v>1495</v>
       </c>
       <c r="T374" t="s">
         <v>110</v>
@@ -19485,10 +19482,10 @@
     </row>
     <row r="375" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B375" t="s">
         <v>1489</v>
-      </c>
-      <c r="B375" t="s">
-        <v>1490</v>
       </c>
       <c r="D375" t="s">
         <v>1012</v>
@@ -19500,16 +19497,16 @@
         <v>82</v>
       </c>
       <c r="J375" t="s">
+        <v>1495</v>
+      </c>
+      <c r="L375" s="1" t="s">
         <v>1496</v>
       </c>
-      <c r="L375" s="1" t="s">
+      <c r="R375" t="s">
+        <v>30</v>
+      </c>
+      <c r="S375" t="s">
         <v>1497</v>
-      </c>
-      <c r="R375" t="s">
-        <v>30</v>
-      </c>
-      <c r="S375" t="s">
-        <v>1498</v>
       </c>
       <c r="T375" t="s">
         <v>398</v>
@@ -19523,25 +19520,25 @@
     </row>
     <row r="376" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B376" t="s">
         <v>1489</v>
-      </c>
-      <c r="B376" t="s">
-        <v>1490</v>
       </c>
       <c r="D376">
         <v>1893</v>
       </c>
       <c r="E376" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F376" t="s">
         <v>1499</v>
       </c>
-      <c r="F376" t="s">
+      <c r="J376" t="s">
         <v>1500</v>
       </c>
-      <c r="J376" t="s">
+      <c r="L376" s="1" t="s">
         <v>1501</v>
-      </c>
-      <c r="L376" s="1" t="s">
-        <v>1502</v>
       </c>
       <c r="R376" t="s">
         <v>30</v>
@@ -19561,10 +19558,10 @@
     </row>
     <row r="377" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B377" t="s">
         <v>1503</v>
-      </c>
-      <c r="B377" t="s">
-        <v>1504</v>
       </c>
       <c r="D377" t="s">
         <v>382</v>
@@ -19573,13 +19570,13 @@
         <v>131</v>
       </c>
       <c r="F377" t="s">
+        <v>1504</v>
+      </c>
+      <c r="J377" t="s">
         <v>1505</v>
       </c>
-      <c r="J377" t="s">
+      <c r="L377" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="L377" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="R377" t="s">
         <v>30</v>
@@ -19599,10 +19596,10 @@
     </row>
     <row r="378" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B378" t="s">
         <v>1503</v>
-      </c>
-      <c r="B378" t="s">
-        <v>1504</v>
       </c>
       <c r="D378" t="s">
         <v>55</v>
@@ -19611,13 +19608,13 @@
         <v>131</v>
       </c>
       <c r="F378" t="s">
+        <v>1507</v>
+      </c>
+      <c r="J378" t="s">
         <v>1508</v>
       </c>
-      <c r="J378" t="s">
+      <c r="L378" s="1" t="s">
         <v>1509</v>
-      </c>
-      <c r="L378" s="1" t="s">
-        <v>1510</v>
       </c>
       <c r="R378" t="s">
         <v>30</v>
@@ -19637,10 +19634,10 @@
     </row>
     <row r="379" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B379" t="s">
         <v>1503</v>
-      </c>
-      <c r="B379" t="s">
-        <v>1504</v>
       </c>
       <c r="D379" t="s">
         <v>55</v>
@@ -19652,10 +19649,10 @@
         <v>477</v>
       </c>
       <c r="J379" t="s">
+        <v>1510</v>
+      </c>
+      <c r="L379" s="1" t="s">
         <v>1511</v>
-      </c>
-      <c r="L379" s="1" t="s">
-        <v>1512</v>
       </c>
       <c r="R379" t="s">
         <v>30</v>
@@ -19675,25 +19672,25 @@
     </row>
     <row r="380" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B380" t="s">
         <v>1503</v>
-      </c>
-      <c r="B380" t="s">
-        <v>1504</v>
       </c>
       <c r="D380" t="s">
         <v>55</v>
       </c>
       <c r="E380" t="s">
+        <v>1512</v>
+      </c>
+      <c r="F380" t="s">
         <v>1513</v>
       </c>
-      <c r="F380" t="s">
+      <c r="J380" t="s">
         <v>1514</v>
       </c>
-      <c r="J380" t="s">
+      <c r="L380" s="1" t="s">
         <v>1515</v>
-      </c>
-      <c r="L380" s="1" t="s">
-        <v>1516</v>
       </c>
       <c r="R380" t="s">
         <v>30</v>
@@ -19713,10 +19710,10 @@
     </row>
     <row r="381" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B381" t="s">
         <v>1503</v>
-      </c>
-      <c r="B381" t="s">
-        <v>1504</v>
       </c>
       <c r="D381" t="s">
         <v>225</v>
@@ -19725,13 +19722,13 @@
         <v>145</v>
       </c>
       <c r="F381" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="J381" t="s">
+        <v>1516</v>
+      </c>
+      <c r="L381" s="1" t="s">
         <v>1517</v>
-      </c>
-      <c r="L381" s="1" t="s">
-        <v>1518</v>
       </c>
       <c r="R381" t="s">
         <v>30</v>
@@ -19751,10 +19748,10 @@
     </row>
     <row r="382" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B382" t="s">
         <v>1503</v>
-      </c>
-      <c r="B382" t="s">
-        <v>1504</v>
       </c>
       <c r="D382" t="s">
         <v>225</v>
@@ -19766,10 +19763,10 @@
         <v>386</v>
       </c>
       <c r="J382" t="s">
+        <v>1518</v>
+      </c>
+      <c r="L382" s="1" t="s">
         <v>1519</v>
-      </c>
-      <c r="L382" s="1" t="s">
-        <v>1520</v>
       </c>
       <c r="R382" t="s">
         <v>30</v>
@@ -19789,10 +19786,10 @@
     </row>
     <row r="383" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B383" t="s">
         <v>1503</v>
-      </c>
-      <c r="B383" t="s">
-        <v>1504</v>
       </c>
       <c r="D383" t="s">
         <v>225</v>
@@ -19804,10 +19801,10 @@
         <v>63</v>
       </c>
       <c r="J383" t="s">
+        <v>1520</v>
+      </c>
+      <c r="L383" s="1" t="s">
         <v>1521</v>
-      </c>
-      <c r="L383" s="1" t="s">
-        <v>1522</v>
       </c>
       <c r="R383" t="s">
         <v>30</v>
@@ -19827,10 +19824,10 @@
     </row>
     <row r="384" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B384" t="s">
         <v>1503</v>
-      </c>
-      <c r="B384" t="s">
-        <v>1504</v>
       </c>
       <c r="D384" t="s">
         <v>786</v>
@@ -19839,13 +19836,13 @@
         <v>131</v>
       </c>
       <c r="F384" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="J384" t="s">
+        <v>1522</v>
+      </c>
+      <c r="L384" s="1" t="s">
         <v>1523</v>
-      </c>
-      <c r="L384" s="1" t="s">
-        <v>1524</v>
       </c>
       <c r="R384" t="s">
         <v>30</v>
@@ -19865,10 +19862,10 @@
     </row>
     <row r="385" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B385" t="s">
         <v>1503</v>
-      </c>
-      <c r="B385" t="s">
-        <v>1504</v>
       </c>
       <c r="D385" t="s">
         <v>786</v>
@@ -19880,10 +19877,10 @@
         <v>82</v>
       </c>
       <c r="J385" t="s">
+        <v>1524</v>
+      </c>
+      <c r="L385" s="1" t="s">
         <v>1525</v>
-      </c>
-      <c r="L385" s="1" t="s">
-        <v>1526</v>
       </c>
       <c r="R385" t="s">
         <v>30</v>
@@ -19903,10 +19900,10 @@
     </row>
     <row r="386" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B386" t="s">
         <v>1503</v>
-      </c>
-      <c r="B386" t="s">
-        <v>1504</v>
       </c>
       <c r="D386" t="s">
         <v>240</v>
@@ -19918,10 +19915,10 @@
         <v>82</v>
       </c>
       <c r="J386" t="s">
+        <v>1526</v>
+      </c>
+      <c r="L386" s="1" t="s">
         <v>1527</v>
-      </c>
-      <c r="L386" s="1" t="s">
-        <v>1528</v>
       </c>
       <c r="R386" t="s">
         <v>30</v>
@@ -19941,10 +19938,10 @@
     </row>
     <row r="387" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B387" t="s">
         <v>1503</v>
-      </c>
-      <c r="B387" t="s">
-        <v>1504</v>
       </c>
       <c r="D387">
         <v>1890</v>
@@ -19953,13 +19950,13 @@
         <v>131</v>
       </c>
       <c r="F387" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="J387" t="s">
+        <v>1528</v>
+      </c>
+      <c r="L387" s="1" t="s">
         <v>1529</v>
-      </c>
-      <c r="L387" s="1" t="s">
-        <v>1530</v>
       </c>
       <c r="R387" t="s">
         <v>30</v>
@@ -19979,10 +19976,10 @@
     </row>
     <row r="388" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B388" t="s">
         <v>1503</v>
-      </c>
-      <c r="B388" t="s">
-        <v>1504</v>
       </c>
       <c r="D388" t="s">
         <v>990</v>
@@ -19994,10 +19991,10 @@
         <v>82</v>
       </c>
       <c r="J388" t="s">
+        <v>1530</v>
+      </c>
+      <c r="L388" s="1" t="s">
         <v>1531</v>
-      </c>
-      <c r="L388" s="1" t="s">
-        <v>1532</v>
       </c>
       <c r="R388" t="s">
         <v>30</v>
@@ -20017,10 +20014,10 @@
     </row>
     <row r="389" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B389" t="s">
         <v>1533</v>
-      </c>
-      <c r="B389" t="s">
-        <v>1534</v>
       </c>
       <c r="D389" t="s">
         <v>61</v>
@@ -20032,19 +20029,19 @@
         <v>82</v>
       </c>
       <c r="J389" t="s">
+        <v>1534</v>
+      </c>
+      <c r="L389" s="1" t="s">
         <v>1535</v>
       </c>
-      <c r="L389" s="1" t="s">
+      <c r="R389" t="s">
+        <v>30</v>
+      </c>
+      <c r="S389" t="s">
+        <v>31</v>
+      </c>
+      <c r="T389" t="s">
         <v>1536</v>
-      </c>
-      <c r="R389" t="s">
-        <v>30</v>
-      </c>
-      <c r="S389" t="s">
-        <v>31</v>
-      </c>
-      <c r="T389" t="s">
-        <v>1537</v>
       </c>
       <c r="U389" t="s">
         <v>1101</v>
@@ -20055,10 +20052,10 @@
     </row>
     <row r="390" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B390" t="s">
         <v>1533</v>
-      </c>
-      <c r="B390" t="s">
-        <v>1534</v>
       </c>
       <c r="D390" t="s">
         <v>1012</v>
@@ -20070,10 +20067,10 @@
         <v>82</v>
       </c>
       <c r="J390" t="s">
+        <v>1537</v>
+      </c>
+      <c r="L390" s="1" t="s">
         <v>1538</v>
-      </c>
-      <c r="L390" s="1" t="s">
-        <v>1539</v>
       </c>
       <c r="R390" t="s">
         <v>30</v>
@@ -20093,25 +20090,25 @@
     </row>
     <row r="391" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B391" t="s">
         <v>1533</v>
-      </c>
-      <c r="B391" t="s">
-        <v>1534</v>
       </c>
       <c r="D391">
         <v>1890</v>
       </c>
       <c r="E391" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="F391" t="s">
+        <v>1539</v>
+      </c>
+      <c r="J391" t="s">
         <v>1540</v>
       </c>
-      <c r="J391" t="s">
+      <c r="L391" s="1" t="s">
         <v>1541</v>
-      </c>
-      <c r="L391" s="1" t="s">
-        <v>1542</v>
       </c>
       <c r="R391" t="s">
         <v>30</v>
@@ -20131,10 +20128,10 @@
     </row>
     <row r="392" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B392" t="s">
         <v>1533</v>
-      </c>
-      <c r="B392" t="s">
-        <v>1534</v>
       </c>
       <c r="D392">
         <v>1892</v>
@@ -20143,13 +20140,13 @@
         <v>178</v>
       </c>
       <c r="F392" t="s">
+        <v>1542</v>
+      </c>
+      <c r="J392" t="s">
         <v>1543</v>
       </c>
-      <c r="J392" t="s">
+      <c r="L392" s="1" t="s">
         <v>1544</v>
-      </c>
-      <c r="L392" s="1" t="s">
-        <v>1545</v>
       </c>
       <c r="R392" t="s">
         <v>30</v>
@@ -20169,10 +20166,10 @@
     </row>
     <row r="393" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B393" t="s">
         <v>1546</v>
-      </c>
-      <c r="B393" t="s">
-        <v>1547</v>
       </c>
       <c r="D393" t="s">
         <v>786</v>
@@ -20184,10 +20181,10 @@
         <v>36</v>
       </c>
       <c r="J393" t="s">
+        <v>1547</v>
+      </c>
+      <c r="L393" s="1" t="s">
         <v>1548</v>
-      </c>
-      <c r="L393" s="1" t="s">
-        <v>1549</v>
       </c>
       <c r="R393" t="s">
         <v>30</v>
@@ -20199,7 +20196,7 @@
         <v>285</v>
       </c>
       <c r="U393" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="W393">
         <v>3</v>
@@ -20207,13 +20204,13 @@
     </row>
     <row r="394" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B394" t="s">
         <v>1546</v>
       </c>
-      <c r="B394" t="s">
-        <v>1547</v>
-      </c>
       <c r="D394" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="E394" t="s">
         <v>26</v>
@@ -20222,22 +20219,22 @@
         <v>41</v>
       </c>
       <c r="J394" t="s">
+        <v>1551</v>
+      </c>
+      <c r="L394" s="1" t="s">
         <v>1552</v>
       </c>
-      <c r="L394" s="1" t="s">
+      <c r="R394" t="s">
+        <v>30</v>
+      </c>
+      <c r="S394" t="s">
+        <v>31</v>
+      </c>
+      <c r="T394" t="s">
         <v>1553</v>
       </c>
-      <c r="R394" t="s">
-        <v>30</v>
-      </c>
-      <c r="S394" t="s">
-        <v>31</v>
-      </c>
-      <c r="T394" t="s">
+      <c r="U394" t="s">
         <v>1554</v>
-      </c>
-      <c r="U394" t="s">
-        <v>1555</v>
       </c>
       <c r="W394">
         <v>3</v>
@@ -20245,10 +20242,10 @@
     </row>
     <row r="395" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B395" t="s">
         <v>1546</v>
-      </c>
-      <c r="B395" t="s">
-        <v>1547</v>
       </c>
       <c r="D395">
         <v>1895</v>
@@ -20260,10 +20257,10 @@
         <v>36</v>
       </c>
       <c r="J395" t="s">
+        <v>1555</v>
+      </c>
+      <c r="L395" s="1" t="s">
         <v>1556</v>
-      </c>
-      <c r="L395" s="1" t="s">
-        <v>1557</v>
       </c>
       <c r="R395" t="s">
         <v>30</v>
@@ -20283,10 +20280,10 @@
     </row>
     <row r="396" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B396" t="s">
         <v>1546</v>
-      </c>
-      <c r="B396" t="s">
-        <v>1547</v>
       </c>
       <c r="D396">
         <v>1899</v>
@@ -20298,19 +20295,19 @@
         <v>36</v>
       </c>
       <c r="J396" t="s">
+        <v>1557</v>
+      </c>
+      <c r="L396" s="1" t="s">
         <v>1558</v>
       </c>
-      <c r="L396" s="1" t="s">
+      <c r="R396" t="s">
+        <v>30</v>
+      </c>
+      <c r="S396" t="s">
+        <v>31</v>
+      </c>
+      <c r="T396" t="s">
         <v>1559</v>
-      </c>
-      <c r="R396" t="s">
-        <v>30</v>
-      </c>
-      <c r="S396" t="s">
-        <v>31</v>
-      </c>
-      <c r="T396" t="s">
-        <v>1560</v>
       </c>
       <c r="U396" t="s">
         <v>1188</v>
@@ -20324,7 +20321,7 @@
         <v>1081</v>
       </c>
       <c r="B397" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D397" t="s">
         <v>655</v>
@@ -20333,13 +20330,13 @@
         <v>145</v>
       </c>
       <c r="F397" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="J397" t="s">
+        <v>1561</v>
+      </c>
+      <c r="L397" s="1" t="s">
         <v>1562</v>
-      </c>
-      <c r="L397" s="1" t="s">
-        <v>1563</v>
       </c>
       <c r="R397" t="s">
         <v>30</v>
@@ -20362,7 +20359,7 @@
         <v>1081</v>
       </c>
       <c r="B398" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D398" t="s">
         <v>201</v>
@@ -20371,13 +20368,13 @@
         <v>145</v>
       </c>
       <c r="F398" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="J398" t="s">
+        <v>1563</v>
+      </c>
+      <c r="L398" s="1" t="s">
         <v>1564</v>
-      </c>
-      <c r="L398" s="1" t="s">
-        <v>1565</v>
       </c>
       <c r="R398" t="s">
         <v>30</v>
@@ -20400,7 +20397,7 @@
         <v>1081</v>
       </c>
       <c r="B399" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D399" t="s">
         <v>61</v>
@@ -20412,10 +20409,10 @@
         <v>82</v>
       </c>
       <c r="J399" t="s">
+        <v>1565</v>
+      </c>
+      <c r="L399" s="1" t="s">
         <v>1566</v>
-      </c>
-      <c r="L399" s="1" t="s">
-        <v>1567</v>
       </c>
       <c r="R399" t="s">
         <v>30</v>
@@ -20424,7 +20421,7 @@
         <v>668</v>
       </c>
       <c r="T399" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="U399" t="s">
         <v>122</v>
@@ -20438,7 +20435,7 @@
         <v>1081</v>
       </c>
       <c r="B400" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D400" t="s">
         <v>61</v>
@@ -20450,10 +20447,10 @@
         <v>82</v>
       </c>
       <c r="J400" t="s">
+        <v>1568</v>
+      </c>
+      <c r="L400" s="1" t="s">
         <v>1569</v>
-      </c>
-      <c r="L400" s="1" t="s">
-        <v>1570</v>
       </c>
       <c r="R400" t="s">
         <v>30</v>
@@ -20476,7 +20473,7 @@
         <v>1081</v>
       </c>
       <c r="B401" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D401" t="s">
         <v>61</v>
@@ -20488,10 +20485,10 @@
         <v>82</v>
       </c>
       <c r="J401" t="s">
+        <v>1570</v>
+      </c>
+      <c r="L401" s="1" t="s">
         <v>1571</v>
-      </c>
-      <c r="L401" s="1" t="s">
-        <v>1572</v>
       </c>
       <c r="R401" t="s">
         <v>30</v>
@@ -20500,7 +20497,7 @@
         <v>668</v>
       </c>
       <c r="T401" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="U401" t="s">
         <v>76</v>
@@ -20514,7 +20511,7 @@
         <v>1081</v>
       </c>
       <c r="B402" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D402">
         <v>1891</v>
@@ -20526,10 +20523,10 @@
         <v>82</v>
       </c>
       <c r="J402" t="s">
+        <v>1572</v>
+      </c>
+      <c r="L402" s="1" t="s">
         <v>1573</v>
-      </c>
-      <c r="L402" s="1" t="s">
-        <v>1574</v>
       </c>
       <c r="R402" t="s">
         <v>30</v>
@@ -20552,7 +20549,7 @@
         <v>1081</v>
       </c>
       <c r="B403" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D403">
         <v>1890</v>
@@ -20564,10 +20561,10 @@
         <v>82</v>
       </c>
       <c r="J403" t="s">
+        <v>1574</v>
+      </c>
+      <c r="L403" s="1" t="s">
         <v>1575</v>
-      </c>
-      <c r="L403" s="1" t="s">
-        <v>1576</v>
       </c>
       <c r="R403" t="s">
         <v>30</v>
@@ -20579,7 +20576,7 @@
         <v>428</v>
       </c>
       <c r="U403" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="W403">
         <v>2</v>
@@ -20590,7 +20587,7 @@
         <v>1081</v>
       </c>
       <c r="B404" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D404">
         <v>1895</v>
@@ -20599,25 +20596,25 @@
         <v>145</v>
       </c>
       <c r="F404" t="s">
+        <v>1577</v>
+      </c>
+      <c r="J404" t="s">
         <v>1578</v>
       </c>
-      <c r="J404" t="s">
+      <c r="L404" s="1" t="s">
         <v>1579</v>
       </c>
-      <c r="L404" s="1" t="s">
+      <c r="R404" t="s">
+        <v>30</v>
+      </c>
+      <c r="S404" t="s">
         <v>1580</v>
       </c>
-      <c r="R404" t="s">
-        <v>30</v>
-      </c>
-      <c r="S404" t="s">
+      <c r="T404" t="s">
         <v>1581</v>
       </c>
-      <c r="T404" t="s">
+      <c r="U404" t="s">
         <v>1582</v>
-      </c>
-      <c r="U404" t="s">
-        <v>1583</v>
       </c>
       <c r="W404">
         <v>2</v>
@@ -20625,10 +20622,10 @@
     </row>
     <row r="405" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B405" t="s">
         <v>1584</v>
-      </c>
-      <c r="B405" t="s">
-        <v>1585</v>
       </c>
       <c r="D405" t="s">
         <v>55</v>
@@ -20640,19 +20637,19 @@
         <v>179</v>
       </c>
       <c r="J405" t="s">
+        <v>1585</v>
+      </c>
+      <c r="L405" s="1" t="s">
         <v>1586</v>
       </c>
-      <c r="L405" s="1" t="s">
+      <c r="R405" t="s">
+        <v>30</v>
+      </c>
+      <c r="S405" t="s">
+        <v>31</v>
+      </c>
+      <c r="T405" t="s">
         <v>1587</v>
-      </c>
-      <c r="R405" t="s">
-        <v>30</v>
-      </c>
-      <c r="S405" t="s">
-        <v>31</v>
-      </c>
-      <c r="T405" t="s">
-        <v>1588</v>
       </c>
       <c r="U405" t="s">
         <v>559</v>
@@ -20663,25 +20660,25 @@
     </row>
     <row r="406" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B406" t="s">
         <v>1584</v>
-      </c>
-      <c r="B406" t="s">
-        <v>1585</v>
       </c>
       <c r="D406" t="s">
         <v>669</v>
       </c>
       <c r="E406" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F406" t="s">
         <v>1589</v>
       </c>
-      <c r="F406" t="s">
+      <c r="J406" t="s">
         <v>1590</v>
       </c>
-      <c r="J406" t="s">
+      <c r="L406" s="1" t="s">
         <v>1591</v>
-      </c>
-      <c r="L406" s="1" t="s">
-        <v>1592</v>
       </c>
       <c r="R406" t="s">
         <v>30</v>
@@ -20701,10 +20698,10 @@
     </row>
     <row r="407" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B407" t="s">
         <v>1584</v>
-      </c>
-      <c r="B407" t="s">
-        <v>1585</v>
       </c>
       <c r="D407">
         <v>1894</v>
@@ -20716,7 +20713,7 @@
         <v>1124</v>
       </c>
       <c r="L407" s="1" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="R407" t="s">
         <v>30</v>
@@ -20725,7 +20722,7 @@
         <v>31</v>
       </c>
       <c r="T407" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="U407" t="s">
         <v>130</v>
@@ -20736,10 +20733,10 @@
     </row>
     <row r="408" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B408" t="s">
         <v>1584</v>
-      </c>
-      <c r="B408" t="s">
-        <v>1585</v>
       </c>
       <c r="D408">
         <v>1895</v>
@@ -20748,10 +20745,10 @@
         <v>56</v>
       </c>
       <c r="J408" t="s">
+        <v>1593</v>
+      </c>
+      <c r="L408" s="1" t="s">
         <v>1594</v>
-      </c>
-      <c r="L408" s="1" t="s">
-        <v>1595</v>
       </c>
       <c r="R408" t="s">
         <v>30</v>
@@ -20763,7 +20760,7 @@
         <v>925</v>
       </c>
       <c r="U408" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="W408">
         <v>3</v>
@@ -20771,13 +20768,13 @@
     </row>
     <row r="409" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B409" t="s">
         <v>1596</v>
       </c>
-      <c r="B409" t="s">
+      <c r="D409" t="s">
         <v>1597</v>
-      </c>
-      <c r="D409" t="s">
-        <v>1598</v>
       </c>
       <c r="E409" t="s">
         <v>112</v>
@@ -20786,10 +20783,10 @@
         <v>113</v>
       </c>
       <c r="J409" t="s">
+        <v>1598</v>
+      </c>
+      <c r="L409" s="1" t="s">
         <v>1599</v>
-      </c>
-      <c r="L409" s="1" t="s">
-        <v>1600</v>
       </c>
       <c r="R409" t="s">
         <v>30</v>
@@ -20809,10 +20806,10 @@
     </row>
     <row r="410" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B410" t="s">
         <v>1596</v>
-      </c>
-      <c r="B410" t="s">
-        <v>1597</v>
       </c>
       <c r="D410" t="s">
         <v>976</v>
@@ -20824,10 +20821,10 @@
         <v>82</v>
       </c>
       <c r="J410" t="s">
+        <v>1600</v>
+      </c>
+      <c r="L410" s="1" t="s">
         <v>1601</v>
-      </c>
-      <c r="L410" s="1" t="s">
-        <v>1602</v>
       </c>
       <c r="R410" t="s">
         <v>30</v>
@@ -20847,10 +20844,10 @@
     </row>
     <row r="411" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B411" t="s">
         <v>1596</v>
-      </c>
-      <c r="B411" t="s">
-        <v>1597</v>
       </c>
       <c r="D411">
         <v>1875</v>
@@ -20859,13 +20856,13 @@
         <v>447</v>
       </c>
       <c r="F411" t="s">
+        <v>1602</v>
+      </c>
+      <c r="J411" t="s">
         <v>1603</v>
       </c>
-      <c r="J411" t="s">
+      <c r="L411" s="1" t="s">
         <v>1604</v>
-      </c>
-      <c r="L411" s="1" t="s">
-        <v>1605</v>
       </c>
       <c r="R411" t="s">
         <v>30</v>
@@ -20885,25 +20882,25 @@
     </row>
     <row r="412" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B412" t="s">
         <v>1596</v>
       </c>
-      <c r="B412" t="s">
-        <v>1597</v>
-      </c>
       <c r="D412" t="s">
+        <v>1605</v>
+      </c>
+      <c r="E412" t="s">
         <v>1606</v>
       </c>
-      <c r="E412" t="s">
+      <c r="F412" t="s">
         <v>1607</v>
       </c>
-      <c r="F412" t="s">
+      <c r="J412" t="s">
         <v>1608</v>
       </c>
-      <c r="J412" t="s">
+      <c r="L412" s="1" t="s">
         <v>1609</v>
-      </c>
-      <c r="L412" s="1" t="s">
-        <v>1610</v>
       </c>
       <c r="R412" t="s">
         <v>30</v>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4F6753-D2D3-4B74-810E-4B483E1F2FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266E4E25-3768-4C64-93EC-7F11FD1C0F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="16275" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4405" uniqueCount="1611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4405" uniqueCount="1612">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2528,9 +2528,6 @@
     <t>Florence</t>
   </si>
   <si>
-    <t>Les Offices</t>
-  </si>
-  <si>
     <t>"Le camp italien après la bataille de Magenta"</t>
   </si>
   <si>
@@ -3413,9 +3410,6 @@
     <t>Birmingham</t>
   </si>
   <si>
-    <t>Muzeum and Art Gallery</t>
-  </si>
-  <si>
     <t>"La Jeune Aveugle"</t>
   </si>
   <si>
@@ -4866,6 +4860,15 @@
   </si>
   <si>
     <t>Galerie nationale d'Ecosse</t>
+  </si>
+  <si>
+    <t>Galerie des Offices</t>
+  </si>
+  <si>
+    <t>Museum and Art Gallery</t>
+  </si>
+  <si>
+    <t>Getty Center</t>
   </si>
 </sst>
 </file>
@@ -8474,7 +8477,7 @@
         <v>447</v>
       </c>
       <c r="F85" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="J85" t="s">
         <v>448</v>
@@ -8667,10 +8670,10 @@
         <v>441</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="L90" s="4" t="s">
         <v>473</v>
@@ -11853,25 +11856,25 @@
         <v>830</v>
       </c>
       <c r="F174" t="s">
+        <v>1609</v>
+      </c>
+      <c r="J174" t="s">
         <v>831</v>
       </c>
-      <c r="J174" t="s">
+      <c r="L174" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="L174" s="1" t="s">
+      <c r="R174" t="s">
+        <v>30</v>
+      </c>
+      <c r="S174" t="s">
+        <v>31</v>
+      </c>
+      <c r="T174" t="s">
         <v>833</v>
       </c>
-      <c r="R174" t="s">
-        <v>30</v>
-      </c>
-      <c r="S174" t="s">
-        <v>31</v>
-      </c>
-      <c r="T174" t="s">
+      <c r="U174" t="s">
         <v>834</v>
-      </c>
-      <c r="U174" t="s">
-        <v>835</v>
       </c>
       <c r="W174">
         <v>3</v>
@@ -11891,13 +11894,13 @@
         <v>830</v>
       </c>
       <c r="F175" t="s">
+        <v>835</v>
+      </c>
+      <c r="J175" t="s">
         <v>836</v>
       </c>
-      <c r="J175" t="s">
+      <c r="L175" s="1" t="s">
         <v>837</v>
-      </c>
-      <c r="L175" s="1" t="s">
-        <v>838</v>
       </c>
       <c r="R175" t="s">
         <v>30</v>
@@ -11906,10 +11909,10 @@
         <v>205</v>
       </c>
       <c r="T175" t="s">
+        <v>838</v>
+      </c>
+      <c r="U175" t="s">
         <v>839</v>
-      </c>
-      <c r="U175" t="s">
-        <v>840</v>
       </c>
       <c r="W175">
         <v>3</v>
@@ -11929,13 +11932,13 @@
         <v>830</v>
       </c>
       <c r="F176" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="J176" t="s">
+        <v>840</v>
+      </c>
+      <c r="L176" s="1" t="s">
         <v>841</v>
-      </c>
-      <c r="L176" s="1" t="s">
-        <v>842</v>
       </c>
       <c r="R176" t="s">
         <v>30</v>
@@ -11944,10 +11947,10 @@
         <v>205</v>
       </c>
       <c r="T176" t="s">
+        <v>842</v>
+      </c>
+      <c r="U176" t="s">
         <v>843</v>
-      </c>
-      <c r="U176" t="s">
-        <v>844</v>
       </c>
       <c r="W176">
         <v>3</v>
@@ -11964,16 +11967,16 @@
         <v>1880</v>
       </c>
       <c r="E177" t="s">
+        <v>844</v>
+      </c>
+      <c r="F177" t="s">
         <v>845</v>
       </c>
-      <c r="F177" t="s">
+      <c r="J177" t="s">
         <v>846</v>
       </c>
-      <c r="J177" t="s">
+      <c r="L177" s="1" t="s">
         <v>847</v>
-      </c>
-      <c r="L177" s="1" t="s">
-        <v>848</v>
       </c>
       <c r="R177" t="s">
         <v>30</v>
@@ -11993,25 +11996,25 @@
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>848</v>
+      </c>
+      <c r="B178" t="s">
         <v>849</v>
       </c>
-      <c r="B178" t="s">
+      <c r="D178" t="s">
         <v>850</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
         <v>851</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
         <v>852</v>
       </c>
-      <c r="F178" t="s">
+      <c r="J178" t="s">
         <v>853</v>
       </c>
-      <c r="J178" t="s">
+      <c r="L178" s="1" t="s">
         <v>854</v>
-      </c>
-      <c r="L178" s="1" t="s">
-        <v>855</v>
       </c>
       <c r="R178" t="s">
         <v>30</v>
@@ -12031,25 +12034,25 @@
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>848</v>
+      </c>
+      <c r="B179" t="s">
         <v>849</v>
-      </c>
-      <c r="B179" t="s">
-        <v>850</v>
       </c>
       <c r="D179" t="s">
         <v>735</v>
       </c>
       <c r="E179" t="s">
+        <v>851</v>
+      </c>
+      <c r="F179" t="s">
         <v>852</v>
       </c>
-      <c r="F179" t="s">
-        <v>853</v>
-      </c>
       <c r="J179" t="s">
+        <v>855</v>
+      </c>
+      <c r="L179" s="1" t="s">
         <v>856</v>
-      </c>
-      <c r="L179" s="1" t="s">
-        <v>857</v>
       </c>
       <c r="R179" t="s">
         <v>30</v>
@@ -12069,13 +12072,13 @@
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>848</v>
+      </c>
+      <c r="B180" t="s">
         <v>849</v>
       </c>
-      <c r="B180" t="s">
-        <v>850</v>
-      </c>
       <c r="D180" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E180" t="s">
         <v>195</v>
@@ -12084,10 +12087,10 @@
         <v>202</v>
       </c>
       <c r="J180" t="s">
+        <v>858</v>
+      </c>
+      <c r="L180" s="1" t="s">
         <v>859</v>
-      </c>
-      <c r="L180" s="1" t="s">
-        <v>860</v>
       </c>
       <c r="R180" t="s">
         <v>30</v>
@@ -12107,25 +12110,25 @@
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>848</v>
+      </c>
+      <c r="B181" t="s">
         <v>849</v>
-      </c>
-      <c r="B181" t="s">
-        <v>850</v>
       </c>
       <c r="D181">
         <v>1818</v>
       </c>
       <c r="E181" t="s">
+        <v>860</v>
+      </c>
+      <c r="F181" t="s">
         <v>861</v>
       </c>
-      <c r="F181" t="s">
+      <c r="J181" t="s">
         <v>862</v>
       </c>
-      <c r="J181" t="s">
+      <c r="L181" s="1" t="s">
         <v>863</v>
-      </c>
-      <c r="L181" s="1" t="s">
-        <v>864</v>
       </c>
       <c r="R181" t="s">
         <v>30</v>
@@ -12148,7 +12151,7 @@
         <v>365</v>
       </c>
       <c r="B182" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D182" t="s">
         <v>225</v>
@@ -12160,10 +12163,10 @@
         <v>476</v>
       </c>
       <c r="J182" t="s">
+        <v>865</v>
+      </c>
+      <c r="L182" s="1" t="s">
         <v>866</v>
-      </c>
-      <c r="L182" s="1" t="s">
-        <v>867</v>
       </c>
       <c r="R182" t="s">
         <v>30</v>
@@ -12172,7 +12175,7 @@
         <v>205</v>
       </c>
       <c r="T182" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="U182" t="s">
         <v>518</v>
@@ -12186,7 +12189,7 @@
         <v>365</v>
       </c>
       <c r="B183" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D183" t="s">
         <v>225</v>
@@ -12195,13 +12198,13 @@
         <v>145</v>
       </c>
       <c r="F183" t="s">
+        <v>868</v>
+      </c>
+      <c r="J183" t="s">
         <v>869</v>
       </c>
-      <c r="J183" t="s">
+      <c r="L183" s="1" t="s">
         <v>870</v>
-      </c>
-      <c r="L183" s="1" t="s">
-        <v>871</v>
       </c>
       <c r="R183" t="s">
         <v>30</v>
@@ -12224,7 +12227,7 @@
         <v>365</v>
       </c>
       <c r="B184" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D184" t="s">
         <v>240</v>
@@ -12236,10 +12239,10 @@
         <v>82</v>
       </c>
       <c r="J184" t="s">
+        <v>871</v>
+      </c>
+      <c r="L184" s="1" t="s">
         <v>872</v>
-      </c>
-      <c r="L184" s="1" t="s">
-        <v>873</v>
       </c>
       <c r="R184" t="s">
         <v>30</v>
@@ -12262,7 +12265,7 @@
         <v>365</v>
       </c>
       <c r="B185" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D185" t="s">
         <v>654</v>
@@ -12274,10 +12277,10 @@
         <v>82</v>
       </c>
       <c r="J185" t="s">
+        <v>873</v>
+      </c>
+      <c r="L185" s="1" t="s">
         <v>874</v>
-      </c>
-      <c r="L185" s="1" t="s">
-        <v>875</v>
       </c>
       <c r="R185" t="s">
         <v>30</v>
@@ -12289,7 +12292,7 @@
         <v>199</v>
       </c>
       <c r="U185" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="W185">
         <v>1</v>
@@ -12300,7 +12303,7 @@
         <v>365</v>
       </c>
       <c r="B186" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D186" t="s">
         <v>201</v>
@@ -12312,10 +12315,10 @@
         <v>401</v>
       </c>
       <c r="J186" t="s">
+        <v>876</v>
+      </c>
+      <c r="L186" s="1" t="s">
         <v>877</v>
-      </c>
-      <c r="L186" s="1" t="s">
-        <v>878</v>
       </c>
       <c r="R186" t="s">
         <v>30</v>
@@ -12338,34 +12341,34 @@
         <v>365</v>
       </c>
       <c r="B187" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D187" t="s">
+        <v>878</v>
+      </c>
+      <c r="E187" t="s">
         <v>879</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
         <v>880</v>
       </c>
-      <c r="F187" t="s">
+      <c r="J187" t="s">
         <v>881</v>
       </c>
-      <c r="J187" t="s">
+      <c r="L187" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="L187" s="1" t="s">
+      <c r="R187" t="s">
+        <v>30</v>
+      </c>
+      <c r="S187" t="s">
+        <v>31</v>
+      </c>
+      <c r="T187" t="s">
         <v>883</v>
       </c>
-      <c r="R187" t="s">
-        <v>30</v>
-      </c>
-      <c r="S187" t="s">
-        <v>31</v>
-      </c>
-      <c r="T187" t="s">
+      <c r="U187" t="s">
         <v>884</v>
-      </c>
-      <c r="U187" t="s">
-        <v>885</v>
       </c>
       <c r="W187">
         <v>1</v>
@@ -12376,7 +12379,7 @@
         <v>365</v>
       </c>
       <c r="B188" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D188">
         <v>1888</v>
@@ -12385,13 +12388,13 @@
         <v>441</v>
       </c>
       <c r="F188" t="s">
+        <v>885</v>
+      </c>
+      <c r="J188" t="s">
         <v>886</v>
       </c>
-      <c r="J188" t="s">
+      <c r="L188" s="1" t="s">
         <v>887</v>
-      </c>
-      <c r="L188" s="1" t="s">
-        <v>888</v>
       </c>
       <c r="R188" t="s">
         <v>30</v>
@@ -12414,7 +12417,7 @@
         <v>365</v>
       </c>
       <c r="B189" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D189">
         <v>1889</v>
@@ -12423,13 +12426,13 @@
         <v>603</v>
       </c>
       <c r="F189" t="s">
+        <v>888</v>
+      </c>
+      <c r="J189" t="s">
         <v>889</v>
       </c>
-      <c r="J189" t="s">
+      <c r="L189" s="1" t="s">
         <v>890</v>
-      </c>
-      <c r="L189" s="1" t="s">
-        <v>891</v>
       </c>
       <c r="R189" t="s">
         <v>30</v>
@@ -12452,7 +12455,7 @@
         <v>365</v>
       </c>
       <c r="B190" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D190">
         <v>1888</v>
@@ -12464,10 +12467,10 @@
         <v>82</v>
       </c>
       <c r="J190" t="s">
+        <v>891</v>
+      </c>
+      <c r="L190" s="1" t="s">
         <v>892</v>
-      </c>
-      <c r="L190" s="1" t="s">
-        <v>893</v>
       </c>
       <c r="R190" t="s">
         <v>30</v>
@@ -12490,7 +12493,7 @@
         <v>365</v>
       </c>
       <c r="B191" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D191">
         <v>1891</v>
@@ -12502,10 +12505,10 @@
         <v>146</v>
       </c>
       <c r="J191" t="s">
+        <v>893</v>
+      </c>
+      <c r="L191" s="1" t="s">
         <v>894</v>
-      </c>
-      <c r="L191" s="1" t="s">
-        <v>895</v>
       </c>
       <c r="R191" t="s">
         <v>30</v>
@@ -12528,7 +12531,7 @@
         <v>365</v>
       </c>
       <c r="B192" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D192">
         <v>1892</v>
@@ -12537,13 +12540,13 @@
         <v>208</v>
       </c>
       <c r="F192" t="s">
+        <v>895</v>
+      </c>
+      <c r="J192" t="s">
         <v>896</v>
       </c>
-      <c r="J192" t="s">
+      <c r="L192" s="1" t="s">
         <v>897</v>
-      </c>
-      <c r="L192" s="1" t="s">
-        <v>898</v>
       </c>
       <c r="R192" t="s">
         <v>30</v>
@@ -12566,7 +12569,7 @@
         <v>365</v>
       </c>
       <c r="B193" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D193">
         <v>1894</v>
@@ -12578,10 +12581,10 @@
         <v>711</v>
       </c>
       <c r="J193" t="s">
+        <v>898</v>
+      </c>
+      <c r="L193" s="1" t="s">
         <v>899</v>
-      </c>
-      <c r="L193" s="1" t="s">
-        <v>900</v>
       </c>
       <c r="R193" t="s">
         <v>30</v>
@@ -12604,10 +12607,10 @@
         <v>414</v>
       </c>
       <c r="B194" t="s">
+        <v>900</v>
+      </c>
+      <c r="D194" t="s">
         <v>901</v>
-      </c>
-      <c r="D194" t="s">
-        <v>902</v>
       </c>
       <c r="E194" t="s">
         <v>81</v>
@@ -12616,22 +12619,22 @@
         <v>417</v>
       </c>
       <c r="J194" t="s">
+        <v>902</v>
+      </c>
+      <c r="L194" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="L194" s="1" t="s">
+      <c r="R194" t="s">
+        <v>30</v>
+      </c>
+      <c r="S194" t="s">
+        <v>31</v>
+      </c>
+      <c r="T194" t="s">
         <v>904</v>
       </c>
-      <c r="R194" t="s">
-        <v>30</v>
-      </c>
-      <c r="S194" t="s">
-        <v>31</v>
-      </c>
-      <c r="T194" t="s">
+      <c r="U194" t="s">
         <v>905</v>
-      </c>
-      <c r="U194" t="s">
-        <v>906</v>
       </c>
       <c r="W194">
         <v>1</v>
@@ -12642,22 +12645,22 @@
         <v>414</v>
       </c>
       <c r="B195" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D195" t="s">
+        <v>906</v>
+      </c>
+      <c r="E195" t="s">
         <v>907</v>
       </c>
-      <c r="E195" t="s">
+      <c r="F195" t="s">
         <v>908</v>
       </c>
-      <c r="F195" t="s">
+      <c r="J195" t="s">
         <v>909</v>
       </c>
-      <c r="J195" t="s">
+      <c r="L195" s="1" t="s">
         <v>910</v>
-      </c>
-      <c r="L195" s="1" t="s">
-        <v>911</v>
       </c>
       <c r="R195" t="s">
         <v>30</v>
@@ -12680,10 +12683,10 @@
         <v>414</v>
       </c>
       <c r="B196" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D196" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E196" t="s">
         <v>81</v>
@@ -12692,22 +12695,22 @@
         <v>417</v>
       </c>
       <c r="J196" t="s">
+        <v>912</v>
+      </c>
+      <c r="L196" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="L196" s="1" t="s">
+      <c r="R196" t="s">
+        <v>30</v>
+      </c>
+      <c r="S196" t="s">
+        <v>31</v>
+      </c>
+      <c r="T196" t="s">
         <v>914</v>
       </c>
-      <c r="R196" t="s">
-        <v>30</v>
-      </c>
-      <c r="S196" t="s">
-        <v>31</v>
-      </c>
-      <c r="T196" t="s">
+      <c r="U196" t="s">
         <v>915</v>
-      </c>
-      <c r="U196" t="s">
-        <v>916</v>
       </c>
       <c r="W196">
         <v>1</v>
@@ -12718,25 +12721,25 @@
         <v>414</v>
       </c>
       <c r="B197" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D197" t="s">
+        <v>916</v>
+      </c>
+      <c r="E197" t="s">
         <v>917</v>
-      </c>
-      <c r="E197" t="s">
-        <v>918</v>
       </c>
       <c r="F197" t="s">
         <v>346</v>
       </c>
       <c r="J197" t="s">
+        <v>918</v>
+      </c>
+      <c r="L197" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="L197" s="1" t="s">
+      <c r="M197" t="s">
         <v>920</v>
-      </c>
-      <c r="M197" t="s">
-        <v>921</v>
       </c>
       <c r="R197" t="s">
         <v>30</v>
@@ -12759,7 +12762,7 @@
         <v>414</v>
       </c>
       <c r="B198" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D198" t="s">
         <v>475</v>
@@ -12771,10 +12774,10 @@
         <v>417</v>
       </c>
       <c r="J198" t="s">
+        <v>921</v>
+      </c>
+      <c r="L198" s="1" t="s">
         <v>922</v>
-      </c>
-      <c r="L198" s="1" t="s">
-        <v>923</v>
       </c>
       <c r="R198" t="s">
         <v>30</v>
@@ -12786,7 +12789,7 @@
         <v>76</v>
       </c>
       <c r="U198" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="W198">
         <v>2</v>
@@ -12797,25 +12800,25 @@
         <v>414</v>
       </c>
       <c r="B199" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D199" t="s">
+        <v>924</v>
+      </c>
+      <c r="E199" t="s">
         <v>925</v>
       </c>
-      <c r="E199" t="s">
+      <c r="F199" t="s">
         <v>926</v>
       </c>
-      <c r="F199" t="s">
+      <c r="J199" t="s">
         <v>927</v>
       </c>
-      <c r="J199" t="s">
+      <c r="L199" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="L199" s="1" t="s">
-        <v>929</v>
-      </c>
       <c r="M199" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="R199" t="s">
         <v>30</v>
@@ -12838,10 +12841,10 @@
         <v>414</v>
       </c>
       <c r="B200" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D200" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E200" t="s">
         <v>178</v>
@@ -12850,10 +12853,10 @@
         <v>476</v>
       </c>
       <c r="J200" t="s">
+        <v>930</v>
+      </c>
+      <c r="L200" s="1" t="s">
         <v>931</v>
-      </c>
-      <c r="L200" s="1" t="s">
-        <v>932</v>
       </c>
       <c r="R200" t="s">
         <v>30</v>
@@ -12865,7 +12868,7 @@
         <v>675</v>
       </c>
       <c r="U200" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="W200">
         <v>2</v>
@@ -12876,22 +12879,22 @@
         <v>414</v>
       </c>
       <c r="B201" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D201" t="s">
+        <v>933</v>
+      </c>
+      <c r="E201" t="s">
         <v>934</v>
       </c>
-      <c r="E201" t="s">
+      <c r="F201" t="s">
         <v>935</v>
       </c>
-      <c r="F201" t="s">
+      <c r="J201" t="s">
         <v>936</v>
       </c>
-      <c r="J201" t="s">
+      <c r="L201" s="1" t="s">
         <v>937</v>
-      </c>
-      <c r="L201" s="1" t="s">
-        <v>938</v>
       </c>
       <c r="R201" t="s">
         <v>30</v>
@@ -12911,13 +12914,13 @@
     </row>
     <row r="202" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>938</v>
+      </c>
+      <c r="B202" t="s">
         <v>939</v>
       </c>
-      <c r="B202" t="s">
+      <c r="D202" t="s">
         <v>940</v>
-      </c>
-      <c r="D202" t="s">
-        <v>941</v>
       </c>
       <c r="E202" t="s">
         <v>81</v>
@@ -12926,10 +12929,10 @@
         <v>82</v>
       </c>
       <c r="J202" t="s">
+        <v>941</v>
+      </c>
+      <c r="L202" s="1" t="s">
         <v>942</v>
-      </c>
-      <c r="L202" s="1" t="s">
-        <v>943</v>
       </c>
       <c r="R202" t="s">
         <v>30</v>
@@ -12941,7 +12944,7 @@
         <v>482</v>
       </c>
       <c r="U202" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="W202">
         <v>3</v>
@@ -12949,25 +12952,25 @@
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>938</v>
+      </c>
+      <c r="B203" t="s">
         <v>939</v>
-      </c>
-      <c r="B203" t="s">
-        <v>940</v>
       </c>
       <c r="D203" t="s">
         <v>434</v>
       </c>
       <c r="E203" t="s">
+        <v>851</v>
+      </c>
+      <c r="F203" t="s">
         <v>852</v>
       </c>
-      <c r="F203" t="s">
-        <v>853</v>
-      </c>
       <c r="J203" t="s">
+        <v>944</v>
+      </c>
+      <c r="L203" s="1" t="s">
         <v>945</v>
-      </c>
-      <c r="L203" s="1" t="s">
-        <v>946</v>
       </c>
       <c r="R203" t="s">
         <v>30</v>
@@ -12987,25 +12990,25 @@
     </row>
     <row r="204" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>938</v>
+      </c>
+      <c r="B204" t="s">
         <v>939</v>
-      </c>
-      <c r="B204" t="s">
-        <v>940</v>
       </c>
       <c r="D204">
         <v>1872</v>
       </c>
       <c r="E204" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F204" t="s">
         <v>73</v>
       </c>
       <c r="J204" t="s">
+        <v>947</v>
+      </c>
+      <c r="L204" s="1" t="s">
         <v>948</v>
-      </c>
-      <c r="L204" s="1" t="s">
-        <v>949</v>
       </c>
       <c r="R204" t="s">
         <v>30</v>
@@ -13025,25 +13028,25 @@
     </row>
     <row r="205" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>938</v>
+      </c>
+      <c r="B205" t="s">
         <v>939</v>
-      </c>
-      <c r="B205" t="s">
-        <v>940</v>
       </c>
       <c r="D205">
         <v>1879</v>
       </c>
       <c r="E205" t="s">
+        <v>949</v>
+      </c>
+      <c r="F205" t="s">
         <v>950</v>
       </c>
-      <c r="F205" t="s">
+      <c r="J205" t="s">
         <v>951</v>
       </c>
-      <c r="J205" t="s">
+      <c r="L205" s="1" t="s">
         <v>952</v>
-      </c>
-      <c r="L205" s="1" t="s">
-        <v>953</v>
       </c>
       <c r="R205" t="s">
         <v>30</v>
@@ -13063,25 +13066,25 @@
     </row>
     <row r="206" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>953</v>
+      </c>
+      <c r="B206" t="s">
         <v>954</v>
-      </c>
-      <c r="B206" t="s">
-        <v>955</v>
       </c>
       <c r="D206" t="s">
         <v>742</v>
       </c>
       <c r="E206" t="s">
+        <v>955</v>
+      </c>
+      <c r="F206" t="s">
         <v>956</v>
       </c>
-      <c r="F206" t="s">
+      <c r="J206" t="s">
         <v>957</v>
       </c>
-      <c r="J206" t="s">
+      <c r="L206" s="1" t="s">
         <v>958</v>
-      </c>
-      <c r="L206" s="1" t="s">
-        <v>959</v>
       </c>
       <c r="R206" t="s">
         <v>30</v>
@@ -13101,25 +13104,25 @@
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>953</v>
+      </c>
+      <c r="B207" t="s">
         <v>954</v>
       </c>
-      <c r="B207" t="s">
+      <c r="D207" t="s">
+        <v>959</v>
+      </c>
+      <c r="E207" t="s">
         <v>955</v>
       </c>
-      <c r="D207" t="s">
+      <c r="F207" t="s">
+        <v>956</v>
+      </c>
+      <c r="J207" t="s">
         <v>960</v>
       </c>
-      <c r="E207" t="s">
-        <v>956</v>
-      </c>
-      <c r="F207" t="s">
-        <v>957</v>
-      </c>
-      <c r="J207" t="s">
+      <c r="L207" s="1" t="s">
         <v>961</v>
-      </c>
-      <c r="L207" s="1" t="s">
-        <v>962</v>
       </c>
       <c r="R207" t="s">
         <v>30</v>
@@ -13139,37 +13142,37 @@
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>953</v>
+      </c>
+      <c r="B208" t="s">
         <v>954</v>
-      </c>
-      <c r="B208" t="s">
-        <v>955</v>
       </c>
       <c r="D208">
         <v>1823</v>
       </c>
       <c r="E208" t="s">
+        <v>962</v>
+      </c>
+      <c r="F208" t="s">
         <v>963</v>
       </c>
-      <c r="F208" t="s">
+      <c r="J208" t="s">
         <v>964</v>
       </c>
-      <c r="J208" t="s">
+      <c r="L208" s="1" t="s">
         <v>965</v>
       </c>
-      <c r="L208" s="1" t="s">
+      <c r="R208" t="s">
+        <v>30</v>
+      </c>
+      <c r="S208" t="s">
+        <v>31</v>
+      </c>
+      <c r="T208" t="s">
         <v>966</v>
       </c>
-      <c r="R208" t="s">
-        <v>30</v>
-      </c>
-      <c r="S208" t="s">
-        <v>31</v>
-      </c>
-      <c r="T208" t="s">
+      <c r="U208" t="s">
         <v>967</v>
-      </c>
-      <c r="U208" t="s">
-        <v>968</v>
       </c>
       <c r="W208">
         <v>3</v>
@@ -13177,10 +13180,10 @@
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>953</v>
+      </c>
+      <c r="B209" t="s">
         <v>954</v>
-      </c>
-      <c r="B209" t="s">
-        <v>955</v>
       </c>
       <c r="D209">
         <v>1867</v>
@@ -13189,13 +13192,13 @@
         <v>46</v>
       </c>
       <c r="F209" t="s">
+        <v>968</v>
+      </c>
+      <c r="J209" t="s">
         <v>969</v>
       </c>
-      <c r="J209" t="s">
+      <c r="L209" s="1" t="s">
         <v>970</v>
-      </c>
-      <c r="L209" s="1" t="s">
-        <v>971</v>
       </c>
       <c r="R209" t="s">
         <v>30</v>
@@ -13207,7 +13210,7 @@
         <v>165</v>
       </c>
       <c r="U209" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="W209">
         <v>3</v>
@@ -13215,25 +13218,25 @@
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>972</v>
+      </c>
+      <c r="B210" t="s">
         <v>973</v>
       </c>
-      <c r="B210" t="s">
+      <c r="D210" t="s">
         <v>974</v>
-      </c>
-      <c r="D210" t="s">
-        <v>975</v>
       </c>
       <c r="E210" t="s">
         <v>81</v>
       </c>
       <c r="F210" t="s">
+        <v>975</v>
+      </c>
+      <c r="J210" t="s">
         <v>976</v>
       </c>
-      <c r="J210" t="s">
+      <c r="L210" s="1" t="s">
         <v>977</v>
-      </c>
-      <c r="L210" s="1" t="s">
-        <v>978</v>
       </c>
       <c r="R210" t="s">
         <v>30</v>
@@ -13245,7 +13248,7 @@
         <v>116</v>
       </c>
       <c r="U210" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="W210">
         <v>3</v>
@@ -13253,10 +13256,10 @@
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>972</v>
+      </c>
+      <c r="B211" t="s">
         <v>973</v>
-      </c>
-      <c r="B211" t="s">
-        <v>974</v>
       </c>
       <c r="D211" t="s">
         <v>382</v>
@@ -13268,19 +13271,19 @@
         <v>82</v>
       </c>
       <c r="J211" t="s">
+        <v>979</v>
+      </c>
+      <c r="L211" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="L211" s="1" t="s">
+      <c r="R211" t="s">
+        <v>30</v>
+      </c>
+      <c r="S211" t="s">
+        <v>31</v>
+      </c>
+      <c r="T211" t="s">
         <v>981</v>
-      </c>
-      <c r="R211" t="s">
-        <v>30</v>
-      </c>
-      <c r="S211" t="s">
-        <v>31</v>
-      </c>
-      <c r="T211" t="s">
-        <v>982</v>
       </c>
       <c r="U211" t="s">
         <v>140</v>
@@ -13291,10 +13294,10 @@
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>972</v>
+      </c>
+      <c r="B212" t="s">
         <v>973</v>
-      </c>
-      <c r="B212" t="s">
-        <v>974</v>
       </c>
       <c r="D212">
         <v>1883</v>
@@ -13306,11 +13309,11 @@
         <v>82</v>
       </c>
       <c r="J212" t="s">
+        <v>982</v>
+      </c>
+      <c r="L212" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="L212" s="1" t="s">
-        <v>984</v>
-      </c>
       <c r="R212" t="s">
         <v>30</v>
       </c>
@@ -13318,7 +13321,7 @@
         <v>31</v>
       </c>
       <c r="T212" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="U212" t="s">
         <v>306</v>
@@ -13329,10 +13332,10 @@
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>972</v>
+      </c>
+      <c r="B213" t="s">
         <v>973</v>
-      </c>
-      <c r="B213" t="s">
-        <v>974</v>
       </c>
       <c r="D213">
         <v>1888</v>
@@ -13341,13 +13344,13 @@
         <v>81</v>
       </c>
       <c r="F213" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="J213" t="s">
+        <v>984</v>
+      </c>
+      <c r="L213" s="1" t="s">
         <v>985</v>
-      </c>
-      <c r="L213" s="1" t="s">
-        <v>986</v>
       </c>
       <c r="R213" t="s">
         <v>30</v>
@@ -13367,25 +13370,25 @@
     </row>
     <row r="214" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>986</v>
+      </c>
+      <c r="B214" t="s">
         <v>987</v>
       </c>
-      <c r="B214" t="s">
+      <c r="D214" t="s">
         <v>988</v>
       </c>
-      <c r="D214" t="s">
+      <c r="E214" t="s">
         <v>989</v>
       </c>
-      <c r="E214" t="s">
+      <c r="F214" t="s">
         <v>990</v>
       </c>
-      <c r="F214" t="s">
+      <c r="J214" t="s">
         <v>991</v>
       </c>
-      <c r="J214" t="s">
+      <c r="L214" s="1" t="s">
         <v>992</v>
-      </c>
-      <c r="L214" s="1" t="s">
-        <v>993</v>
       </c>
       <c r="R214" t="s">
         <v>30</v>
@@ -13397,7 +13400,7 @@
         <v>290</v>
       </c>
       <c r="U214" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="W214">
         <v>3</v>
@@ -13405,10 +13408,10 @@
     </row>
     <row r="215" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>986</v>
+      </c>
+      <c r="B215" t="s">
         <v>987</v>
-      </c>
-      <c r="B215" t="s">
-        <v>988</v>
       </c>
       <c r="D215">
         <v>1892</v>
@@ -13420,22 +13423,22 @@
         <v>569</v>
       </c>
       <c r="J215" t="s">
+        <v>994</v>
+      </c>
+      <c r="L215" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="L215" s="1" t="s">
+      <c r="R215" t="s">
+        <v>30</v>
+      </c>
+      <c r="S215" t="s">
         <v>996</v>
-      </c>
-      <c r="R215" t="s">
-        <v>30</v>
-      </c>
-      <c r="S215" t="s">
-        <v>997</v>
       </c>
       <c r="T215" t="s">
         <v>213</v>
       </c>
       <c r="U215" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="W215">
         <v>3</v>
@@ -13443,37 +13446,37 @@
     </row>
     <row r="216" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>986</v>
+      </c>
+      <c r="B216" t="s">
         <v>987</v>
-      </c>
-      <c r="B216" t="s">
-        <v>988</v>
       </c>
       <c r="D216" t="s">
         <v>405</v>
       </c>
       <c r="E216" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F216" t="s">
         <v>209</v>
       </c>
       <c r="J216" t="s">
+        <v>998</v>
+      </c>
+      <c r="L216" s="1" t="s">
         <v>999</v>
       </c>
-      <c r="L216" s="1" t="s">
-        <v>1000</v>
-      </c>
       <c r="R216" t="s">
         <v>30</v>
       </c>
       <c r="S216" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="T216" t="s">
         <v>413</v>
       </c>
       <c r="U216" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="W216">
         <v>3</v>
@@ -13481,10 +13484,10 @@
     </row>
     <row r="217" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>986</v>
+      </c>
+      <c r="B217" t="s">
         <v>987</v>
-      </c>
-      <c r="B217" t="s">
-        <v>988</v>
       </c>
       <c r="D217">
         <v>1892</v>
@@ -13496,19 +13499,19 @@
         <v>209</v>
       </c>
       <c r="J217" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L217" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="L217" s="1" t="s">
+      <c r="R217" t="s">
+        <v>30</v>
+      </c>
+      <c r="S217" t="s">
+        <v>31</v>
+      </c>
+      <c r="T217" t="s">
         <v>1003</v>
-      </c>
-      <c r="R217" t="s">
-        <v>30</v>
-      </c>
-      <c r="S217" t="s">
-        <v>31</v>
-      </c>
-      <c r="T217" t="s">
-        <v>1004</v>
       </c>
       <c r="U217" t="s">
         <v>110</v>
@@ -13519,26 +13522,26 @@
     </row>
     <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B218" t="s">
         <v>1005</v>
-      </c>
-      <c r="B218" t="s">
-        <v>1006</v>
       </c>
       <c r="D218" t="s">
         <v>194</v>
       </c>
       <c r="E218" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F218" t="s">
         <v>1007</v>
       </c>
-      <c r="F218" t="s">
+      <c r="J218" t="s">
         <v>1008</v>
       </c>
-      <c r="J218" t="s">
+      <c r="L218" s="1" t="s">
         <v>1009</v>
       </c>
-      <c r="L218" s="1" t="s">
-        <v>1010</v>
-      </c>
       <c r="R218" t="s">
         <v>30</v>
       </c>
@@ -13546,7 +13549,7 @@
         <v>31</v>
       </c>
       <c r="T218" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="U218" t="s">
         <v>156</v>
@@ -13557,13 +13560,13 @@
     </row>
     <row r="219" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B219" t="s">
         <v>1005</v>
       </c>
-      <c r="B219" t="s">
-        <v>1006</v>
-      </c>
       <c r="D219" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E219" t="s">
         <v>145</v>
@@ -13572,10 +13575,10 @@
         <v>146</v>
       </c>
       <c r="J219" t="s">
+        <v>1011</v>
+      </c>
+      <c r="L219" s="1" t="s">
         <v>1012</v>
-      </c>
-      <c r="L219" s="1" t="s">
-        <v>1013</v>
       </c>
       <c r="R219" t="s">
         <v>30</v>
@@ -13595,10 +13598,10 @@
     </row>
     <row r="220" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B220" t="s">
         <v>1005</v>
-      </c>
-      <c r="B220" t="s">
-        <v>1006</v>
       </c>
       <c r="D220" t="s">
         <v>688</v>
@@ -13610,19 +13613,19 @@
         <v>113</v>
       </c>
       <c r="J220" t="s">
+        <v>1013</v>
+      </c>
+      <c r="L220" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="L220" s="1" t="s">
+      <c r="R220" t="s">
+        <v>30</v>
+      </c>
+      <c r="S220" t="s">
+        <v>31</v>
+      </c>
+      <c r="T220" t="s">
         <v>1015</v>
-      </c>
-      <c r="R220" t="s">
-        <v>30</v>
-      </c>
-      <c r="S220" t="s">
-        <v>31</v>
-      </c>
-      <c r="T220" t="s">
-        <v>1016</v>
       </c>
       <c r="U220" t="s">
         <v>110</v>
@@ -13633,10 +13636,10 @@
     </row>
     <row r="221" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B221" t="s">
         <v>1005</v>
-      </c>
-      <c r="B221" t="s">
-        <v>1006</v>
       </c>
       <c r="D221">
         <v>1893</v>
@@ -13645,13 +13648,13 @@
         <v>72</v>
       </c>
       <c r="F221" t="s">
+        <v>1016</v>
+      </c>
+      <c r="J221" t="s">
         <v>1017</v>
       </c>
-      <c r="J221" t="s">
+      <c r="L221" s="1" t="s">
         <v>1018</v>
-      </c>
-      <c r="L221" s="1" t="s">
-        <v>1019</v>
       </c>
       <c r="R221" t="s">
         <v>30</v>
@@ -13671,25 +13674,25 @@
     </row>
     <row r="222" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B222" t="s">
         <v>1020</v>
       </c>
-      <c r="B222" t="s">
+      <c r="D222" t="s">
         <v>1021</v>
-      </c>
-      <c r="D222" t="s">
-        <v>1022</v>
       </c>
       <c r="E222" t="s">
         <v>81</v>
       </c>
       <c r="F222" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J222" t="s">
         <v>1023</v>
       </c>
-      <c r="J222" t="s">
+      <c r="L222" s="1" t="s">
         <v>1024</v>
-      </c>
-      <c r="L222" s="1" t="s">
-        <v>1025</v>
       </c>
       <c r="R222" t="s">
         <v>30</v>
@@ -13709,10 +13712,10 @@
     </row>
     <row r="223" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B223" t="s">
         <v>1020</v>
-      </c>
-      <c r="B223" t="s">
-        <v>1021</v>
       </c>
       <c r="D223" t="s">
         <v>634</v>
@@ -13724,10 +13727,10 @@
         <v>417</v>
       </c>
       <c r="J223" t="s">
+        <v>1025</v>
+      </c>
+      <c r="L223" s="1" t="s">
         <v>1026</v>
-      </c>
-      <c r="L223" s="1" t="s">
-        <v>1027</v>
       </c>
       <c r="R223" t="s">
         <v>30</v>
@@ -13747,10 +13750,10 @@
     </row>
     <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B224" t="s">
         <v>1020</v>
-      </c>
-      <c r="B224" t="s">
-        <v>1021</v>
       </c>
       <c r="D224" t="s">
         <v>454</v>
@@ -13762,10 +13765,10 @@
         <v>417</v>
       </c>
       <c r="J224" t="s">
+        <v>1027</v>
+      </c>
+      <c r="L224" s="1" t="s">
         <v>1028</v>
-      </c>
-      <c r="L224" s="1" t="s">
-        <v>1029</v>
       </c>
       <c r="R224" t="s">
         <v>30</v>
@@ -13785,25 +13788,25 @@
     </row>
     <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B225" t="s">
         <v>1020</v>
       </c>
-      <c r="B225" t="s">
-        <v>1021</v>
-      </c>
       <c r="D225" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E225" t="s">
         <v>145</v>
       </c>
       <c r="F225" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J225" t="s">
         <v>1031</v>
       </c>
-      <c r="J225" t="s">
+      <c r="L225" s="1" t="s">
         <v>1032</v>
-      </c>
-      <c r="L225" s="1" t="s">
-        <v>1033</v>
       </c>
       <c r="R225" t="s">
         <v>30</v>
@@ -13823,13 +13826,13 @@
     </row>
     <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B226" t="s">
         <v>1020</v>
       </c>
-      <c r="B226" t="s">
-        <v>1021</v>
-      </c>
       <c r="D226" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E226" t="s">
         <v>81</v>
@@ -13838,16 +13841,16 @@
         <v>417</v>
       </c>
       <c r="J226" t="s">
+        <v>1034</v>
+      </c>
+      <c r="L226" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="L226" s="1" t="s">
+      <c r="R226" t="s">
+        <v>30</v>
+      </c>
+      <c r="S226" t="s">
         <v>1036</v>
-      </c>
-      <c r="R226" t="s">
-        <v>30</v>
-      </c>
-      <c r="S226" t="s">
-        <v>1037</v>
       </c>
       <c r="T226" t="s">
         <v>51</v>
@@ -13861,10 +13864,10 @@
     </row>
     <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B227" t="s">
         <v>1020</v>
-      </c>
-      <c r="B227" t="s">
-        <v>1021</v>
       </c>
       <c r="D227">
         <v>1856</v>
@@ -13876,16 +13879,16 @@
         <v>82</v>
       </c>
       <c r="J227" t="s">
+        <v>1037</v>
+      </c>
+      <c r="L227" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="L227" s="1" t="s">
+      <c r="R227" t="s">
+        <v>30</v>
+      </c>
+      <c r="S227" t="s">
         <v>1039</v>
-      </c>
-      <c r="R227" t="s">
-        <v>30</v>
-      </c>
-      <c r="S227" t="s">
-        <v>1040</v>
       </c>
       <c r="T227" t="s">
         <v>127</v>
@@ -13899,10 +13902,10 @@
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B228" t="s">
         <v>1020</v>
-      </c>
-      <c r="B228" t="s">
-        <v>1021</v>
       </c>
       <c r="D228">
         <v>1808</v>
@@ -13914,19 +13917,19 @@
         <v>417</v>
       </c>
       <c r="J228" t="s">
+        <v>1040</v>
+      </c>
+      <c r="L228" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="L228" s="1" t="s">
+      <c r="R228" t="s">
+        <v>30</v>
+      </c>
+      <c r="S228" t="s">
+        <v>1039</v>
+      </c>
+      <c r="T228" t="s">
         <v>1042</v>
-      </c>
-      <c r="R228" t="s">
-        <v>30</v>
-      </c>
-      <c r="S228" t="s">
-        <v>1040</v>
-      </c>
-      <c r="T228" t="s">
-        <v>1043</v>
       </c>
       <c r="U228" t="s">
         <v>110</v>
@@ -13937,34 +13940,34 @@
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B229" t="s">
         <v>1020</v>
-      </c>
-      <c r="B229" t="s">
-        <v>1021</v>
       </c>
       <c r="D229">
         <v>1824</v>
       </c>
       <c r="E229" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F229" t="s">
         <v>1044</v>
       </c>
-      <c r="F229" t="s">
+      <c r="J229" t="s">
         <v>1045</v>
       </c>
-      <c r="J229" t="s">
+      <c r="L229" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="L229" s="1" t="s">
+      <c r="R229" t="s">
+        <v>30</v>
+      </c>
+      <c r="S229" t="s">
         <v>1047</v>
       </c>
-      <c r="R229" t="s">
-        <v>30</v>
-      </c>
-      <c r="S229" t="s">
+      <c r="T229" t="s">
         <v>1048</v>
-      </c>
-      <c r="T229" t="s">
-        <v>1049</v>
       </c>
       <c r="U229" t="s">
         <v>617</v>
@@ -13975,10 +13978,10 @@
     </row>
     <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B230" t="s">
         <v>1020</v>
-      </c>
-      <c r="B230" t="s">
-        <v>1021</v>
       </c>
       <c r="D230">
         <v>1827</v>
@@ -13990,22 +13993,22 @@
         <v>417</v>
       </c>
       <c r="J230" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L230" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="L230" s="1" t="s">
+      <c r="R230" t="s">
+        <v>30</v>
+      </c>
+      <c r="S230" t="s">
+        <v>1039</v>
+      </c>
+      <c r="T230" t="s">
         <v>1051</v>
       </c>
-      <c r="R230" t="s">
-        <v>30</v>
-      </c>
-      <c r="S230" t="s">
-        <v>1040</v>
-      </c>
-      <c r="T230" t="s">
+      <c r="U230" t="s">
         <v>1052</v>
-      </c>
-      <c r="U230" t="s">
-        <v>1053</v>
       </c>
       <c r="W230">
         <v>1</v>
@@ -14013,34 +14016,34 @@
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B231" t="s">
         <v>1020</v>
-      </c>
-      <c r="B231" t="s">
-        <v>1021</v>
       </c>
       <c r="D231">
         <v>1811</v>
       </c>
       <c r="E231" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F231" t="s">
         <v>1054</v>
       </c>
-      <c r="F231" t="s">
+      <c r="J231" t="s">
         <v>1055</v>
       </c>
-      <c r="J231" t="s">
+      <c r="L231" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="L231" s="1" t="s">
+      <c r="R231" t="s">
+        <v>30</v>
+      </c>
+      <c r="S231" t="s">
+        <v>1039</v>
+      </c>
+      <c r="T231" t="s">
         <v>1057</v>
-      </c>
-      <c r="R231" t="s">
-        <v>30</v>
-      </c>
-      <c r="S231" t="s">
-        <v>1040</v>
-      </c>
-      <c r="T231" t="s">
-        <v>1058</v>
       </c>
       <c r="U231" t="s">
         <v>233</v>
@@ -14051,10 +14054,10 @@
     </row>
     <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B232" t="s">
         <v>1020</v>
-      </c>
-      <c r="B232" t="s">
-        <v>1021</v>
       </c>
       <c r="D232">
         <v>1806</v>
@@ -14066,16 +14069,16 @@
         <v>417</v>
       </c>
       <c r="J232" t="s">
+        <v>1058</v>
+      </c>
+      <c r="L232" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="L232" s="1" t="s">
-        <v>1060</v>
-      </c>
       <c r="R232" t="s">
         <v>30</v>
       </c>
       <c r="S232" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="T232" t="s">
         <v>117</v>
@@ -14089,10 +14092,10 @@
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B233" t="s">
         <v>1020</v>
-      </c>
-      <c r="B233" t="s">
-        <v>1021</v>
       </c>
       <c r="D233">
         <v>1808</v>
@@ -14104,19 +14107,19 @@
         <v>417</v>
       </c>
       <c r="J233" t="s">
+        <v>1060</v>
+      </c>
+      <c r="L233" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="L233" s="1" t="s">
+      <c r="R233" t="s">
+        <v>30</v>
+      </c>
+      <c r="S233" t="s">
+        <v>1039</v>
+      </c>
+      <c r="T233" t="s">
         <v>1062</v>
-      </c>
-      <c r="R233" t="s">
-        <v>30</v>
-      </c>
-      <c r="S233" t="s">
-        <v>1040</v>
-      </c>
-      <c r="T233" t="s">
-        <v>1063</v>
       </c>
       <c r="U233" t="s">
         <v>644</v>
@@ -14127,10 +14130,10 @@
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B234" t="s">
         <v>1064</v>
-      </c>
-      <c r="B234" t="s">
-        <v>1065</v>
       </c>
       <c r="D234" t="s">
         <v>25</v>
@@ -14142,10 +14145,10 @@
         <v>146</v>
       </c>
       <c r="J234" t="s">
+        <v>1065</v>
+      </c>
+      <c r="L234" s="1" t="s">
         <v>1066</v>
-      </c>
-      <c r="L234" s="1" t="s">
-        <v>1067</v>
       </c>
       <c r="R234" t="s">
         <v>30</v>
@@ -14157,7 +14160,7 @@
         <v>135</v>
       </c>
       <c r="U234" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="W234">
         <v>3</v>
@@ -14165,13 +14168,13 @@
     </row>
     <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B235" t="s">
         <v>1064</v>
       </c>
-      <c r="B235" t="s">
-        <v>1065</v>
-      </c>
       <c r="D235" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E235" t="s">
         <v>81</v>
@@ -14180,10 +14183,10 @@
         <v>82</v>
       </c>
       <c r="J235" t="s">
+        <v>1068</v>
+      </c>
+      <c r="L235" s="1" t="s">
         <v>1069</v>
-      </c>
-      <c r="L235" s="1" t="s">
-        <v>1070</v>
       </c>
       <c r="R235" t="s">
         <v>30</v>
@@ -14195,7 +14198,7 @@
         <v>135</v>
       </c>
       <c r="U235" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="W235">
         <v>3</v>
@@ -14203,37 +14206,37 @@
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B236" t="s">
         <v>1064</v>
-      </c>
-      <c r="B236" t="s">
-        <v>1065</v>
       </c>
       <c r="D236">
         <v>1876</v>
       </c>
       <c r="E236" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F236" t="s">
         <v>1071</v>
       </c>
-      <c r="F236" t="s">
+      <c r="J236" t="s">
         <v>1072</v>
       </c>
-      <c r="J236" t="s">
+      <c r="L236" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="L236" s="1" t="s">
+      <c r="R236" t="s">
+        <v>30</v>
+      </c>
+      <c r="S236" t="s">
+        <v>31</v>
+      </c>
+      <c r="T236" t="s">
         <v>1074</v>
       </c>
-      <c r="R236" t="s">
-        <v>30</v>
-      </c>
-      <c r="S236" t="s">
-        <v>31</v>
-      </c>
-      <c r="T236" t="s">
-        <v>1075</v>
-      </c>
       <c r="U236" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="W236">
         <v>3</v>
@@ -14241,10 +14244,10 @@
     </row>
     <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B237" t="s">
         <v>1064</v>
-      </c>
-      <c r="B237" t="s">
-        <v>1065</v>
       </c>
       <c r="D237">
         <v>1856</v>
@@ -14253,13 +14256,13 @@
         <v>621</v>
       </c>
       <c r="F237" t="s">
+        <v>1075</v>
+      </c>
+      <c r="J237" t="s">
         <v>1076</v>
       </c>
-      <c r="J237" t="s">
+      <c r="L237" s="1" t="s">
         <v>1077</v>
-      </c>
-      <c r="L237" s="1" t="s">
-        <v>1078</v>
       </c>
       <c r="R237" t="s">
         <v>30</v>
@@ -14271,7 +14274,7 @@
         <v>176</v>
       </c>
       <c r="U237" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="W237">
         <v>3</v>
@@ -14279,13 +14282,13 @@
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B238" t="s">
         <v>1080</v>
       </c>
-      <c r="B238" t="s">
+      <c r="D238" t="s">
         <v>1081</v>
-      </c>
-      <c r="D238" t="s">
-        <v>1082</v>
       </c>
       <c r="E238" t="s">
         <v>81</v>
@@ -14294,10 +14297,10 @@
         <v>82</v>
       </c>
       <c r="J238" t="s">
+        <v>1082</v>
+      </c>
+      <c r="L238" s="1" t="s">
         <v>1083</v>
-      </c>
-      <c r="L238" s="1" t="s">
-        <v>1084</v>
       </c>
       <c r="R238" t="s">
         <v>30</v>
@@ -14317,10 +14320,10 @@
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B239" t="s">
         <v>1080</v>
-      </c>
-      <c r="B239" t="s">
-        <v>1081</v>
       </c>
       <c r="D239" t="s">
         <v>144</v>
@@ -14332,10 +14335,10 @@
         <v>82</v>
       </c>
       <c r="J239" t="s">
+        <v>1084</v>
+      </c>
+      <c r="L239" s="1" t="s">
         <v>1085</v>
-      </c>
-      <c r="L239" s="1" t="s">
-        <v>1086</v>
       </c>
       <c r="R239" t="s">
         <v>30</v>
@@ -14355,10 +14358,10 @@
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B240" t="s">
         <v>1080</v>
-      </c>
-      <c r="B240" t="s">
-        <v>1081</v>
       </c>
       <c r="D240" t="s">
         <v>144</v>
@@ -14370,10 +14373,10 @@
         <v>82</v>
       </c>
       <c r="J240" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L240" s="1" t="s">
         <v>1087</v>
-      </c>
-      <c r="L240" s="1" t="s">
-        <v>1088</v>
       </c>
       <c r="R240" t="s">
         <v>30</v>
@@ -14393,10 +14396,10 @@
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B241" t="s">
         <v>1080</v>
-      </c>
-      <c r="B241" t="s">
-        <v>1081</v>
       </c>
       <c r="D241" t="s">
         <v>151</v>
@@ -14408,19 +14411,19 @@
         <v>82</v>
       </c>
       <c r="J241" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L241" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="L241" s="1" t="s">
+      <c r="R241" t="s">
+        <v>30</v>
+      </c>
+      <c r="S241" t="s">
+        <v>31</v>
+      </c>
+      <c r="T241" t="s">
         <v>1090</v>
-      </c>
-      <c r="R241" t="s">
-        <v>30</v>
-      </c>
-      <c r="S241" t="s">
-        <v>31</v>
-      </c>
-      <c r="T241" t="s">
-        <v>1091</v>
       </c>
       <c r="U241" t="s">
         <v>90</v>
@@ -14431,13 +14434,13 @@
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B242" t="s">
         <v>1080</v>
       </c>
-      <c r="B242" t="s">
-        <v>1081</v>
-      </c>
       <c r="D242" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="E242" t="s">
         <v>81</v>
@@ -14446,10 +14449,10 @@
         <v>82</v>
       </c>
       <c r="J242" t="s">
+        <v>1092</v>
+      </c>
+      <c r="L242" s="1" t="s">
         <v>1093</v>
-      </c>
-      <c r="L242" s="1" t="s">
-        <v>1094</v>
       </c>
       <c r="R242" t="s">
         <v>30</v>
@@ -14469,10 +14472,10 @@
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B243" t="s">
         <v>1080</v>
-      </c>
-      <c r="B243" t="s">
-        <v>1081</v>
       </c>
       <c r="D243" t="s">
         <v>694</v>
@@ -14484,10 +14487,10 @@
         <v>569</v>
       </c>
       <c r="J243" t="s">
+        <v>1094</v>
+      </c>
+      <c r="L243" s="1" t="s">
         <v>1095</v>
-      </c>
-      <c r="L243" s="1" t="s">
-        <v>1096</v>
       </c>
       <c r="R243" t="s">
         <v>30</v>
@@ -14507,25 +14510,25 @@
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B244" t="s">
         <v>1080</v>
-      </c>
-      <c r="B244" t="s">
-        <v>1081</v>
       </c>
       <c r="D244" t="s">
         <v>694</v>
       </c>
       <c r="E244" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="F244" t="s">
         <v>346</v>
       </c>
       <c r="J244" t="s">
+        <v>1097</v>
+      </c>
+      <c r="L244" s="1" t="s">
         <v>1098</v>
-      </c>
-      <c r="L244" s="1" t="s">
-        <v>1099</v>
       </c>
       <c r="R244" t="s">
         <v>30</v>
@@ -14537,7 +14540,7 @@
         <v>39</v>
       </c>
       <c r="U244" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="W244">
         <v>1</v>
@@ -14545,37 +14548,37 @@
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B245" t="s">
         <v>1080</v>
-      </c>
-      <c r="B245" t="s">
-        <v>1081</v>
       </c>
       <c r="D245" t="s">
         <v>334</v>
       </c>
       <c r="E245" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F245" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J245" t="s">
         <v>1101</v>
       </c>
-      <c r="J245" t="s">
+      <c r="L245" s="1" t="s">
         <v>1102</v>
       </c>
-      <c r="L245" s="1" t="s">
+      <c r="R245" t="s">
+        <v>30</v>
+      </c>
+      <c r="S245" t="s">
+        <v>31</v>
+      </c>
+      <c r="T245" t="s">
         <v>1103</v>
       </c>
-      <c r="R245" t="s">
-        <v>30</v>
-      </c>
-      <c r="S245" t="s">
-        <v>31</v>
-      </c>
-      <c r="T245" t="s">
-        <v>1104</v>
-      </c>
       <c r="U245" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="W245">
         <v>1</v>
@@ -14583,26 +14586,26 @@
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B246" t="s">
         <v>1080</v>
       </c>
-      <c r="B246" t="s">
-        <v>1081</v>
-      </c>
       <c r="D246" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E246" t="s">
         <v>1105</v>
-      </c>
-      <c r="E246" t="s">
-        <v>1106</v>
       </c>
       <c r="F246" t="s">
         <v>202</v>
       </c>
       <c r="J246" t="s">
+        <v>1106</v>
+      </c>
+      <c r="L246" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="L246" s="1" t="s">
-        <v>1108</v>
-      </c>
       <c r="R246" t="s">
         <v>30</v>
       </c>
@@ -14610,7 +14613,7 @@
         <v>31</v>
       </c>
       <c r="T246" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="U246" t="s">
         <v>213</v>
@@ -14621,13 +14624,13 @@
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B247" t="s">
         <v>1080</v>
       </c>
-      <c r="B247" t="s">
-        <v>1081</v>
-      </c>
       <c r="D247" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="E247" t="s">
         <v>178</v>
@@ -14636,19 +14639,19 @@
         <v>386</v>
       </c>
       <c r="J247" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L247" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="L247" s="1" t="s">
+      <c r="R247" t="s">
+        <v>30</v>
+      </c>
+      <c r="S247" t="s">
+        <v>31</v>
+      </c>
+      <c r="T247" t="s">
         <v>1111</v>
-      </c>
-      <c r="R247" t="s">
-        <v>30</v>
-      </c>
-      <c r="S247" t="s">
-        <v>31</v>
-      </c>
-      <c r="T247" t="s">
-        <v>1112</v>
       </c>
       <c r="U247" t="s">
         <v>318</v>
@@ -14659,10 +14662,10 @@
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B248" t="s">
         <v>1080</v>
-      </c>
-      <c r="B248" t="s">
-        <v>1081</v>
       </c>
       <c r="D248">
         <v>1872</v>
@@ -14674,11 +14677,11 @@
         <v>82</v>
       </c>
       <c r="J248" t="s">
+        <v>1112</v>
+      </c>
+      <c r="L248" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="L248" s="1" t="s">
-        <v>1114</v>
-      </c>
       <c r="R248" t="s">
         <v>30</v>
       </c>
@@ -14686,7 +14689,7 @@
         <v>31</v>
       </c>
       <c r="T248" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="U248" t="s">
         <v>175</v>
@@ -14697,10 +14700,10 @@
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B249" t="s">
         <v>1080</v>
-      </c>
-      <c r="B249" t="s">
-        <v>1081</v>
       </c>
       <c r="D249">
         <v>1868</v>
@@ -14712,10 +14715,10 @@
         <v>82</v>
       </c>
       <c r="J249" t="s">
+        <v>1114</v>
+      </c>
+      <c r="L249" s="1" t="s">
         <v>1115</v>
-      </c>
-      <c r="L249" s="1" t="s">
-        <v>1116</v>
       </c>
       <c r="R249" t="s">
         <v>30</v>
@@ -14735,10 +14738,10 @@
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B250" t="s">
         <v>1117</v>
-      </c>
-      <c r="B250" t="s">
-        <v>1118</v>
       </c>
       <c r="D250" t="s">
         <v>525</v>
@@ -14750,10 +14753,10 @@
         <v>179</v>
       </c>
       <c r="J250" t="s">
+        <v>1118</v>
+      </c>
+      <c r="L250" s="1" t="s">
         <v>1119</v>
-      </c>
-      <c r="L250" s="1" t="s">
-        <v>1120</v>
       </c>
       <c r="R250" t="s">
         <v>30</v>
@@ -14765,7 +14768,7 @@
         <v>658</v>
       </c>
       <c r="U250" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="W250">
         <v>3</v>
@@ -14773,13 +14776,13 @@
     </row>
     <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B251" t="s">
         <v>1117</v>
       </c>
-      <c r="B251" t="s">
-        <v>1118</v>
-      </c>
       <c r="D251" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E251" t="s">
         <v>178</v>
@@ -14788,10 +14791,10 @@
         <v>179</v>
       </c>
       <c r="J251" t="s">
+        <v>1122</v>
+      </c>
+      <c r="L251" s="1" t="s">
         <v>1123</v>
-      </c>
-      <c r="L251" s="1" t="s">
-        <v>1124</v>
       </c>
       <c r="R251" t="s">
         <v>30</v>
@@ -14811,25 +14814,25 @@
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B252" t="s">
         <v>1117</v>
-      </c>
-      <c r="B252" t="s">
-        <v>1118</v>
       </c>
       <c r="D252">
         <v>1856</v>
       </c>
       <c r="E252" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F252" t="s">
+        <v>1610</v>
+      </c>
+      <c r="J252" t="s">
         <v>1125</v>
       </c>
-      <c r="F252" t="s">
+      <c r="L252" s="1" t="s">
         <v>1126</v>
-      </c>
-      <c r="J252" t="s">
-        <v>1127</v>
-      </c>
-      <c r="L252" s="1" t="s">
-        <v>1128</v>
       </c>
       <c r="R252" t="s">
         <v>30</v>
@@ -14841,7 +14844,7 @@
         <v>718</v>
       </c>
       <c r="U252" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="W252">
         <v>3</v>
@@ -14849,10 +14852,10 @@
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B253" t="s">
         <v>1117</v>
-      </c>
-      <c r="B253" t="s">
-        <v>1118</v>
       </c>
       <c r="D253">
         <v>1886</v>
@@ -14861,13 +14864,13 @@
         <v>291</v>
       </c>
       <c r="F253" t="s">
+        <v>1127</v>
+      </c>
+      <c r="J253" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L253" s="1" t="s">
         <v>1129</v>
-      </c>
-      <c r="J253" t="s">
-        <v>1130</v>
-      </c>
-      <c r="L253" s="1" t="s">
-        <v>1131</v>
       </c>
       <c r="R253" t="s">
         <v>30</v>
@@ -14879,7 +14882,7 @@
         <v>105</v>
       </c>
       <c r="U253" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="W253">
         <v>3</v>
@@ -14887,25 +14890,25 @@
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B254" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="D254">
         <v>1850</v>
       </c>
       <c r="E254" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F254" t="s">
+        <v>1132</v>
+      </c>
+      <c r="J254" t="s">
+        <v>1133</v>
+      </c>
+      <c r="L254" s="1" t="s">
         <v>1134</v>
-      </c>
-      <c r="J254" t="s">
-        <v>1135</v>
-      </c>
-      <c r="L254" s="1" t="s">
-        <v>1136</v>
       </c>
       <c r="R254" t="s">
         <v>30</v>
@@ -14925,13 +14928,13 @@
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B255" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="D255" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="E255" t="s">
         <v>81</v>
@@ -14940,10 +14943,10 @@
         <v>82</v>
       </c>
       <c r="J255" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="R255" t="s">
         <v>30</v>
@@ -14963,13 +14966,13 @@
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B256" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="D256" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="E256" t="s">
         <v>81</v>
@@ -14978,10 +14981,10 @@
         <v>82</v>
       </c>
       <c r="J256" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="R256" t="s">
         <v>30</v>
@@ -14990,7 +14993,7 @@
         <v>31</v>
       </c>
       <c r="T256" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="U256" t="s">
         <v>360</v>
@@ -15001,10 +15004,10 @@
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B257" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="D257">
         <v>1863</v>
@@ -15016,10 +15019,10 @@
         <v>82</v>
       </c>
       <c r="J257" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="R257" t="s">
         <v>30</v>
@@ -15039,13 +15042,13 @@
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B258" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="D258" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="E258" t="s">
         <v>81</v>
@@ -15057,7 +15060,7 @@
         <v>64</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="R258" t="s">
         <v>30</v>
@@ -15077,10 +15080,10 @@
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B259" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="D259">
         <v>1848</v>
@@ -15092,10 +15095,10 @@
         <v>82</v>
       </c>
       <c r="J259" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="R259" t="s">
         <v>30</v>
@@ -15115,13 +15118,13 @@
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B260" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="D260" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="E260" t="s">
         <v>81</v>
@@ -15130,10 +15133,10 @@
         <v>82</v>
       </c>
       <c r="J260" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="R260" t="s">
         <v>30</v>
@@ -15153,10 +15156,10 @@
     </row>
     <row r="261" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B261" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="D261">
         <v>1872</v>
@@ -15168,10 +15171,10 @@
         <v>82</v>
       </c>
       <c r="J261" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="R261" t="s">
         <v>30</v>
@@ -15191,10 +15194,10 @@
     </row>
     <row r="262" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B262" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D262" t="s">
         <v>440</v>
@@ -15206,10 +15209,10 @@
         <v>146</v>
       </c>
       <c r="J262" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="R262" t="s">
         <v>30</v>
@@ -15229,10 +15232,10 @@
     </row>
     <row r="263" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B263" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D263" t="s">
         <v>440</v>
@@ -15244,10 +15247,10 @@
         <v>401</v>
       </c>
       <c r="J263" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="R263" t="s">
         <v>30</v>
@@ -15267,10 +15270,10 @@
     </row>
     <row r="264" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B264" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D264" t="s">
         <v>194</v>
@@ -15282,10 +15285,10 @@
         <v>82</v>
       </c>
       <c r="J264" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="R264" t="s">
         <v>30</v>
@@ -15305,10 +15308,10 @@
     </row>
     <row r="265" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B265" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D265" t="s">
         <v>194</v>
@@ -15317,13 +15320,13 @@
         <v>81</v>
       </c>
       <c r="F265" t="s">
+        <v>1160</v>
+      </c>
+      <c r="J265" t="s">
+        <v>1161</v>
+      </c>
+      <c r="L265" s="1" t="s">
         <v>1162</v>
-      </c>
-      <c r="J265" t="s">
-        <v>1163</v>
-      </c>
-      <c r="L265" s="1" t="s">
-        <v>1164</v>
       </c>
       <c r="R265" t="s">
         <v>30</v>
@@ -15335,7 +15338,7 @@
         <v>398</v>
       </c>
       <c r="U265" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="W265">
         <v>1</v>
@@ -15343,10 +15346,10 @@
     </row>
     <row r="266" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B266" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D266" t="s">
         <v>370</v>
@@ -15358,10 +15361,10 @@
         <v>82</v>
       </c>
       <c r="J266" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="R266" t="s">
         <v>30</v>
@@ -15381,10 +15384,10 @@
     </row>
     <row r="267" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B267" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D267" t="s">
         <v>355</v>
@@ -15396,10 +15399,10 @@
         <v>82</v>
       </c>
       <c r="J267" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="R267" t="s">
         <v>30</v>
@@ -15419,10 +15422,10 @@
     </row>
     <row r="268" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B268" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D268" t="s">
         <v>714</v>
@@ -15434,10 +15437,10 @@
         <v>82</v>
       </c>
       <c r="J268" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="R268" t="s">
         <v>30</v>
@@ -15457,10 +15460,10 @@
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B269" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D269" t="s">
         <v>714</v>
@@ -15472,10 +15475,10 @@
         <v>401</v>
       </c>
       <c r="J269" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="R269" t="s">
         <v>30</v>
@@ -15495,10 +15498,10 @@
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B270" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D270" t="s">
         <v>240</v>
@@ -15510,10 +15513,10 @@
         <v>146</v>
       </c>
       <c r="J270" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="R270" t="s">
         <v>30</v>
@@ -15533,10 +15536,10 @@
     </row>
     <row r="271" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B271" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D271" t="s">
         <v>654</v>
@@ -15548,10 +15551,10 @@
         <v>720</v>
       </c>
       <c r="J271" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="R271" t="s">
         <v>30</v>
@@ -15571,13 +15574,13 @@
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B272" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D272" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E272" t="s">
         <v>81</v>
@@ -15586,10 +15589,10 @@
         <v>82</v>
       </c>
       <c r="J272" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="R272" t="s">
         <v>30</v>
@@ -15609,10 +15612,10 @@
     </row>
     <row r="273" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B273" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D273">
         <v>1869</v>
@@ -15624,10 +15627,10 @@
         <v>82</v>
       </c>
       <c r="J273" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="R273" t="s">
         <v>30</v>
@@ -15650,10 +15653,10 @@
         <v>319</v>
       </c>
       <c r="B274" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="D274" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="E274" t="s">
         <v>81</v>
@@ -15662,10 +15665,10 @@
         <v>82</v>
       </c>
       <c r="J274" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="R274" t="s">
         <v>30</v>
@@ -15674,7 +15677,7 @@
         <v>205</v>
       </c>
       <c r="T274" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="U274" t="s">
         <v>117</v>
@@ -15688,7 +15691,7 @@
         <v>319</v>
       </c>
       <c r="B275" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="D275" t="s">
         <v>325</v>
@@ -15700,10 +15703,10 @@
         <v>82</v>
       </c>
       <c r="J275" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="R275" s="2" t="s">
         <v>173</v>
@@ -15712,7 +15715,7 @@
         <v>173</v>
       </c>
       <c r="T275" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="U275" t="s">
         <v>404</v>
@@ -15726,7 +15729,7 @@
         <v>319</v>
       </c>
       <c r="B276" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="D276">
         <v>1864</v>
@@ -15738,10 +15741,10 @@
         <v>146</v>
       </c>
       <c r="J276" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="R276" t="s">
         <v>30</v>
@@ -15753,7 +15756,7 @@
         <v>553</v>
       </c>
       <c r="U276" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="W276">
         <v>3</v>
@@ -15764,22 +15767,22 @@
         <v>319</v>
       </c>
       <c r="B277" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="D277" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="E277" t="s">
         <v>81</v>
       </c>
       <c r="F277" t="s">
+        <v>1190</v>
+      </c>
+      <c r="J277" t="s">
+        <v>1191</v>
+      </c>
+      <c r="L277" s="1" t="s">
         <v>1192</v>
-      </c>
-      <c r="J277" t="s">
-        <v>1193</v>
-      </c>
-      <c r="L277" s="1" t="s">
-        <v>1194</v>
       </c>
       <c r="R277" t="s">
         <v>30</v>
@@ -15791,7 +15794,7 @@
         <v>71</v>
       </c>
       <c r="U277" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="W277">
         <v>3</v>
@@ -15799,10 +15802,10 @@
     </row>
     <row r="278" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B278" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D278" t="s">
         <v>194</v>
@@ -15814,10 +15817,10 @@
         <v>82</v>
       </c>
       <c r="J278" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="L278" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="R278" t="s">
         <v>30</v>
@@ -15826,7 +15829,7 @@
         <v>31</v>
       </c>
       <c r="T278" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="U278" t="s">
         <v>378</v>
@@ -15837,10 +15840,10 @@
     </row>
     <row r="279" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B279" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D279" t="s">
         <v>694</v>
@@ -15852,10 +15855,10 @@
         <v>82</v>
       </c>
       <c r="J279" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="L279" s="1" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="R279" t="s">
         <v>30</v>
@@ -15867,7 +15870,7 @@
         <v>378</v>
       </c>
       <c r="U279" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="W279">
         <v>2</v>
@@ -15875,10 +15878,10 @@
     </row>
     <row r="280" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B280" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D280" t="s">
         <v>321</v>
@@ -15887,22 +15890,22 @@
         <v>81</v>
       </c>
       <c r="F280" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="J280" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L280" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="R280" t="s">
+        <v>30</v>
+      </c>
+      <c r="S280" t="s">
+        <v>31</v>
+      </c>
+      <c r="T280" t="s">
         <v>1202</v>
-      </c>
-      <c r="L280" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="R280" t="s">
-        <v>30</v>
-      </c>
-      <c r="S280" t="s">
-        <v>31</v>
-      </c>
-      <c r="T280" t="s">
-        <v>1204</v>
       </c>
       <c r="U280" t="s">
         <v>378</v>
@@ -15913,13 +15916,13 @@
     </row>
     <row r="281" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B281" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D281" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="E281" t="s">
         <v>101</v>
@@ -15928,10 +15931,10 @@
         <v>335</v>
       </c>
       <c r="J281" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="L281" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="R281" t="s">
         <v>30</v>
@@ -15951,25 +15954,25 @@
     </row>
     <row r="282" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B282" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D282" t="s">
         <v>262</v>
       </c>
       <c r="E282" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F282" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J282" t="s">
         <v>1208</v>
       </c>
-      <c r="F282" t="s">
+      <c r="L282" s="1" t="s">
         <v>1209</v>
-      </c>
-      <c r="J282" t="s">
-        <v>1210</v>
-      </c>
-      <c r="L282" s="1" t="s">
-        <v>1211</v>
       </c>
       <c r="R282" t="s">
         <v>30</v>
@@ -15989,10 +15992,10 @@
     </row>
     <row r="283" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B283" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D283">
         <v>1879</v>
@@ -16004,10 +16007,10 @@
         <v>82</v>
       </c>
       <c r="J283" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="R283" t="s">
         <v>30</v>
@@ -16027,10 +16030,10 @@
     </row>
     <row r="284" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B284" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D284">
         <v>1881</v>
@@ -16039,10 +16042,10 @@
         <v>56</v>
       </c>
       <c r="J284" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="R284" t="s">
         <v>30</v>
@@ -16062,10 +16065,10 @@
     </row>
     <row r="285" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B285" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D285">
         <v>1891</v>
@@ -16074,13 +16077,13 @@
         <v>81</v>
       </c>
       <c r="F285" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="J285" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="R285" t="s">
         <v>30</v>
@@ -16089,7 +16092,7 @@
         <v>31</v>
       </c>
       <c r="T285" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="U285" t="s">
         <v>775</v>
@@ -16100,10 +16103,10 @@
     </row>
     <row r="286" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B286" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="D286" t="s">
         <v>61</v>
@@ -16112,16 +16115,16 @@
         <v>56</v>
       </c>
       <c r="J286" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="R286" s="2" t="s">
         <v>173</v>
       </c>
       <c r="S286" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="T286" t="s">
         <v>451</v>
@@ -16135,34 +16138,34 @@
     </row>
     <row r="287" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B287" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="D287">
         <v>1899</v>
       </c>
       <c r="E287" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F287" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="J287" t="s">
         <v>103</v>
       </c>
       <c r="L287" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="R287" t="s">
+        <v>30</v>
+      </c>
+      <c r="S287" t="s">
+        <v>1224</v>
+      </c>
+      <c r="T287" t="s">
         <v>1225</v>
-      </c>
-      <c r="R287" t="s">
-        <v>30</v>
-      </c>
-      <c r="S287" t="s">
-        <v>1226</v>
-      </c>
-      <c r="T287" t="s">
-        <v>1227</v>
       </c>
       <c r="U287" t="s">
         <v>183</v>
@@ -16173,34 +16176,34 @@
     </row>
     <row r="288" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B288" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="D288">
         <v>1896</v>
       </c>
       <c r="F288" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G288" t="s">
+        <v>1227</v>
+      </c>
+      <c r="J288" t="s">
         <v>1228</v>
       </c>
-      <c r="G288" t="s">
+      <c r="L288" s="1" t="s">
         <v>1229</v>
       </c>
-      <c r="J288" t="s">
+      <c r="R288" t="s">
+        <v>30</v>
+      </c>
+      <c r="S288" t="s">
+        <v>1224</v>
+      </c>
+      <c r="T288" t="s">
         <v>1230</v>
-      </c>
-      <c r="L288" s="1" t="s">
-        <v>1231</v>
-      </c>
-      <c r="R288" t="s">
-        <v>30</v>
-      </c>
-      <c r="S288" t="s">
-        <v>1226</v>
-      </c>
-      <c r="T288" t="s">
-        <v>1232</v>
       </c>
       <c r="U288" t="s">
         <v>519</v>
@@ -16211,10 +16214,10 @@
     </row>
     <row r="289" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B289" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="D289">
         <v>1896</v>
@@ -16226,16 +16229,16 @@
         <v>64</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="R289" t="s">
         <v>30</v>
       </c>
       <c r="S289" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="T289" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="U289" t="s">
         <v>519</v>
@@ -16246,31 +16249,31 @@
     </row>
     <row r="290" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="B290" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="D290" t="s">
         <v>201</v>
       </c>
       <c r="E290" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F290" t="s">
+        <v>1235</v>
+      </c>
+      <c r="J290" t="s">
         <v>1236</v>
       </c>
-      <c r="F290" t="s">
+      <c r="L290" s="1" t="s">
         <v>1237</v>
       </c>
-      <c r="J290" t="s">
+      <c r="R290" t="s">
+        <v>30</v>
+      </c>
+      <c r="S290" t="s">
         <v>1238</v>
-      </c>
-      <c r="L290" s="1" t="s">
-        <v>1239</v>
-      </c>
-      <c r="R290" t="s">
-        <v>30</v>
-      </c>
-      <c r="S290" t="s">
-        <v>1240</v>
       </c>
       <c r="T290" t="s">
         <v>156</v>
@@ -16284,25 +16287,25 @@
     </row>
     <row r="291" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="B291" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="D291" t="s">
         <v>61</v>
       </c>
       <c r="E291" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="F291" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J291" t="s">
+        <v>1240</v>
+      </c>
+      <c r="L291" s="1" t="s">
         <v>1241</v>
-      </c>
-      <c r="J291" t="s">
-        <v>1242</v>
-      </c>
-      <c r="L291" s="1" t="s">
-        <v>1243</v>
       </c>
       <c r="R291" t="s">
         <v>30</v>
@@ -16322,25 +16325,25 @@
     </row>
     <row r="292" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="B292" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="D292">
         <v>1894</v>
       </c>
       <c r="E292" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="F292" t="s">
+        <v>1242</v>
+      </c>
+      <c r="J292" t="s">
+        <v>1243</v>
+      </c>
+      <c r="L292" s="1" t="s">
         <v>1244</v>
-      </c>
-      <c r="J292" t="s">
-        <v>1245</v>
-      </c>
-      <c r="L292" s="1" t="s">
-        <v>1246</v>
       </c>
       <c r="R292" t="s">
         <v>30</v>
@@ -16360,34 +16363,34 @@
     </row>
     <row r="293" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B293" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D293" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E293" t="s">
         <v>1234</v>
       </c>
-      <c r="B293" t="s">
-        <v>1235</v>
-      </c>
-      <c r="D293" t="s">
+      <c r="F293" t="s">
+        <v>1242</v>
+      </c>
+      <c r="J293" t="s">
+        <v>1246</v>
+      </c>
+      <c r="L293" s="1" t="s">
         <v>1247</v>
       </c>
-      <c r="E293" t="s">
-        <v>1236</v>
-      </c>
-      <c r="F293" t="s">
-        <v>1244</v>
-      </c>
-      <c r="J293" t="s">
+      <c r="R293" t="s">
+        <v>30</v>
+      </c>
+      <c r="S293" t="s">
+        <v>31</v>
+      </c>
+      <c r="T293" t="s">
         <v>1248</v>
-      </c>
-      <c r="L293" s="1" t="s">
-        <v>1249</v>
-      </c>
-      <c r="R293" t="s">
-        <v>30</v>
-      </c>
-      <c r="S293" t="s">
-        <v>31</v>
-      </c>
-      <c r="T293" t="s">
-        <v>1250</v>
       </c>
       <c r="U293" t="s">
         <v>653</v>
@@ -16398,10 +16401,10 @@
     </row>
     <row r="294" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B294" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D294">
         <v>1867</v>
@@ -16413,22 +16416,22 @@
         <v>146</v>
       </c>
       <c r="J294" t="s">
+        <v>1251</v>
+      </c>
+      <c r="L294" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="R294" t="s">
+        <v>30</v>
+      </c>
+      <c r="S294" t="s">
+        <v>31</v>
+      </c>
+      <c r="T294" t="s">
         <v>1253</v>
       </c>
-      <c r="L294" s="1" t="s">
-        <v>1254</v>
-      </c>
-      <c r="R294" t="s">
-        <v>30</v>
-      </c>
-      <c r="S294" t="s">
-        <v>31</v>
-      </c>
-      <c r="T294" t="s">
-        <v>1255</v>
-      </c>
       <c r="U294" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="W294">
         <v>2</v>
@@ -16436,10 +16439,10 @@
     </row>
     <row r="295" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B295" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D295" t="s">
         <v>370</v>
@@ -16451,10 +16454,10 @@
         <v>82</v>
       </c>
       <c r="J295" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="R295" t="s">
         <v>30</v>
@@ -16474,10 +16477,10 @@
     </row>
     <row r="296" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B296" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D296" t="s">
         <v>334</v>
@@ -16489,10 +16492,10 @@
         <v>82</v>
       </c>
       <c r="J296" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="L296" s="1" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="R296" t="s">
         <v>30</v>
@@ -16512,13 +16515,13 @@
     </row>
     <row r="297" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B297" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D297" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E297" t="s">
         <v>81</v>
@@ -16527,10 +16530,10 @@
         <v>82</v>
       </c>
       <c r="J297" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="R297" t="s">
         <v>30</v>
@@ -16550,13 +16553,13 @@
     </row>
     <row r="298" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B298" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D298" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E298" t="s">
         <v>81</v>
@@ -16565,19 +16568,19 @@
         <v>82</v>
       </c>
       <c r="J298" t="s">
+        <v>1261</v>
+      </c>
+      <c r="L298" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="R298" t="s">
+        <v>30</v>
+      </c>
+      <c r="S298" t="s">
+        <v>31</v>
+      </c>
+      <c r="T298" t="s">
         <v>1263</v>
-      </c>
-      <c r="L298" s="1" t="s">
-        <v>1264</v>
-      </c>
-      <c r="R298" t="s">
-        <v>30</v>
-      </c>
-      <c r="S298" t="s">
-        <v>31</v>
-      </c>
-      <c r="T298" t="s">
-        <v>1265</v>
       </c>
       <c r="U298" t="s">
         <v>369</v>
@@ -16588,25 +16591,25 @@
     </row>
     <row r="299" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B299" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D299">
         <v>1898</v>
       </c>
       <c r="E299" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F299" t="s">
         <v>346</v>
       </c>
       <c r="J299" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="R299" t="s">
         <v>30</v>
@@ -16626,10 +16629,10 @@
     </row>
     <row r="300" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B300" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D300">
         <v>1867</v>
@@ -16638,13 +16641,13 @@
         <v>145</v>
       </c>
       <c r="F300" t="s">
+        <v>1267</v>
+      </c>
+      <c r="J300" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L300" s="1" t="s">
         <v>1269</v>
-      </c>
-      <c r="J300" t="s">
-        <v>1270</v>
-      </c>
-      <c r="L300" s="1" t="s">
-        <v>1271</v>
       </c>
       <c r="R300" t="s">
         <v>30</v>
@@ -16664,22 +16667,22 @@
     </row>
     <row r="301" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B301" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D301">
         <v>1896</v>
       </c>
       <c r="F301" t="s">
+        <v>1270</v>
+      </c>
+      <c r="J301" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L301" s="1" t="s">
         <v>1272</v>
-      </c>
-      <c r="J301" t="s">
-        <v>1273</v>
-      </c>
-      <c r="L301" s="1" t="s">
-        <v>1274</v>
       </c>
       <c r="R301" t="s">
         <v>30</v>
@@ -16691,7 +16694,7 @@
         <v>130</v>
       </c>
       <c r="U301" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="W301">
         <v>2</v>
@@ -16702,7 +16705,7 @@
         <v>238</v>
       </c>
       <c r="B302" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D302" t="s">
         <v>34</v>
@@ -16714,10 +16717,10 @@
         <v>417</v>
       </c>
       <c r="J302" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="R302" t="s">
         <v>30</v>
@@ -16740,10 +16743,10 @@
         <v>238</v>
       </c>
       <c r="B303" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D303" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="E303" t="s">
         <v>81</v>
@@ -16752,10 +16755,10 @@
         <v>82</v>
       </c>
       <c r="J303" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="R303" t="s">
         <v>30</v>
@@ -16778,7 +16781,7 @@
         <v>238</v>
       </c>
       <c r="B304" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D304">
         <v>1879</v>
@@ -16790,19 +16793,19 @@
         <v>82</v>
       </c>
       <c r="J304" t="s">
+        <v>1280</v>
+      </c>
+      <c r="L304" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="R304" t="s">
+        <v>30</v>
+      </c>
+      <c r="S304" t="s">
+        <v>31</v>
+      </c>
+      <c r="T304" t="s">
         <v>1282</v>
-      </c>
-      <c r="L304" s="1" t="s">
-        <v>1283</v>
-      </c>
-      <c r="R304" t="s">
-        <v>30</v>
-      </c>
-      <c r="S304" t="s">
-        <v>31</v>
-      </c>
-      <c r="T304" t="s">
-        <v>1284</v>
       </c>
       <c r="U304" t="s">
         <v>286</v>
@@ -16816,34 +16819,34 @@
         <v>238</v>
       </c>
       <c r="B305" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D305" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="E305" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F305" t="s">
         <v>346</v>
       </c>
       <c r="J305" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L305" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="R305" t="s">
+        <v>30</v>
+      </c>
+      <c r="S305" t="s">
+        <v>31</v>
+      </c>
+      <c r="T305" t="s">
         <v>1286</v>
       </c>
-      <c r="L305" s="1" t="s">
+      <c r="U305" t="s">
         <v>1287</v>
-      </c>
-      <c r="R305" t="s">
-        <v>30</v>
-      </c>
-      <c r="S305" t="s">
-        <v>31</v>
-      </c>
-      <c r="T305" t="s">
-        <v>1288</v>
-      </c>
-      <c r="U305" t="s">
-        <v>1289</v>
       </c>
       <c r="W305">
         <v>3</v>
@@ -16851,10 +16854,10 @@
     </row>
     <row r="306" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B306" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="D306" t="s">
         <v>34</v>
@@ -16866,10 +16869,10 @@
         <v>82</v>
       </c>
       <c r="J306" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="R306" t="s">
         <v>30</v>
@@ -16889,10 +16892,10 @@
     </row>
     <row r="307" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B307" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="D307" t="s">
         <v>785</v>
@@ -16904,10 +16907,10 @@
         <v>82</v>
       </c>
       <c r="J307" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="R307" t="s">
         <v>30</v>
@@ -16916,7 +16919,7 @@
         <v>657</v>
       </c>
       <c r="T307" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="U307" t="s">
         <v>428</v>
@@ -16927,10 +16930,10 @@
     </row>
     <row r="308" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B308" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="D308">
         <v>1892</v>
@@ -16942,10 +16945,10 @@
         <v>532</v>
       </c>
       <c r="J308" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="R308" t="s">
         <v>30</v>
@@ -16954,7 +16957,7 @@
         <v>31</v>
       </c>
       <c r="T308" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="U308" t="s">
         <v>518</v>
@@ -16965,10 +16968,10 @@
     </row>
     <row r="309" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B309" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="D309">
         <v>1890</v>
@@ -16980,19 +16983,19 @@
         <v>113</v>
       </c>
       <c r="J309" t="s">
+        <v>1296</v>
+      </c>
+      <c r="L309" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="R309" t="s">
+        <v>30</v>
+      </c>
+      <c r="S309" t="s">
+        <v>31</v>
+      </c>
+      <c r="T309" t="s">
         <v>1298</v>
-      </c>
-      <c r="L309" s="1" t="s">
-        <v>1299</v>
-      </c>
-      <c r="R309" t="s">
-        <v>30</v>
-      </c>
-      <c r="S309" t="s">
-        <v>31</v>
-      </c>
-      <c r="T309" t="s">
-        <v>1300</v>
       </c>
       <c r="U309" t="s">
         <v>230</v>
@@ -17003,10 +17006,10 @@
     </row>
     <row r="310" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B310" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D310" t="s">
         <v>694</v>
@@ -17018,10 +17021,10 @@
         <v>386</v>
       </c>
       <c r="J310" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="R310" t="s">
         <v>30</v>
@@ -17041,10 +17044,10 @@
     </row>
     <row r="311" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B311" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D311" t="s">
         <v>325</v>
@@ -17056,10 +17059,10 @@
         <v>82</v>
       </c>
       <c r="J311" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="R311" t="s">
         <v>30</v>
@@ -17071,7 +17074,7 @@
         <v>250</v>
       </c>
       <c r="U311" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="W311">
         <v>1</v>
@@ -17079,10 +17082,10 @@
     </row>
     <row r="312" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B312" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D312" t="s">
         <v>325</v>
@@ -17094,10 +17097,10 @@
         <v>82</v>
       </c>
       <c r="J312" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="R312" t="s">
         <v>30</v>
@@ -17117,10 +17120,10 @@
     </row>
     <row r="313" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B313" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D313" t="s">
         <v>325</v>
@@ -17132,10 +17135,10 @@
         <v>82</v>
       </c>
       <c r="J313" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="R313" t="s">
         <v>30</v>
@@ -17155,10 +17158,10 @@
     </row>
     <row r="314" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B314" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D314" t="s">
         <v>355</v>
@@ -17170,10 +17173,10 @@
         <v>146</v>
       </c>
       <c r="J314" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="R314" t="s">
         <v>30</v>
@@ -17182,7 +17185,7 @@
         <v>31</v>
       </c>
       <c r="T314" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="U314" t="s">
         <v>307</v>
@@ -17193,13 +17196,13 @@
     </row>
     <row r="315" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B315" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D315" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="E315" t="s">
         <v>112</v>
@@ -17208,10 +17211,10 @@
         <v>579</v>
       </c>
       <c r="J315" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="R315" t="s">
         <v>30</v>
@@ -17223,7 +17226,7 @@
         <v>318</v>
       </c>
       <c r="U315" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="W315">
         <v>1</v>
@@ -17231,10 +17234,10 @@
     </row>
     <row r="316" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B316" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D316" t="s">
         <v>34</v>
@@ -17246,10 +17249,10 @@
         <v>711</v>
       </c>
       <c r="J316" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="R316" t="s">
         <v>30</v>
@@ -17269,13 +17272,13 @@
     </row>
     <row r="317" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B317" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D317" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="E317" t="s">
         <v>81</v>
@@ -17284,13 +17287,13 @@
         <v>82</v>
       </c>
       <c r="J317" t="s">
+        <v>1318</v>
+      </c>
+      <c r="L317" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="M317" t="s">
         <v>1320</v>
-      </c>
-      <c r="L317" s="1" t="s">
-        <v>1321</v>
-      </c>
-      <c r="M317" t="s">
-        <v>1322</v>
       </c>
       <c r="R317" t="s">
         <v>30</v>
@@ -17310,13 +17313,13 @@
     </row>
     <row r="318" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B318" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D318" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="E318" t="s">
         <v>81</v>
@@ -17325,13 +17328,13 @@
         <v>82</v>
       </c>
       <c r="J318" t="s">
+        <v>1321</v>
+      </c>
+      <c r="L318" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="M318" t="s">
         <v>1323</v>
-      </c>
-      <c r="L318" s="1" t="s">
-        <v>1324</v>
-      </c>
-      <c r="M318" t="s">
-        <v>1325</v>
       </c>
       <c r="R318" t="s">
         <v>30</v>
@@ -17351,25 +17354,25 @@
     </row>
     <row r="319" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B319" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D319" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="E319" t="s">
         <v>72</v>
       </c>
       <c r="F319" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="J319" t="s">
         <v>410</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="R319" t="s">
         <v>30</v>
@@ -17389,10 +17392,10 @@
     </row>
     <row r="320" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B320" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D320" t="s">
         <v>654</v>
@@ -17404,10 +17407,10 @@
         <v>82</v>
       </c>
       <c r="J320" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="R320" t="s">
         <v>30</v>
@@ -17427,10 +17430,10 @@
     </row>
     <row r="321" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B321" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D321">
         <v>1877</v>
@@ -17442,10 +17445,10 @@
         <v>146</v>
       </c>
       <c r="J321" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="R321" t="s">
         <v>30</v>
@@ -17465,13 +17468,13 @@
     </row>
     <row r="322" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B322" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D322" t="s">
         <v>1333</v>
-      </c>
-      <c r="B322" t="s">
-        <v>1334</v>
-      </c>
-      <c r="D322" t="s">
-        <v>1335</v>
       </c>
       <c r="E322" t="s">
         <v>26</v>
@@ -17480,10 +17483,10 @@
         <v>41</v>
       </c>
       <c r="J322" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="R322" t="s">
         <v>30</v>
@@ -17503,13 +17506,13 @@
     </row>
     <row r="323" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B323" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="D323" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="E323" t="s">
         <v>26</v>
@@ -17518,22 +17521,22 @@
         <v>41</v>
       </c>
       <c r="J323" t="s">
+        <v>1337</v>
+      </c>
+      <c r="L323" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="R323" t="s">
+        <v>30</v>
+      </c>
+      <c r="S323" t="s">
+        <v>31</v>
+      </c>
+      <c r="T323" t="s">
         <v>1339</v>
       </c>
-      <c r="L323" s="1" t="s">
+      <c r="U323" t="s">
         <v>1340</v>
-      </c>
-      <c r="R323" t="s">
-        <v>30</v>
-      </c>
-      <c r="S323" t="s">
-        <v>31</v>
-      </c>
-      <c r="T323" t="s">
-        <v>1341</v>
-      </c>
-      <c r="U323" t="s">
-        <v>1342</v>
       </c>
       <c r="W323">
         <v>3</v>
@@ -17541,13 +17544,13 @@
     </row>
     <row r="324" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B324" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="D324" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="E324" t="s">
         <v>35</v>
@@ -17556,10 +17559,10 @@
         <v>36</v>
       </c>
       <c r="J324" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="R324" t="s">
         <v>30</v>
@@ -17568,7 +17571,7 @@
         <v>31</v>
       </c>
       <c r="T324" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="U324" t="s">
         <v>629</v>
@@ -17579,13 +17582,13 @@
     </row>
     <row r="325" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B325" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="D325" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="E325" t="s">
         <v>35</v>
@@ -17594,10 +17597,10 @@
         <v>36</v>
       </c>
       <c r="J325" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="R325" t="s">
         <v>30</v>
@@ -17617,13 +17620,13 @@
     </row>
     <row r="326" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B326" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D326" t="s">
         <v>1349</v>
-      </c>
-      <c r="B326" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D326" t="s">
-        <v>1351</v>
       </c>
       <c r="E326" t="s">
         <v>178</v>
@@ -17632,10 +17635,10 @@
         <v>179</v>
       </c>
       <c r="J326" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="R326" t="s">
         <v>30</v>
@@ -17655,10 +17658,10 @@
     </row>
     <row r="327" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B327" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="D327" t="s">
         <v>694</v>
@@ -17670,10 +17673,10 @@
         <v>179</v>
       </c>
       <c r="J327" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="R327" t="s">
         <v>30</v>
@@ -17693,13 +17696,13 @@
     </row>
     <row r="328" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B328" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="D328" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="E328" t="s">
         <v>178</v>
@@ -17708,10 +17711,10 @@
         <v>179</v>
       </c>
       <c r="J328" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="R328" t="s">
         <v>30</v>
@@ -17731,10 +17734,10 @@
     </row>
     <row r="329" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B329" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="D329" t="s">
         <v>525</v>
@@ -17746,10 +17749,10 @@
         <v>179</v>
       </c>
       <c r="J329" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="R329" t="s">
         <v>30</v>
@@ -17772,10 +17775,10 @@
         <v>414</v>
       </c>
       <c r="B330" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="D330" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="E330" t="s">
         <v>81</v>
@@ -17784,10 +17787,10 @@
         <v>417</v>
       </c>
       <c r="J330" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="R330" t="s">
         <v>30</v>
@@ -17810,7 +17813,7 @@
         <v>414</v>
       </c>
       <c r="B331" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="D331" t="s">
         <v>536</v>
@@ -17822,10 +17825,10 @@
         <v>417</v>
       </c>
       <c r="J331" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="R331" t="s">
         <v>30</v>
@@ -17834,7 +17837,7 @@
         <v>31</v>
       </c>
       <c r="T331" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="U331" t="s">
         <v>110</v>
@@ -17848,10 +17851,10 @@
         <v>414</v>
       </c>
       <c r="B332" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="D332" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="E332" t="s">
         <v>81</v>
@@ -17860,19 +17863,19 @@
         <v>417</v>
       </c>
       <c r="J332" t="s">
+        <v>1366</v>
+      </c>
+      <c r="L332" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="R332" t="s">
+        <v>30</v>
+      </c>
+      <c r="S332" t="s">
+        <v>31</v>
+      </c>
+      <c r="T332" t="s">
         <v>1368</v>
-      </c>
-      <c r="L332" s="1" t="s">
-        <v>1369</v>
-      </c>
-      <c r="R332" t="s">
-        <v>30</v>
-      </c>
-      <c r="S332" t="s">
-        <v>31</v>
-      </c>
-      <c r="T332" t="s">
-        <v>1370</v>
       </c>
       <c r="U332" t="s">
         <v>804</v>
@@ -17886,10 +17889,10 @@
         <v>414</v>
       </c>
       <c r="B333" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="D333" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E333" t="s">
         <v>81</v>
@@ -17898,10 +17901,10 @@
         <v>417</v>
       </c>
       <c r="J333" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="L333" s="1" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="R333" t="s">
         <v>30</v>
@@ -17910,7 +17913,7 @@
         <v>31</v>
       </c>
       <c r="T333" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="U333" t="s">
         <v>644</v>
@@ -17921,13 +17924,13 @@
     </row>
     <row r="334" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B334" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D334" t="s">
         <v>1374</v>
-      </c>
-      <c r="B334" t="s">
-        <v>1375</v>
-      </c>
-      <c r="D334" t="s">
-        <v>1376</v>
       </c>
       <c r="E334" t="s">
         <v>145</v>
@@ -17936,19 +17939,19 @@
         <v>146</v>
       </c>
       <c r="J334" t="s">
+        <v>1375</v>
+      </c>
+      <c r="L334" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="R334" t="s">
+        <v>30</v>
+      </c>
+      <c r="S334" t="s">
+        <v>31</v>
+      </c>
+      <c r="T334" t="s">
         <v>1377</v>
-      </c>
-      <c r="L334" s="1" t="s">
-        <v>1378</v>
-      </c>
-      <c r="R334" t="s">
-        <v>30</v>
-      </c>
-      <c r="S334" t="s">
-        <v>31</v>
-      </c>
-      <c r="T334" t="s">
-        <v>1379</v>
       </c>
       <c r="U334" t="s">
         <v>100</v>
@@ -17959,10 +17962,10 @@
     </row>
     <row r="335" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="B335" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D335" t="s">
         <v>382</v>
@@ -17974,10 +17977,10 @@
         <v>179</v>
       </c>
       <c r="J335" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="R335" t="s">
         <v>30</v>
@@ -17989,7 +17992,7 @@
         <v>552</v>
       </c>
       <c r="U335" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="W335">
         <v>3</v>
@@ -17997,37 +18000,37 @@
     </row>
     <row r="336" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="B336" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D336">
         <v>1882</v>
       </c>
       <c r="E336" t="s">
+        <v>879</v>
+      </c>
+      <c r="F336" t="s">
         <v>880</v>
       </c>
-      <c r="F336" t="s">
-        <v>881</v>
-      </c>
       <c r="J336" t="s">
+        <v>1380</v>
+      </c>
+      <c r="L336" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="R336" t="s">
+        <v>30</v>
+      </c>
+      <c r="S336" t="s">
+        <v>31</v>
+      </c>
+      <c r="T336" t="s">
         <v>1382</v>
       </c>
-      <c r="L336" s="1" t="s">
+      <c r="U336" t="s">
         <v>1383</v>
-      </c>
-      <c r="R336" t="s">
-        <v>30</v>
-      </c>
-      <c r="S336" t="s">
-        <v>31</v>
-      </c>
-      <c r="T336" t="s">
-        <v>1384</v>
-      </c>
-      <c r="U336" t="s">
-        <v>1385</v>
       </c>
       <c r="W336">
         <v>3</v>
@@ -18035,26 +18038,26 @@
     </row>
     <row r="337" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="B337" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D337">
         <v>1882</v>
       </c>
       <c r="E337" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F337" t="s">
+        <v>1384</v>
+      </c>
+      <c r="J337" t="s">
+        <v>1385</v>
+      </c>
+      <c r="L337" s="1" t="s">
         <v>1386</v>
       </c>
-      <c r="J337" t="s">
-        <v>1387</v>
-      </c>
-      <c r="L337" s="1" t="s">
-        <v>1388</v>
-      </c>
       <c r="R337" t="s">
         <v>30</v>
       </c>
@@ -18062,10 +18065,10 @@
         <v>31</v>
       </c>
       <c r="T337" t="s">
+        <v>833</v>
+      </c>
+      <c r="U337" t="s">
         <v>834</v>
-      </c>
-      <c r="U337" t="s">
-        <v>835</v>
       </c>
       <c r="W337">
         <v>3</v>
@@ -18076,7 +18079,7 @@
         <v>365</v>
       </c>
       <c r="B338" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="D338" t="s">
         <v>55</v>
@@ -18088,10 +18091,10 @@
         <v>82</v>
       </c>
       <c r="J338" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="R338" t="s">
         <v>30</v>
@@ -18114,7 +18117,7 @@
         <v>365</v>
       </c>
       <c r="B339" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="D339" t="s">
         <v>225</v>
@@ -18126,10 +18129,10 @@
         <v>82</v>
       </c>
       <c r="J339" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="L339" s="1" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="R339" t="s">
         <v>30</v>
@@ -18152,22 +18155,22 @@
         <v>365</v>
       </c>
       <c r="B340" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="D340" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="E340" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="F340" t="s">
         <v>346</v>
       </c>
       <c r="J340" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="R340" t="s">
         <v>30</v>
@@ -18190,7 +18193,7 @@
         <v>365</v>
       </c>
       <c r="B341" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="D341">
         <v>1892</v>
@@ -18202,10 +18205,10 @@
         <v>82</v>
       </c>
       <c r="J341" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="R341" t="s">
         <v>30</v>
@@ -18225,10 +18228,10 @@
     </row>
     <row r="342" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B342" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D342" t="s">
         <v>296</v>
@@ -18240,19 +18243,19 @@
         <v>476</v>
       </c>
       <c r="J342" t="s">
+        <v>1400</v>
+      </c>
+      <c r="L342" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="R342" t="s">
+        <v>30</v>
+      </c>
+      <c r="S342" t="s">
+        <v>31</v>
+      </c>
+      <c r="T342" t="s">
         <v>1402</v>
-      </c>
-      <c r="L342" s="1" t="s">
-        <v>1403</v>
-      </c>
-      <c r="R342" t="s">
-        <v>30</v>
-      </c>
-      <c r="S342" t="s">
-        <v>31</v>
-      </c>
-      <c r="T342" t="s">
-        <v>1404</v>
       </c>
       <c r="U342" t="s">
         <v>265</v>
@@ -18263,10 +18266,10 @@
     </row>
     <row r="343" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B343" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D343" t="s">
         <v>724</v>
@@ -18278,10 +18281,10 @@
         <v>335</v>
       </c>
       <c r="J343" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="L343" s="1" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="R343" t="s">
         <v>30</v>
@@ -18301,26 +18304,26 @@
     </row>
     <row r="344" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B344" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D344" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E344" t="s">
         <v>178</v>
       </c>
       <c r="F344" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J344" t="s">
+        <v>1406</v>
+      </c>
+      <c r="L344" s="1" t="s">
         <v>1407</v>
       </c>
-      <c r="J344" t="s">
-        <v>1408</v>
-      </c>
-      <c r="L344" s="1" t="s">
-        <v>1409</v>
-      </c>
       <c r="R344" t="s">
         <v>30</v>
       </c>
@@ -18328,7 +18331,7 @@
         <v>31</v>
       </c>
       <c r="T344" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="U344" t="s">
         <v>67</v>
@@ -18339,25 +18342,25 @@
     </row>
     <row r="345" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B345" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D345" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E345" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F345" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J345" t="s">
         <v>1410</v>
       </c>
-      <c r="F345" t="s">
+      <c r="L345" s="1" t="s">
         <v>1411</v>
-      </c>
-      <c r="J345" t="s">
-        <v>1412</v>
-      </c>
-      <c r="L345" s="1" t="s">
-        <v>1413</v>
       </c>
       <c r="R345" t="s">
         <v>30</v>
@@ -18377,10 +18380,10 @@
     </row>
     <row r="346" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B346" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D346" t="s">
         <v>240</v>
@@ -18392,10 +18395,10 @@
         <v>82</v>
       </c>
       <c r="J346" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="L346" s="1" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="R346" t="s">
         <v>30</v>
@@ -18415,25 +18418,25 @@
     </row>
     <row r="347" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B347" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D347" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="E347" t="s">
         <v>72</v>
       </c>
       <c r="F347" t="s">
+        <v>1415</v>
+      </c>
+      <c r="J347" t="s">
+        <v>1416</v>
+      </c>
+      <c r="L347" s="1" t="s">
         <v>1417</v>
-      </c>
-      <c r="J347" t="s">
-        <v>1418</v>
-      </c>
-      <c r="L347" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="R347" t="s">
         <v>30</v>
@@ -18453,13 +18456,13 @@
     </row>
     <row r="348" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B348" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D348" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="E348" t="s">
         <v>145</v>
@@ -18468,10 +18471,10 @@
         <v>146</v>
       </c>
       <c r="J348" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="L348" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="R348" t="s">
         <v>30</v>
@@ -18491,10 +18494,10 @@
     </row>
     <row r="349" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B349" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D349">
         <v>1890</v>
@@ -18503,13 +18506,13 @@
         <v>145</v>
       </c>
       <c r="F349" t="s">
+        <v>1421</v>
+      </c>
+      <c r="J349" t="s">
+        <v>1422</v>
+      </c>
+      <c r="L349" s="1" t="s">
         <v>1423</v>
-      </c>
-      <c r="J349" t="s">
-        <v>1424</v>
-      </c>
-      <c r="L349" s="1" t="s">
-        <v>1425</v>
       </c>
       <c r="R349" t="s">
         <v>30</v>
@@ -18532,7 +18535,7 @@
         <v>365</v>
       </c>
       <c r="B350" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="D350" t="s">
         <v>785</v>
@@ -18541,13 +18544,13 @@
         <v>145</v>
       </c>
       <c r="F350" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="J350" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="L350" s="1" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="R350" t="s">
         <v>30</v>
@@ -18570,22 +18573,22 @@
         <v>365</v>
       </c>
       <c r="B351" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="D351" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E351" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F351" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J351" t="s">
         <v>1429</v>
       </c>
-      <c r="F351" t="s">
+      <c r="L351" s="1" t="s">
         <v>1430</v>
-      </c>
-      <c r="J351" t="s">
-        <v>1431</v>
-      </c>
-      <c r="L351" s="1" t="s">
-        <v>1432</v>
       </c>
       <c r="R351" t="s">
         <v>30</v>
@@ -18608,7 +18611,7 @@
         <v>365</v>
       </c>
       <c r="B352" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="D352">
         <v>1892</v>
@@ -18620,10 +18623,10 @@
         <v>82</v>
       </c>
       <c r="J352" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="L352" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="R352" t="s">
         <v>30</v>
@@ -18646,7 +18649,7 @@
         <v>365</v>
       </c>
       <c r="B353" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="D353">
         <v>1895</v>
@@ -18658,10 +18661,10 @@
         <v>82</v>
       </c>
       <c r="J353" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="L353" s="1" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="R353" t="s">
         <v>30</v>
@@ -18681,10 +18684,10 @@
     </row>
     <row r="354" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B354" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D354" t="s">
         <v>321</v>
@@ -18696,10 +18699,10 @@
         <v>82</v>
       </c>
       <c r="J354" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="L354" s="1" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="R354" t="s">
         <v>30</v>
@@ -18719,25 +18722,25 @@
     </row>
     <row r="355" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B355" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D355" t="s">
         <v>325</v>
       </c>
       <c r="E355" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="F355" t="s">
         <v>346</v>
       </c>
       <c r="J355" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="L355" s="1" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="R355" t="s">
         <v>30</v>
@@ -18757,10 +18760,10 @@
     </row>
     <row r="356" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B356" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D356" t="s">
         <v>325</v>
@@ -18772,10 +18775,10 @@
         <v>146</v>
       </c>
       <c r="J356" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="L356" s="1" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="R356" t="s">
         <v>30</v>
@@ -18795,10 +18798,10 @@
     </row>
     <row r="357" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B357" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D357" t="s">
         <v>325</v>
@@ -18810,10 +18813,10 @@
         <v>82</v>
       </c>
       <c r="J357" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="L357" s="1" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="R357" t="s">
         <v>30</v>
@@ -18833,10 +18836,10 @@
     </row>
     <row r="358" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B358" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D358" t="s">
         <v>785</v>
@@ -18848,10 +18851,10 @@
         <v>82</v>
       </c>
       <c r="J358" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="L358" s="1" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="R358" t="s">
         <v>30</v>
@@ -18871,10 +18874,10 @@
     </row>
     <row r="359" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B359" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D359">
         <v>1872</v>
@@ -18886,10 +18889,10 @@
         <v>146</v>
       </c>
       <c r="J359" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="L359" s="1" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="R359" t="s">
         <v>30</v>
@@ -18909,10 +18912,10 @@
     </row>
     <row r="360" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B360" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D360">
         <v>1870</v>
@@ -18924,10 +18927,10 @@
         <v>82</v>
       </c>
       <c r="J360" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="L360" s="1" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="R360" t="s">
         <v>30</v>
@@ -18947,10 +18950,10 @@
     </row>
     <row r="361" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B361" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D361">
         <v>1873</v>
@@ -18962,10 +18965,10 @@
         <v>82</v>
       </c>
       <c r="J361" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="L361" s="1" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="R361" t="s">
         <v>30</v>
@@ -18988,7 +18991,7 @@
         <v>813</v>
       </c>
       <c r="B362" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="D362" t="s">
         <v>694</v>
@@ -19000,10 +19003,10 @@
         <v>179</v>
       </c>
       <c r="J362" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="L362" s="1" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="R362" t="s">
         <v>30</v>
@@ -19026,22 +19029,22 @@
         <v>813</v>
       </c>
       <c r="B363" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="D363" t="s">
         <v>334</v>
       </c>
       <c r="E363" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F363" t="s">
+        <v>1457</v>
+      </c>
+      <c r="J363" t="s">
         <v>1458</v>
       </c>
-      <c r="F363" t="s">
+      <c r="L363" s="1" t="s">
         <v>1459</v>
-      </c>
-      <c r="J363" t="s">
-        <v>1460</v>
-      </c>
-      <c r="L363" s="1" t="s">
-        <v>1461</v>
       </c>
       <c r="R363" t="s">
         <v>30</v>
@@ -19064,7 +19067,7 @@
         <v>813</v>
       </c>
       <c r="B364" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="D364">
         <v>1873</v>
@@ -19073,13 +19076,13 @@
         <v>178</v>
       </c>
       <c r="F364" t="s">
+        <v>1460</v>
+      </c>
+      <c r="J364" t="s">
+        <v>1461</v>
+      </c>
+      <c r="L364" s="1" t="s">
         <v>1462</v>
-      </c>
-      <c r="J364" t="s">
-        <v>1463</v>
-      </c>
-      <c r="L364" s="1" t="s">
-        <v>1464</v>
       </c>
       <c r="R364" t="s">
         <v>30</v>
@@ -19091,7 +19094,7 @@
         <v>106</v>
       </c>
       <c r="U364" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="W364">
         <v>2</v>
@@ -19102,7 +19105,7 @@
         <v>813</v>
       </c>
       <c r="B365" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="D365">
         <v>1876</v>
@@ -19114,10 +19117,10 @@
         <v>179</v>
       </c>
       <c r="J365" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="L365" s="1" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="R365" t="s">
         <v>30</v>
@@ -19137,10 +19140,10 @@
     </row>
     <row r="366" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B366" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="D366" t="s">
         <v>742</v>
@@ -19152,10 +19155,10 @@
         <v>476</v>
       </c>
       <c r="J366" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="L366" s="1" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="R366" t="s">
         <v>30</v>
@@ -19167,7 +19170,7 @@
         <v>59</v>
       </c>
       <c r="U366" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="W366">
         <v>2</v>
@@ -19175,13 +19178,13 @@
     </row>
     <row r="367" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B367" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="D367" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="E367" t="s">
         <v>178</v>
@@ -19190,10 +19193,10 @@
         <v>476</v>
       </c>
       <c r="J367" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="L367" s="1" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="R367" t="s">
         <v>30</v>
@@ -19213,10 +19216,10 @@
     </row>
     <row r="368" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B368" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="D368">
         <v>1837</v>
@@ -19228,10 +19231,10 @@
         <v>179</v>
       </c>
       <c r="J368" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="L368" s="1" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="R368" t="s">
         <v>30</v>
@@ -19251,25 +19254,25 @@
     </row>
     <row r="369" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B369" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="D369" t="s">
         <v>768</v>
       </c>
       <c r="E369" t="s">
+        <v>879</v>
+      </c>
+      <c r="F369" t="s">
         <v>880</v>
       </c>
-      <c r="F369" t="s">
-        <v>881</v>
-      </c>
       <c r="J369" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="L369" s="1" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="R369" t="s">
         <v>30</v>
@@ -19281,7 +19284,7 @@
         <v>156</v>
       </c>
       <c r="U369" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="W369">
         <v>2</v>
@@ -19289,10 +19292,10 @@
     </row>
     <row r="370" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B370" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="D370" t="s">
         <v>458</v>
@@ -19304,10 +19307,10 @@
         <v>179</v>
       </c>
       <c r="J370" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="L370" s="1" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="R370" t="s">
         <v>30</v>
@@ -19327,10 +19330,10 @@
     </row>
     <row r="371" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B371" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="D371" t="s">
         <v>416</v>
@@ -19342,10 +19345,10 @@
         <v>476</v>
       </c>
       <c r="J371" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="L371" s="1" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="R371" t="s">
         <v>30</v>
@@ -19365,10 +19368,10 @@
     </row>
     <row r="372" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B372" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="D372">
         <v>1815</v>
@@ -19380,10 +19383,10 @@
         <v>476</v>
       </c>
       <c r="J372" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="L372" s="1" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="R372" t="s">
         <v>30</v>
@@ -19403,10 +19406,10 @@
     </row>
     <row r="373" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B373" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="D373">
         <v>1817</v>
@@ -19418,10 +19421,10 @@
         <v>476</v>
       </c>
       <c r="J373" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="L373" s="1" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="R373" t="s">
         <v>30</v>
@@ -19441,31 +19444,31 @@
     </row>
     <row r="374" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B374" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D374" t="s">
         <v>654</v>
       </c>
       <c r="E374" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F374" t="s">
+        <v>1488</v>
+      </c>
+      <c r="J374" t="s">
         <v>1489</v>
       </c>
-      <c r="F374" t="s">
+      <c r="L374" s="1" t="s">
         <v>1490</v>
       </c>
-      <c r="J374" t="s">
+      <c r="R374" t="s">
+        <v>30</v>
+      </c>
+      <c r="S374" t="s">
         <v>1491</v>
-      </c>
-      <c r="L374" s="1" t="s">
-        <v>1492</v>
-      </c>
-      <c r="R374" t="s">
-        <v>30</v>
-      </c>
-      <c r="S374" t="s">
-        <v>1493</v>
       </c>
       <c r="T374" t="s">
         <v>110</v>
@@ -19479,13 +19482,13 @@
     </row>
     <row r="375" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B375" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D375" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E375" t="s">
         <v>81</v>
@@ -19494,16 +19497,16 @@
         <v>82</v>
       </c>
       <c r="J375" t="s">
+        <v>1492</v>
+      </c>
+      <c r="L375" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="R375" t="s">
+        <v>30</v>
+      </c>
+      <c r="S375" t="s">
         <v>1494</v>
-      </c>
-      <c r="L375" s="1" t="s">
-        <v>1495</v>
-      </c>
-      <c r="R375" t="s">
-        <v>30</v>
-      </c>
-      <c r="S375" t="s">
-        <v>1496</v>
       </c>
       <c r="T375" t="s">
         <v>398</v>
@@ -19517,25 +19520,25 @@
     </row>
     <row r="376" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B376" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D376">
         <v>1893</v>
       </c>
       <c r="E376" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F376" t="s">
+        <v>1496</v>
+      </c>
+      <c r="J376" t="s">
         <v>1497</v>
       </c>
-      <c r="F376" t="s">
+      <c r="L376" s="1" t="s">
         <v>1498</v>
-      </c>
-      <c r="J376" t="s">
-        <v>1499</v>
-      </c>
-      <c r="L376" s="1" t="s">
-        <v>1500</v>
       </c>
       <c r="R376" t="s">
         <v>30</v>
@@ -19555,10 +19558,10 @@
     </row>
     <row r="377" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B377" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D377" t="s">
         <v>382</v>
@@ -19567,13 +19570,13 @@
         <v>131</v>
       </c>
       <c r="F377" t="s">
+        <v>1501</v>
+      </c>
+      <c r="J377" t="s">
+        <v>1502</v>
+      </c>
+      <c r="L377" s="1" t="s">
         <v>1503</v>
-      </c>
-      <c r="J377" t="s">
-        <v>1504</v>
-      </c>
-      <c r="L377" s="1" t="s">
-        <v>1505</v>
       </c>
       <c r="R377" t="s">
         <v>30</v>
@@ -19593,10 +19596,10 @@
     </row>
     <row r="378" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B378" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D378" t="s">
         <v>55</v>
@@ -19605,13 +19608,13 @@
         <v>131</v>
       </c>
       <c r="F378" t="s">
+        <v>1504</v>
+      </c>
+      <c r="J378" t="s">
+        <v>1505</v>
+      </c>
+      <c r="L378" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="J378" t="s">
-        <v>1507</v>
-      </c>
-      <c r="L378" s="1" t="s">
-        <v>1508</v>
       </c>
       <c r="R378" t="s">
         <v>30</v>
@@ -19631,10 +19634,10 @@
     </row>
     <row r="379" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B379" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D379" t="s">
         <v>55</v>
@@ -19646,10 +19649,10 @@
         <v>476</v>
       </c>
       <c r="J379" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="L379" s="1" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="R379" t="s">
         <v>30</v>
@@ -19669,25 +19672,25 @@
     </row>
     <row r="380" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B380" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D380" t="s">
         <v>55</v>
       </c>
       <c r="E380" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F380" t="s">
+        <v>1510</v>
+      </c>
+      <c r="J380" t="s">
         <v>1511</v>
       </c>
-      <c r="F380" t="s">
+      <c r="L380" s="1" t="s">
         <v>1512</v>
-      </c>
-      <c r="J380" t="s">
-        <v>1513</v>
-      </c>
-      <c r="L380" s="1" t="s">
-        <v>1514</v>
       </c>
       <c r="R380" t="s">
         <v>30</v>
@@ -19707,10 +19710,10 @@
     </row>
     <row r="381" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B381" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D381" t="s">
         <v>225</v>
@@ -19719,13 +19722,13 @@
         <v>145</v>
       </c>
       <c r="F381" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="J381" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="L381" s="1" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="R381" t="s">
         <v>30</v>
@@ -19745,10 +19748,10 @@
     </row>
     <row r="382" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B382" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D382" t="s">
         <v>225</v>
@@ -19760,10 +19763,10 @@
         <v>386</v>
       </c>
       <c r="J382" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="L382" s="1" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="R382" t="s">
         <v>30</v>
@@ -19783,10 +19786,10 @@
     </row>
     <row r="383" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B383" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D383" t="s">
         <v>225</v>
@@ -19795,13 +19798,13 @@
         <v>62</v>
       </c>
       <c r="F383" t="s">
-        <v>63</v>
+        <v>1611</v>
       </c>
       <c r="J383" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="L383" s="1" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="R383" t="s">
         <v>30</v>
@@ -19821,10 +19824,10 @@
     </row>
     <row r="384" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B384" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D384" t="s">
         <v>785</v>
@@ -19833,13 +19836,13 @@
         <v>131</v>
       </c>
       <c r="F384" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="J384" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="L384" s="1" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="R384" t="s">
         <v>30</v>
@@ -19851,7 +19854,7 @@
         <v>518</v>
       </c>
       <c r="U384" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="W384">
         <v>1</v>
@@ -19859,10 +19862,10 @@
     </row>
     <row r="385" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B385" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D385" t="s">
         <v>785</v>
@@ -19874,10 +19877,10 @@
         <v>82</v>
       </c>
       <c r="J385" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="L385" s="1" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="R385" t="s">
         <v>30</v>
@@ -19886,7 +19889,7 @@
         <v>31</v>
       </c>
       <c r="T385" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="U385" t="s">
         <v>130</v>
@@ -19897,10 +19900,10 @@
     </row>
     <row r="386" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B386" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D386" t="s">
         <v>240</v>
@@ -19912,10 +19915,10 @@
         <v>82</v>
       </c>
       <c r="J386" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="L386" s="1" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="R386" t="s">
         <v>30</v>
@@ -19935,10 +19938,10 @@
     </row>
     <row r="387" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B387" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D387">
         <v>1890</v>
@@ -19947,13 +19950,13 @@
         <v>131</v>
       </c>
       <c r="F387" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="J387" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="L387" s="1" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="R387" t="s">
         <v>30</v>
@@ -19973,13 +19976,13 @@
     </row>
     <row r="388" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B388" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D388" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E388" t="s">
         <v>81</v>
@@ -19988,10 +19991,10 @@
         <v>82</v>
       </c>
       <c r="J388" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="L388" s="1" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="R388" t="s">
         <v>30</v>
@@ -20011,10 +20014,10 @@
     </row>
     <row r="389" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="B389" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="D389" t="s">
         <v>61</v>
@@ -20026,22 +20029,22 @@
         <v>82</v>
       </c>
       <c r="J389" t="s">
+        <v>1531</v>
+      </c>
+      <c r="L389" s="1" t="s">
+        <v>1532</v>
+      </c>
+      <c r="R389" t="s">
+        <v>30</v>
+      </c>
+      <c r="S389" t="s">
+        <v>31</v>
+      </c>
+      <c r="T389" t="s">
         <v>1533</v>
       </c>
-      <c r="L389" s="1" t="s">
-        <v>1534</v>
-      </c>
-      <c r="R389" t="s">
-        <v>30</v>
-      </c>
-      <c r="S389" t="s">
-        <v>31</v>
-      </c>
-      <c r="T389" t="s">
-        <v>1535</v>
-      </c>
       <c r="U389" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="W389">
         <v>3</v>
@@ -20049,13 +20052,13 @@
     </row>
     <row r="390" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="B390" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="D390" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E390" t="s">
         <v>81</v>
@@ -20064,10 +20067,10 @@
         <v>82</v>
       </c>
       <c r="J390" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="L390" s="1" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="R390" t="s">
         <v>30</v>
@@ -20076,7 +20079,7 @@
         <v>31</v>
       </c>
       <c r="T390" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="U390" t="s">
         <v>91</v>
@@ -20087,25 +20090,25 @@
     </row>
     <row r="391" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="B391" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="D391">
         <v>1890</v>
       </c>
       <c r="E391" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="F391" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J391" t="s">
+        <v>1537</v>
+      </c>
+      <c r="L391" s="1" t="s">
         <v>1538</v>
-      </c>
-      <c r="J391" t="s">
-        <v>1539</v>
-      </c>
-      <c r="L391" s="1" t="s">
-        <v>1540</v>
       </c>
       <c r="R391" t="s">
         <v>30</v>
@@ -20125,10 +20128,10 @@
     </row>
     <row r="392" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="B392" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="D392">
         <v>1892</v>
@@ -20137,13 +20140,13 @@
         <v>178</v>
       </c>
       <c r="F392" t="s">
+        <v>1539</v>
+      </c>
+      <c r="J392" t="s">
+        <v>1540</v>
+      </c>
+      <c r="L392" s="1" t="s">
         <v>1541</v>
-      </c>
-      <c r="J392" t="s">
-        <v>1542</v>
-      </c>
-      <c r="L392" s="1" t="s">
-        <v>1543</v>
       </c>
       <c r="R392" t="s">
         <v>30</v>
@@ -20163,10 +20166,10 @@
     </row>
     <row r="393" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="B393" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="D393" t="s">
         <v>785</v>
@@ -20178,10 +20181,10 @@
         <v>36</v>
       </c>
       <c r="J393" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="L393" s="1" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="R393" t="s">
         <v>30</v>
@@ -20193,7 +20196,7 @@
         <v>285</v>
       </c>
       <c r="U393" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="W393">
         <v>3</v>
@@ -20201,13 +20204,13 @@
     </row>
     <row r="394" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="B394" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="D394" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="E394" t="s">
         <v>26</v>
@@ -20216,22 +20219,22 @@
         <v>41</v>
       </c>
       <c r="J394" t="s">
+        <v>1548</v>
+      </c>
+      <c r="L394" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="R394" t="s">
+        <v>30</v>
+      </c>
+      <c r="S394" t="s">
+        <v>31</v>
+      </c>
+      <c r="T394" t="s">
         <v>1550</v>
       </c>
-      <c r="L394" s="1" t="s">
+      <c r="U394" t="s">
         <v>1551</v>
-      </c>
-      <c r="R394" t="s">
-        <v>30</v>
-      </c>
-      <c r="S394" t="s">
-        <v>31</v>
-      </c>
-      <c r="T394" t="s">
-        <v>1552</v>
-      </c>
-      <c r="U394" t="s">
-        <v>1553</v>
       </c>
       <c r="W394">
         <v>3</v>
@@ -20239,10 +20242,10 @@
     </row>
     <row r="395" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="B395" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="D395">
         <v>1895</v>
@@ -20254,10 +20257,10 @@
         <v>36</v>
       </c>
       <c r="J395" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="L395" s="1" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="R395" t="s">
         <v>30</v>
@@ -20269,7 +20272,7 @@
         <v>300</v>
       </c>
       <c r="U395" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="W395">
         <v>3</v>
@@ -20277,10 +20280,10 @@
     </row>
     <row r="396" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="B396" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="D396">
         <v>1899</v>
@@ -20292,22 +20295,22 @@
         <v>36</v>
       </c>
       <c r="J396" t="s">
+        <v>1554</v>
+      </c>
+      <c r="L396" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="R396" t="s">
+        <v>30</v>
+      </c>
+      <c r="S396" t="s">
+        <v>31</v>
+      </c>
+      <c r="T396" t="s">
         <v>1556</v>
       </c>
-      <c r="L396" s="1" t="s">
-        <v>1557</v>
-      </c>
-      <c r="R396" t="s">
-        <v>30</v>
-      </c>
-      <c r="S396" t="s">
-        <v>31</v>
-      </c>
-      <c r="T396" t="s">
-        <v>1558</v>
-      </c>
       <c r="U396" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="W396">
         <v>3</v>
@@ -20315,10 +20318,10 @@
     </row>
     <row r="397" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B397" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="D397" t="s">
         <v>654</v>
@@ -20327,13 +20330,13 @@
         <v>145</v>
       </c>
       <c r="F397" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="J397" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="L397" s="1" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="R397" t="s">
         <v>30</v>
@@ -20342,7 +20345,7 @@
         <v>657</v>
       </c>
       <c r="T397" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="U397" t="s">
         <v>378</v>
@@ -20353,10 +20356,10 @@
     </row>
     <row r="398" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B398" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="D398" t="s">
         <v>201</v>
@@ -20365,13 +20368,13 @@
         <v>145</v>
       </c>
       <c r="F398" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="J398" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="L398" s="1" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="R398" t="s">
         <v>30</v>
@@ -20383,7 +20386,7 @@
         <v>378</v>
       </c>
       <c r="U398" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="W398">
         <v>2</v>
@@ -20391,10 +20394,10 @@
     </row>
     <row r="399" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B399" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="D399" t="s">
         <v>61</v>
@@ -20406,10 +20409,10 @@
         <v>82</v>
       </c>
       <c r="J399" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="L399" s="1" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="R399" t="s">
         <v>30</v>
@@ -20418,7 +20421,7 @@
         <v>667</v>
       </c>
       <c r="T399" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="U399" t="s">
         <v>122</v>
@@ -20429,10 +20432,10 @@
     </row>
     <row r="400" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B400" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="D400" t="s">
         <v>61</v>
@@ -20444,10 +20447,10 @@
         <v>82</v>
       </c>
       <c r="J400" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L400" s="1" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="R400" t="s">
         <v>30</v>
@@ -20467,10 +20470,10 @@
     </row>
     <row r="401" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B401" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="D401" t="s">
         <v>61</v>
@@ -20482,10 +20485,10 @@
         <v>82</v>
       </c>
       <c r="J401" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="L401" s="1" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="R401" t="s">
         <v>30</v>
@@ -20494,7 +20497,7 @@
         <v>667</v>
       </c>
       <c r="T401" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="U401" t="s">
         <v>76</v>
@@ -20505,10 +20508,10 @@
     </row>
     <row r="402" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B402" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="D402">
         <v>1891</v>
@@ -20520,10 +20523,10 @@
         <v>82</v>
       </c>
       <c r="J402" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="L402" s="1" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="R402" t="s">
         <v>30</v>
@@ -20543,10 +20546,10 @@
     </row>
     <row r="403" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B403" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="D403">
         <v>1890</v>
@@ -20558,10 +20561,10 @@
         <v>82</v>
       </c>
       <c r="J403" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="L403" s="1" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="R403" t="s">
         <v>30</v>
@@ -20573,7 +20576,7 @@
         <v>428</v>
       </c>
       <c r="U403" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="W403">
         <v>2</v>
@@ -20581,10 +20584,10 @@
     </row>
     <row r="404" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B404" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="D404">
         <v>1895</v>
@@ -20593,25 +20596,25 @@
         <v>145</v>
       </c>
       <c r="F404" t="s">
+        <v>1574</v>
+      </c>
+      <c r="J404" t="s">
+        <v>1575</v>
+      </c>
+      <c r="L404" s="1" t="s">
         <v>1576</v>
       </c>
-      <c r="J404" t="s">
+      <c r="R404" t="s">
+        <v>30</v>
+      </c>
+      <c r="S404" t="s">
         <v>1577</v>
       </c>
-      <c r="L404" s="1" t="s">
+      <c r="T404" t="s">
         <v>1578</v>
       </c>
-      <c r="R404" t="s">
-        <v>30</v>
-      </c>
-      <c r="S404" t="s">
+      <c r="U404" t="s">
         <v>1579</v>
-      </c>
-      <c r="T404" t="s">
-        <v>1580</v>
-      </c>
-      <c r="U404" t="s">
-        <v>1581</v>
       </c>
       <c r="W404">
         <v>2</v>
@@ -20619,10 +20622,10 @@
     </row>
     <row r="405" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B405" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="D405" t="s">
         <v>55</v>
@@ -20634,19 +20637,19 @@
         <v>179</v>
       </c>
       <c r="J405" t="s">
+        <v>1582</v>
+      </c>
+      <c r="L405" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="R405" t="s">
+        <v>30</v>
+      </c>
+      <c r="S405" t="s">
+        <v>31</v>
+      </c>
+      <c r="T405" t="s">
         <v>1584</v>
-      </c>
-      <c r="L405" s="1" t="s">
-        <v>1585</v>
-      </c>
-      <c r="R405" t="s">
-        <v>30</v>
-      </c>
-      <c r="S405" t="s">
-        <v>31</v>
-      </c>
-      <c r="T405" t="s">
-        <v>1586</v>
       </c>
       <c r="U405" t="s">
         <v>558</v>
@@ -20657,25 +20660,25 @@
     </row>
     <row r="406" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B406" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="D406" t="s">
         <v>668</v>
       </c>
       <c r="E406" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F406" t="s">
+        <v>1586</v>
+      </c>
+      <c r="J406" t="s">
         <v>1587</v>
       </c>
-      <c r="F406" t="s">
+      <c r="L406" s="1" t="s">
         <v>1588</v>
-      </c>
-      <c r="J406" t="s">
-        <v>1589</v>
-      </c>
-      <c r="L406" s="1" t="s">
-        <v>1590</v>
       </c>
       <c r="R406" t="s">
         <v>30</v>
@@ -20695,10 +20698,10 @@
     </row>
     <row r="407" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B407" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="D407">
         <v>1894</v>
@@ -20707,10 +20710,10 @@
         <v>56</v>
       </c>
       <c r="J407" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="L407" s="1" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="R407" t="s">
         <v>30</v>
@@ -20719,7 +20722,7 @@
         <v>31</v>
       </c>
       <c r="T407" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="U407" t="s">
         <v>130</v>
@@ -20730,10 +20733,10 @@
     </row>
     <row r="408" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B408" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="D408">
         <v>1895</v>
@@ -20742,10 +20745,10 @@
         <v>56</v>
       </c>
       <c r="J408" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="L408" s="1" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="R408" t="s">
         <v>30</v>
@@ -20754,10 +20757,10 @@
         <v>31</v>
       </c>
       <c r="T408" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="U408" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="W408">
         <v>3</v>
@@ -20765,13 +20768,13 @@
     </row>
     <row r="409" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B409" t="s">
+        <v>1593</v>
+      </c>
+      <c r="D409" t="s">
         <v>1594</v>
-      </c>
-      <c r="B409" t="s">
-        <v>1595</v>
-      </c>
-      <c r="D409" t="s">
-        <v>1596</v>
       </c>
       <c r="E409" t="s">
         <v>112</v>
@@ -20780,10 +20783,10 @@
         <v>113</v>
       </c>
       <c r="J409" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="L409" s="1" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="R409" t="s">
         <v>30</v>
@@ -20803,13 +20806,13 @@
     </row>
     <row r="410" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="B410" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="D410" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E410" t="s">
         <v>81</v>
@@ -20818,10 +20821,10 @@
         <v>82</v>
       </c>
       <c r="J410" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="L410" s="1" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="R410" t="s">
         <v>30</v>
@@ -20841,10 +20844,10 @@
     </row>
     <row r="411" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="B411" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="D411">
         <v>1875</v>
@@ -20853,19 +20856,19 @@
         <v>447</v>
       </c>
       <c r="F411" t="s">
+        <v>1599</v>
+      </c>
+      <c r="J411" t="s">
+        <v>1600</v>
+      </c>
+      <c r="L411" s="1" t="s">
         <v>1601</v>
       </c>
-      <c r="J411" t="s">
-        <v>1602</v>
-      </c>
-      <c r="L411" s="1" t="s">
-        <v>1603</v>
-      </c>
       <c r="R411" t="s">
         <v>30</v>
       </c>
       <c r="S411" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="T411" t="s">
         <v>116</v>
@@ -20879,25 +20882,25 @@
     </row>
     <row r="412" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="B412" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="D412" t="s">
+        <v>1602</v>
+      </c>
+      <c r="E412" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F412" t="s">
         <v>1604</v>
       </c>
-      <c r="E412" t="s">
+      <c r="J412" t="s">
         <v>1605</v>
       </c>
-      <c r="F412" t="s">
+      <c r="L412" s="1" t="s">
         <v>1606</v>
-      </c>
-      <c r="J412" t="s">
-        <v>1607</v>
-      </c>
-      <c r="L412" s="1" t="s">
-        <v>1608</v>
       </c>
       <c r="R412" t="s">
         <v>30</v>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -25517,286 +25517,294 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/10/Henri_de_Toulouse-Lautrec_-_At_the_Moulin_Rouge_-_1928.610_-_Art_Institute_of_Chicago.jpg/1280px-Henri_de_Toulouse-Lautrec_-_At_the_Moulin_Rouge_-_1928.610_-_Art_Institute_of_Chicago.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/%28Albi%29_Femme_qui_tire_son_bas_1894_-_Toulouse-Lautrec_-_Mus%C3%A9e_Toulouse-Lautrec_MTL.177.jpg/960px-%28Albi%29_Femme_qui_tire_son_bas_1894_-_Toulouse-Lautrec_-_Mus%C3%A9e_Toulouse-Lautrec_MTL.177.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L189" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L190" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L191" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L197" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L208" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L209" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L210" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L212" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L214" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L215" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L216" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L217" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L218" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L219" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L220" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L221" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L222" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L223" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L224" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L225" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L226" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L227" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L228" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L229" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L230" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L232" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L233" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L234" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L236" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L238" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L242" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L243" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L244" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L245" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L246" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L247" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L248" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L249" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L250" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L251" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L252" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L253" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L254" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L255" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L256" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L257" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L258" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L259" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L260" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L261" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L262" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L263" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L264" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L265" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L266" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L267" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L268" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L269" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L270" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L271" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L272" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L273" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L274" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L275" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L276" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L277" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L278" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L279" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L280" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L281" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L282" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L283" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L284" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L285" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L286" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L287" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L288" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L289" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L290" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L291" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L292" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L293" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L294" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L295" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L296" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L297" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L298" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L299" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L300" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L301" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L302" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L303" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L304" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L305" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L306" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L307" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L308" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L309" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L310" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L311" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L312" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L313" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L314" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L315" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L316" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L317" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L318" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L319" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L320" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L321" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L322" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L323" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L324" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L325" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L326" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L327" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L328" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L329" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L330" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L331" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L332" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L333" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L334" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L335" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L336" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L337" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L338" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L339" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L340" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L341" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L342" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L343" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L344" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L345" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L346" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L347" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L348" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L349" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L350" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L351" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L352" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L353" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L354" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L355" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L356" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L357" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L358" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L359" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L360" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L361" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L362" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L363" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L364" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L365" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L366" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L367" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L368" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L369" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L370" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L371" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L372" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L373" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L374" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L375" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L376" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L377" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L378" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L379" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L380" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L381" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L382" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L383" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L384" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L385" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L386" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L387" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L388" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L389" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L390" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L391" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L392" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L393" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L394" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L395" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L396" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L397" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L398" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L399" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L400" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L401" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L402" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L403" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L404" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L405" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L406" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L407" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L408" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L409" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L410" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L411" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L412" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L418" r:id="rId417"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F40DB02-9B7E-4D21-A153-DEF291805397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632C4F91-3152-492C-BC91-0DD1602CE6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3646,9 +3646,6 @@
     <t>"Le Cri"</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Edvard%20Munch%20-%20The%20Scream%20-%20Google%20Art%20Project.jpg?width=1200</t>
-  </si>
-  <si>
     <t>Huile, tempera et pastel sur carton</t>
   </si>
   <si>
@@ -4808,6 +4805,9 @@
   </si>
   <si>
     <t>1892-1893</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/Edvard_Munch_-_The_Scream.jpg/960px-Edvard_Munch_-_The_Scream.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
   </si>
 </sst>
 </file>
@@ -5490,7 +5490,7 @@
         <v>31</v>
       </c>
       <c r="T7" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="U7" t="s">
         <v>66</v>
@@ -5870,10 +5870,10 @@
         <v>31</v>
       </c>
       <c r="T17" t="s">
+        <v>1563</v>
+      </c>
+      <c r="U17" t="s">
         <v>1564</v>
-      </c>
-      <c r="U17" t="s">
-        <v>1565</v>
       </c>
       <c r="W17">
         <v>2</v>
@@ -6101,7 +6101,7 @@
         <v>109</v>
       </c>
       <c r="U23" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="W23">
         <v>3</v>
@@ -7136,10 +7136,10 @@
         <v>31</v>
       </c>
       <c r="T50" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="U50" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="W50">
         <v>3</v>
@@ -7799,10 +7799,10 @@
         <v>330</v>
       </c>
       <c r="E68" t="s">
+        <v>1566</v>
+      </c>
+      <c r="F68" t="s">
         <v>1567</v>
-      </c>
-      <c r="F68" t="s">
-        <v>1568</v>
       </c>
       <c r="J68" t="s">
         <v>370</v>
@@ -7872,7 +7872,7 @@
         <v>362</v>
       </c>
       <c r="D70" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="E70" t="s">
         <v>79</v>
@@ -8024,7 +8024,7 @@
         <v>362</v>
       </c>
       <c r="D74" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="E74" t="s">
         <v>144</v>
@@ -8162,7 +8162,7 @@
         <v>155</v>
       </c>
       <c r="U77" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="W77">
         <v>1</v>
@@ -8390,7 +8390,7 @@
         <v>535</v>
       </c>
       <c r="U83" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="W83">
         <v>3</v>
@@ -8428,7 +8428,7 @@
         <v>244</v>
       </c>
       <c r="U84" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="W84">
         <v>3</v>
@@ -9173,7 +9173,7 @@
         <v>55</v>
       </c>
       <c r="F104" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="J104" t="s">
         <v>517</v>
@@ -9708,7 +9708,7 @@
         <v>567</v>
       </c>
       <c r="F118" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="J118" t="s">
         <v>568</v>
@@ -10030,7 +10030,7 @@
         <v>603</v>
       </c>
       <c r="U126" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="W126">
         <v>1</v>
@@ -10766,7 +10766,7 @@
         <v>683</v>
       </c>
       <c r="D146" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="E146" t="s">
         <v>79</v>
@@ -10787,7 +10787,7 @@
         <v>31</v>
       </c>
       <c r="T146" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="U146" t="s">
         <v>686</v>
@@ -11246,7 +11246,7 @@
         <v>732</v>
       </c>
       <c r="U158" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="W158">
         <v>1</v>
@@ -11433,10 +11433,10 @@
         <v>31</v>
       </c>
       <c r="T163" t="s">
+        <v>1577</v>
+      </c>
+      <c r="U163" t="s">
         <v>1578</v>
-      </c>
-      <c r="U163" t="s">
-        <v>1579</v>
       </c>
       <c r="W163">
         <v>1</v>
@@ -11588,7 +11588,7 @@
         <v>767</v>
       </c>
       <c r="U167" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="W167">
         <v>1</v>
@@ -11626,7 +11626,7 @@
         <v>770</v>
       </c>
       <c r="U168" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="W168">
         <v>1</v>
@@ -11778,10 +11778,10 @@
         <v>31</v>
       </c>
       <c r="T172" t="s">
+        <v>1581</v>
+      </c>
+      <c r="U172" t="s">
         <v>1582</v>
-      </c>
-      <c r="U172" t="s">
-        <v>1583</v>
       </c>
       <c r="W172">
         <v>3</v>
@@ -11857,7 +11857,7 @@
         <v>198</v>
       </c>
       <c r="U174" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="W174">
         <v>3</v>
@@ -12216,10 +12216,10 @@
         <v>1872</v>
       </c>
       <c r="E184" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F184" t="s">
         <v>1585</v>
-      </c>
-      <c r="F184" t="s">
-        <v>1586</v>
       </c>
       <c r="J184" t="s">
         <v>831</v>
@@ -12482,10 +12482,10 @@
         <v>222</v>
       </c>
       <c r="E191" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F191" t="s">
         <v>1587</v>
-      </c>
-      <c r="F191" t="s">
-        <v>1588</v>
       </c>
       <c r="J191" t="s">
         <v>857</v>
@@ -12842,7 +12842,7 @@
         <v>803</v>
       </c>
       <c r="U200" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="W200">
         <v>1</v>
@@ -13087,13 +13087,13 @@
         <v>886</v>
       </c>
       <c r="D207" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="E207" t="s">
         <v>909</v>
       </c>
       <c r="F207" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="J207" t="s">
         <v>910</v>
@@ -14540,7 +14540,7 @@
         <v>612</v>
       </c>
       <c r="F245" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="J245" t="s">
         <v>1055</v>
@@ -15192,7 +15192,7 @@
         <v>1109</v>
       </c>
       <c r="L262" s="6" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="R262" t="s">
         <v>30</v>
@@ -16562,20 +16562,20 @@
       <c r="J298" t="s">
         <v>1207</v>
       </c>
-      <c r="L298" s="1" t="s">
+      <c r="L298" s="6" t="s">
+        <v>1595</v>
+      </c>
+      <c r="R298" t="s">
+        <v>30</v>
+      </c>
+      <c r="S298" t="s">
         <v>1208</v>
-      </c>
-      <c r="R298" t="s">
-        <v>30</v>
-      </c>
-      <c r="S298" t="s">
-        <v>1209</v>
       </c>
       <c r="T298" t="s">
         <v>154</v>
       </c>
       <c r="U298" t="s">
-        <v>129</v>
+        <v>51</v>
       </c>
       <c r="W298">
         <v>1</v>
@@ -16595,13 +16595,13 @@
         <v>1205</v>
       </c>
       <c r="F299" t="s">
+        <v>1209</v>
+      </c>
+      <c r="J299" t="s">
         <v>1210</v>
       </c>
-      <c r="J299" t="s">
+      <c r="L299" s="1" t="s">
         <v>1211</v>
-      </c>
-      <c r="L299" s="1" t="s">
-        <v>1212</v>
       </c>
       <c r="R299" t="s">
         <v>30</v>
@@ -16636,10 +16636,10 @@
         <v>1206</v>
       </c>
       <c r="J300" t="s">
+        <v>1212</v>
+      </c>
+      <c r="L300" s="1" t="s">
         <v>1213</v>
-      </c>
-      <c r="L300" s="1" t="s">
-        <v>1214</v>
       </c>
       <c r="R300" t="s">
         <v>30</v>
@@ -16665,7 +16665,7 @@
         <v>1204</v>
       </c>
       <c r="D301" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="E301" t="s">
         <v>1205</v>
@@ -16674,22 +16674,22 @@
         <v>1206</v>
       </c>
       <c r="J301" t="s">
+        <v>1215</v>
+      </c>
+      <c r="L301" s="1" t="s">
         <v>1216</v>
       </c>
-      <c r="L301" s="1" t="s">
+      <c r="R301" t="s">
+        <v>30</v>
+      </c>
+      <c r="S301" t="s">
+        <v>31</v>
+      </c>
+      <c r="T301" t="s">
         <v>1217</v>
       </c>
-      <c r="R301" t="s">
-        <v>30</v>
-      </c>
-      <c r="S301" t="s">
-        <v>31</v>
-      </c>
-      <c r="T301" t="s">
+      <c r="U301" t="s">
         <v>1218</v>
-      </c>
-      <c r="U301" t="s">
-        <v>1219</v>
       </c>
       <c r="W301">
         <v>1</v>
@@ -16697,10 +16697,10 @@
     </row>
     <row r="302" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B302" t="s">
         <v>1220</v>
-      </c>
-      <c r="B302" t="s">
-        <v>1221</v>
       </c>
       <c r="D302">
         <v>1867</v>
@@ -16712,19 +16712,19 @@
         <v>145</v>
       </c>
       <c r="J302" t="s">
+        <v>1221</v>
+      </c>
+      <c r="L302" s="1" t="s">
         <v>1222</v>
       </c>
-      <c r="L302" s="1" t="s">
+      <c r="R302" t="s">
+        <v>30</v>
+      </c>
+      <c r="S302" t="s">
+        <v>31</v>
+      </c>
+      <c r="T302" t="s">
         <v>1223</v>
-      </c>
-      <c r="R302" t="s">
-        <v>30</v>
-      </c>
-      <c r="S302" t="s">
-        <v>31</v>
-      </c>
-      <c r="T302" t="s">
-        <v>1224</v>
       </c>
       <c r="U302" t="s">
         <v>1078</v>
@@ -16735,10 +16735,10 @@
     </row>
     <row r="303" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B303" t="s">
         <v>1220</v>
-      </c>
-      <c r="B303" t="s">
-        <v>1221</v>
       </c>
       <c r="D303" t="s">
         <v>366</v>
@@ -16750,10 +16750,10 @@
         <v>80</v>
       </c>
       <c r="J303" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L303" s="1" t="s">
         <v>1225</v>
-      </c>
-      <c r="L303" s="1" t="s">
-        <v>1226</v>
       </c>
       <c r="R303" t="s">
         <v>30</v>
@@ -16773,10 +16773,10 @@
     </row>
     <row r="304" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B304" t="s">
         <v>1220</v>
-      </c>
-      <c r="B304" t="s">
-        <v>1221</v>
       </c>
       <c r="D304" t="s">
         <v>330</v>
@@ -16788,10 +16788,10 @@
         <v>80</v>
       </c>
       <c r="J304" t="s">
+        <v>1226</v>
+      </c>
+      <c r="L304" s="1" t="s">
         <v>1227</v>
-      </c>
-      <c r="L304" s="1" t="s">
-        <v>1228</v>
       </c>
       <c r="R304" t="s">
         <v>30</v>
@@ -16811,10 +16811,10 @@
     </row>
     <row r="305" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B305" t="s">
         <v>1220</v>
-      </c>
-      <c r="B305" t="s">
-        <v>1221</v>
       </c>
       <c r="D305">
         <v>1881</v>
@@ -16826,10 +16826,10 @@
         <v>80</v>
       </c>
       <c r="J305" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L305" s="1" t="s">
         <v>1230</v>
-      </c>
-      <c r="L305" s="1" t="s">
-        <v>1231</v>
       </c>
       <c r="R305" t="s">
         <v>30</v>
@@ -16849,13 +16849,13 @@
     </row>
     <row r="306" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B306" t="s">
         <v>1220</v>
       </c>
-      <c r="B306" t="s">
-        <v>1221</v>
-      </c>
       <c r="D306" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E306" t="s">
         <v>176</v>
@@ -16864,10 +16864,10 @@
         <v>468</v>
       </c>
       <c r="J306" t="s">
+        <v>1231</v>
+      </c>
+      <c r="L306" s="1" t="s">
         <v>1232</v>
-      </c>
-      <c r="L306" s="1" t="s">
-        <v>1233</v>
       </c>
       <c r="R306" t="s">
         <v>30</v>
@@ -16887,25 +16887,25 @@
     </row>
     <row r="307" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B307" t="s">
         <v>1220</v>
-      </c>
-      <c r="B307" t="s">
-        <v>1221</v>
       </c>
       <c r="D307">
         <v>1898</v>
       </c>
       <c r="E307" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="F307" t="s">
         <v>341</v>
       </c>
       <c r="J307" t="s">
+        <v>1234</v>
+      </c>
+      <c r="L307" s="1" t="s">
         <v>1235</v>
-      </c>
-      <c r="L307" s="1" t="s">
-        <v>1236</v>
       </c>
       <c r="R307" t="s">
         <v>30</v>
@@ -16925,10 +16925,10 @@
     </row>
     <row r="308" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B308" t="s">
         <v>1220</v>
-      </c>
-      <c r="B308" t="s">
-        <v>1221</v>
       </c>
       <c r="D308">
         <v>1867</v>
@@ -16937,13 +16937,13 @@
         <v>144</v>
       </c>
       <c r="F308" t="s">
+        <v>1236</v>
+      </c>
+      <c r="J308" t="s">
         <v>1237</v>
       </c>
-      <c r="J308" t="s">
+      <c r="L308" s="1" t="s">
         <v>1238</v>
-      </c>
-      <c r="L308" s="1" t="s">
-        <v>1239</v>
       </c>
       <c r="R308" t="s">
         <v>30</v>
@@ -16963,25 +16963,25 @@
     </row>
     <row r="309" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B309" t="s">
         <v>1220</v>
-      </c>
-      <c r="B309" t="s">
-        <v>1221</v>
       </c>
       <c r="D309">
         <v>1896</v>
       </c>
       <c r="E309" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F309" t="s">
         <v>1240</v>
       </c>
-      <c r="F309" t="s">
+      <c r="J309" t="s">
         <v>1241</v>
       </c>
-      <c r="J309" t="s">
+      <c r="L309" s="1" t="s">
         <v>1242</v>
-      </c>
-      <c r="L309" s="1" t="s">
-        <v>1243</v>
       </c>
       <c r="R309" t="s">
         <v>30</v>
@@ -17004,7 +17004,7 @@
         <v>236</v>
       </c>
       <c r="B310" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="D310" t="s">
         <v>34</v>
@@ -17016,10 +17016,10 @@
         <v>80</v>
       </c>
       <c r="J310" t="s">
+        <v>1244</v>
+      </c>
+      <c r="L310" s="1" t="s">
         <v>1245</v>
-      </c>
-      <c r="L310" s="1" t="s">
-        <v>1246</v>
       </c>
       <c r="R310" t="s">
         <v>30</v>
@@ -17042,7 +17042,7 @@
         <v>236</v>
       </c>
       <c r="B311" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="D311" t="s">
         <v>199</v>
@@ -17054,10 +17054,10 @@
         <v>80</v>
       </c>
       <c r="J311" t="s">
+        <v>1246</v>
+      </c>
+      <c r="L311" s="1" t="s">
         <v>1247</v>
-      </c>
-      <c r="L311" s="1" t="s">
-        <v>1248</v>
       </c>
       <c r="R311" t="s">
         <v>30</v>
@@ -17080,7 +17080,7 @@
         <v>236</v>
       </c>
       <c r="B312" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="D312">
         <v>1879</v>
@@ -17092,10 +17092,10 @@
         <v>80</v>
       </c>
       <c r="J312" t="s">
+        <v>1248</v>
+      </c>
+      <c r="L312" s="1" t="s">
         <v>1249</v>
-      </c>
-      <c r="L312" s="1" t="s">
-        <v>1250</v>
       </c>
       <c r="R312" t="s">
         <v>30</v>
@@ -17118,10 +17118,10 @@
         <v>236</v>
       </c>
       <c r="B313" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="D313" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E313" t="s">
         <v>903</v>
@@ -17130,22 +17130,22 @@
         <v>341</v>
       </c>
       <c r="J313" t="s">
+        <v>1251</v>
+      </c>
+      <c r="L313" s="1" t="s">
         <v>1252</v>
       </c>
-      <c r="L313" s="1" t="s">
+      <c r="R313" t="s">
+        <v>30</v>
+      </c>
+      <c r="S313" t="s">
+        <v>31</v>
+      </c>
+      <c r="T313" t="s">
         <v>1253</v>
       </c>
-      <c r="R313" t="s">
-        <v>30</v>
-      </c>
-      <c r="S313" t="s">
-        <v>31</v>
-      </c>
-      <c r="T313" t="s">
+      <c r="U313" t="s">
         <v>1254</v>
-      </c>
-      <c r="U313" t="s">
-        <v>1255</v>
       </c>
       <c r="W313">
         <v>3</v>
@@ -17153,10 +17153,10 @@
     </row>
     <row r="314" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B314" t="s">
         <v>1256</v>
-      </c>
-      <c r="B314" t="s">
-        <v>1257</v>
       </c>
       <c r="D314" t="s">
         <v>34</v>
@@ -17168,10 +17168,10 @@
         <v>80</v>
       </c>
       <c r="J314" t="s">
+        <v>1257</v>
+      </c>
+      <c r="L314" s="1" t="s">
         <v>1258</v>
-      </c>
-      <c r="L314" s="1" t="s">
-        <v>1259</v>
       </c>
       <c r="R314" t="s">
         <v>30</v>
@@ -17191,10 +17191,10 @@
     </row>
     <row r="315" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B315" t="s">
         <v>1256</v>
-      </c>
-      <c r="B315" t="s">
-        <v>1257</v>
       </c>
       <c r="D315" t="s">
         <v>810</v>
@@ -17206,10 +17206,10 @@
         <v>80</v>
       </c>
       <c r="J315" t="s">
+        <v>1259</v>
+      </c>
+      <c r="L315" s="1" t="s">
         <v>1260</v>
-      </c>
-      <c r="L315" s="1" t="s">
-        <v>1261</v>
       </c>
       <c r="R315" t="s">
         <v>30</v>
@@ -17229,10 +17229,10 @@
     </row>
     <row r="316" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B316" t="s">
         <v>1256</v>
-      </c>
-      <c r="B316" t="s">
-        <v>1257</v>
       </c>
       <c r="D316">
         <v>1910</v>
@@ -17244,10 +17244,10 @@
         <v>532</v>
       </c>
       <c r="J316" t="s">
+        <v>1261</v>
+      </c>
+      <c r="L316" s="1" t="s">
         <v>1262</v>
-      </c>
-      <c r="L316" s="1" t="s">
-        <v>1263</v>
       </c>
       <c r="R316" t="s">
         <v>30</v>
@@ -17267,10 +17267,10 @@
     </row>
     <row r="317" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B317" t="s">
         <v>1256</v>
-      </c>
-      <c r="B317" t="s">
-        <v>1257</v>
       </c>
       <c r="D317">
         <v>1890</v>
@@ -17282,10 +17282,10 @@
         <v>112</v>
       </c>
       <c r="J317" t="s">
+        <v>1263</v>
+      </c>
+      <c r="L317" s="1" t="s">
         <v>1264</v>
-      </c>
-      <c r="L317" s="1" t="s">
-        <v>1265</v>
       </c>
       <c r="R317" t="s">
         <v>30</v>
@@ -17305,10 +17305,10 @@
     </row>
     <row r="318" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B318" t="s">
         <v>1266</v>
-      </c>
-      <c r="B318" t="s">
-        <v>1267</v>
       </c>
       <c r="D318" t="s">
         <v>696</v>
@@ -17320,10 +17320,10 @@
         <v>382</v>
       </c>
       <c r="J318" t="s">
+        <v>1267</v>
+      </c>
+      <c r="L318" s="1" t="s">
         <v>1268</v>
-      </c>
-      <c r="L318" s="1" t="s">
-        <v>1269</v>
       </c>
       <c r="R318" t="s">
         <v>30</v>
@@ -17343,10 +17343,10 @@
     </row>
     <row r="319" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B319" t="s">
         <v>1266</v>
-      </c>
-      <c r="B319" t="s">
-        <v>1267</v>
       </c>
       <c r="D319" t="s">
         <v>321</v>
@@ -17358,10 +17358,10 @@
         <v>80</v>
       </c>
       <c r="J319" t="s">
+        <v>1269</v>
+      </c>
+      <c r="L319" s="1" t="s">
         <v>1270</v>
-      </c>
-      <c r="L319" s="1" t="s">
-        <v>1271</v>
       </c>
       <c r="R319" t="s">
         <v>30</v>
@@ -17373,7 +17373,7 @@
         <v>248</v>
       </c>
       <c r="U319" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="W319">
         <v>1</v>
@@ -17381,10 +17381,10 @@
     </row>
     <row r="320" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B320" t="s">
         <v>1266</v>
-      </c>
-      <c r="B320" t="s">
-        <v>1267</v>
       </c>
       <c r="D320" t="s">
         <v>321</v>
@@ -17396,10 +17396,10 @@
         <v>80</v>
       </c>
       <c r="J320" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L320" s="1" t="s">
         <v>1273</v>
-      </c>
-      <c r="L320" s="1" t="s">
-        <v>1274</v>
       </c>
       <c r="R320" t="s">
         <v>30</v>
@@ -17419,10 +17419,10 @@
     </row>
     <row r="321" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B321" t="s">
         <v>1266</v>
-      </c>
-      <c r="B321" t="s">
-        <v>1267</v>
       </c>
       <c r="D321" t="s">
         <v>321</v>
@@ -17434,10 +17434,10 @@
         <v>80</v>
       </c>
       <c r="J321" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L321" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="L321" s="1" t="s">
-        <v>1276</v>
       </c>
       <c r="R321" t="s">
         <v>30</v>
@@ -17457,10 +17457,10 @@
     </row>
     <row r="322" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B322" t="s">
         <v>1266</v>
-      </c>
-      <c r="B322" t="s">
-        <v>1267</v>
       </c>
       <c r="D322" t="s">
         <v>350</v>
@@ -17472,10 +17472,10 @@
         <v>145</v>
       </c>
       <c r="J322" t="s">
+        <v>1276</v>
+      </c>
+      <c r="L322" s="1" t="s">
         <v>1277</v>
-      </c>
-      <c r="L322" s="1" t="s">
-        <v>1278</v>
       </c>
       <c r="R322" t="s">
         <v>30</v>
@@ -17495,13 +17495,13 @@
     </row>
     <row r="323" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B323" t="s">
         <v>1266</v>
       </c>
-      <c r="B323" t="s">
-        <v>1267</v>
-      </c>
       <c r="D323" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E323" t="s">
         <v>111</v>
@@ -17510,10 +17510,10 @@
         <v>571</v>
       </c>
       <c r="J323" t="s">
+        <v>1279</v>
+      </c>
+      <c r="L323" s="1" t="s">
         <v>1280</v>
-      </c>
-      <c r="L323" s="1" t="s">
-        <v>1281</v>
       </c>
       <c r="R323" t="s">
         <v>30</v>
@@ -17525,7 +17525,7 @@
         <v>314</v>
       </c>
       <c r="U323" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="W323">
         <v>1</v>
@@ -17533,10 +17533,10 @@
     </row>
     <row r="324" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B324" t="s">
         <v>1266</v>
-      </c>
-      <c r="B324" t="s">
-        <v>1267</v>
       </c>
       <c r="D324" t="s">
         <v>34</v>
@@ -17548,10 +17548,10 @@
         <v>101</v>
       </c>
       <c r="J324" t="s">
+        <v>1282</v>
+      </c>
+      <c r="L324" s="1" t="s">
         <v>1283</v>
-      </c>
-      <c r="L324" s="1" t="s">
-        <v>1284</v>
       </c>
       <c r="R324" t="s">
         <v>30</v>
@@ -17571,10 +17571,10 @@
     </row>
     <row r="325" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B325" t="s">
         <v>1266</v>
-      </c>
-      <c r="B325" t="s">
-        <v>1267</v>
       </c>
       <c r="D325" t="s">
         <v>199</v>
@@ -17586,13 +17586,13 @@
         <v>80</v>
       </c>
       <c r="J325" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L325" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="L325" s="1" t="s">
+      <c r="M325" t="s">
         <v>1286</v>
-      </c>
-      <c r="M325" t="s">
-        <v>1287</v>
       </c>
       <c r="R325" t="s">
         <v>30</v>
@@ -17612,10 +17612,10 @@
     </row>
     <row r="326" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B326" t="s">
         <v>1266</v>
-      </c>
-      <c r="B326" t="s">
-        <v>1267</v>
       </c>
       <c r="D326" t="s">
         <v>199</v>
@@ -17627,13 +17627,13 @@
         <v>80</v>
       </c>
       <c r="J326" t="s">
+        <v>1287</v>
+      </c>
+      <c r="L326" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="L326" s="1" t="s">
+      <c r="M326" t="s">
         <v>1289</v>
-      </c>
-      <c r="M326" t="s">
-        <v>1290</v>
       </c>
       <c r="R326" t="s">
         <v>30</v>
@@ -17653,13 +17653,13 @@
     </row>
     <row r="327" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B327" t="s">
         <v>1266</v>
       </c>
-      <c r="B327" t="s">
-        <v>1267</v>
-      </c>
       <c r="D327" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="E327" t="s">
         <v>71</v>
@@ -17671,7 +17671,7 @@
         <v>402</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="R327" t="s">
         <v>30</v>
@@ -17691,10 +17691,10 @@
     </row>
     <row r="328" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B328" t="s">
         <v>1266</v>
-      </c>
-      <c r="B328" t="s">
-        <v>1267</v>
       </c>
       <c r="D328" t="s">
         <v>635</v>
@@ -17706,10 +17706,10 @@
         <v>80</v>
       </c>
       <c r="J328" t="s">
+        <v>1292</v>
+      </c>
+      <c r="L328" s="1" t="s">
         <v>1293</v>
-      </c>
-      <c r="L328" s="1" t="s">
-        <v>1294</v>
       </c>
       <c r="R328" t="s">
         <v>30</v>
@@ -17729,10 +17729,10 @@
     </row>
     <row r="329" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B329" t="s">
         <v>1266</v>
-      </c>
-      <c r="B329" t="s">
-        <v>1267</v>
       </c>
       <c r="D329">
         <v>1877</v>
@@ -17744,10 +17744,10 @@
         <v>145</v>
       </c>
       <c r="J329" t="s">
+        <v>1294</v>
+      </c>
+      <c r="L329" s="1" t="s">
         <v>1295</v>
-      </c>
-      <c r="L329" s="1" t="s">
-        <v>1296</v>
       </c>
       <c r="R329" t="s">
         <v>30</v>
@@ -17767,13 +17767,13 @@
     </row>
     <row r="330" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B330" t="s">
         <v>1297</v>
       </c>
-      <c r="B330" t="s">
+      <c r="D330" t="s">
         <v>1298</v>
-      </c>
-      <c r="D330" t="s">
-        <v>1299</v>
       </c>
       <c r="E330" t="s">
         <v>26</v>
@@ -17782,10 +17782,10 @@
         <v>27</v>
       </c>
       <c r="J330" t="s">
+        <v>1299</v>
+      </c>
+      <c r="L330" s="1" t="s">
         <v>1300</v>
-      </c>
-      <c r="L330" s="1" t="s">
-        <v>1301</v>
       </c>
       <c r="R330" t="s">
         <v>30</v>
@@ -17805,13 +17805,13 @@
     </row>
     <row r="331" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B331" t="s">
         <v>1297</v>
       </c>
-      <c r="B331" t="s">
-        <v>1298</v>
-      </c>
       <c r="D331" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="E331" t="s">
         <v>26</v>
@@ -17820,22 +17820,22 @@
         <v>27</v>
       </c>
       <c r="J331" t="s">
+        <v>1302</v>
+      </c>
+      <c r="L331" s="1" t="s">
         <v>1303</v>
       </c>
-      <c r="L331" s="1" t="s">
+      <c r="R331" t="s">
+        <v>30</v>
+      </c>
+      <c r="S331" t="s">
+        <v>31</v>
+      </c>
+      <c r="T331" t="s">
         <v>1304</v>
       </c>
-      <c r="R331" t="s">
-        <v>30</v>
-      </c>
-      <c r="S331" t="s">
-        <v>31</v>
-      </c>
-      <c r="T331" t="s">
+      <c r="U331" t="s">
         <v>1305</v>
-      </c>
-      <c r="U331" t="s">
-        <v>1306</v>
       </c>
       <c r="W331">
         <v>3</v>
@@ -17843,13 +17843,13 @@
     </row>
     <row r="332" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B332" t="s">
         <v>1297</v>
       </c>
-      <c r="B332" t="s">
-        <v>1298</v>
-      </c>
       <c r="D332" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="E332" t="s">
         <v>35</v>
@@ -17858,11 +17858,11 @@
         <v>36</v>
       </c>
       <c r="J332" t="s">
+        <v>1307</v>
+      </c>
+      <c r="L332" s="1" t="s">
         <v>1308</v>
       </c>
-      <c r="L332" s="1" t="s">
-        <v>1309</v>
-      </c>
       <c r="R332" t="s">
         <v>30</v>
       </c>
@@ -17870,7 +17870,7 @@
         <v>31</v>
       </c>
       <c r="T332" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="U332" t="s">
         <v>619</v>
@@ -17881,13 +17881,13 @@
     </row>
     <row r="333" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B333" t="s">
         <v>1297</v>
       </c>
-      <c r="B333" t="s">
-        <v>1298</v>
-      </c>
       <c r="D333" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E333" t="s">
         <v>35</v>
@@ -17896,10 +17896,10 @@
         <v>36</v>
       </c>
       <c r="J333" t="s">
+        <v>1310</v>
+      </c>
+      <c r="L333" s="1" t="s">
         <v>1311</v>
-      </c>
-      <c r="L333" s="1" t="s">
-        <v>1312</v>
       </c>
       <c r="R333" t="s">
         <v>30</v>
@@ -17919,13 +17919,13 @@
     </row>
     <row r="334" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B334" t="s">
         <v>1313</v>
       </c>
-      <c r="B334" t="s">
+      <c r="D334" t="s">
         <v>1314</v>
-      </c>
-      <c r="D334" t="s">
-        <v>1315</v>
       </c>
       <c r="E334" t="s">
         <v>176</v>
@@ -17934,10 +17934,10 @@
         <v>177</v>
       </c>
       <c r="J334" t="s">
+        <v>1315</v>
+      </c>
+      <c r="L334" s="1" t="s">
         <v>1316</v>
-      </c>
-      <c r="L334" s="1" t="s">
-        <v>1317</v>
       </c>
       <c r="R334" t="s">
         <v>30</v>
@@ -17957,10 +17957,10 @@
     </row>
     <row r="335" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B335" t="s">
         <v>1313</v>
-      </c>
-      <c r="B335" t="s">
-        <v>1314</v>
       </c>
       <c r="D335" t="s">
         <v>696</v>
@@ -17972,10 +17972,10 @@
         <v>177</v>
       </c>
       <c r="J335" t="s">
+        <v>1317</v>
+      </c>
+      <c r="L335" s="1" t="s">
         <v>1318</v>
-      </c>
-      <c r="L335" s="1" t="s">
-        <v>1319</v>
       </c>
       <c r="R335" t="s">
         <v>30</v>
@@ -17995,13 +17995,13 @@
     </row>
     <row r="336" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B336" t="s">
         <v>1313</v>
       </c>
-      <c r="B336" t="s">
-        <v>1314</v>
-      </c>
       <c r="D336" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="E336" t="s">
         <v>176</v>
@@ -18010,10 +18010,10 @@
         <v>177</v>
       </c>
       <c r="J336" t="s">
+        <v>1319</v>
+      </c>
+      <c r="L336" s="1" t="s">
         <v>1320</v>
-      </c>
-      <c r="L336" s="1" t="s">
-        <v>1321</v>
       </c>
       <c r="R336" t="s">
         <v>30</v>
@@ -18033,10 +18033,10 @@
     </row>
     <row r="337" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B337" t="s">
         <v>1313</v>
-      </c>
-      <c r="B337" t="s">
-        <v>1314</v>
       </c>
       <c r="D337" t="s">
         <v>525</v>
@@ -18048,10 +18048,10 @@
         <v>177</v>
       </c>
       <c r="J337" t="s">
+        <v>1321</v>
+      </c>
+      <c r="L337" s="1" t="s">
         <v>1322</v>
-      </c>
-      <c r="L337" s="1" t="s">
-        <v>1323</v>
       </c>
       <c r="R337" t="s">
         <v>30</v>
@@ -18074,10 +18074,10 @@
         <v>406</v>
       </c>
       <c r="B338" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D338" t="s">
         <v>1324</v>
-      </c>
-      <c r="D338" t="s">
-        <v>1325</v>
       </c>
       <c r="E338" t="s">
         <v>79</v>
@@ -18086,10 +18086,10 @@
         <v>409</v>
       </c>
       <c r="J338" t="s">
+        <v>1325</v>
+      </c>
+      <c r="L338" s="1" t="s">
         <v>1326</v>
-      </c>
-      <c r="L338" s="1" t="s">
-        <v>1327</v>
       </c>
       <c r="R338" t="s">
         <v>30</v>
@@ -18112,7 +18112,7 @@
         <v>406</v>
       </c>
       <c r="B339" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="D339" t="s">
         <v>536</v>
@@ -18124,10 +18124,10 @@
         <v>409</v>
       </c>
       <c r="J339" t="s">
+        <v>1327</v>
+      </c>
+      <c r="L339" s="1" t="s">
         <v>1328</v>
-      </c>
-      <c r="L339" s="1" t="s">
-        <v>1329</v>
       </c>
       <c r="R339" t="s">
         <v>30</v>
@@ -18150,10 +18150,10 @@
         <v>406</v>
       </c>
       <c r="B340" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="D340" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="E340" t="s">
         <v>79</v>
@@ -18162,19 +18162,19 @@
         <v>409</v>
       </c>
       <c r="J340" t="s">
+        <v>1330</v>
+      </c>
+      <c r="L340" s="1" t="s">
         <v>1331</v>
       </c>
-      <c r="L340" s="1" t="s">
+      <c r="R340" t="s">
+        <v>30</v>
+      </c>
+      <c r="S340" t="s">
+        <v>31</v>
+      </c>
+      <c r="T340" t="s">
         <v>1332</v>
-      </c>
-      <c r="R340" t="s">
-        <v>30</v>
-      </c>
-      <c r="S340" t="s">
-        <v>31</v>
-      </c>
-      <c r="T340" t="s">
-        <v>1333</v>
       </c>
       <c r="U340" t="s">
         <v>796</v>
@@ -18188,10 +18188,10 @@
         <v>406</v>
       </c>
       <c r="B341" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="D341" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="E341" t="s">
         <v>79</v>
@@ -18200,10 +18200,10 @@
         <v>409</v>
       </c>
       <c r="J341" t="s">
+        <v>1334</v>
+      </c>
+      <c r="L341" s="1" t="s">
         <v>1335</v>
-      </c>
-      <c r="L341" s="1" t="s">
-        <v>1336</v>
       </c>
       <c r="R341" t="s">
         <v>30</v>
@@ -18223,13 +18223,13 @@
     </row>
     <row r="342" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B342" t="s">
         <v>1337</v>
       </c>
-      <c r="B342" t="s">
+      <c r="D342" t="s">
         <v>1338</v>
-      </c>
-      <c r="D342" t="s">
-        <v>1339</v>
       </c>
       <c r="E342" t="s">
         <v>144</v>
@@ -18238,19 +18238,19 @@
         <v>145</v>
       </c>
       <c r="J342" t="s">
+        <v>1339</v>
+      </c>
+      <c r="L342" s="1" t="s">
         <v>1340</v>
       </c>
-      <c r="L342" s="1" t="s">
+      <c r="R342" t="s">
+        <v>30</v>
+      </c>
+      <c r="S342" t="s">
+        <v>31</v>
+      </c>
+      <c r="T342" t="s">
         <v>1341</v>
-      </c>
-      <c r="R342" t="s">
-        <v>30</v>
-      </c>
-      <c r="S342" t="s">
-        <v>31</v>
-      </c>
-      <c r="T342" t="s">
-        <v>1342</v>
       </c>
       <c r="U342" t="s">
         <v>99</v>
@@ -18261,10 +18261,10 @@
     </row>
     <row r="343" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B343" t="s">
         <v>1337</v>
-      </c>
-      <c r="B343" t="s">
-        <v>1338</v>
       </c>
       <c r="D343" t="s">
         <v>378</v>
@@ -18276,10 +18276,10 @@
         <v>177</v>
       </c>
       <c r="J343" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L343" s="1" t="s">
         <v>1343</v>
-      </c>
-      <c r="L343" s="1" t="s">
-        <v>1344</v>
       </c>
       <c r="R343" t="s">
         <v>30</v>
@@ -18299,10 +18299,10 @@
     </row>
     <row r="344" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B344" t="s">
         <v>1337</v>
-      </c>
-      <c r="B344" t="s">
-        <v>1338</v>
       </c>
       <c r="D344">
         <v>1882</v>
@@ -18314,22 +18314,22 @@
         <v>676</v>
       </c>
       <c r="J344" t="s">
+        <v>1344</v>
+      </c>
+      <c r="L344" s="1" t="s">
         <v>1345</v>
       </c>
-      <c r="L344" s="1" t="s">
+      <c r="R344" t="s">
+        <v>30</v>
+      </c>
+      <c r="S344" t="s">
+        <v>31</v>
+      </c>
+      <c r="T344" t="s">
         <v>1346</v>
       </c>
-      <c r="R344" t="s">
-        <v>30</v>
-      </c>
-      <c r="S344" t="s">
-        <v>31</v>
-      </c>
-      <c r="T344" t="s">
+      <c r="U344" t="s">
         <v>1347</v>
-      </c>
-      <c r="U344" t="s">
-        <v>1348</v>
       </c>
       <c r="W344">
         <v>3</v>
@@ -18337,10 +18337,10 @@
     </row>
     <row r="345" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B345" t="s">
         <v>1337</v>
-      </c>
-      <c r="B345" t="s">
-        <v>1338</v>
       </c>
       <c r="D345">
         <v>1882</v>
@@ -18349,13 +18349,13 @@
         <v>675</v>
       </c>
       <c r="F345" t="s">
+        <v>1348</v>
+      </c>
+      <c r="J345" t="s">
         <v>1349</v>
       </c>
-      <c r="J345" t="s">
+      <c r="L345" s="1" t="s">
         <v>1350</v>
-      </c>
-      <c r="L345" s="1" t="s">
-        <v>1351</v>
       </c>
       <c r="R345" t="s">
         <v>30</v>
@@ -18378,7 +18378,7 @@
         <v>361</v>
       </c>
       <c r="B346" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D346" t="s">
         <v>54</v>
@@ -18390,10 +18390,10 @@
         <v>80</v>
       </c>
       <c r="J346" t="s">
+        <v>1352</v>
+      </c>
+      <c r="L346" s="1" t="s">
         <v>1353</v>
-      </c>
-      <c r="L346" s="1" t="s">
-        <v>1354</v>
       </c>
       <c r="R346" t="s">
         <v>30</v>
@@ -18416,7 +18416,7 @@
         <v>361</v>
       </c>
       <c r="B347" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D347" t="s">
         <v>222</v>
@@ -18428,10 +18428,10 @@
         <v>80</v>
       </c>
       <c r="J347" t="s">
+        <v>1354</v>
+      </c>
+      <c r="L347" s="1" t="s">
         <v>1355</v>
-      </c>
-      <c r="L347" s="1" t="s">
-        <v>1356</v>
       </c>
       <c r="R347" t="s">
         <v>30</v>
@@ -18454,22 +18454,22 @@
         <v>361</v>
       </c>
       <c r="B348" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D348" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E348" t="s">
         <v>1357</v>
-      </c>
-      <c r="E348" t="s">
-        <v>1358</v>
       </c>
       <c r="F348" t="s">
         <v>341</v>
       </c>
       <c r="J348" t="s">
+        <v>1358</v>
+      </c>
+      <c r="L348" s="1" t="s">
         <v>1359</v>
-      </c>
-      <c r="L348" s="1" t="s">
-        <v>1360</v>
       </c>
       <c r="R348" t="s">
         <v>30</v>
@@ -18492,7 +18492,7 @@
         <v>361</v>
       </c>
       <c r="B349" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D349">
         <v>1892</v>
@@ -18504,10 +18504,10 @@
         <v>80</v>
       </c>
       <c r="J349" t="s">
+        <v>1360</v>
+      </c>
+      <c r="L349" s="1" t="s">
         <v>1361</v>
-      </c>
-      <c r="L349" s="1" t="s">
-        <v>1362</v>
       </c>
       <c r="R349" t="s">
         <v>30</v>
@@ -18527,10 +18527,10 @@
     </row>
     <row r="350" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B350" t="s">
         <v>1363</v>
-      </c>
-      <c r="B350" t="s">
-        <v>1364</v>
       </c>
       <c r="D350" t="s">
         <v>293</v>
@@ -18542,19 +18542,19 @@
         <v>468</v>
       </c>
       <c r="J350" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L350" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="L350" s="1" t="s">
+      <c r="R350" t="s">
+        <v>30</v>
+      </c>
+      <c r="S350" t="s">
+        <v>31</v>
+      </c>
+      <c r="T350" t="s">
         <v>1366</v>
-      </c>
-      <c r="R350" t="s">
-        <v>30</v>
-      </c>
-      <c r="S350" t="s">
-        <v>31</v>
-      </c>
-      <c r="T350" t="s">
-        <v>1367</v>
       </c>
       <c r="U350" t="s">
         <v>263</v>
@@ -18565,10 +18565,10 @@
     </row>
     <row r="351" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B351" t="s">
         <v>1363</v>
-      </c>
-      <c r="B351" t="s">
-        <v>1364</v>
       </c>
       <c r="D351" t="s">
         <v>723</v>
@@ -18580,10 +18580,10 @@
         <v>101</v>
       </c>
       <c r="J351" t="s">
+        <v>1367</v>
+      </c>
+      <c r="L351" s="1" t="s">
         <v>1368</v>
-      </c>
-      <c r="L351" s="1" t="s">
-        <v>1369</v>
       </c>
       <c r="R351" t="s">
         <v>30</v>
@@ -18595,7 +18595,7 @@
         <v>40</v>
       </c>
       <c r="U351" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="W351">
         <v>2</v>
@@ -18603,10 +18603,10 @@
     </row>
     <row r="352" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B352" t="s">
         <v>1363</v>
-      </c>
-      <c r="B352" t="s">
-        <v>1364</v>
       </c>
       <c r="D352" t="s">
         <v>971</v>
@@ -18618,10 +18618,10 @@
         <v>382</v>
       </c>
       <c r="J352" t="s">
+        <v>1370</v>
+      </c>
+      <c r="L352" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="L352" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="R352" t="s">
         <v>30</v>
@@ -18641,25 +18641,25 @@
     </row>
     <row r="353" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B353" t="s">
         <v>1363</v>
-      </c>
-      <c r="B353" t="s">
-        <v>1364</v>
       </c>
       <c r="D353" t="s">
         <v>971</v>
       </c>
       <c r="E353" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F353" t="s">
         <v>1373</v>
       </c>
-      <c r="F353" t="s">
+      <c r="J353" t="s">
         <v>1374</v>
       </c>
-      <c r="J353" t="s">
+      <c r="L353" s="1" t="s">
         <v>1375</v>
-      </c>
-      <c r="L353" s="1" t="s">
-        <v>1376</v>
       </c>
       <c r="R353" t="s">
         <v>30</v>
@@ -18679,10 +18679,10 @@
     </row>
     <row r="354" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B354" t="s">
         <v>1363</v>
-      </c>
-      <c r="B354" t="s">
-        <v>1364</v>
       </c>
       <c r="D354" t="s">
         <v>238</v>
@@ -18694,10 +18694,10 @@
         <v>80</v>
       </c>
       <c r="J354" t="s">
+        <v>1376</v>
+      </c>
+      <c r="L354" s="1" t="s">
         <v>1377</v>
-      </c>
-      <c r="L354" s="1" t="s">
-        <v>1378</v>
       </c>
       <c r="R354" t="s">
         <v>30</v>
@@ -18717,25 +18717,25 @@
     </row>
     <row r="355" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B355" t="s">
         <v>1363</v>
       </c>
-      <c r="B355" t="s">
-        <v>1364</v>
-      </c>
       <c r="D355" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="E355" t="s">
         <v>71</v>
       </c>
       <c r="F355" t="s">
+        <v>1379</v>
+      </c>
+      <c r="J355" t="s">
         <v>1380</v>
       </c>
-      <c r="J355" t="s">
+      <c r="L355" s="1" t="s">
         <v>1381</v>
-      </c>
-      <c r="L355" s="1" t="s">
-        <v>1382</v>
       </c>
       <c r="R355" t="s">
         <v>30</v>
@@ -18755,10 +18755,10 @@
     </row>
     <row r="356" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B356" t="s">
         <v>1363</v>
-      </c>
-      <c r="B356" t="s">
-        <v>1364</v>
       </c>
       <c r="D356" t="s">
         <v>661</v>
@@ -18770,10 +18770,10 @@
         <v>145</v>
       </c>
       <c r="J356" t="s">
+        <v>1382</v>
+      </c>
+      <c r="L356" s="1" t="s">
         <v>1383</v>
-      </c>
-      <c r="L356" s="1" t="s">
-        <v>1384</v>
       </c>
       <c r="R356" t="s">
         <v>30</v>
@@ -18793,10 +18793,10 @@
     </row>
     <row r="357" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B357" t="s">
         <v>1363</v>
-      </c>
-      <c r="B357" t="s">
-        <v>1364</v>
       </c>
       <c r="D357">
         <v>1890</v>
@@ -18808,10 +18808,10 @@
         <v>372</v>
       </c>
       <c r="J357" t="s">
+        <v>1384</v>
+      </c>
+      <c r="L357" s="1" t="s">
         <v>1385</v>
-      </c>
-      <c r="L357" s="1" t="s">
-        <v>1386</v>
       </c>
       <c r="R357" t="s">
         <v>30</v>
@@ -18834,7 +18834,7 @@
         <v>361</v>
       </c>
       <c r="B358" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="D358" t="s">
         <v>810</v>
@@ -18846,10 +18846,10 @@
         <v>372</v>
       </c>
       <c r="J358" t="s">
+        <v>1387</v>
+      </c>
+      <c r="L358" s="1" t="s">
         <v>1388</v>
-      </c>
-      <c r="L358" s="1" t="s">
-        <v>1389</v>
       </c>
       <c r="R358" t="s">
         <v>30</v>
@@ -18872,22 +18872,22 @@
         <v>361</v>
       </c>
       <c r="B359" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="D359" t="s">
         <v>993</v>
       </c>
       <c r="E359" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F359" t="s">
         <v>1390</v>
       </c>
-      <c r="F359" t="s">
+      <c r="J359" t="s">
         <v>1391</v>
       </c>
-      <c r="J359" t="s">
+      <c r="L359" s="1" t="s">
         <v>1392</v>
-      </c>
-      <c r="L359" s="1" t="s">
-        <v>1393</v>
       </c>
       <c r="R359" t="s">
         <v>30</v>
@@ -18910,7 +18910,7 @@
         <v>361</v>
       </c>
       <c r="B360" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="D360">
         <v>1892</v>
@@ -18922,10 +18922,10 @@
         <v>80</v>
       </c>
       <c r="J360" t="s">
+        <v>1393</v>
+      </c>
+      <c r="L360" s="1" t="s">
         <v>1394</v>
-      </c>
-      <c r="L360" s="1" t="s">
-        <v>1395</v>
       </c>
       <c r="R360" t="s">
         <v>30</v>
@@ -18948,7 +18948,7 @@
         <v>361</v>
       </c>
       <c r="B361" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="D361">
         <v>1895</v>
@@ -18960,10 +18960,10 @@
         <v>80</v>
       </c>
       <c r="J361" t="s">
+        <v>1395</v>
+      </c>
+      <c r="L361" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="L361" s="1" t="s">
-        <v>1397</v>
       </c>
       <c r="R361" t="s">
         <v>30</v>
@@ -18983,10 +18983,10 @@
     </row>
     <row r="362" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B362" t="s">
         <v>1398</v>
-      </c>
-      <c r="B362" t="s">
-        <v>1399</v>
       </c>
       <c r="D362" t="s">
         <v>317</v>
@@ -18998,10 +18998,10 @@
         <v>80</v>
       </c>
       <c r="J362" t="s">
+        <v>1399</v>
+      </c>
+      <c r="L362" s="1" t="s">
         <v>1400</v>
-      </c>
-      <c r="L362" s="1" t="s">
-        <v>1401</v>
       </c>
       <c r="R362" t="s">
         <v>30</v>
@@ -19021,25 +19021,25 @@
     </row>
     <row r="363" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B363" t="s">
         <v>1398</v>
-      </c>
-      <c r="B363" t="s">
-        <v>1399</v>
       </c>
       <c r="D363" t="s">
         <v>321</v>
       </c>
       <c r="E363" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="F363" t="s">
         <v>341</v>
       </c>
       <c r="J363" t="s">
+        <v>1402</v>
+      </c>
+      <c r="L363" s="1" t="s">
         <v>1403</v>
-      </c>
-      <c r="L363" s="1" t="s">
-        <v>1404</v>
       </c>
       <c r="R363" t="s">
         <v>30</v>
@@ -19059,10 +19059,10 @@
     </row>
     <row r="364" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B364" t="s">
         <v>1398</v>
-      </c>
-      <c r="B364" t="s">
-        <v>1399</v>
       </c>
       <c r="D364" t="s">
         <v>321</v>
@@ -19074,10 +19074,10 @@
         <v>145</v>
       </c>
       <c r="J364" t="s">
+        <v>1404</v>
+      </c>
+      <c r="L364" s="1" t="s">
         <v>1405</v>
-      </c>
-      <c r="L364" s="1" t="s">
-        <v>1406</v>
       </c>
       <c r="R364" t="s">
         <v>30</v>
@@ -19097,10 +19097,10 @@
     </row>
     <row r="365" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B365" t="s">
         <v>1398</v>
-      </c>
-      <c r="B365" t="s">
-        <v>1399</v>
       </c>
       <c r="D365" t="s">
         <v>321</v>
@@ -19109,13 +19109,13 @@
         <v>612</v>
       </c>
       <c r="F365" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="J365" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="L365" s="1" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="R365" t="s">
         <v>30</v>
@@ -19135,10 +19135,10 @@
     </row>
     <row r="366" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B366" t="s">
         <v>1398</v>
-      </c>
-      <c r="B366" t="s">
-        <v>1399</v>
       </c>
       <c r="D366" t="s">
         <v>810</v>
@@ -19150,10 +19150,10 @@
         <v>80</v>
       </c>
       <c r="J366" t="s">
+        <v>1407</v>
+      </c>
+      <c r="L366" s="1" t="s">
         <v>1408</v>
-      </c>
-      <c r="L366" s="1" t="s">
-        <v>1409</v>
       </c>
       <c r="R366" t="s">
         <v>30</v>
@@ -19173,10 +19173,10 @@
     </row>
     <row r="367" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B367" t="s">
         <v>1398</v>
-      </c>
-      <c r="B367" t="s">
-        <v>1399</v>
       </c>
       <c r="D367">
         <v>1872</v>
@@ -19188,10 +19188,10 @@
         <v>145</v>
       </c>
       <c r="J367" t="s">
+        <v>1409</v>
+      </c>
+      <c r="L367" s="1" t="s">
         <v>1410</v>
-      </c>
-      <c r="L367" s="1" t="s">
-        <v>1411</v>
       </c>
       <c r="R367" t="s">
         <v>30</v>
@@ -19211,10 +19211,10 @@
     </row>
     <row r="368" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B368" t="s">
         <v>1398</v>
-      </c>
-      <c r="B368" t="s">
-        <v>1399</v>
       </c>
       <c r="D368">
         <v>1870</v>
@@ -19226,10 +19226,10 @@
         <v>80</v>
       </c>
       <c r="J368" t="s">
+        <v>1411</v>
+      </c>
+      <c r="L368" s="1" t="s">
         <v>1412</v>
-      </c>
-      <c r="L368" s="1" t="s">
-        <v>1413</v>
       </c>
       <c r="R368" t="s">
         <v>30</v>
@@ -19249,10 +19249,10 @@
     </row>
     <row r="369" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B369" t="s">
         <v>1398</v>
-      </c>
-      <c r="B369" t="s">
-        <v>1399</v>
       </c>
       <c r="D369">
         <v>1873</v>
@@ -19264,10 +19264,10 @@
         <v>80</v>
       </c>
       <c r="J369" t="s">
+        <v>1413</v>
+      </c>
+      <c r="L369" s="1" t="s">
         <v>1414</v>
-      </c>
-      <c r="L369" s="1" t="s">
-        <v>1415</v>
       </c>
       <c r="R369" t="s">
         <v>30</v>
@@ -19290,7 +19290,7 @@
         <v>804</v>
       </c>
       <c r="B370" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="D370" t="s">
         <v>696</v>
@@ -19302,10 +19302,10 @@
         <v>177</v>
       </c>
       <c r="J370" t="s">
+        <v>1416</v>
+      </c>
+      <c r="L370" s="1" t="s">
         <v>1417</v>
-      </c>
-      <c r="L370" s="1" t="s">
-        <v>1418</v>
       </c>
       <c r="R370" t="s">
         <v>30</v>
@@ -19328,22 +19328,22 @@
         <v>804</v>
       </c>
       <c r="B371" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="D371" t="s">
         <v>330</v>
       </c>
       <c r="E371" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F371" t="s">
         <v>1419</v>
       </c>
-      <c r="F371" t="s">
+      <c r="J371" t="s">
         <v>1420</v>
       </c>
-      <c r="J371" t="s">
+      <c r="L371" s="1" t="s">
         <v>1421</v>
-      </c>
-      <c r="L371" s="1" t="s">
-        <v>1422</v>
       </c>
       <c r="R371" t="s">
         <v>30</v>
@@ -19366,7 +19366,7 @@
         <v>804</v>
       </c>
       <c r="B372" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="D372">
         <v>1873</v>
@@ -19375,13 +19375,13 @@
         <v>176</v>
       </c>
       <c r="F372" t="s">
+        <v>1422</v>
+      </c>
+      <c r="J372" t="s">
         <v>1423</v>
       </c>
-      <c r="J372" t="s">
+      <c r="L372" s="1" t="s">
         <v>1424</v>
-      </c>
-      <c r="L372" s="1" t="s">
-        <v>1425</v>
       </c>
       <c r="R372" t="s">
         <v>30</v>
@@ -19404,7 +19404,7 @@
         <v>804</v>
       </c>
       <c r="B373" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="D373">
         <v>1876</v>
@@ -19416,10 +19416,10 @@
         <v>177</v>
       </c>
       <c r="J373" t="s">
+        <v>1425</v>
+      </c>
+      <c r="L373" s="1" t="s">
         <v>1426</v>
-      </c>
-      <c r="L373" s="1" t="s">
-        <v>1427</v>
       </c>
       <c r="R373" t="s">
         <v>30</v>
@@ -19439,10 +19439,10 @@
     </row>
     <row r="374" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B374" t="s">
         <v>1428</v>
-      </c>
-      <c r="B374" t="s">
-        <v>1429</v>
       </c>
       <c r="D374">
         <v>1829</v>
@@ -19454,10 +19454,10 @@
         <v>468</v>
       </c>
       <c r="J374" t="s">
+        <v>1429</v>
+      </c>
+      <c r="L374" s="1" t="s">
         <v>1430</v>
-      </c>
-      <c r="L374" s="1" t="s">
-        <v>1431</v>
       </c>
       <c r="R374" t="s">
         <v>30</v>
@@ -19469,7 +19469,7 @@
         <v>59</v>
       </c>
       <c r="U374" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="W374">
         <v>2</v>
@@ -19477,13 +19477,13 @@
     </row>
     <row r="375" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B375" t="s">
         <v>1428</v>
       </c>
-      <c r="B375" t="s">
-        <v>1429</v>
-      </c>
       <c r="D375" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="E375" t="s">
         <v>176</v>
@@ -19492,10 +19492,10 @@
         <v>468</v>
       </c>
       <c r="J375" t="s">
+        <v>1432</v>
+      </c>
+      <c r="L375" s="1" t="s">
         <v>1433</v>
-      </c>
-      <c r="L375" s="1" t="s">
-        <v>1434</v>
       </c>
       <c r="R375" t="s">
         <v>30</v>
@@ -19515,10 +19515,10 @@
     </row>
     <row r="376" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B376" t="s">
         <v>1428</v>
-      </c>
-      <c r="B376" t="s">
-        <v>1429</v>
       </c>
       <c r="D376">
         <v>1837</v>
@@ -19530,10 +19530,10 @@
         <v>177</v>
       </c>
       <c r="J376" t="s">
+        <v>1434</v>
+      </c>
+      <c r="L376" s="1" t="s">
         <v>1435</v>
-      </c>
-      <c r="L376" s="1" t="s">
-        <v>1436</v>
       </c>
       <c r="R376" t="s">
         <v>30</v>
@@ -19553,10 +19553,10 @@
     </row>
     <row r="377" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B377" t="s">
         <v>1428</v>
-      </c>
-      <c r="B377" t="s">
-        <v>1429</v>
       </c>
       <c r="D377" t="s">
         <v>764</v>
@@ -19568,10 +19568,10 @@
         <v>676</v>
       </c>
       <c r="J377" t="s">
+        <v>1436</v>
+      </c>
+      <c r="L377" s="1" t="s">
         <v>1437</v>
-      </c>
-      <c r="L377" s="1" t="s">
-        <v>1438</v>
       </c>
       <c r="R377" t="s">
         <v>30</v>
@@ -19591,10 +19591,10 @@
     </row>
     <row r="378" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B378" t="s">
         <v>1428</v>
-      </c>
-      <c r="B378" t="s">
-        <v>1429</v>
       </c>
       <c r="D378" t="s">
         <v>449</v>
@@ -19606,10 +19606,10 @@
         <v>177</v>
       </c>
       <c r="J378" t="s">
+        <v>1438</v>
+      </c>
+      <c r="L378" s="1" t="s">
         <v>1439</v>
-      </c>
-      <c r="L378" s="1" t="s">
-        <v>1440</v>
       </c>
       <c r="R378" t="s">
         <v>30</v>
@@ -19629,13 +19629,13 @@
     </row>
     <row r="379" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B379" t="s">
         <v>1428</v>
       </c>
-      <c r="B379" t="s">
-        <v>1429</v>
-      </c>
       <c r="D379" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="E379" t="s">
         <v>176</v>
@@ -19644,10 +19644,10 @@
         <v>468</v>
       </c>
       <c r="J379" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L379" s="1" t="s">
         <v>1442</v>
-      </c>
-      <c r="L379" s="1" t="s">
-        <v>1443</v>
       </c>
       <c r="R379" t="s">
         <v>30</v>
@@ -19667,10 +19667,10 @@
     </row>
     <row r="380" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B380" t="s">
         <v>1428</v>
-      </c>
-      <c r="B380" t="s">
-        <v>1429</v>
       </c>
       <c r="D380">
         <v>1815</v>
@@ -19682,10 +19682,10 @@
         <v>468</v>
       </c>
       <c r="J380" t="s">
+        <v>1443</v>
+      </c>
+      <c r="L380" s="1" t="s">
         <v>1444</v>
-      </c>
-      <c r="L380" s="1" t="s">
-        <v>1445</v>
       </c>
       <c r="R380" t="s">
         <v>30</v>
@@ -19705,10 +19705,10 @@
     </row>
     <row r="381" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B381" t="s">
         <v>1428</v>
-      </c>
-      <c r="B381" t="s">
-        <v>1429</v>
       </c>
       <c r="D381">
         <v>1817</v>
@@ -19720,10 +19720,10 @@
         <v>468</v>
       </c>
       <c r="J381" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L381" s="1" t="s">
         <v>1446</v>
-      </c>
-      <c r="L381" s="1" t="s">
-        <v>1447</v>
       </c>
       <c r="R381" t="s">
         <v>30</v>
@@ -19743,13 +19743,13 @@
     </row>
     <row r="382" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B382" t="s">
         <v>1448</v>
       </c>
-      <c r="B382" t="s">
-        <v>1449</v>
-      </c>
       <c r="D382" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="E382" t="s">
         <v>239</v>
@@ -19758,16 +19758,16 @@
         <v>664</v>
       </c>
       <c r="J382" t="s">
+        <v>1449</v>
+      </c>
+      <c r="L382" s="1" t="s">
         <v>1450</v>
       </c>
-      <c r="L382" s="1" t="s">
+      <c r="R382" t="s">
+        <v>30</v>
+      </c>
+      <c r="S382" t="s">
         <v>1451</v>
-      </c>
-      <c r="R382" t="s">
-        <v>30</v>
-      </c>
-      <c r="S382" t="s">
-        <v>1452</v>
       </c>
       <c r="T382" t="s">
         <v>109</v>
@@ -19781,10 +19781,10 @@
     </row>
     <row r="383" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B383" t="s">
         <v>1448</v>
-      </c>
-      <c r="B383" t="s">
-        <v>1449</v>
       </c>
       <c r="D383" t="s">
         <v>993</v>
@@ -19796,16 +19796,16 @@
         <v>80</v>
       </c>
       <c r="J383" t="s">
+        <v>1452</v>
+      </c>
+      <c r="L383" s="1" t="s">
         <v>1453</v>
       </c>
-      <c r="L383" s="1" t="s">
+      <c r="R383" t="s">
+        <v>30</v>
+      </c>
+      <c r="S383" t="s">
         <v>1454</v>
-      </c>
-      <c r="R383" t="s">
-        <v>30</v>
-      </c>
-      <c r="S383" t="s">
-        <v>1455</v>
       </c>
       <c r="T383" t="s">
         <v>392</v>
@@ -19819,25 +19819,25 @@
     </row>
     <row r="384" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B384" t="s">
         <v>1448</v>
-      </c>
-      <c r="B384" t="s">
-        <v>1449</v>
       </c>
       <c r="D384">
         <v>1893</v>
       </c>
       <c r="E384" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F384" t="s">
         <v>1456</v>
       </c>
-      <c r="F384" t="s">
+      <c r="J384" t="s">
         <v>1457</v>
       </c>
-      <c r="J384" t="s">
+      <c r="L384" s="1" t="s">
         <v>1458</v>
-      </c>
-      <c r="L384" s="1" t="s">
-        <v>1459</v>
       </c>
       <c r="R384" t="s">
         <v>30</v>
@@ -19857,10 +19857,10 @@
     </row>
     <row r="385" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B385" t="s">
         <v>1448</v>
-      </c>
-      <c r="B385" t="s">
-        <v>1449</v>
       </c>
       <c r="D385">
         <v>1899</v>
@@ -19872,10 +19872,10 @@
         <v>80</v>
       </c>
       <c r="J385" t="s">
+        <v>1459</v>
+      </c>
+      <c r="L385" s="6" t="s">
         <v>1460</v>
-      </c>
-      <c r="L385" s="6" t="s">
-        <v>1461</v>
       </c>
       <c r="R385" t="s">
         <v>30</v>
@@ -19895,10 +19895,10 @@
     </row>
     <row r="386" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B386" t="s">
         <v>1462</v>
-      </c>
-      <c r="B386" t="s">
-        <v>1463</v>
       </c>
       <c r="D386" t="s">
         <v>378</v>
@@ -19907,13 +19907,13 @@
         <v>130</v>
       </c>
       <c r="F386" t="s">
+        <v>1463</v>
+      </c>
+      <c r="J386" t="s">
         <v>1464</v>
       </c>
-      <c r="J386" t="s">
+      <c r="L386" s="1" t="s">
         <v>1465</v>
-      </c>
-      <c r="L386" s="1" t="s">
-        <v>1466</v>
       </c>
       <c r="R386" t="s">
         <v>30</v>
@@ -19933,10 +19933,10 @@
     </row>
     <row r="387" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B387" t="s">
         <v>1462</v>
-      </c>
-      <c r="B387" t="s">
-        <v>1463</v>
       </c>
       <c r="D387" t="s">
         <v>54</v>
@@ -19945,13 +19945,13 @@
         <v>130</v>
       </c>
       <c r="F387" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="J387" t="s">
+        <v>1466</v>
+      </c>
+      <c r="L387" s="1" t="s">
         <v>1467</v>
-      </c>
-      <c r="L387" s="1" t="s">
-        <v>1468</v>
       </c>
       <c r="R387" t="s">
         <v>30</v>
@@ -19971,10 +19971,10 @@
     </row>
     <row r="388" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B388" t="s">
         <v>1462</v>
-      </c>
-      <c r="B388" t="s">
-        <v>1463</v>
       </c>
       <c r="D388" t="s">
         <v>54</v>
@@ -19983,13 +19983,13 @@
         <v>130</v>
       </c>
       <c r="F388" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="J388" t="s">
+        <v>1468</v>
+      </c>
+      <c r="L388" s="1" t="s">
         <v>1469</v>
-      </c>
-      <c r="L388" s="1" t="s">
-        <v>1470</v>
       </c>
       <c r="R388" t="s">
         <v>30</v>
@@ -20009,25 +20009,25 @@
     </row>
     <row r="389" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B389" t="s">
         <v>1462</v>
-      </c>
-      <c r="B389" t="s">
-        <v>1463</v>
       </c>
       <c r="D389" t="s">
         <v>54</v>
       </c>
       <c r="E389" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F389" t="s">
         <v>1471</v>
       </c>
-      <c r="F389" t="s">
+      <c r="J389" t="s">
         <v>1472</v>
       </c>
-      <c r="J389" t="s">
+      <c r="L389" s="1" t="s">
         <v>1473</v>
-      </c>
-      <c r="L389" s="1" t="s">
-        <v>1474</v>
       </c>
       <c r="R389" t="s">
         <v>30</v>
@@ -20047,10 +20047,10 @@
     </row>
     <row r="390" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B390" t="s">
         <v>1462</v>
-      </c>
-      <c r="B390" t="s">
-        <v>1463</v>
       </c>
       <c r="D390" t="s">
         <v>222</v>
@@ -20062,10 +20062,10 @@
         <v>372</v>
       </c>
       <c r="J390" t="s">
+        <v>1474</v>
+      </c>
+      <c r="L390" s="1" t="s">
         <v>1475</v>
-      </c>
-      <c r="L390" s="1" t="s">
-        <v>1476</v>
       </c>
       <c r="R390" t="s">
         <v>30</v>
@@ -20085,10 +20085,10 @@
     </row>
     <row r="391" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B391" t="s">
         <v>1462</v>
-      </c>
-      <c r="B391" t="s">
-        <v>1463</v>
       </c>
       <c r="D391" t="s">
         <v>222</v>
@@ -20100,10 +20100,10 @@
         <v>382</v>
       </c>
       <c r="J391" t="s">
+        <v>1476</v>
+      </c>
+      <c r="L391" s="1" t="s">
         <v>1477</v>
-      </c>
-      <c r="L391" s="1" t="s">
-        <v>1478</v>
       </c>
       <c r="R391" t="s">
         <v>30</v>
@@ -20123,10 +20123,10 @@
     </row>
     <row r="392" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B392" t="s">
         <v>1462</v>
-      </c>
-      <c r="B392" t="s">
-        <v>1463</v>
       </c>
       <c r="D392" t="s">
         <v>222</v>
@@ -20138,10 +20138,10 @@
         <v>63</v>
       </c>
       <c r="J392" t="s">
+        <v>1478</v>
+      </c>
+      <c r="L392" s="1" t="s">
         <v>1479</v>
-      </c>
-      <c r="L392" s="1" t="s">
-        <v>1480</v>
       </c>
       <c r="R392" t="s">
         <v>30</v>
@@ -20161,10 +20161,10 @@
     </row>
     <row r="393" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B393" t="s">
         <v>1462</v>
-      </c>
-      <c r="B393" t="s">
-        <v>1463</v>
       </c>
       <c r="D393" t="s">
         <v>810</v>
@@ -20173,13 +20173,13 @@
         <v>130</v>
       </c>
       <c r="F393" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="J393" t="s">
+        <v>1480</v>
+      </c>
+      <c r="L393" s="1" t="s">
         <v>1481</v>
-      </c>
-      <c r="L393" s="1" t="s">
-        <v>1482</v>
       </c>
       <c r="R393" t="s">
         <v>30</v>
@@ -20199,10 +20199,10 @@
     </row>
     <row r="394" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B394" t="s">
         <v>1462</v>
-      </c>
-      <c r="B394" t="s">
-        <v>1463</v>
       </c>
       <c r="D394" t="s">
         <v>810</v>
@@ -20214,10 +20214,10 @@
         <v>80</v>
       </c>
       <c r="J394" t="s">
+        <v>1482</v>
+      </c>
+      <c r="L394" s="1" t="s">
         <v>1483</v>
-      </c>
-      <c r="L394" s="1" t="s">
-        <v>1484</v>
       </c>
       <c r="R394" t="s">
         <v>30</v>
@@ -20237,10 +20237,10 @@
     </row>
     <row r="395" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B395" t="s">
         <v>1462</v>
-      </c>
-      <c r="B395" t="s">
-        <v>1463</v>
       </c>
       <c r="D395">
         <v>1890</v>
@@ -20252,10 +20252,10 @@
         <v>80</v>
       </c>
       <c r="J395" t="s">
+        <v>1484</v>
+      </c>
+      <c r="L395" s="1" t="s">
         <v>1485</v>
-      </c>
-      <c r="L395" s="1" t="s">
-        <v>1486</v>
       </c>
       <c r="R395" t="s">
         <v>30</v>
@@ -20275,10 +20275,10 @@
     </row>
     <row r="396" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B396" t="s">
         <v>1462</v>
-      </c>
-      <c r="B396" t="s">
-        <v>1463</v>
       </c>
       <c r="D396">
         <v>1890</v>
@@ -20287,13 +20287,13 @@
         <v>130</v>
       </c>
       <c r="F396" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="J396" t="s">
+        <v>1486</v>
+      </c>
+      <c r="L396" s="1" t="s">
         <v>1487</v>
-      </c>
-      <c r="L396" s="1" t="s">
-        <v>1488</v>
       </c>
       <c r="R396" t="s">
         <v>30</v>
@@ -20313,10 +20313,10 @@
     </row>
     <row r="397" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B397" t="s">
         <v>1462</v>
-      </c>
-      <c r="B397" t="s">
-        <v>1463</v>
       </c>
       <c r="D397" t="s">
         <v>971</v>
@@ -20328,10 +20328,10 @@
         <v>80</v>
       </c>
       <c r="J397" t="s">
+        <v>1488</v>
+      </c>
+      <c r="L397" s="1" t="s">
         <v>1489</v>
-      </c>
-      <c r="L397" s="1" t="s">
-        <v>1490</v>
       </c>
       <c r="R397" t="s">
         <v>30</v>
@@ -20351,10 +20351,10 @@
     </row>
     <row r="398" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B398" t="s">
         <v>1491</v>
-      </c>
-      <c r="B398" t="s">
-        <v>1492</v>
       </c>
       <c r="D398" t="s">
         <v>61</v>
@@ -20366,19 +20366,19 @@
         <v>326</v>
       </c>
       <c r="J398" t="s">
+        <v>1492</v>
+      </c>
+      <c r="L398" s="1" t="s">
         <v>1493</v>
       </c>
-      <c r="L398" s="1" t="s">
+      <c r="R398" t="s">
+        <v>30</v>
+      </c>
+      <c r="S398" t="s">
+        <v>31</v>
+      </c>
+      <c r="T398" t="s">
         <v>1494</v>
-      </c>
-      <c r="R398" t="s">
-        <v>30</v>
-      </c>
-      <c r="S398" t="s">
-        <v>31</v>
-      </c>
-      <c r="T398" t="s">
-        <v>1495</v>
       </c>
       <c r="U398" t="s">
         <v>1078</v>
@@ -20389,10 +20389,10 @@
     </row>
     <row r="399" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B399" t="s">
         <v>1491</v>
-      </c>
-      <c r="B399" t="s">
-        <v>1492</v>
       </c>
       <c r="D399" t="s">
         <v>993</v>
@@ -20404,10 +20404,10 @@
         <v>309</v>
       </c>
       <c r="J399" t="s">
+        <v>1495</v>
+      </c>
+      <c r="L399" s="1" t="s">
         <v>1496</v>
-      </c>
-      <c r="L399" s="1" t="s">
-        <v>1497</v>
       </c>
       <c r="R399" t="s">
         <v>30</v>
@@ -20427,25 +20427,25 @@
     </row>
     <row r="400" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B400" t="s">
         <v>1491</v>
-      </c>
-      <c r="B400" t="s">
-        <v>1492</v>
       </c>
       <c r="D400">
         <v>1890</v>
       </c>
       <c r="E400" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F400" t="s">
         <v>1373</v>
       </c>
-      <c r="F400" t="s">
-        <v>1374</v>
-      </c>
       <c r="J400" t="s">
+        <v>1497</v>
+      </c>
+      <c r="L400" s="1" t="s">
         <v>1498</v>
-      </c>
-      <c r="L400" s="1" t="s">
-        <v>1499</v>
       </c>
       <c r="R400" t="s">
         <v>30</v>
@@ -20465,10 +20465,10 @@
     </row>
     <row r="401" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B401" t="s">
         <v>1491</v>
-      </c>
-      <c r="B401" t="s">
-        <v>1492</v>
       </c>
       <c r="D401">
         <v>1892</v>
@@ -20480,10 +20480,10 @@
         <v>468</v>
       </c>
       <c r="J401" t="s">
+        <v>1499</v>
+      </c>
+      <c r="L401" s="1" t="s">
         <v>1500</v>
-      </c>
-      <c r="L401" s="1" t="s">
-        <v>1501</v>
       </c>
       <c r="R401" t="s">
         <v>30</v>
@@ -20503,10 +20503,10 @@
     </row>
     <row r="402" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B402" t="s">
         <v>1502</v>
-      </c>
-      <c r="B402" t="s">
-        <v>1503</v>
       </c>
       <c r="D402" t="s">
         <v>810</v>
@@ -20518,10 +20518,10 @@
         <v>36</v>
       </c>
       <c r="J402" t="s">
+        <v>1503</v>
+      </c>
+      <c r="L402" s="1" t="s">
         <v>1504</v>
-      </c>
-      <c r="L402" s="1" t="s">
-        <v>1505</v>
       </c>
       <c r="R402" t="s">
         <v>30</v>
@@ -20533,7 +20533,7 @@
         <v>282</v>
       </c>
       <c r="U402" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="W402">
         <v>3</v>
@@ -20541,13 +20541,13 @@
     </row>
     <row r="403" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B403" t="s">
         <v>1502</v>
       </c>
-      <c r="B403" t="s">
-        <v>1503</v>
-      </c>
       <c r="D403" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="E403" t="s">
         <v>35</v>
@@ -20556,22 +20556,22 @@
         <v>36</v>
       </c>
       <c r="J403" t="s">
+        <v>1507</v>
+      </c>
+      <c r="L403" s="1" t="s">
         <v>1508</v>
       </c>
-      <c r="L403" s="1" t="s">
+      <c r="R403" t="s">
+        <v>30</v>
+      </c>
+      <c r="S403" t="s">
+        <v>31</v>
+      </c>
+      <c r="T403" t="s">
         <v>1509</v>
       </c>
-      <c r="R403" t="s">
-        <v>30</v>
-      </c>
-      <c r="S403" t="s">
-        <v>31</v>
-      </c>
-      <c r="T403" t="s">
+      <c r="U403" t="s">
         <v>1510</v>
-      </c>
-      <c r="U403" t="s">
-        <v>1511</v>
       </c>
       <c r="W403">
         <v>3</v>
@@ -20579,10 +20579,10 @@
     </row>
     <row r="404" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B404" t="s">
         <v>1502</v>
-      </c>
-      <c r="B404" t="s">
-        <v>1503</v>
       </c>
       <c r="D404">
         <v>1895</v>
@@ -20594,10 +20594,10 @@
         <v>36</v>
       </c>
       <c r="J404" t="s">
+        <v>1511</v>
+      </c>
+      <c r="L404" s="1" t="s">
         <v>1512</v>
-      </c>
-      <c r="L404" s="1" t="s">
-        <v>1513</v>
       </c>
       <c r="R404" t="s">
         <v>30</v>
@@ -20609,7 +20609,7 @@
         <v>297</v>
       </c>
       <c r="U404" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="W404">
         <v>3</v>
@@ -20617,10 +20617,10 @@
     </row>
     <row r="405" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B405" t="s">
         <v>1502</v>
-      </c>
-      <c r="B405" t="s">
-        <v>1503</v>
       </c>
       <c r="D405">
         <v>1899</v>
@@ -20632,19 +20632,19 @@
         <v>36</v>
       </c>
       <c r="J405" t="s">
+        <v>1513</v>
+      </c>
+      <c r="L405" s="1" t="s">
         <v>1514</v>
       </c>
-      <c r="L405" s="1" t="s">
+      <c r="R405" t="s">
+        <v>30</v>
+      </c>
+      <c r="S405" t="s">
+        <v>31</v>
+      </c>
+      <c r="T405" t="s">
         <v>1515</v>
-      </c>
-      <c r="R405" t="s">
-        <v>30</v>
-      </c>
-      <c r="S405" t="s">
-        <v>31</v>
-      </c>
-      <c r="T405" t="s">
-        <v>1516</v>
       </c>
       <c r="U405" t="s">
         <v>1160</v>
@@ -20658,7 +20658,7 @@
         <v>1057</v>
       </c>
       <c r="B406" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D406" t="s">
         <v>635</v>
@@ -20670,10 +20670,10 @@
         <v>372</v>
       </c>
       <c r="J406" t="s">
+        <v>1517</v>
+      </c>
+      <c r="L406" s="1" t="s">
         <v>1518</v>
-      </c>
-      <c r="L406" s="1" t="s">
-        <v>1519</v>
       </c>
       <c r="R406" t="s">
         <v>30</v>
@@ -20696,7 +20696,7 @@
         <v>1057</v>
       </c>
       <c r="B407" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D407" t="s">
         <v>353</v>
@@ -20708,10 +20708,10 @@
         <v>372</v>
       </c>
       <c r="J407" t="s">
+        <v>1519</v>
+      </c>
+      <c r="L407" s="1" t="s">
         <v>1520</v>
-      </c>
-      <c r="L407" s="1" t="s">
-        <v>1521</v>
       </c>
       <c r="R407" t="s">
         <v>30</v>
@@ -20734,7 +20734,7 @@
         <v>1057</v>
       </c>
       <c r="B408" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D408" t="s">
         <v>61</v>
@@ -20746,10 +20746,10 @@
         <v>80</v>
       </c>
       <c r="J408" t="s">
+        <v>1521</v>
+      </c>
+      <c r="L408" s="1" t="s">
         <v>1522</v>
-      </c>
-      <c r="L408" s="1" t="s">
-        <v>1523</v>
       </c>
       <c r="R408" t="s">
         <v>30</v>
@@ -20758,7 +20758,7 @@
         <v>645</v>
       </c>
       <c r="T408" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="U408" t="s">
         <v>121</v>
@@ -20772,7 +20772,7 @@
         <v>1057</v>
       </c>
       <c r="B409" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D409" t="s">
         <v>61</v>
@@ -20784,10 +20784,10 @@
         <v>80</v>
       </c>
       <c r="J409" t="s">
+        <v>1524</v>
+      </c>
+      <c r="L409" s="1" t="s">
         <v>1525</v>
-      </c>
-      <c r="L409" s="1" t="s">
-        <v>1526</v>
       </c>
       <c r="R409" t="s">
         <v>30</v>
@@ -20810,7 +20810,7 @@
         <v>1057</v>
       </c>
       <c r="B410" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D410" t="s">
         <v>61</v>
@@ -20822,10 +20822,10 @@
         <v>80</v>
       </c>
       <c r="J410" t="s">
+        <v>1526</v>
+      </c>
+      <c r="L410" s="1" t="s">
         <v>1527</v>
-      </c>
-      <c r="L410" s="1" t="s">
-        <v>1528</v>
       </c>
       <c r="R410" t="s">
         <v>30</v>
@@ -20834,7 +20834,7 @@
         <v>645</v>
       </c>
       <c r="T410" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="U410" t="s">
         <v>75</v>
@@ -20848,7 +20848,7 @@
         <v>1057</v>
       </c>
       <c r="B411" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D411">
         <v>1891</v>
@@ -20860,10 +20860,10 @@
         <v>80</v>
       </c>
       <c r="J411" t="s">
+        <v>1528</v>
+      </c>
+      <c r="L411" s="1" t="s">
         <v>1529</v>
-      </c>
-      <c r="L411" s="1" t="s">
-        <v>1530</v>
       </c>
       <c r="R411" t="s">
         <v>30</v>
@@ -20886,7 +20886,7 @@
         <v>1057</v>
       </c>
       <c r="B412" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D412">
         <v>1890</v>
@@ -20898,10 +20898,10 @@
         <v>80</v>
       </c>
       <c r="J412" t="s">
+        <v>1530</v>
+      </c>
+      <c r="L412" s="1" t="s">
         <v>1531</v>
-      </c>
-      <c r="L412" s="1" t="s">
-        <v>1532</v>
       </c>
       <c r="R412" t="s">
         <v>30</v>
@@ -20924,7 +20924,7 @@
         <v>1057</v>
       </c>
       <c r="B413" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D413">
         <v>1895</v>
@@ -20936,22 +20936,22 @@
         <v>145</v>
       </c>
       <c r="J413" t="s">
+        <v>1532</v>
+      </c>
+      <c r="L413" s="1" t="s">
         <v>1533</v>
       </c>
-      <c r="L413" s="1" t="s">
+      <c r="R413" t="s">
+        <v>30</v>
+      </c>
+      <c r="S413" t="s">
         <v>1534</v>
       </c>
-      <c r="R413" t="s">
-        <v>30</v>
-      </c>
-      <c r="S413" t="s">
+      <c r="T413" t="s">
         <v>1535</v>
       </c>
-      <c r="T413" t="s">
+      <c r="U413" t="s">
         <v>1536</v>
-      </c>
-      <c r="U413" t="s">
-        <v>1537</v>
       </c>
       <c r="W413">
         <v>2</v>
@@ -20959,10 +20959,10 @@
     </row>
     <row r="414" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B414" t="s">
         <v>1538</v>
-      </c>
-      <c r="B414" t="s">
-        <v>1539</v>
       </c>
       <c r="D414" t="s">
         <v>54</v>
@@ -20974,19 +20974,19 @@
         <v>177</v>
       </c>
       <c r="J414" t="s">
+        <v>1539</v>
+      </c>
+      <c r="L414" s="1" t="s">
         <v>1540</v>
       </c>
-      <c r="L414" s="1" t="s">
+      <c r="R414" t="s">
+        <v>30</v>
+      </c>
+      <c r="S414" t="s">
+        <v>31</v>
+      </c>
+      <c r="T414" t="s">
         <v>1541</v>
-      </c>
-      <c r="R414" t="s">
-        <v>30</v>
-      </c>
-      <c r="S414" t="s">
-        <v>31</v>
-      </c>
-      <c r="T414" t="s">
-        <v>1542</v>
       </c>
       <c r="U414" t="s">
         <v>555</v>
@@ -20997,25 +20997,25 @@
     </row>
     <row r="415" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B415" t="s">
         <v>1538</v>
-      </c>
-      <c r="B415" t="s">
-        <v>1539</v>
       </c>
       <c r="D415">
         <v>1896</v>
       </c>
       <c r="E415" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F415" t="s">
+        <v>1240</v>
+      </c>
+      <c r="J415" t="s">
         <v>1543</v>
       </c>
-      <c r="F415" t="s">
-        <v>1241</v>
-      </c>
-      <c r="J415" t="s">
+      <c r="L415" s="1" t="s">
         <v>1544</v>
-      </c>
-      <c r="L415" s="1" t="s">
-        <v>1545</v>
       </c>
       <c r="R415" t="s">
         <v>30</v>
@@ -21035,10 +21035,10 @@
     </row>
     <row r="416" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B416" t="s">
         <v>1538</v>
-      </c>
-      <c r="B416" t="s">
-        <v>1539</v>
       </c>
       <c r="D416">
         <v>1894</v>
@@ -21053,7 +21053,7 @@
         <v>1098</v>
       </c>
       <c r="L416" s="1" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="R416" t="s">
         <v>30</v>
@@ -21062,7 +21062,7 @@
         <v>31</v>
       </c>
       <c r="T416" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="U416" t="s">
         <v>129</v>
@@ -21073,10 +21073,10 @@
     </row>
     <row r="417" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B417" t="s">
         <v>1538</v>
-      </c>
-      <c r="B417" t="s">
-        <v>1539</v>
       </c>
       <c r="D417">
         <v>1895</v>
@@ -21088,10 +21088,10 @@
         <v>56</v>
       </c>
       <c r="J417" t="s">
+        <v>1546</v>
+      </c>
+      <c r="L417" s="1" t="s">
         <v>1547</v>
-      </c>
-      <c r="L417" s="1" t="s">
-        <v>1548</v>
       </c>
       <c r="R417" t="s">
         <v>30</v>
@@ -21103,7 +21103,7 @@
         <v>659</v>
       </c>
       <c r="U417" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="W417">
         <v>3</v>
@@ -21111,13 +21111,13 @@
     </row>
     <row r="418" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B418" t="s">
         <v>1549</v>
       </c>
-      <c r="B418" t="s">
+      <c r="D418" t="s">
         <v>1550</v>
-      </c>
-      <c r="D418" t="s">
-        <v>1551</v>
       </c>
       <c r="E418" t="s">
         <v>111</v>
@@ -21126,10 +21126,10 @@
         <v>112</v>
       </c>
       <c r="J418" t="s">
+        <v>1551</v>
+      </c>
+      <c r="L418" s="1" t="s">
         <v>1552</v>
-      </c>
-      <c r="L418" s="1" t="s">
-        <v>1553</v>
       </c>
       <c r="R418" t="s">
         <v>30</v>
@@ -21149,10 +21149,10 @@
     </row>
     <row r="419" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B419" t="s">
         <v>1549</v>
-      </c>
-      <c r="B419" t="s">
-        <v>1550</v>
       </c>
       <c r="D419" t="s">
         <v>957</v>
@@ -21164,10 +21164,10 @@
         <v>80</v>
       </c>
       <c r="J419" t="s">
+        <v>1553</v>
+      </c>
+      <c r="L419" s="1" t="s">
         <v>1554</v>
-      </c>
-      <c r="L419" s="1" t="s">
-        <v>1555</v>
       </c>
       <c r="R419" t="s">
         <v>30</v>
@@ -21187,10 +21187,10 @@
     </row>
     <row r="420" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B420" t="s">
         <v>1549</v>
-      </c>
-      <c r="B420" t="s">
-        <v>1550</v>
       </c>
       <c r="D420">
         <v>1875</v>
@@ -21202,10 +21202,10 @@
         <v>438</v>
       </c>
       <c r="J420" t="s">
+        <v>1555</v>
+      </c>
+      <c r="L420" s="1" t="s">
         <v>1556</v>
-      </c>
-      <c r="L420" s="1" t="s">
-        <v>1557</v>
       </c>
       <c r="R420" t="s">
         <v>30</v>
@@ -21225,25 +21225,25 @@
     </row>
     <row r="421" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B421" t="s">
         <v>1549</v>
       </c>
-      <c r="B421" t="s">
-        <v>1550</v>
-      </c>
       <c r="D421" t="s">
+        <v>1557</v>
+      </c>
+      <c r="E421" t="s">
         <v>1558</v>
       </c>
-      <c r="E421" t="s">
+      <c r="F421" t="s">
         <v>1559</v>
       </c>
-      <c r="F421" t="s">
+      <c r="J421" t="s">
         <v>1560</v>
       </c>
-      <c r="J421" t="s">
+      <c r="L421" s="1" t="s">
         <v>1561</v>
-      </c>
-      <c r="L421" s="1" t="s">
-        <v>1562</v>
       </c>
       <c r="R421" t="s">
         <v>30</v>
@@ -21558,131 +21558,131 @@
     <hyperlink ref="L295" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
     <hyperlink ref="L296" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
     <hyperlink ref="L297" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="L298" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="L299" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="L300" r:id="rId298" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="L301" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="L302" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="L303" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="L304" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="L305" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="L306" r:id="rId304" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="L307" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="L308" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="L309" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="L310" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="L311" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="L312" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="L313" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="L314" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="L315" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="L316" r:id="rId314" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="L317" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="L318" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="L319" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="L320" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="L321" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="L322" r:id="rId320" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="L323" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="L324" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="L325" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="L326" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="L327" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="L328" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="L329" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="L330" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="L331" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="L332" r:id="rId330" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="L333" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="L334" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="L335" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="L336" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="L337" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="L338" r:id="rId336" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="L339" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="L340" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="L341" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="L342" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="L343" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="L344" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="L345" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="L346" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="L347" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="L348" r:id="rId346" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="L349" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="L350" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="L351" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="L352" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="L353" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="L354" r:id="rId352" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="L355" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="L356" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="L357" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="L358" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="L359" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="L360" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="L361" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="L362" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="L363" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="L364" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="L365" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="L366" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="L367" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="L368" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="L369" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="L370" r:id="rId368" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="L371" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="L372" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="L373" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="L374" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="L375" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="L376" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="L377" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="L378" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="L379" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="L380" r:id="rId378" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="L381" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="L382" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="L383" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="L384" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="L385" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="L386" r:id="rId384" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="L387" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="L388" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="L389" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="L390" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="L391" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="L392" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="L393" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="L394" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="L395" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="L396" r:id="rId394" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="L397" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="L398" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="L399" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="L400" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="L401" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="L402" r:id="rId400" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="L403" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="L404" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="L405" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="L406" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="L407" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="L408" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="L409" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="L410" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="L411" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="L412" r:id="rId410" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="L413" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="L414" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="L415" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="L416" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="L417" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="L418" r:id="rId416" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="L419" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="L420" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="L421" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="L262" r:id="rId420" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/Jean-Fran%C3%A7ois_Millet_-_The_Sower_-_Google_Art_Project.jpg/960px-Jean-Fran%C3%A7ois_Millet_-_The_Sower_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AD55A34B-4E25-4396-B911-838D251D201A}"/>
+    <hyperlink ref="L299" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="L300" r:id="rId297" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="L301" r:id="rId298" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="L302" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="L303" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="L304" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="L305" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="L306" r:id="rId303" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="L307" r:id="rId304" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="L308" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="L309" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="L310" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="L311" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="L312" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="L313" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="L314" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="L315" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="L316" r:id="rId313" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="L317" r:id="rId314" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="L318" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="L319" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="L320" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="L321" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="L322" r:id="rId319" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="L323" r:id="rId320" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="L324" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="L325" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="L326" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="L327" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="L328" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="L329" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="L330" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="L331" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="L332" r:id="rId329" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="L333" r:id="rId330" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="L334" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="L335" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="L336" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="L337" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="L338" r:id="rId335" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="L339" r:id="rId336" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="L340" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="L341" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="L342" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="L343" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="L344" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="L345" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="L346" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="L347" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="L348" r:id="rId345" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="L349" r:id="rId346" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="L350" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="L351" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="L352" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="L353" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="L354" r:id="rId351" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="L355" r:id="rId352" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="L356" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="L357" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="L358" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="L359" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="L360" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="L361" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="L362" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="L363" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="L364" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="L365" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="L366" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="L367" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="L368" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="L369" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="L370" r:id="rId367" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="L371" r:id="rId368" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="L372" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="L373" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="L374" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="L375" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="L376" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="L377" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="L378" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="L379" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="L380" r:id="rId377" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="L381" r:id="rId378" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="L382" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="L383" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="L384" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="L385" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="L386" r:id="rId383" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="L387" r:id="rId384" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="L388" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="L389" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="L390" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="L391" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="L392" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="L393" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="L394" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="L395" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="L396" r:id="rId393" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="L397" r:id="rId394" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="L398" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="L399" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="L400" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="L401" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="L402" r:id="rId399" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="L403" r:id="rId400" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="L404" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="L405" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="L406" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="L407" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="L408" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="L409" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="L410" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="L411" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="L412" r:id="rId409" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="L413" r:id="rId410" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="L414" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="L415" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="L416" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="L417" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="L418" r:id="rId415" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="L419" r:id="rId416" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="L420" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="L421" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="L262" r:id="rId419" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/Jean-Fran%C3%A7ois_Millet_-_The_Sower_-_Google_Art_Project.jpg/960px-Jean-Fran%C3%A7ois_Millet_-_The_Sower_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AD55A34B-4E25-4396-B911-838D251D201A}"/>
+    <hyperlink ref="L298" r:id="rId420" xr:uid="{DDE94C4E-CF54-4E41-BCDD-0E2DF2D957BF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8081FD6-3ACE-44C3-BFE9-D0A543974FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D021AEE-55F0-4474-A715-4CB48AC75822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15030" yWindow="45" windowWidth="13770" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -2110,9 +2110,6 @@
     <t>1874</t>
   </si>
   <si>
-    <t>"Répétitions de ballet sur scène"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/c/c9/Edgar_Degas_-_Ballet_Rehearsal_on_Stage_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -4438,9 +4435,6 @@
     <t>"Le Café de nuit"</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5e/Vincent_Willem_van_Gogh_076.jpg/1280px-Vincent_Willem_van_Gogh_076.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>"La Nuit étoilée"</t>
   </si>
   <si>
@@ -4808,6 +4802,12 @@
   </si>
   <si>
     <t>"L'Homme au balcon, boulevard Haussmann"</t>
+  </si>
+  <si>
+    <t>"Répétition d'un ballet sur scène"</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Van_Gogh_-_The_Night_Caf%C3%A9_%281888%29.jpg/1280px-Van_Gogh_-_The_Night_Caf%C3%A9_%281888%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -5490,7 +5490,7 @@
         <v>31</v>
       </c>
       <c r="T7" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="U7" t="s">
         <v>66</v>
@@ -5870,10 +5870,10 @@
         <v>31</v>
       </c>
       <c r="T17" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="U17" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="W17">
         <v>2</v>
@@ -6101,7 +6101,7 @@
         <v>109</v>
       </c>
       <c r="U23" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="W23">
         <v>3</v>
@@ -7136,10 +7136,10 @@
         <v>31</v>
       </c>
       <c r="T50" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="U50" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="W50">
         <v>3</v>
@@ -7463,7 +7463,7 @@
         <v>56</v>
       </c>
       <c r="J59" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>338</v>
@@ -7799,10 +7799,10 @@
         <v>330</v>
       </c>
       <c r="E68" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="F68" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J68" t="s">
         <v>369</v>
@@ -7872,7 +7872,7 @@
         <v>361</v>
       </c>
       <c r="D70" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="E70" t="s">
         <v>79</v>
@@ -8007,7 +8007,7 @@
         <v>31</v>
       </c>
       <c r="T73" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="U73" t="s">
         <v>345</v>
@@ -8024,7 +8024,7 @@
         <v>361</v>
       </c>
       <c r="D74" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="E74" t="s">
         <v>144</v>
@@ -8162,7 +8162,7 @@
         <v>155</v>
       </c>
       <c r="U77" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="W77">
         <v>1</v>
@@ -8390,7 +8390,7 @@
         <v>534</v>
       </c>
       <c r="U83" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="W83">
         <v>3</v>
@@ -8428,7 +8428,7 @@
         <v>244</v>
       </c>
       <c r="U84" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="W84">
         <v>3</v>
@@ -9173,7 +9173,7 @@
         <v>55</v>
       </c>
       <c r="F104" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="J104" t="s">
         <v>516</v>
@@ -9267,7 +9267,7 @@
         <v>374</v>
       </c>
       <c r="U106" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="W106">
         <v>1</v>
@@ -9708,7 +9708,7 @@
         <v>566</v>
       </c>
       <c r="F118" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="J118" t="s">
         <v>567</v>
@@ -10030,7 +10030,7 @@
         <v>602</v>
       </c>
       <c r="U126" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="W126">
         <v>1</v>
@@ -10766,7 +10766,7 @@
         <v>682</v>
       </c>
       <c r="D146" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="E146" t="s">
         <v>79</v>
@@ -10787,7 +10787,7 @@
         <v>31</v>
       </c>
       <c r="T146" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="U146" t="s">
         <v>685</v>
@@ -10927,16 +10927,16 @@
         <v>80</v>
       </c>
       <c r="J150" t="s">
+        <v>1594</v>
+      </c>
+      <c r="L150" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="L150" s="1" t="s">
+      <c r="R150" t="s">
+        <v>30</v>
+      </c>
+      <c r="S150" t="s">
         <v>697</v>
-      </c>
-      <c r="R150" t="s">
-        <v>30</v>
-      </c>
-      <c r="S150" t="s">
-        <v>698</v>
       </c>
       <c r="T150" t="s">
         <v>364</v>
@@ -10956,7 +10956,7 @@
         <v>682</v>
       </c>
       <c r="D151" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E151" t="s">
         <v>79</v>
@@ -10965,10 +10965,10 @@
         <v>80</v>
       </c>
       <c r="J151" t="s">
+        <v>699</v>
+      </c>
+      <c r="L151" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="L151" s="1" t="s">
-        <v>701</v>
       </c>
       <c r="R151" t="s">
         <v>30</v>
@@ -10994,7 +10994,7 @@
         <v>682</v>
       </c>
       <c r="D152" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E152" t="s">
         <v>79</v>
@@ -11003,19 +11003,19 @@
         <v>80</v>
       </c>
       <c r="J152" t="s">
+        <v>702</v>
+      </c>
+      <c r="L152" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="L152" s="1" t="s">
+      <c r="R152" t="s">
+        <v>30</v>
+      </c>
+      <c r="S152" t="s">
         <v>704</v>
       </c>
-      <c r="R152" t="s">
-        <v>30</v>
-      </c>
-      <c r="S152" t="s">
+      <c r="T152" t="s">
         <v>705</v>
-      </c>
-      <c r="T152" t="s">
-        <v>706</v>
       </c>
       <c r="U152" t="s">
         <v>134</v>
@@ -11041,10 +11041,10 @@
         <v>467</v>
       </c>
       <c r="J153" t="s">
+        <v>706</v>
+      </c>
+      <c r="L153" s="1" t="s">
         <v>707</v>
-      </c>
-      <c r="L153" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="R153" t="s">
         <v>30</v>
@@ -11056,7 +11056,7 @@
         <v>337</v>
       </c>
       <c r="U153" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="W153">
         <v>1</v>
@@ -11070,7 +11070,7 @@
         <v>682</v>
       </c>
       <c r="D154" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E154" t="s">
         <v>100</v>
@@ -11079,10 +11079,10 @@
         <v>101</v>
       </c>
       <c r="J154" t="s">
+        <v>710</v>
+      </c>
+      <c r="L154" s="1" t="s">
         <v>711</v>
-      </c>
-      <c r="L154" s="1" t="s">
-        <v>712</v>
       </c>
       <c r="R154" t="s">
         <v>30</v>
@@ -11108,7 +11108,7 @@
         <v>682</v>
       </c>
       <c r="D155" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E155" t="s">
         <v>79</v>
@@ -11117,22 +11117,22 @@
         <v>80</v>
       </c>
       <c r="J155" t="s">
+        <v>713</v>
+      </c>
+      <c r="L155" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="L155" s="1" t="s">
+      <c r="R155" t="s">
+        <v>30</v>
+      </c>
+      <c r="S155" t="s">
         <v>715</v>
-      </c>
-      <c r="R155" t="s">
-        <v>30</v>
-      </c>
-      <c r="S155" t="s">
-        <v>716</v>
       </c>
       <c r="T155" t="s">
         <v>115</v>
       </c>
       <c r="U155" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="W155">
         <v>1</v>
@@ -11152,19 +11152,19 @@
         <v>35</v>
       </c>
       <c r="F156" t="s">
+        <v>717</v>
+      </c>
+      <c r="J156" t="s">
         <v>718</v>
       </c>
-      <c r="J156" t="s">
+      <c r="L156" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="L156" s="1" t="s">
+      <c r="R156" t="s">
+        <v>30</v>
+      </c>
+      <c r="S156" t="s">
         <v>720</v>
-      </c>
-      <c r="R156" t="s">
-        <v>30</v>
-      </c>
-      <c r="S156" t="s">
-        <v>721</v>
       </c>
       <c r="T156" t="s">
         <v>364</v>
@@ -11184,7 +11184,7 @@
         <v>682</v>
       </c>
       <c r="D157" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E157" t="s">
         <v>79</v>
@@ -11193,19 +11193,19 @@
         <v>80</v>
       </c>
       <c r="J157" t="s">
+        <v>722</v>
+      </c>
+      <c r="L157" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="L157" s="1" t="s">
+      <c r="R157" t="s">
+        <v>30</v>
+      </c>
+      <c r="S157" t="s">
+        <v>31</v>
+      </c>
+      <c r="T157" t="s">
         <v>724</v>
-      </c>
-      <c r="R157" t="s">
-        <v>30</v>
-      </c>
-      <c r="S157" t="s">
-        <v>31</v>
-      </c>
-      <c r="T157" t="s">
-        <v>725</v>
       </c>
       <c r="U157" t="s">
         <v>346</v>
@@ -11216,13 +11216,13 @@
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>725</v>
+      </c>
+      <c r="B158" t="s">
         <v>726</v>
       </c>
-      <c r="B158" t="s">
+      <c r="D158" t="s">
         <v>727</v>
-      </c>
-      <c r="D158" t="s">
-        <v>728</v>
       </c>
       <c r="E158" t="s">
         <v>79</v>
@@ -11231,22 +11231,22 @@
         <v>408</v>
       </c>
       <c r="J158" t="s">
+        <v>728</v>
+      </c>
+      <c r="L158" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="L158" s="1" t="s">
+      <c r="R158" t="s">
+        <v>30</v>
+      </c>
+      <c r="S158" t="s">
+        <v>31</v>
+      </c>
+      <c r="T158" t="s">
         <v>730</v>
       </c>
-      <c r="R158" t="s">
-        <v>30</v>
-      </c>
-      <c r="S158" t="s">
-        <v>31</v>
-      </c>
-      <c r="T158" t="s">
-        <v>731</v>
-      </c>
       <c r="U158" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="W158">
         <v>1</v>
@@ -11254,10 +11254,10 @@
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>725</v>
+      </c>
+      <c r="B159" t="s">
         <v>726</v>
-      </c>
-      <c r="B159" t="s">
-        <v>727</v>
       </c>
       <c r="D159">
         <v>1824</v>
@@ -11269,10 +11269,10 @@
         <v>408</v>
       </c>
       <c r="J159" t="s">
+        <v>732</v>
+      </c>
+      <c r="L159" s="1" t="s">
         <v>733</v>
-      </c>
-      <c r="L159" s="1" t="s">
-        <v>734</v>
       </c>
       <c r="R159" t="s">
         <v>30</v>
@@ -11292,13 +11292,13 @@
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>725</v>
+      </c>
+      <c r="B160" t="s">
         <v>726</v>
       </c>
-      <c r="B160" t="s">
-        <v>727</v>
-      </c>
       <c r="D160" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E160" t="s">
         <v>79</v>
@@ -11307,22 +11307,22 @@
         <v>408</v>
       </c>
       <c r="J160" t="s">
+        <v>735</v>
+      </c>
+      <c r="L160" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="L160" s="1" t="s">
+      <c r="R160" t="s">
+        <v>30</v>
+      </c>
+      <c r="S160" t="s">
+        <v>31</v>
+      </c>
+      <c r="T160" t="s">
         <v>737</v>
       </c>
-      <c r="R160" t="s">
-        <v>30</v>
-      </c>
-      <c r="S160" t="s">
-        <v>31</v>
-      </c>
-      <c r="T160" t="s">
+      <c r="U160" t="s">
         <v>738</v>
-      </c>
-      <c r="U160" t="s">
-        <v>739</v>
       </c>
       <c r="W160">
         <v>1</v>
@@ -11330,13 +11330,13 @@
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>725</v>
+      </c>
+      <c r="B161" t="s">
         <v>726</v>
       </c>
-      <c r="B161" t="s">
-        <v>727</v>
-      </c>
       <c r="D161" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E161" t="s">
         <v>79</v>
@@ -11345,22 +11345,22 @@
         <v>408</v>
       </c>
       <c r="J161" t="s">
+        <v>740</v>
+      </c>
+      <c r="L161" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="L161" s="1" t="s">
+      <c r="R161" t="s">
+        <v>30</v>
+      </c>
+      <c r="S161" t="s">
+        <v>31</v>
+      </c>
+      <c r="T161" t="s">
         <v>742</v>
       </c>
-      <c r="R161" t="s">
-        <v>30</v>
-      </c>
-      <c r="S161" t="s">
-        <v>31</v>
-      </c>
-      <c r="T161" t="s">
+      <c r="U161" t="s">
         <v>743</v>
-      </c>
-      <c r="U161" t="s">
-        <v>744</v>
       </c>
       <c r="W161">
         <v>1</v>
@@ -11368,10 +11368,10 @@
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>725</v>
+      </c>
+      <c r="B162" t="s">
         <v>726</v>
-      </c>
-      <c r="B162" t="s">
-        <v>727</v>
       </c>
       <c r="D162" t="s">
         <v>493</v>
@@ -11383,10 +11383,10 @@
         <v>408</v>
       </c>
       <c r="J162" t="s">
+        <v>744</v>
+      </c>
+      <c r="L162" s="1" t="s">
         <v>745</v>
-      </c>
-      <c r="L162" s="1" t="s">
-        <v>746</v>
       </c>
       <c r="R162" t="s">
         <v>30</v>
@@ -11398,7 +11398,7 @@
         <v>230</v>
       </c>
       <c r="U162" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="W162">
         <v>1</v>
@@ -11406,26 +11406,26 @@
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>725</v>
+      </c>
+      <c r="B163" t="s">
         <v>726</v>
       </c>
-      <c r="B163" t="s">
-        <v>727</v>
-      </c>
       <c r="D163" t="s">
+        <v>747</v>
+      </c>
+      <c r="E163" t="s">
         <v>748</v>
-      </c>
-      <c r="E163" t="s">
-        <v>749</v>
       </c>
       <c r="F163" t="s">
         <v>340</v>
       </c>
       <c r="J163" t="s">
+        <v>749</v>
+      </c>
+      <c r="L163" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="L163" s="1" t="s">
-        <v>751</v>
-      </c>
       <c r="R163" t="s">
         <v>30</v>
       </c>
@@ -11433,10 +11433,10 @@
         <v>31</v>
       </c>
       <c r="T163" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="U163" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="W163">
         <v>1</v>
@@ -11444,13 +11444,13 @@
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>725</v>
+      </c>
+      <c r="B164" t="s">
         <v>726</v>
       </c>
-      <c r="B164" t="s">
-        <v>727</v>
-      </c>
       <c r="D164" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E164" t="s">
         <v>79</v>
@@ -11459,10 +11459,10 @@
         <v>408</v>
       </c>
       <c r="J164" t="s">
+        <v>753</v>
+      </c>
+      <c r="L164" s="1" t="s">
         <v>754</v>
-      </c>
-      <c r="L164" s="1" t="s">
-        <v>755</v>
       </c>
       <c r="R164" t="s">
         <v>30</v>
@@ -11474,7 +11474,7 @@
         <v>158</v>
       </c>
       <c r="U164" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="W164">
         <v>1</v>
@@ -11482,13 +11482,13 @@
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>725</v>
+      </c>
+      <c r="B165" t="s">
         <v>726</v>
       </c>
-      <c r="B165" t="s">
-        <v>727</v>
-      </c>
       <c r="D165" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E165" t="s">
         <v>79</v>
@@ -11500,7 +11500,7 @@
         <v>102</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="R165" t="s">
         <v>30</v>
@@ -11520,10 +11520,10 @@
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>725</v>
+      </c>
+      <c r="B166" t="s">
         <v>726</v>
-      </c>
-      <c r="B166" t="s">
-        <v>727</v>
       </c>
       <c r="D166">
         <v>1837</v>
@@ -11535,22 +11535,22 @@
         <v>586</v>
       </c>
       <c r="J166" t="s">
+        <v>758</v>
+      </c>
+      <c r="L166" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="L166" s="1" t="s">
+      <c r="R166" t="s">
+        <v>30</v>
+      </c>
+      <c r="S166" t="s">
+        <v>31</v>
+      </c>
+      <c r="T166" t="s">
         <v>760</v>
       </c>
-      <c r="R166" t="s">
-        <v>30</v>
-      </c>
-      <c r="S166" t="s">
-        <v>31</v>
-      </c>
-      <c r="T166" t="s">
+      <c r="U166" t="s">
         <v>761</v>
-      </c>
-      <c r="U166" t="s">
-        <v>762</v>
       </c>
       <c r="W166">
         <v>1</v>
@@ -11558,13 +11558,13 @@
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>725</v>
+      </c>
+      <c r="B167" t="s">
         <v>726</v>
       </c>
-      <c r="B167" t="s">
-        <v>727</v>
-      </c>
       <c r="D167" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E167" t="s">
         <v>79</v>
@@ -11573,22 +11573,22 @@
         <v>408</v>
       </c>
       <c r="J167" t="s">
+        <v>763</v>
+      </c>
+      <c r="L167" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="L167" s="1" t="s">
+      <c r="R167" t="s">
+        <v>30</v>
+      </c>
+      <c r="S167" t="s">
+        <v>31</v>
+      </c>
+      <c r="T167" t="s">
         <v>765</v>
       </c>
-      <c r="R167" t="s">
-        <v>30</v>
-      </c>
-      <c r="S167" t="s">
-        <v>31</v>
-      </c>
-      <c r="T167" t="s">
-        <v>766</v>
-      </c>
       <c r="U167" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="W167">
         <v>1</v>
@@ -11596,10 +11596,10 @@
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>725</v>
+      </c>
+      <c r="B168" t="s">
         <v>726</v>
-      </c>
-      <c r="B168" t="s">
-        <v>727</v>
       </c>
       <c r="D168" t="s">
         <v>529</v>
@@ -11611,22 +11611,22 @@
         <v>118</v>
       </c>
       <c r="J168" t="s">
+        <v>766</v>
+      </c>
+      <c r="L168" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="L168" s="1" t="s">
+      <c r="R168" t="s">
+        <v>30</v>
+      </c>
+      <c r="S168" t="s">
+        <v>31</v>
+      </c>
+      <c r="T168" t="s">
         <v>768</v>
       </c>
-      <c r="R168" t="s">
-        <v>30</v>
-      </c>
-      <c r="S168" t="s">
-        <v>31</v>
-      </c>
-      <c r="T168" t="s">
-        <v>769</v>
-      </c>
       <c r="U168" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="W168">
         <v>1</v>
@@ -11634,10 +11634,10 @@
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>725</v>
+      </c>
+      <c r="B169" t="s">
         <v>726</v>
-      </c>
-      <c r="B169" t="s">
-        <v>727</v>
       </c>
       <c r="D169" t="s">
         <v>424</v>
@@ -11646,28 +11646,28 @@
         <v>79</v>
       </c>
       <c r="F169" t="s">
+        <v>769</v>
+      </c>
+      <c r="J169" t="s">
         <v>770</v>
       </c>
-      <c r="J169" t="s">
+      <c r="L169" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="L169" s="1" t="s">
+      <c r="M169" t="s">
         <v>772</v>
       </c>
-      <c r="M169" t="s">
+      <c r="R169" t="s">
+        <v>30</v>
+      </c>
+      <c r="S169" t="s">
         <v>773</v>
       </c>
-      <c r="R169" t="s">
-        <v>30</v>
-      </c>
-      <c r="S169" t="s">
+      <c r="T169" t="s">
         <v>774</v>
       </c>
-      <c r="T169" t="s">
+      <c r="U169" t="s">
         <v>775</v>
-      </c>
-      <c r="U169" t="s">
-        <v>776</v>
       </c>
       <c r="W169">
         <v>1</v>
@@ -11675,10 +11675,10 @@
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>776</v>
+      </c>
+      <c r="B170" t="s">
         <v>777</v>
-      </c>
-      <c r="B170" t="s">
-        <v>778</v>
       </c>
       <c r="D170" t="s">
         <v>222</v>
@@ -11690,10 +11690,10 @@
         <v>136</v>
       </c>
       <c r="J170" t="s">
+        <v>778</v>
+      </c>
+      <c r="L170" s="1" t="s">
         <v>779</v>
-      </c>
-      <c r="L170" s="1" t="s">
-        <v>780</v>
       </c>
       <c r="R170" t="s">
         <v>30</v>
@@ -11713,10 +11713,10 @@
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>776</v>
+      </c>
+      <c r="B171" t="s">
         <v>777</v>
-      </c>
-      <c r="B171" t="s">
-        <v>778</v>
       </c>
       <c r="D171" t="s">
         <v>352</v>
@@ -11728,10 +11728,10 @@
         <v>80</v>
       </c>
       <c r="J171" t="s">
+        <v>780</v>
+      </c>
+      <c r="L171" s="1" t="s">
         <v>781</v>
-      </c>
-      <c r="L171" s="1" t="s">
-        <v>782</v>
       </c>
       <c r="R171" t="s">
         <v>30</v>
@@ -11740,7 +11740,7 @@
         <v>637</v>
       </c>
       <c r="T171" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="U171" t="s">
         <v>69</v>
@@ -11751,10 +11751,10 @@
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>776</v>
+      </c>
+      <c r="B172" t="s">
         <v>777</v>
-      </c>
-      <c r="B172" t="s">
-        <v>778</v>
       </c>
       <c r="D172">
         <v>1900</v>
@@ -11766,11 +11766,11 @@
         <v>80</v>
       </c>
       <c r="J172" t="s">
+        <v>783</v>
+      </c>
+      <c r="L172" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="L172" s="1" t="s">
-        <v>785</v>
-      </c>
       <c r="R172" t="s">
         <v>30</v>
       </c>
@@ -11778,10 +11778,10 @@
         <v>31</v>
       </c>
       <c r="T172" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="U172" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="W172">
         <v>3</v>
@@ -11789,10 +11789,10 @@
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>776</v>
+      </c>
+      <c r="B173" t="s">
         <v>777</v>
-      </c>
-      <c r="B173" t="s">
-        <v>778</v>
       </c>
       <c r="D173">
         <v>1892</v>
@@ -11804,22 +11804,22 @@
         <v>136</v>
       </c>
       <c r="J173" t="s">
+        <v>785</v>
+      </c>
+      <c r="L173" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="L173" s="1" t="s">
+      <c r="R173" t="s">
+        <v>30</v>
+      </c>
+      <c r="S173" t="s">
+        <v>31</v>
+      </c>
+      <c r="T173" t="s">
         <v>787</v>
       </c>
-      <c r="R173" t="s">
-        <v>30</v>
-      </c>
-      <c r="S173" t="s">
-        <v>31</v>
-      </c>
-      <c r="T173" t="s">
-        <v>788</v>
-      </c>
       <c r="U173" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="W173">
         <v>3</v>
@@ -11830,7 +11830,7 @@
         <v>442</v>
       </c>
       <c r="B174" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D174" t="s">
         <v>192</v>
@@ -11842,10 +11842,10 @@
         <v>72</v>
       </c>
       <c r="J174" t="s">
+        <v>789</v>
+      </c>
+      <c r="L174" s="1" t="s">
         <v>790</v>
-      </c>
-      <c r="L174" s="1" t="s">
-        <v>791</v>
       </c>
       <c r="R174" t="s">
         <v>30</v>
@@ -11857,7 +11857,7 @@
         <v>198</v>
       </c>
       <c r="U174" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="W174">
         <v>3</v>
@@ -11868,7 +11868,7 @@
         <v>442</v>
       </c>
       <c r="B175" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D175" t="s">
         <v>317</v>
@@ -11880,10 +11880,10 @@
         <v>72</v>
       </c>
       <c r="J175" t="s">
+        <v>792</v>
+      </c>
+      <c r="L175" s="1" t="s">
         <v>793</v>
-      </c>
-      <c r="L175" s="1" t="s">
-        <v>794</v>
       </c>
       <c r="R175" t="s">
         <v>30</v>
@@ -11895,7 +11895,7 @@
         <v>584</v>
       </c>
       <c r="U175" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="W175">
         <v>3</v>
@@ -11906,22 +11906,22 @@
         <v>442</v>
       </c>
       <c r="B176" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D176">
         <v>1885</v>
       </c>
       <c r="E176" t="s">
+        <v>795</v>
+      </c>
+      <c r="F176" t="s">
         <v>796</v>
       </c>
-      <c r="F176" t="s">
+      <c r="J176" t="s">
         <v>797</v>
       </c>
-      <c r="J176" t="s">
+      <c r="L176" s="1" t="s">
         <v>798</v>
-      </c>
-      <c r="L176" s="1" t="s">
-        <v>799</v>
       </c>
       <c r="R176" t="s">
         <v>30</v>
@@ -11944,7 +11944,7 @@
         <v>442</v>
       </c>
       <c r="B177" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D177">
         <v>1899</v>
@@ -11956,10 +11956,10 @@
         <v>72</v>
       </c>
       <c r="J177" t="s">
+        <v>799</v>
+      </c>
+      <c r="L177" s="1" t="s">
         <v>800</v>
-      </c>
-      <c r="L177" s="1" t="s">
-        <v>801</v>
       </c>
       <c r="R177" t="s">
         <v>30</v>
@@ -11971,7 +11971,7 @@
         <v>155</v>
       </c>
       <c r="U177" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="W177">
         <v>3</v>
@@ -11979,10 +11979,10 @@
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>802</v>
+      </c>
+      <c r="B178" t="s">
         <v>803</v>
-      </c>
-      <c r="B178" t="s">
-        <v>804</v>
       </c>
       <c r="D178" t="s">
         <v>54</v>
@@ -11994,22 +11994,22 @@
         <v>63</v>
       </c>
       <c r="J178" t="s">
+        <v>804</v>
+      </c>
+      <c r="L178" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="L178" s="1" t="s">
+      <c r="R178" t="s">
+        <v>30</v>
+      </c>
+      <c r="S178" t="s">
+        <v>31</v>
+      </c>
+      <c r="T178" t="s">
         <v>806</v>
       </c>
-      <c r="R178" t="s">
-        <v>30</v>
-      </c>
-      <c r="S178" t="s">
-        <v>31</v>
-      </c>
-      <c r="T178" t="s">
+      <c r="U178" t="s">
         <v>807</v>
-      </c>
-      <c r="U178" t="s">
-        <v>808</v>
       </c>
       <c r="W178">
         <v>3</v>
@@ -12017,13 +12017,13 @@
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>802</v>
+      </c>
+      <c r="B179" t="s">
         <v>803</v>
       </c>
-      <c r="B179" t="s">
-        <v>804</v>
-      </c>
       <c r="D179" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E179" t="s">
         <v>308</v>
@@ -12032,10 +12032,10 @@
         <v>309</v>
       </c>
       <c r="J179" t="s">
+        <v>809</v>
+      </c>
+      <c r="L179" s="1" t="s">
         <v>810</v>
-      </c>
-      <c r="L179" s="1" t="s">
-        <v>811</v>
       </c>
       <c r="R179" t="s">
         <v>30</v>
@@ -12055,10 +12055,10 @@
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>802</v>
+      </c>
+      <c r="B180" t="s">
         <v>803</v>
-      </c>
-      <c r="B180" t="s">
-        <v>804</v>
       </c>
       <c r="D180">
         <v>1891</v>
@@ -12070,10 +12070,10 @@
         <v>309</v>
       </c>
       <c r="J180" t="s">
+        <v>811</v>
+      </c>
+      <c r="L180" s="1" t="s">
         <v>812</v>
-      </c>
-      <c r="L180" s="1" t="s">
-        <v>813</v>
       </c>
       <c r="R180" t="s">
         <v>30</v>
@@ -12093,25 +12093,25 @@
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>802</v>
+      </c>
+      <c r="B181" t="s">
         <v>803</v>
-      </c>
-      <c r="B181" t="s">
-        <v>804</v>
       </c>
       <c r="D181">
         <v>1899</v>
       </c>
       <c r="E181" t="s">
+        <v>813</v>
+      </c>
+      <c r="F181" t="s">
         <v>814</v>
       </c>
-      <c r="F181" t="s">
+      <c r="J181" t="s">
         <v>815</v>
       </c>
-      <c r="J181" t="s">
+      <c r="L181" s="1" t="s">
         <v>816</v>
-      </c>
-      <c r="L181" s="1" t="s">
-        <v>817</v>
       </c>
       <c r="R181" t="s">
         <v>30</v>
@@ -12131,37 +12131,37 @@
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>817</v>
+      </c>
+      <c r="B182" t="s">
         <v>818</v>
-      </c>
-      <c r="B182" t="s">
-        <v>819</v>
       </c>
       <c r="D182" t="s">
         <v>424</v>
       </c>
       <c r="E182" t="s">
+        <v>819</v>
+      </c>
+      <c r="F182" t="s">
         <v>820</v>
       </c>
-      <c r="F182" t="s">
+      <c r="J182" t="s">
         <v>821</v>
       </c>
-      <c r="J182" t="s">
+      <c r="L182" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="L182" s="1" t="s">
+      <c r="R182" t="s">
+        <v>30</v>
+      </c>
+      <c r="S182" t="s">
+        <v>31</v>
+      </c>
+      <c r="T182" t="s">
         <v>823</v>
       </c>
-      <c r="R182" t="s">
-        <v>30</v>
-      </c>
-      <c r="S182" t="s">
-        <v>31</v>
-      </c>
-      <c r="T182" t="s">
+      <c r="U182" t="s">
         <v>824</v>
-      </c>
-      <c r="U182" t="s">
-        <v>825</v>
       </c>
       <c r="W182">
         <v>3</v>
@@ -12169,25 +12169,25 @@
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>817</v>
+      </c>
+      <c r="B183" t="s">
         <v>818</v>
-      </c>
-      <c r="B183" t="s">
-        <v>819</v>
       </c>
       <c r="D183" t="s">
         <v>150</v>
       </c>
       <c r="E183" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F183" t="s">
+        <v>825</v>
+      </c>
+      <c r="J183" t="s">
         <v>826</v>
       </c>
-      <c r="J183" t="s">
+      <c r="L183" s="1" t="s">
         <v>827</v>
-      </c>
-      <c r="L183" s="1" t="s">
-        <v>828</v>
       </c>
       <c r="R183" t="s">
         <v>30</v>
@@ -12196,7 +12196,7 @@
         <v>202</v>
       </c>
       <c r="T183" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="U183" t="s">
         <v>189</v>
@@ -12207,25 +12207,25 @@
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>817</v>
+      </c>
+      <c r="B184" t="s">
         <v>818</v>
-      </c>
-      <c r="B184" t="s">
-        <v>819</v>
       </c>
       <c r="D184">
         <v>1872</v>
       </c>
       <c r="E184" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="F184" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="J184" t="s">
+        <v>829</v>
+      </c>
+      <c r="L184" s="1" t="s">
         <v>830</v>
-      </c>
-      <c r="L184" s="1" t="s">
-        <v>831</v>
       </c>
       <c r="R184" t="s">
         <v>30</v>
@@ -12234,10 +12234,10 @@
         <v>202</v>
       </c>
       <c r="T184" t="s">
+        <v>831</v>
+      </c>
+      <c r="U184" t="s">
         <v>832</v>
-      </c>
-      <c r="U184" t="s">
-        <v>833</v>
       </c>
       <c r="W184">
         <v>3</v>
@@ -12245,25 +12245,25 @@
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>817</v>
+      </c>
+      <c r="B185" t="s">
         <v>818</v>
-      </c>
-      <c r="B185" t="s">
-        <v>819</v>
       </c>
       <c r="D185">
         <v>1880</v>
       </c>
       <c r="E185" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F185" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="J185" t="s">
+        <v>833</v>
+      </c>
+      <c r="L185" s="1" t="s">
         <v>834</v>
-      </c>
-      <c r="L185" s="1" t="s">
-        <v>835</v>
       </c>
       <c r="R185" t="s">
         <v>30</v>
@@ -12283,25 +12283,25 @@
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>835</v>
+      </c>
+      <c r="B186" t="s">
         <v>836</v>
       </c>
-      <c r="B186" t="s">
+      <c r="D186" t="s">
         <v>837</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
         <v>838</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
         <v>839</v>
       </c>
-      <c r="F186" t="s">
+      <c r="J186" t="s">
         <v>840</v>
       </c>
-      <c r="J186" t="s">
+      <c r="L186" s="1" t="s">
         <v>841</v>
-      </c>
-      <c r="L186" s="1" t="s">
-        <v>842</v>
       </c>
       <c r="R186" t="s">
         <v>30</v>
@@ -12321,25 +12321,25 @@
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>835</v>
+      </c>
+      <c r="B187" t="s">
         <v>836</v>
       </c>
-      <c r="B187" t="s">
-        <v>837</v>
-      </c>
       <c r="D187" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E187" t="s">
+        <v>838</v>
+      </c>
+      <c r="F187" t="s">
         <v>839</v>
       </c>
-      <c r="F187" t="s">
-        <v>840</v>
-      </c>
       <c r="J187" t="s">
+        <v>842</v>
+      </c>
+      <c r="L187" s="1" t="s">
         <v>843</v>
-      </c>
-      <c r="L187" s="1" t="s">
-        <v>844</v>
       </c>
       <c r="R187" t="s">
         <v>30</v>
@@ -12359,13 +12359,13 @@
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>835</v>
+      </c>
+      <c r="B188" t="s">
         <v>836</v>
       </c>
-      <c r="B188" t="s">
-        <v>837</v>
-      </c>
       <c r="D188" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E188" t="s">
         <v>193</v>
@@ -12374,10 +12374,10 @@
         <v>194</v>
       </c>
       <c r="J188" t="s">
+        <v>845</v>
+      </c>
+      <c r="L188" s="1" t="s">
         <v>846</v>
-      </c>
-      <c r="L188" s="1" t="s">
-        <v>847</v>
       </c>
       <c r="R188" t="s">
         <v>30</v>
@@ -12389,7 +12389,7 @@
         <v>99</v>
       </c>
       <c r="U188" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="W188">
         <v>3</v>
@@ -12397,25 +12397,25 @@
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>835</v>
+      </c>
+      <c r="B189" t="s">
         <v>836</v>
-      </c>
-      <c r="B189" t="s">
-        <v>837</v>
       </c>
       <c r="D189">
         <v>1818</v>
       </c>
       <c r="E189" t="s">
+        <v>847</v>
+      </c>
+      <c r="F189" t="s">
         <v>848</v>
       </c>
-      <c r="F189" t="s">
+      <c r="J189" t="s">
         <v>849</v>
       </c>
-      <c r="J189" t="s">
+      <c r="L189" s="1" t="s">
         <v>850</v>
-      </c>
-      <c r="L189" s="1" t="s">
-        <v>851</v>
       </c>
       <c r="R189" t="s">
         <v>30</v>
@@ -12438,7 +12438,7 @@
         <v>360</v>
       </c>
       <c r="B190" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D190" t="s">
         <v>222</v>
@@ -12450,10 +12450,10 @@
         <v>112</v>
       </c>
       <c r="J190" t="s">
+        <v>852</v>
+      </c>
+      <c r="L190" s="1" t="s">
         <v>853</v>
-      </c>
-      <c r="L190" s="1" t="s">
-        <v>854</v>
       </c>
       <c r="R190" t="s">
         <v>30</v>
@@ -12462,7 +12462,7 @@
         <v>202</v>
       </c>
       <c r="T190" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="U190" t="s">
         <v>518</v>
@@ -12476,22 +12476,22 @@
         <v>360</v>
       </c>
       <c r="B191" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D191" t="s">
         <v>222</v>
       </c>
       <c r="E191" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="F191" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="J191" t="s">
+        <v>855</v>
+      </c>
+      <c r="L191" s="1" t="s">
         <v>856</v>
-      </c>
-      <c r="L191" s="1" t="s">
-        <v>857</v>
       </c>
       <c r="R191" t="s">
         <v>30</v>
@@ -12514,7 +12514,7 @@
         <v>360</v>
       </c>
       <c r="B192" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D192" t="s">
         <v>238</v>
@@ -12526,10 +12526,10 @@
         <v>80</v>
       </c>
       <c r="J192" t="s">
+        <v>857</v>
+      </c>
+      <c r="L192" s="1" t="s">
         <v>858</v>
-      </c>
-      <c r="L192" s="1" t="s">
-        <v>859</v>
       </c>
       <c r="R192" t="s">
         <v>30</v>
@@ -12552,7 +12552,7 @@
         <v>360</v>
       </c>
       <c r="B193" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D193" t="s">
         <v>634</v>
@@ -12564,10 +12564,10 @@
         <v>80</v>
       </c>
       <c r="J193" t="s">
+        <v>859</v>
+      </c>
+      <c r="L193" s="1" t="s">
         <v>860</v>
-      </c>
-      <c r="L193" s="1" t="s">
-        <v>861</v>
       </c>
       <c r="R193" t="s">
         <v>30</v>
@@ -12579,7 +12579,7 @@
         <v>197</v>
       </c>
       <c r="U193" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="W193">
         <v>1</v>
@@ -12590,7 +12590,7 @@
         <v>360</v>
       </c>
       <c r="B194" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D194" t="s">
         <v>352</v>
@@ -12602,10 +12602,10 @@
         <v>393</v>
       </c>
       <c r="J194" t="s">
+        <v>862</v>
+      </c>
+      <c r="L194" s="1" t="s">
         <v>863</v>
-      </c>
-      <c r="L194" s="1" t="s">
-        <v>864</v>
       </c>
       <c r="R194" t="s">
         <v>30</v>
@@ -12628,10 +12628,10 @@
         <v>360</v>
       </c>
       <c r="B195" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D195" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E195" t="s">
         <v>674</v>
@@ -12640,22 +12640,22 @@
         <v>675</v>
       </c>
       <c r="J195" t="s">
+        <v>865</v>
+      </c>
+      <c r="L195" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="L195" s="1" t="s">
+      <c r="R195" t="s">
+        <v>30</v>
+      </c>
+      <c r="S195" t="s">
+        <v>31</v>
+      </c>
+      <c r="T195" t="s">
         <v>867</v>
       </c>
-      <c r="R195" t="s">
-        <v>30</v>
-      </c>
-      <c r="S195" t="s">
-        <v>31</v>
-      </c>
-      <c r="T195" t="s">
+      <c r="U195" t="s">
         <v>868</v>
-      </c>
-      <c r="U195" t="s">
-        <v>869</v>
       </c>
       <c r="W195">
         <v>1</v>
@@ -12666,7 +12666,7 @@
         <v>360</v>
       </c>
       <c r="B196" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D196">
         <v>1888</v>
@@ -12675,13 +12675,13 @@
         <v>430</v>
       </c>
       <c r="F196" t="s">
+        <v>869</v>
+      </c>
+      <c r="J196" t="s">
         <v>870</v>
       </c>
-      <c r="J196" t="s">
+      <c r="L196" s="1" t="s">
         <v>871</v>
-      </c>
-      <c r="L196" s="1" t="s">
-        <v>872</v>
       </c>
       <c r="R196" t="s">
         <v>30</v>
@@ -12704,22 +12704,22 @@
         <v>360</v>
       </c>
       <c r="B197" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D197">
         <v>1889</v>
       </c>
       <c r="E197" t="s">
+        <v>872</v>
+      </c>
+      <c r="F197" t="s">
         <v>873</v>
       </c>
-      <c r="F197" t="s">
+      <c r="J197" t="s">
         <v>874</v>
       </c>
-      <c r="J197" t="s">
+      <c r="L197" s="1" t="s">
         <v>875</v>
-      </c>
-      <c r="L197" s="1" t="s">
-        <v>876</v>
       </c>
       <c r="R197" t="s">
         <v>30</v>
@@ -12742,7 +12742,7 @@
         <v>360</v>
       </c>
       <c r="B198" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D198">
         <v>1888</v>
@@ -12754,10 +12754,10 @@
         <v>80</v>
       </c>
       <c r="J198" t="s">
+        <v>876</v>
+      </c>
+      <c r="L198" s="1" t="s">
         <v>877</v>
-      </c>
-      <c r="L198" s="1" t="s">
-        <v>878</v>
       </c>
       <c r="R198" t="s">
         <v>30</v>
@@ -12780,7 +12780,7 @@
         <v>360</v>
       </c>
       <c r="B199" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D199">
         <v>1891</v>
@@ -12792,10 +12792,10 @@
         <v>145</v>
       </c>
       <c r="J199" t="s">
+        <v>878</v>
+      </c>
+      <c r="L199" s="1" t="s">
         <v>879</v>
-      </c>
-      <c r="L199" s="1" t="s">
-        <v>880</v>
       </c>
       <c r="R199" t="s">
         <v>30</v>
@@ -12818,7 +12818,7 @@
         <v>360</v>
       </c>
       <c r="B200" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D200">
         <v>1892</v>
@@ -12827,11 +12827,11 @@
         <v>56</v>
       </c>
       <c r="J200" t="s">
+        <v>880</v>
+      </c>
+      <c r="L200" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="L200" s="1" t="s">
-        <v>882</v>
-      </c>
       <c r="R200" t="s">
         <v>30</v>
       </c>
@@ -12839,10 +12839,10 @@
         <v>31</v>
       </c>
       <c r="T200" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="U200" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="W200">
         <v>1</v>
@@ -12853,7 +12853,7 @@
         <v>360</v>
       </c>
       <c r="B201" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D201">
         <v>1894</v>
@@ -12865,10 +12865,10 @@
         <v>101</v>
       </c>
       <c r="J201" t="s">
+        <v>882</v>
+      </c>
+      <c r="L201" s="1" t="s">
         <v>883</v>
-      </c>
-      <c r="L201" s="1" t="s">
-        <v>884</v>
       </c>
       <c r="R201" t="s">
         <v>30</v>
@@ -12891,10 +12891,10 @@
         <v>405</v>
       </c>
       <c r="B202" t="s">
+        <v>884</v>
+      </c>
+      <c r="D202" t="s">
         <v>885</v>
-      </c>
-      <c r="D202" t="s">
-        <v>886</v>
       </c>
       <c r="E202" t="s">
         <v>79</v>
@@ -12903,22 +12903,22 @@
         <v>408</v>
       </c>
       <c r="J202" t="s">
+        <v>886</v>
+      </c>
+      <c r="L202" s="1" t="s">
         <v>887</v>
       </c>
-      <c r="L202" s="1" t="s">
+      <c r="R202" t="s">
+        <v>30</v>
+      </c>
+      <c r="S202" t="s">
+        <v>31</v>
+      </c>
+      <c r="T202" t="s">
         <v>888</v>
       </c>
-      <c r="R202" t="s">
-        <v>30</v>
-      </c>
-      <c r="S202" t="s">
-        <v>31</v>
-      </c>
-      <c r="T202" t="s">
+      <c r="U202" t="s">
         <v>889</v>
-      </c>
-      <c r="U202" t="s">
-        <v>890</v>
       </c>
       <c r="W202">
         <v>2</v>
@@ -12929,22 +12929,22 @@
         <v>405</v>
       </c>
       <c r="B203" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D203" t="s">
+        <v>890</v>
+      </c>
+      <c r="E203" t="s">
         <v>891</v>
       </c>
-      <c r="E203" t="s">
+      <c r="F203" t="s">
         <v>892</v>
       </c>
-      <c r="F203" t="s">
+      <c r="J203" t="s">
         <v>893</v>
       </c>
-      <c r="J203" t="s">
+      <c r="L203" s="1" t="s">
         <v>894</v>
-      </c>
-      <c r="L203" s="1" t="s">
-        <v>895</v>
       </c>
       <c r="R203" t="s">
         <v>30</v>
@@ -12967,10 +12967,10 @@
         <v>405</v>
       </c>
       <c r="B204" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D204" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E204" t="s">
         <v>79</v>
@@ -12979,22 +12979,22 @@
         <v>408</v>
       </c>
       <c r="J204" t="s">
+        <v>896</v>
+      </c>
+      <c r="L204" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="L204" s="1" t="s">
+      <c r="R204" t="s">
+        <v>30</v>
+      </c>
+      <c r="S204" t="s">
+        <v>31</v>
+      </c>
+      <c r="T204" t="s">
         <v>898</v>
       </c>
-      <c r="R204" t="s">
-        <v>30</v>
-      </c>
-      <c r="S204" t="s">
-        <v>31</v>
-      </c>
-      <c r="T204" t="s">
+      <c r="U204" t="s">
         <v>899</v>
-      </c>
-      <c r="U204" t="s">
-        <v>900</v>
       </c>
       <c r="W204">
         <v>2</v>
@@ -13005,25 +13005,25 @@
         <v>405</v>
       </c>
       <c r="B205" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D205" t="s">
+        <v>900</v>
+      </c>
+      <c r="E205" t="s">
         <v>901</v>
-      </c>
-      <c r="E205" t="s">
-        <v>902</v>
       </c>
       <c r="F205" t="s">
         <v>340</v>
       </c>
       <c r="J205" t="s">
+        <v>902</v>
+      </c>
+      <c r="L205" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="L205" s="1" t="s">
+      <c r="M205" t="s">
         <v>904</v>
-      </c>
-      <c r="M205" t="s">
-        <v>905</v>
       </c>
       <c r="R205" t="s">
         <v>30</v>
@@ -13035,7 +13035,7 @@
         <v>396</v>
       </c>
       <c r="U205" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="W205">
         <v>2</v>
@@ -13046,7 +13046,7 @@
         <v>405</v>
       </c>
       <c r="B206" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D206" t="s">
         <v>466</v>
@@ -13058,10 +13058,10 @@
         <v>408</v>
       </c>
       <c r="J206" t="s">
+        <v>905</v>
+      </c>
+      <c r="L206" s="1" t="s">
         <v>906</v>
-      </c>
-      <c r="L206" s="1" t="s">
-        <v>907</v>
       </c>
       <c r="R206" t="s">
         <v>30</v>
@@ -13084,25 +13084,25 @@
         <v>405</v>
       </c>
       <c r="B207" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D207" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="E207" t="s">
+        <v>907</v>
+      </c>
+      <c r="F207" t="s">
+        <v>1587</v>
+      </c>
+      <c r="J207" t="s">
         <v>908</v>
       </c>
-      <c r="F207" t="s">
-        <v>1589</v>
-      </c>
-      <c r="J207" t="s">
+      <c r="L207" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="L207" s="1" t="s">
-        <v>910</v>
-      </c>
       <c r="M207" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="R207" t="s">
         <v>30</v>
@@ -13125,10 +13125,10 @@
         <v>405</v>
       </c>
       <c r="B208" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D208" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E208" t="s">
         <v>176</v>
@@ -13137,10 +13137,10 @@
         <v>467</v>
       </c>
       <c r="J208" t="s">
+        <v>911</v>
+      </c>
+      <c r="L208" s="1" t="s">
         <v>912</v>
-      </c>
-      <c r="L208" s="1" t="s">
-        <v>913</v>
       </c>
       <c r="R208" t="s">
         <v>30</v>
@@ -13163,22 +13163,22 @@
         <v>405</v>
       </c>
       <c r="B209" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D209" t="s">
+        <v>913</v>
+      </c>
+      <c r="E209" t="s">
         <v>914</v>
       </c>
-      <c r="E209" t="s">
+      <c r="F209" t="s">
         <v>915</v>
       </c>
-      <c r="F209" t="s">
+      <c r="J209" t="s">
         <v>916</v>
       </c>
-      <c r="J209" t="s">
+      <c r="L209" s="1" t="s">
         <v>917</v>
-      </c>
-      <c r="L209" s="1" t="s">
-        <v>918</v>
       </c>
       <c r="R209" t="s">
         <v>30</v>
@@ -13198,13 +13198,13 @@
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>918</v>
+      </c>
+      <c r="B210" t="s">
         <v>919</v>
       </c>
-      <c r="B210" t="s">
+      <c r="D210" t="s">
         <v>920</v>
-      </c>
-      <c r="D210" t="s">
-        <v>921</v>
       </c>
       <c r="E210" t="s">
         <v>79</v>
@@ -13213,10 +13213,10 @@
         <v>80</v>
       </c>
       <c r="J210" t="s">
+        <v>921</v>
+      </c>
+      <c r="L210" s="1" t="s">
         <v>922</v>
-      </c>
-      <c r="L210" s="1" t="s">
-        <v>923</v>
       </c>
       <c r="R210" t="s">
         <v>30</v>
@@ -13228,7 +13228,7 @@
         <v>473</v>
       </c>
       <c r="U210" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="W210">
         <v>3</v>
@@ -13236,25 +13236,25 @@
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>918</v>
+      </c>
+      <c r="B211" t="s">
         <v>919</v>
-      </c>
-      <c r="B211" t="s">
-        <v>920</v>
       </c>
       <c r="D211" t="s">
         <v>424</v>
       </c>
       <c r="E211" t="s">
+        <v>838</v>
+      </c>
+      <c r="F211" t="s">
         <v>839</v>
       </c>
-      <c r="F211" t="s">
-        <v>840</v>
-      </c>
       <c r="J211" t="s">
+        <v>924</v>
+      </c>
+      <c r="L211" s="1" t="s">
         <v>925</v>
-      </c>
-      <c r="L211" s="1" t="s">
-        <v>926</v>
       </c>
       <c r="R211" t="s">
         <v>30</v>
@@ -13274,25 +13274,25 @@
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>918</v>
+      </c>
+      <c r="B212" t="s">
         <v>919</v>
-      </c>
-      <c r="B212" t="s">
-        <v>920</v>
       </c>
       <c r="D212">
         <v>1872</v>
       </c>
       <c r="E212" t="s">
+        <v>926</v>
+      </c>
+      <c r="F212" t="s">
         <v>927</v>
       </c>
-      <c r="F212" t="s">
+      <c r="J212" t="s">
         <v>928</v>
       </c>
-      <c r="J212" t="s">
+      <c r="L212" s="1" t="s">
         <v>929</v>
-      </c>
-      <c r="L212" s="1" t="s">
-        <v>930</v>
       </c>
       <c r="R212" t="s">
         <v>30</v>
@@ -13312,26 +13312,26 @@
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>918</v>
+      </c>
+      <c r="B213" t="s">
         <v>919</v>
-      </c>
-      <c r="B213" t="s">
-        <v>920</v>
       </c>
       <c r="D213">
         <v>1879</v>
       </c>
       <c r="E213" t="s">
+        <v>930</v>
+      </c>
+      <c r="F213" t="s">
         <v>931</v>
       </c>
-      <c r="F213" t="s">
+      <c r="J213" t="s">
         <v>932</v>
       </c>
-      <c r="J213" t="s">
+      <c r="L213" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="L213" s="1" t="s">
-        <v>934</v>
-      </c>
       <c r="R213" t="s">
         <v>30</v>
       </c>
@@ -13339,7 +13339,7 @@
         <v>31</v>
       </c>
       <c r="T213" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="U213" t="s">
         <v>440</v>
@@ -13350,25 +13350,25 @@
     </row>
     <row r="214" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>934</v>
+      </c>
+      <c r="B214" t="s">
         <v>935</v>
       </c>
-      <c r="B214" t="s">
+      <c r="D214" t="s">
+        <v>739</v>
+      </c>
+      <c r="E214" t="s">
         <v>936</v>
       </c>
-      <c r="D214" t="s">
-        <v>740</v>
-      </c>
-      <c r="E214" t="s">
+      <c r="F214" t="s">
         <v>937</v>
       </c>
-      <c r="F214" t="s">
+      <c r="J214" t="s">
         <v>938</v>
       </c>
-      <c r="J214" t="s">
+      <c r="L214" s="1" t="s">
         <v>939</v>
-      </c>
-      <c r="L214" s="1" t="s">
-        <v>940</v>
       </c>
       <c r="R214" t="s">
         <v>30</v>
@@ -13388,25 +13388,25 @@
     </row>
     <row r="215" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>934</v>
+      </c>
+      <c r="B215" t="s">
         <v>935</v>
       </c>
-      <c r="B215" t="s">
+      <c r="D215" t="s">
+        <v>940</v>
+      </c>
+      <c r="E215" t="s">
         <v>936</v>
       </c>
-      <c r="D215" t="s">
+      <c r="F215" t="s">
+        <v>937</v>
+      </c>
+      <c r="J215" t="s">
         <v>941</v>
       </c>
-      <c r="E215" t="s">
-        <v>937</v>
-      </c>
-      <c r="F215" t="s">
-        <v>938</v>
-      </c>
-      <c r="J215" t="s">
+      <c r="L215" s="1" t="s">
         <v>942</v>
-      </c>
-      <c r="L215" s="1" t="s">
-        <v>943</v>
       </c>
       <c r="R215" t="s">
         <v>30</v>
@@ -13426,37 +13426,37 @@
     </row>
     <row r="216" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>934</v>
+      </c>
+      <c r="B216" t="s">
         <v>935</v>
-      </c>
-      <c r="B216" t="s">
-        <v>936</v>
       </c>
       <c r="D216">
         <v>1823</v>
       </c>
       <c r="E216" t="s">
+        <v>943</v>
+      </c>
+      <c r="F216" t="s">
         <v>944</v>
       </c>
-      <c r="F216" t="s">
+      <c r="J216" t="s">
         <v>945</v>
       </c>
-      <c r="J216" t="s">
+      <c r="L216" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="L216" s="1" t="s">
+      <c r="R216" t="s">
+        <v>30</v>
+      </c>
+      <c r="S216" t="s">
+        <v>31</v>
+      </c>
+      <c r="T216" t="s">
         <v>947</v>
       </c>
-      <c r="R216" t="s">
-        <v>30</v>
-      </c>
-      <c r="S216" t="s">
-        <v>31</v>
-      </c>
-      <c r="T216" t="s">
+      <c r="U216" t="s">
         <v>948</v>
-      </c>
-      <c r="U216" t="s">
-        <v>949</v>
       </c>
       <c r="W216">
         <v>3</v>
@@ -13464,10 +13464,10 @@
     </row>
     <row r="217" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>934</v>
+      </c>
+      <c r="B217" t="s">
         <v>935</v>
-      </c>
-      <c r="B217" t="s">
-        <v>936</v>
       </c>
       <c r="D217">
         <v>1867</v>
@@ -13476,13 +13476,13 @@
         <v>45</v>
       </c>
       <c r="F217" t="s">
+        <v>949</v>
+      </c>
+      <c r="J217" t="s">
         <v>950</v>
       </c>
-      <c r="J217" t="s">
+      <c r="L217" s="1" t="s">
         <v>951</v>
-      </c>
-      <c r="L217" s="1" t="s">
-        <v>952</v>
       </c>
       <c r="R217" t="s">
         <v>30</v>
@@ -13494,7 +13494,7 @@
         <v>163</v>
       </c>
       <c r="U217" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="W217">
         <v>3</v>
@@ -13502,25 +13502,25 @@
     </row>
     <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>953</v>
+      </c>
+      <c r="B218" t="s">
         <v>954</v>
       </c>
-      <c r="B218" t="s">
+      <c r="D218" t="s">
         <v>955</v>
-      </c>
-      <c r="D218" t="s">
-        <v>956</v>
       </c>
       <c r="E218" t="s">
         <v>79</v>
       </c>
       <c r="F218" t="s">
+        <v>956</v>
+      </c>
+      <c r="J218" t="s">
         <v>957</v>
       </c>
-      <c r="J218" t="s">
+      <c r="L218" s="1" t="s">
         <v>958</v>
-      </c>
-      <c r="L218" s="1" t="s">
-        <v>959</v>
       </c>
       <c r="R218" t="s">
         <v>30</v>
@@ -13532,7 +13532,7 @@
         <v>115</v>
       </c>
       <c r="U218" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="W218">
         <v>3</v>
@@ -13540,10 +13540,10 @@
     </row>
     <row r="219" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>953</v>
+      </c>
+      <c r="B219" t="s">
         <v>954</v>
-      </c>
-      <c r="B219" t="s">
-        <v>955</v>
       </c>
       <c r="D219" t="s">
         <v>377</v>
@@ -13555,19 +13555,19 @@
         <v>80</v>
       </c>
       <c r="J219" t="s">
+        <v>960</v>
+      </c>
+      <c r="L219" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="L219" s="1" t="s">
+      <c r="R219" t="s">
+        <v>30</v>
+      </c>
+      <c r="S219" t="s">
+        <v>31</v>
+      </c>
+      <c r="T219" t="s">
         <v>962</v>
-      </c>
-      <c r="R219" t="s">
-        <v>30</v>
-      </c>
-      <c r="S219" t="s">
-        <v>31</v>
-      </c>
-      <c r="T219" t="s">
-        <v>963</v>
       </c>
       <c r="U219" t="s">
         <v>139</v>
@@ -13578,10 +13578,10 @@
     </row>
     <row r="220" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>953</v>
+      </c>
+      <c r="B220" t="s">
         <v>954</v>
-      </c>
-      <c r="B220" t="s">
-        <v>955</v>
       </c>
       <c r="D220">
         <v>1883</v>
@@ -13593,11 +13593,11 @@
         <v>80</v>
       </c>
       <c r="J220" t="s">
+        <v>963</v>
+      </c>
+      <c r="L220" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="L220" s="1" t="s">
-        <v>965</v>
-      </c>
       <c r="R220" t="s">
         <v>30</v>
       </c>
@@ -13605,7 +13605,7 @@
         <v>31</v>
       </c>
       <c r="T220" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="U220" t="s">
         <v>658</v>
@@ -13616,10 +13616,10 @@
     </row>
     <row r="221" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>953</v>
+      </c>
+      <c r="B221" t="s">
         <v>954</v>
-      </c>
-      <c r="B221" t="s">
-        <v>955</v>
       </c>
       <c r="D221">
         <v>1888</v>
@@ -13628,13 +13628,13 @@
         <v>79</v>
       </c>
       <c r="F221" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="J221" t="s">
+        <v>965</v>
+      </c>
+      <c r="L221" s="1" t="s">
         <v>966</v>
-      </c>
-      <c r="L221" s="1" t="s">
-        <v>967</v>
       </c>
       <c r="R221" t="s">
         <v>30</v>
@@ -13654,25 +13654,25 @@
     </row>
     <row r="222" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>967</v>
+      </c>
+      <c r="B222" t="s">
         <v>968</v>
       </c>
-      <c r="B222" t="s">
+      <c r="D222" t="s">
         <v>969</v>
       </c>
-      <c r="D222" t="s">
+      <c r="E222" t="s">
         <v>970</v>
       </c>
-      <c r="E222" t="s">
+      <c r="F222" t="s">
         <v>971</v>
       </c>
-      <c r="F222" t="s">
+      <c r="J222" t="s">
         <v>972</v>
       </c>
-      <c r="J222" t="s">
+      <c r="L222" s="1" t="s">
         <v>973</v>
-      </c>
-      <c r="L222" s="1" t="s">
-        <v>974</v>
       </c>
       <c r="R222" t="s">
         <v>30</v>
@@ -13684,7 +13684,7 @@
         <v>287</v>
       </c>
       <c r="U222" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="W222">
         <v>3</v>
@@ -13692,10 +13692,10 @@
     </row>
     <row r="223" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>967</v>
+      </c>
+      <c r="B223" t="s">
         <v>968</v>
-      </c>
-      <c r="B223" t="s">
-        <v>969</v>
       </c>
       <c r="D223">
         <v>1892</v>
@@ -13707,22 +13707,22 @@
         <v>563</v>
       </c>
       <c r="J223" t="s">
+        <v>975</v>
+      </c>
+      <c r="L223" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="L223" s="1" t="s">
+      <c r="R223" t="s">
+        <v>30</v>
+      </c>
+      <c r="S223" t="s">
         <v>977</v>
-      </c>
-      <c r="R223" t="s">
-        <v>30</v>
-      </c>
-      <c r="S223" t="s">
-        <v>978</v>
       </c>
       <c r="T223" t="s">
         <v>210</v>
       </c>
       <c r="U223" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="W223">
         <v>3</v>
@@ -13730,37 +13730,37 @@
     </row>
     <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>967</v>
+      </c>
+      <c r="B224" t="s">
         <v>968</v>
-      </c>
-      <c r="B224" t="s">
-        <v>969</v>
       </c>
       <c r="D224" t="s">
         <v>397</v>
       </c>
       <c r="E224" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F224" t="s">
         <v>206</v>
       </c>
       <c r="J224" t="s">
+        <v>979</v>
+      </c>
+      <c r="L224" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="L224" s="1" t="s">
-        <v>981</v>
-      </c>
       <c r="R224" t="s">
         <v>30</v>
       </c>
       <c r="S224" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="T224" t="s">
         <v>404</v>
       </c>
       <c r="U224" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="W224">
         <v>3</v>
@@ -13768,10 +13768,10 @@
     </row>
     <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>967</v>
+      </c>
+      <c r="B225" t="s">
         <v>968</v>
-      </c>
-      <c r="B225" t="s">
-        <v>969</v>
       </c>
       <c r="D225">
         <v>1892</v>
@@ -13783,19 +13783,19 @@
         <v>206</v>
       </c>
       <c r="J225" t="s">
+        <v>982</v>
+      </c>
+      <c r="L225" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="L225" s="1" t="s">
+      <c r="R225" t="s">
+        <v>30</v>
+      </c>
+      <c r="S225" t="s">
+        <v>31</v>
+      </c>
+      <c r="T225" t="s">
         <v>984</v>
-      </c>
-      <c r="R225" t="s">
-        <v>30</v>
-      </c>
-      <c r="S225" t="s">
-        <v>31</v>
-      </c>
-      <c r="T225" t="s">
-        <v>985</v>
       </c>
       <c r="U225" t="s">
         <v>109</v>
@@ -13806,26 +13806,26 @@
     </row>
     <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>985</v>
+      </c>
+      <c r="B226" t="s">
         <v>986</v>
-      </c>
-      <c r="B226" t="s">
-        <v>987</v>
       </c>
       <c r="D226" t="s">
         <v>192</v>
       </c>
       <c r="E226" t="s">
+        <v>987</v>
+      </c>
+      <c r="F226" t="s">
         <v>988</v>
       </c>
-      <c r="F226" t="s">
+      <c r="J226" t="s">
         <v>989</v>
       </c>
-      <c r="J226" t="s">
+      <c r="L226" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="L226" s="1" t="s">
-        <v>991</v>
-      </c>
       <c r="R226" t="s">
         <v>30</v>
       </c>
@@ -13833,7 +13833,7 @@
         <v>31</v>
       </c>
       <c r="T226" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="U226" t="s">
         <v>154</v>
@@ -13844,13 +13844,13 @@
     </row>
     <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>985</v>
+      </c>
+      <c r="B227" t="s">
         <v>986</v>
       </c>
-      <c r="B227" t="s">
-        <v>987</v>
-      </c>
       <c r="D227" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E227" t="s">
         <v>144</v>
@@ -13859,10 +13859,10 @@
         <v>145</v>
       </c>
       <c r="J227" t="s">
+        <v>992</v>
+      </c>
+      <c r="L227" s="1" t="s">
         <v>993</v>
-      </c>
-      <c r="L227" s="1" t="s">
-        <v>994</v>
       </c>
       <c r="R227" t="s">
         <v>30</v>
@@ -13882,10 +13882,10 @@
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
+        <v>985</v>
+      </c>
+      <c r="B228" t="s">
         <v>986</v>
-      </c>
-      <c r="B228" t="s">
-        <v>987</v>
       </c>
       <c r="D228" t="s">
         <v>689</v>
@@ -13897,10 +13897,10 @@
         <v>112</v>
       </c>
       <c r="J228" t="s">
+        <v>994</v>
+      </c>
+      <c r="L228" s="1" t="s">
         <v>995</v>
-      </c>
-      <c r="L228" s="1" t="s">
-        <v>996</v>
       </c>
       <c r="R228" t="s">
         <v>30</v>
@@ -13920,10 +13920,10 @@
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>985</v>
+      </c>
+      <c r="B229" t="s">
         <v>986</v>
-      </c>
-      <c r="B229" t="s">
-        <v>987</v>
       </c>
       <c r="D229">
         <v>1893</v>
@@ -13932,13 +13932,13 @@
         <v>71</v>
       </c>
       <c r="F229" t="s">
+        <v>996</v>
+      </c>
+      <c r="J229" t="s">
         <v>997</v>
       </c>
-      <c r="J229" t="s">
+      <c r="L229" s="1" t="s">
         <v>998</v>
-      </c>
-      <c r="L229" s="1" t="s">
-        <v>999</v>
       </c>
       <c r="R229" t="s">
         <v>30</v>
@@ -13958,25 +13958,25 @@
     </row>
     <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>999</v>
+      </c>
+      <c r="B230" t="s">
         <v>1000</v>
       </c>
-      <c r="B230" t="s">
+      <c r="D230" t="s">
         <v>1001</v>
-      </c>
-      <c r="D230" t="s">
-        <v>1002</v>
       </c>
       <c r="E230" t="s">
         <v>79</v>
       </c>
       <c r="F230" t="s">
+        <v>1002</v>
+      </c>
+      <c r="J230" t="s">
         <v>1003</v>
       </c>
-      <c r="J230" t="s">
+      <c r="L230" s="1" t="s">
         <v>1004</v>
-      </c>
-      <c r="L230" s="1" t="s">
-        <v>1005</v>
       </c>
       <c r="R230" t="s">
         <v>30</v>
@@ -13996,10 +13996,10 @@
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>999</v>
+      </c>
+      <c r="B231" t="s">
         <v>1000</v>
-      </c>
-      <c r="B231" t="s">
-        <v>1001</v>
       </c>
       <c r="D231" t="s">
         <v>622</v>
@@ -14011,10 +14011,10 @@
         <v>408</v>
       </c>
       <c r="J231" t="s">
+        <v>1005</v>
+      </c>
+      <c r="L231" s="1" t="s">
         <v>1006</v>
-      </c>
-      <c r="L231" s="1" t="s">
-        <v>1007</v>
       </c>
       <c r="R231" t="s">
         <v>30</v>
@@ -14034,13 +14034,13 @@
     </row>
     <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>999</v>
+      </c>
+      <c r="B232" t="s">
         <v>1000</v>
       </c>
-      <c r="B232" t="s">
-        <v>1001</v>
-      </c>
       <c r="D232" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E232" t="s">
         <v>79</v>
@@ -14049,10 +14049,10 @@
         <v>408</v>
       </c>
       <c r="J232" t="s">
+        <v>1008</v>
+      </c>
+      <c r="L232" s="1" t="s">
         <v>1009</v>
-      </c>
-      <c r="L232" s="1" t="s">
-        <v>1010</v>
       </c>
       <c r="R232" t="s">
         <v>30</v>
@@ -14072,25 +14072,25 @@
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>999</v>
+      </c>
+      <c r="B233" t="s">
         <v>1000</v>
       </c>
-      <c r="B233" t="s">
-        <v>1001</v>
-      </c>
       <c r="D233" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E233" t="s">
         <v>144</v>
       </c>
       <c r="F233" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J233" t="s">
         <v>1012</v>
       </c>
-      <c r="J233" t="s">
+      <c r="L233" s="1" t="s">
         <v>1013</v>
-      </c>
-      <c r="L233" s="1" t="s">
-        <v>1014</v>
       </c>
       <c r="R233" t="s">
         <v>30</v>
@@ -14110,10 +14110,10 @@
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
+        <v>999</v>
+      </c>
+      <c r="B234" t="s">
         <v>1000</v>
-      </c>
-      <c r="B234" t="s">
-        <v>1001</v>
       </c>
       <c r="D234">
         <v>1862</v>
@@ -14125,16 +14125,16 @@
         <v>408</v>
       </c>
       <c r="J234" t="s">
+        <v>1014</v>
+      </c>
+      <c r="L234" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="L234" s="1" t="s">
+      <c r="R234" t="s">
+        <v>30</v>
+      </c>
+      <c r="S234" t="s">
         <v>1016</v>
-      </c>
-      <c r="R234" t="s">
-        <v>30</v>
-      </c>
-      <c r="S234" t="s">
-        <v>1017</v>
       </c>
       <c r="T234" t="s">
         <v>50</v>
@@ -14148,10 +14148,10 @@
     </row>
     <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
+        <v>999</v>
+      </c>
+      <c r="B235" t="s">
         <v>1000</v>
-      </c>
-      <c r="B235" t="s">
-        <v>1001</v>
       </c>
       <c r="D235">
         <v>1856</v>
@@ -14163,16 +14163,16 @@
         <v>80</v>
       </c>
       <c r="J235" t="s">
+        <v>1017</v>
+      </c>
+      <c r="L235" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="L235" s="1" t="s">
+      <c r="R235" t="s">
+        <v>30</v>
+      </c>
+      <c r="S235" t="s">
         <v>1019</v>
-      </c>
-      <c r="R235" t="s">
-        <v>30</v>
-      </c>
-      <c r="S235" t="s">
-        <v>1020</v>
       </c>
       <c r="T235" t="s">
         <v>126</v>
@@ -14186,10 +14186,10 @@
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
+        <v>999</v>
+      </c>
+      <c r="B236" t="s">
         <v>1000</v>
-      </c>
-      <c r="B236" t="s">
-        <v>1001</v>
       </c>
       <c r="D236">
         <v>1808</v>
@@ -14201,19 +14201,19 @@
         <v>408</v>
       </c>
       <c r="J236" t="s">
+        <v>1020</v>
+      </c>
+      <c r="L236" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="L236" s="1" t="s">
+      <c r="R236" t="s">
+        <v>30</v>
+      </c>
+      <c r="S236" t="s">
+        <v>1019</v>
+      </c>
+      <c r="T236" t="s">
         <v>1022</v>
-      </c>
-      <c r="R236" t="s">
-        <v>30</v>
-      </c>
-      <c r="S236" t="s">
-        <v>1020</v>
-      </c>
-      <c r="T236" t="s">
-        <v>1023</v>
       </c>
       <c r="U236" t="s">
         <v>109</v>
@@ -14224,34 +14224,34 @@
     </row>
     <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
+        <v>999</v>
+      </c>
+      <c r="B237" t="s">
         <v>1000</v>
-      </c>
-      <c r="B237" t="s">
-        <v>1001</v>
       </c>
       <c r="D237">
         <v>1824</v>
       </c>
       <c r="E237" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F237" t="s">
         <v>1024</v>
       </c>
-      <c r="F237" t="s">
+      <c r="J237" t="s">
         <v>1025</v>
       </c>
-      <c r="J237" t="s">
+      <c r="L237" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="L237" s="1" t="s">
+      <c r="R237" t="s">
+        <v>30</v>
+      </c>
+      <c r="S237" t="s">
         <v>1027</v>
       </c>
-      <c r="R237" t="s">
-        <v>30</v>
-      </c>
-      <c r="S237" t="s">
+      <c r="T237" t="s">
         <v>1028</v>
-      </c>
-      <c r="T237" t="s">
-        <v>1029</v>
       </c>
       <c r="U237" t="s">
         <v>608</v>
@@ -14262,10 +14262,10 @@
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
+        <v>999</v>
+      </c>
+      <c r="B238" t="s">
         <v>1000</v>
-      </c>
-      <c r="B238" t="s">
-        <v>1001</v>
       </c>
       <c r="D238">
         <v>1827</v>
@@ -14277,22 +14277,22 @@
         <v>408</v>
       </c>
       <c r="J238" t="s">
+        <v>1029</v>
+      </c>
+      <c r="L238" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="L238" s="1" t="s">
+      <c r="R238" t="s">
+        <v>30</v>
+      </c>
+      <c r="S238" t="s">
+        <v>1019</v>
+      </c>
+      <c r="T238" t="s">
         <v>1031</v>
       </c>
-      <c r="R238" t="s">
-        <v>30</v>
-      </c>
-      <c r="S238" t="s">
-        <v>1020</v>
-      </c>
-      <c r="T238" t="s">
+      <c r="U238" t="s">
         <v>1032</v>
-      </c>
-      <c r="U238" t="s">
-        <v>1033</v>
       </c>
       <c r="W238">
         <v>1</v>
@@ -14300,34 +14300,34 @@
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
+        <v>999</v>
+      </c>
+      <c r="B239" t="s">
         <v>1000</v>
-      </c>
-      <c r="B239" t="s">
-        <v>1001</v>
       </c>
       <c r="D239">
         <v>1811</v>
       </c>
       <c r="E239" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F239" t="s">
         <v>1034</v>
       </c>
-      <c r="F239" t="s">
+      <c r="J239" t="s">
         <v>1035</v>
       </c>
-      <c r="J239" t="s">
+      <c r="L239" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="L239" s="1" t="s">
+      <c r="R239" t="s">
+        <v>30</v>
+      </c>
+      <c r="S239" t="s">
+        <v>1019</v>
+      </c>
+      <c r="T239" t="s">
         <v>1037</v>
-      </c>
-      <c r="R239" t="s">
-        <v>30</v>
-      </c>
-      <c r="S239" t="s">
-        <v>1020</v>
-      </c>
-      <c r="T239" t="s">
-        <v>1038</v>
       </c>
       <c r="U239" t="s">
         <v>230</v>
@@ -14338,10 +14338,10 @@
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>999</v>
+      </c>
+      <c r="B240" t="s">
         <v>1000</v>
-      </c>
-      <c r="B240" t="s">
-        <v>1001</v>
       </c>
       <c r="D240">
         <v>1806</v>
@@ -14353,16 +14353,16 @@
         <v>408</v>
       </c>
       <c r="J240" t="s">
+        <v>1038</v>
+      </c>
+      <c r="L240" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="L240" s="1" t="s">
-        <v>1040</v>
-      </c>
       <c r="R240" t="s">
         <v>30</v>
       </c>
       <c r="S240" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="T240" t="s">
         <v>116</v>
@@ -14376,10 +14376,10 @@
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>999</v>
+      </c>
+      <c r="B241" t="s">
         <v>1000</v>
-      </c>
-      <c r="B241" t="s">
-        <v>1001</v>
       </c>
       <c r="D241">
         <v>1808</v>
@@ -14391,19 +14391,19 @@
         <v>408</v>
       </c>
       <c r="J241" t="s">
+        <v>1040</v>
+      </c>
+      <c r="L241" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="L241" s="1" t="s">
-        <v>1042</v>
-      </c>
       <c r="R241" t="s">
         <v>30</v>
       </c>
       <c r="S241" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="T241" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="U241" t="s">
         <v>631</v>
@@ -14414,10 +14414,10 @@
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B242" t="s">
         <v>1043</v>
-      </c>
-      <c r="B242" t="s">
-        <v>1044</v>
       </c>
       <c r="D242" t="s">
         <v>524</v>
@@ -14429,10 +14429,10 @@
         <v>145</v>
       </c>
       <c r="J242" t="s">
+        <v>1044</v>
+      </c>
+      <c r="L242" s="1" t="s">
         <v>1045</v>
-      </c>
-      <c r="L242" s="1" t="s">
-        <v>1046</v>
       </c>
       <c r="R242" t="s">
         <v>30</v>
@@ -14452,10 +14452,10 @@
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B243" t="s">
         <v>1043</v>
-      </c>
-      <c r="B243" t="s">
-        <v>1044</v>
       </c>
       <c r="D243">
         <v>1864</v>
@@ -14467,10 +14467,10 @@
         <v>80</v>
       </c>
       <c r="J243" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L243" s="1" t="s">
         <v>1047</v>
-      </c>
-      <c r="L243" s="1" t="s">
-        <v>1048</v>
       </c>
       <c r="R243" t="s">
         <v>30</v>
@@ -14482,7 +14482,7 @@
         <v>134</v>
       </c>
       <c r="U243" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="W243">
         <v>3</v>
@@ -14490,37 +14490,37 @@
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B244" t="s">
         <v>1043</v>
-      </c>
-      <c r="B244" t="s">
-        <v>1044</v>
       </c>
       <c r="D244">
         <v>1871</v>
       </c>
       <c r="E244" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F244" t="s">
         <v>1049</v>
       </c>
-      <c r="F244" t="s">
+      <c r="J244" t="s">
         <v>1050</v>
       </c>
-      <c r="J244" t="s">
+      <c r="L244" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="L244" s="1" t="s">
+      <c r="R244" t="s">
+        <v>30</v>
+      </c>
+      <c r="S244" t="s">
+        <v>31</v>
+      </c>
+      <c r="T244" t="s">
         <v>1052</v>
       </c>
-      <c r="R244" t="s">
-        <v>30</v>
-      </c>
-      <c r="S244" t="s">
-        <v>31</v>
-      </c>
-      <c r="T244" t="s">
-        <v>1053</v>
-      </c>
       <c r="U244" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="W244">
         <v>3</v>
@@ -14528,10 +14528,10 @@
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B245" t="s">
         <v>1043</v>
-      </c>
-      <c r="B245" t="s">
-        <v>1044</v>
       </c>
       <c r="D245">
         <v>1865</v>
@@ -14540,13 +14540,13 @@
         <v>611</v>
       </c>
       <c r="F245" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="J245" t="s">
+        <v>1053</v>
+      </c>
+      <c r="L245" s="1" t="s">
         <v>1054</v>
-      </c>
-      <c r="L245" s="1" t="s">
-        <v>1055</v>
       </c>
       <c r="R245" t="s">
         <v>30</v>
@@ -14566,13 +14566,13 @@
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B246" t="s">
         <v>1056</v>
       </c>
-      <c r="B246" t="s">
+      <c r="D246" t="s">
         <v>1057</v>
-      </c>
-      <c r="D246" t="s">
-        <v>1058</v>
       </c>
       <c r="E246" t="s">
         <v>176</v>
@@ -14581,11 +14581,11 @@
         <v>467</v>
       </c>
       <c r="J246" t="s">
+        <v>1058</v>
+      </c>
+      <c r="L246" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="L246" s="1" t="s">
-        <v>1060</v>
-      </c>
       <c r="R246" t="s">
         <v>30</v>
       </c>
@@ -14593,10 +14593,10 @@
         <v>31</v>
       </c>
       <c r="T246" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="U246" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="W246">
         <v>1</v>
@@ -14604,10 +14604,10 @@
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B247" t="s">
         <v>1056</v>
-      </c>
-      <c r="B247" t="s">
-        <v>1057</v>
       </c>
       <c r="D247" t="s">
         <v>143</v>
@@ -14619,10 +14619,10 @@
         <v>80</v>
       </c>
       <c r="J247" t="s">
+        <v>1060</v>
+      </c>
+      <c r="L247" s="1" t="s">
         <v>1061</v>
-      </c>
-      <c r="L247" s="1" t="s">
-        <v>1062</v>
       </c>
       <c r="R247" t="s">
         <v>30</v>
@@ -14642,10 +14642,10 @@
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B248" t="s">
         <v>1056</v>
-      </c>
-      <c r="B248" t="s">
-        <v>1057</v>
       </c>
       <c r="D248" t="s">
         <v>143</v>
@@ -14657,10 +14657,10 @@
         <v>80</v>
       </c>
       <c r="J248" t="s">
+        <v>1062</v>
+      </c>
+      <c r="L248" s="1" t="s">
         <v>1063</v>
-      </c>
-      <c r="L248" s="1" t="s">
-        <v>1064</v>
       </c>
       <c r="R248" t="s">
         <v>30</v>
@@ -14672,7 +14672,7 @@
         <v>40</v>
       </c>
       <c r="U248" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="W248">
         <v>1</v>
@@ -14680,10 +14680,10 @@
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B249" t="s">
         <v>1056</v>
-      </c>
-      <c r="B249" t="s">
-        <v>1057</v>
       </c>
       <c r="D249" t="s">
         <v>150</v>
@@ -14695,10 +14695,10 @@
         <v>80</v>
       </c>
       <c r="J249" t="s">
+        <v>1065</v>
+      </c>
+      <c r="L249" s="1" t="s">
         <v>1066</v>
-      </c>
-      <c r="L249" s="1" t="s">
-        <v>1067</v>
       </c>
       <c r="R249" t="s">
         <v>30</v>
@@ -14718,13 +14718,13 @@
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B250" t="s">
         <v>1056</v>
       </c>
-      <c r="B250" t="s">
-        <v>1057</v>
-      </c>
       <c r="D250" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E250" t="s">
         <v>79</v>
@@ -14733,19 +14733,19 @@
         <v>80</v>
       </c>
       <c r="J250" t="s">
+        <v>1068</v>
+      </c>
+      <c r="L250" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="L250" s="1" t="s">
+      <c r="R250" t="s">
+        <v>30</v>
+      </c>
+      <c r="S250" t="s">
+        <v>31</v>
+      </c>
+      <c r="T250" t="s">
         <v>1070</v>
-      </c>
-      <c r="R250" t="s">
-        <v>30</v>
-      </c>
-      <c r="S250" t="s">
-        <v>31</v>
-      </c>
-      <c r="T250" t="s">
-        <v>1071</v>
       </c>
       <c r="U250" t="s">
         <v>329</v>
@@ -14756,10 +14756,10 @@
     </row>
     <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B251" t="s">
         <v>1056</v>
-      </c>
-      <c r="B251" t="s">
-        <v>1057</v>
       </c>
       <c r="D251" t="s">
         <v>695</v>
@@ -14771,10 +14771,10 @@
         <v>563</v>
       </c>
       <c r="J251" t="s">
+        <v>1071</v>
+      </c>
+      <c r="L251" s="1" t="s">
         <v>1072</v>
-      </c>
-      <c r="L251" s="1" t="s">
-        <v>1073</v>
       </c>
       <c r="R251" t="s">
         <v>30</v>
@@ -14794,25 +14794,25 @@
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B252" t="s">
         <v>1056</v>
-      </c>
-      <c r="B252" t="s">
-        <v>1057</v>
       </c>
       <c r="D252" t="s">
         <v>695</v>
       </c>
       <c r="E252" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F252" t="s">
         <v>340</v>
       </c>
       <c r="J252" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L252" s="1" t="s">
         <v>1075</v>
-      </c>
-      <c r="L252" s="1" t="s">
-        <v>1076</v>
       </c>
       <c r="R252" t="s">
         <v>30</v>
@@ -14824,7 +14824,7 @@
         <v>39</v>
       </c>
       <c r="U252" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="W252">
         <v>1</v>
@@ -14832,37 +14832,37 @@
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B253" t="s">
         <v>1056</v>
-      </c>
-      <c r="B253" t="s">
-        <v>1057</v>
       </c>
       <c r="D253" t="s">
         <v>330</v>
       </c>
       <c r="E253" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F253" t="s">
+        <v>1077</v>
+      </c>
+      <c r="J253" t="s">
         <v>1078</v>
       </c>
-      <c r="J253" t="s">
+      <c r="L253" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="L253" s="1" t="s">
+      <c r="R253" t="s">
+        <v>30</v>
+      </c>
+      <c r="S253" t="s">
+        <v>31</v>
+      </c>
+      <c r="T253" t="s">
         <v>1080</v>
       </c>
-      <c r="R253" t="s">
-        <v>30</v>
-      </c>
-      <c r="S253" t="s">
-        <v>31</v>
-      </c>
-      <c r="T253" t="s">
-        <v>1081</v>
-      </c>
       <c r="U253" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="W253">
         <v>1</v>
@@ -14870,10 +14870,10 @@
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B254" t="s">
         <v>1056</v>
-      </c>
-      <c r="B254" t="s">
-        <v>1057</v>
       </c>
       <c r="D254">
         <v>1879</v>
@@ -14885,11 +14885,11 @@
         <v>194</v>
       </c>
       <c r="J254" t="s">
+        <v>1081</v>
+      </c>
+      <c r="L254" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="L254" s="1" t="s">
-        <v>1083</v>
-      </c>
       <c r="R254" t="s">
         <v>30</v>
       </c>
@@ -14897,7 +14897,7 @@
         <v>31</v>
       </c>
       <c r="T254" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="U254" t="s">
         <v>210</v>
@@ -14908,10 +14908,10 @@
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B255" t="s">
         <v>1056</v>
-      </c>
-      <c r="B255" t="s">
-        <v>1057</v>
       </c>
       <c r="D255">
         <v>1882</v>
@@ -14923,19 +14923,19 @@
         <v>381</v>
       </c>
       <c r="J255" t="s">
+        <v>1083</v>
+      </c>
+      <c r="L255" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="L255" s="1" t="s">
+      <c r="R255" t="s">
+        <v>30</v>
+      </c>
+      <c r="S255" t="s">
+        <v>31</v>
+      </c>
+      <c r="T255" t="s">
         <v>1085</v>
-      </c>
-      <c r="R255" t="s">
-        <v>30</v>
-      </c>
-      <c r="S255" t="s">
-        <v>31</v>
-      </c>
-      <c r="T255" t="s">
-        <v>1086</v>
       </c>
       <c r="U255" t="s">
         <v>314</v>
@@ -14946,10 +14946,10 @@
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B256" t="s">
         <v>1056</v>
-      </c>
-      <c r="B256" t="s">
-        <v>1057</v>
       </c>
       <c r="D256">
         <v>1872</v>
@@ -14961,11 +14961,11 @@
         <v>80</v>
       </c>
       <c r="J256" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L256" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="L256" s="1" t="s">
-        <v>1088</v>
-      </c>
       <c r="R256" t="s">
         <v>30</v>
       </c>
@@ -14973,7 +14973,7 @@
         <v>31</v>
       </c>
       <c r="T256" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="U256" t="s">
         <v>173</v>
@@ -14984,10 +14984,10 @@
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B257" t="s">
         <v>1056</v>
-      </c>
-      <c r="B257" t="s">
-        <v>1057</v>
       </c>
       <c r="D257">
         <v>1868</v>
@@ -14999,10 +14999,10 @@
         <v>80</v>
       </c>
       <c r="J257" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L257" s="1" t="s">
         <v>1089</v>
-      </c>
-      <c r="L257" s="1" t="s">
-        <v>1090</v>
       </c>
       <c r="R257" t="s">
         <v>30</v>
@@ -15022,10 +15022,10 @@
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B258" t="s">
         <v>1091</v>
-      </c>
-      <c r="B258" t="s">
-        <v>1092</v>
       </c>
       <c r="D258" t="s">
         <v>524</v>
@@ -15037,10 +15037,10 @@
         <v>177</v>
       </c>
       <c r="J258" t="s">
+        <v>1092</v>
+      </c>
+      <c r="L258" s="1" t="s">
         <v>1093</v>
-      </c>
-      <c r="L258" s="1" t="s">
-        <v>1094</v>
       </c>
       <c r="R258" t="s">
         <v>30</v>
@@ -15052,7 +15052,7 @@
         <v>638</v>
       </c>
       <c r="U258" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="W258">
         <v>3</v>
@@ -15060,13 +15060,13 @@
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B259" t="s">
         <v>1091</v>
       </c>
-      <c r="B259" t="s">
-        <v>1092</v>
-      </c>
       <c r="D259" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="E259" t="s">
         <v>176</v>
@@ -15075,11 +15075,11 @@
         <v>177</v>
       </c>
       <c r="J259" t="s">
+        <v>1096</v>
+      </c>
+      <c r="L259" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="L259" s="1" t="s">
-        <v>1098</v>
-      </c>
       <c r="R259" t="s">
         <v>30</v>
       </c>
@@ -15087,7 +15087,7 @@
         <v>31</v>
       </c>
       <c r="T259" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="U259" t="s">
         <v>477</v>
@@ -15098,26 +15098,26 @@
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B260" t="s">
         <v>1091</v>
-      </c>
-      <c r="B260" t="s">
-        <v>1092</v>
       </c>
       <c r="D260">
         <v>1856</v>
       </c>
       <c r="E260" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F260" t="s">
         <v>1099</v>
       </c>
-      <c r="F260" t="s">
+      <c r="J260" t="s">
         <v>1100</v>
       </c>
-      <c r="J260" t="s">
+      <c r="L260" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="L260" s="1" t="s">
-        <v>1102</v>
-      </c>
       <c r="R260" t="s">
         <v>30</v>
       </c>
@@ -15125,7 +15125,7 @@
         <v>31</v>
       </c>
       <c r="T260" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="U260" t="s">
         <v>680</v>
@@ -15136,10 +15136,10 @@
     </row>
     <row r="261" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B261" t="s">
         <v>1091</v>
-      </c>
-      <c r="B261" t="s">
-        <v>1092</v>
       </c>
       <c r="D261">
         <v>1886</v>
@@ -15148,13 +15148,13 @@
         <v>288</v>
       </c>
       <c r="F261" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J261" t="s">
         <v>1103</v>
       </c>
-      <c r="J261" t="s">
+      <c r="L261" s="1" t="s">
         <v>1104</v>
-      </c>
-      <c r="L261" s="1" t="s">
-        <v>1105</v>
       </c>
       <c r="R261" t="s">
         <v>30</v>
@@ -15166,7 +15166,7 @@
         <v>104</v>
       </c>
       <c r="U261" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="W261">
         <v>3</v>
@@ -15174,10 +15174,10 @@
     </row>
     <row r="262" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B262" t="s">
         <v>1106</v>
-      </c>
-      <c r="B262" t="s">
-        <v>1107</v>
       </c>
       <c r="D262">
         <v>1850</v>
@@ -15189,10 +15189,10 @@
         <v>675</v>
       </c>
       <c r="J262" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="L262" s="6" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="R262" t="s">
         <v>30</v>
@@ -15204,7 +15204,7 @@
         <v>320</v>
       </c>
       <c r="U262" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="W262">
         <v>2</v>
@@ -15212,13 +15212,13 @@
     </row>
     <row r="263" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B263" t="s">
         <v>1106</v>
       </c>
-      <c r="B263" t="s">
-        <v>1107</v>
-      </c>
       <c r="D263" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="E263" t="s">
         <v>79</v>
@@ -15227,11 +15227,11 @@
         <v>80</v>
       </c>
       <c r="J263" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L263" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="L263" s="1" t="s">
-        <v>1111</v>
-      </c>
       <c r="R263" t="s">
         <v>30</v>
       </c>
@@ -15239,7 +15239,7 @@
         <v>31</v>
       </c>
       <c r="T263" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="U263" t="s">
         <v>203</v>
@@ -15250,13 +15250,13 @@
     </row>
     <row r="264" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B264" t="s">
         <v>1106</v>
       </c>
-      <c r="B264" t="s">
-        <v>1107</v>
-      </c>
       <c r="D264" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="E264" t="s">
         <v>79</v>
@@ -15265,11 +15265,11 @@
         <v>80</v>
       </c>
       <c r="J264" t="s">
+        <v>1112</v>
+      </c>
+      <c r="L264" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="L264" s="1" t="s">
-        <v>1114</v>
-      </c>
       <c r="R264" t="s">
         <v>30</v>
       </c>
@@ -15277,7 +15277,7 @@
         <v>31</v>
       </c>
       <c r="T264" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="U264" t="s">
         <v>355</v>
@@ -15288,10 +15288,10 @@
     </row>
     <row r="265" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B265" t="s">
         <v>1106</v>
-      </c>
-      <c r="B265" t="s">
-        <v>1107</v>
       </c>
       <c r="D265">
         <v>1863</v>
@@ -15303,10 +15303,10 @@
         <v>80</v>
       </c>
       <c r="J265" t="s">
+        <v>1114</v>
+      </c>
+      <c r="L265" s="1" t="s">
         <v>1115</v>
-      </c>
-      <c r="L265" s="1" t="s">
-        <v>1116</v>
       </c>
       <c r="R265" t="s">
         <v>30</v>
@@ -15318,7 +15318,7 @@
         <v>324</v>
       </c>
       <c r="U265" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="W265">
         <v>2</v>
@@ -15326,13 +15326,13 @@
     </row>
     <row r="266" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B266" t="s">
         <v>1106</v>
       </c>
-      <c r="B266" t="s">
-        <v>1107</v>
-      </c>
       <c r="D266" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E266" t="s">
         <v>79</v>
@@ -15344,7 +15344,7 @@
         <v>64</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="R266" t="s">
         <v>30</v>
@@ -15364,10 +15364,10 @@
     </row>
     <row r="267" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B267" t="s">
         <v>1106</v>
-      </c>
-      <c r="B267" t="s">
-        <v>1107</v>
       </c>
       <c r="D267">
         <v>1848</v>
@@ -15379,10 +15379,10 @@
         <v>80</v>
       </c>
       <c r="J267" t="s">
+        <v>1118</v>
+      </c>
+      <c r="L267" s="1" t="s">
         <v>1119</v>
-      </c>
-      <c r="L267" s="1" t="s">
-        <v>1120</v>
       </c>
       <c r="R267" t="s">
         <v>30</v>
@@ -15402,13 +15402,13 @@
     </row>
     <row r="268" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B268" t="s">
         <v>1106</v>
       </c>
-      <c r="B268" t="s">
-        <v>1107</v>
-      </c>
       <c r="D268" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E268" t="s">
         <v>79</v>
@@ -15417,10 +15417,10 @@
         <v>80</v>
       </c>
       <c r="J268" t="s">
+        <v>1121</v>
+      </c>
+      <c r="L268" s="1" t="s">
         <v>1122</v>
-      </c>
-      <c r="L268" s="1" t="s">
-        <v>1123</v>
       </c>
       <c r="R268" t="s">
         <v>30</v>
@@ -15440,10 +15440,10 @@
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B269" t="s">
         <v>1106</v>
-      </c>
-      <c r="B269" t="s">
-        <v>1107</v>
       </c>
       <c r="D269">
         <v>1872</v>
@@ -15455,10 +15455,10 @@
         <v>80</v>
       </c>
       <c r="J269" t="s">
+        <v>1123</v>
+      </c>
+      <c r="L269" s="1" t="s">
         <v>1124</v>
-      </c>
-      <c r="L269" s="1" t="s">
-        <v>1125</v>
       </c>
       <c r="R269" t="s">
         <v>30</v>
@@ -15478,10 +15478,10 @@
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B270" t="s">
         <v>1126</v>
-      </c>
-      <c r="B270" t="s">
-        <v>1127</v>
       </c>
       <c r="D270" t="s">
         <v>429</v>
@@ -15493,10 +15493,10 @@
         <v>145</v>
       </c>
       <c r="J270" t="s">
+        <v>1127</v>
+      </c>
+      <c r="L270" s="1" t="s">
         <v>1128</v>
-      </c>
-      <c r="L270" s="1" t="s">
-        <v>1129</v>
       </c>
       <c r="R270" t="s">
         <v>30</v>
@@ -15516,10 +15516,10 @@
     </row>
     <row r="271" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B271" t="s">
         <v>1126</v>
-      </c>
-      <c r="B271" t="s">
-        <v>1127</v>
       </c>
       <c r="D271" t="s">
         <v>429</v>
@@ -15531,10 +15531,10 @@
         <v>393</v>
       </c>
       <c r="J271" t="s">
+        <v>1129</v>
+      </c>
+      <c r="L271" s="1" t="s">
         <v>1130</v>
-      </c>
-      <c r="L271" s="1" t="s">
-        <v>1131</v>
       </c>
       <c r="R271" t="s">
         <v>30</v>
@@ -15546,7 +15546,7 @@
         <v>346</v>
       </c>
       <c r="U271" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="W271">
         <v>1</v>
@@ -15554,10 +15554,10 @@
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B272" t="s">
         <v>1126</v>
-      </c>
-      <c r="B272" t="s">
-        <v>1127</v>
       </c>
       <c r="D272" t="s">
         <v>192</v>
@@ -15569,10 +15569,10 @@
         <v>80</v>
       </c>
       <c r="J272" t="s">
+        <v>1131</v>
+      </c>
+      <c r="L272" s="1" t="s">
         <v>1132</v>
-      </c>
-      <c r="L272" s="1" t="s">
-        <v>1133</v>
       </c>
       <c r="R272" t="s">
         <v>30</v>
@@ -15592,10 +15592,10 @@
     </row>
     <row r="273" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B273" t="s">
         <v>1126</v>
-      </c>
-      <c r="B273" t="s">
-        <v>1127</v>
       </c>
       <c r="D273" t="s">
         <v>192</v>
@@ -15604,13 +15604,13 @@
         <v>79</v>
       </c>
       <c r="F273" t="s">
+        <v>1133</v>
+      </c>
+      <c r="J273" t="s">
         <v>1134</v>
       </c>
-      <c r="J273" t="s">
+      <c r="L273" s="1" t="s">
         <v>1135</v>
-      </c>
-      <c r="L273" s="1" t="s">
-        <v>1136</v>
       </c>
       <c r="R273" t="s">
         <v>30</v>
@@ -15622,7 +15622,7 @@
         <v>391</v>
       </c>
       <c r="U273" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="W273">
         <v>1</v>
@@ -15630,10 +15630,10 @@
     </row>
     <row r="274" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B274" t="s">
         <v>1126</v>
-      </c>
-      <c r="B274" t="s">
-        <v>1127</v>
       </c>
       <c r="D274" t="s">
         <v>365</v>
@@ -15645,10 +15645,10 @@
         <v>80</v>
       </c>
       <c r="J274" t="s">
+        <v>1136</v>
+      </c>
+      <c r="L274" s="1" t="s">
         <v>1137</v>
-      </c>
-      <c r="L274" s="1" t="s">
-        <v>1138</v>
       </c>
       <c r="R274" t="s">
         <v>30</v>
@@ -15668,10 +15668,10 @@
     </row>
     <row r="275" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B275" t="s">
         <v>1126</v>
-      </c>
-      <c r="B275" t="s">
-        <v>1127</v>
       </c>
       <c r="D275" t="s">
         <v>349</v>
@@ -15683,10 +15683,10 @@
         <v>80</v>
       </c>
       <c r="J275" t="s">
+        <v>1138</v>
+      </c>
+      <c r="L275" s="1" t="s">
         <v>1139</v>
-      </c>
-      <c r="L275" s="1" t="s">
-        <v>1140</v>
       </c>
       <c r="R275" t="s">
         <v>30</v>
@@ -15706,13 +15706,13 @@
     </row>
     <row r="276" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B276" t="s">
         <v>1126</v>
       </c>
-      <c r="B276" t="s">
-        <v>1127</v>
-      </c>
       <c r="D276" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E276" t="s">
         <v>79</v>
@@ -15721,10 +15721,10 @@
         <v>80</v>
       </c>
       <c r="J276" t="s">
+        <v>1140</v>
+      </c>
+      <c r="L276" s="1" t="s">
         <v>1141</v>
-      </c>
-      <c r="L276" s="1" t="s">
-        <v>1142</v>
       </c>
       <c r="R276" t="s">
         <v>30</v>
@@ -15744,13 +15744,13 @@
     </row>
     <row r="277" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B277" t="s">
         <v>1126</v>
       </c>
-      <c r="B277" t="s">
-        <v>1127</v>
-      </c>
       <c r="D277" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E277" t="s">
         <v>26</v>
@@ -15759,10 +15759,10 @@
         <v>393</v>
       </c>
       <c r="J277" t="s">
+        <v>1142</v>
+      </c>
+      <c r="L277" s="1" t="s">
         <v>1143</v>
-      </c>
-      <c r="L277" s="1" t="s">
-        <v>1144</v>
       </c>
       <c r="R277" t="s">
         <v>30</v>
@@ -15782,10 +15782,10 @@
     </row>
     <row r="278" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B278" t="s">
         <v>1126</v>
-      </c>
-      <c r="B278" t="s">
-        <v>1127</v>
       </c>
       <c r="D278" t="s">
         <v>238</v>
@@ -15797,10 +15797,10 @@
         <v>80</v>
       </c>
       <c r="J278" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L278" s="1" t="s">
         <v>1145</v>
-      </c>
-      <c r="L278" s="1" t="s">
-        <v>1146</v>
       </c>
       <c r="R278" t="s">
         <v>30</v>
@@ -15820,10 +15820,10 @@
     </row>
     <row r="279" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B279" t="s">
         <v>1126</v>
-      </c>
-      <c r="B279" t="s">
-        <v>1127</v>
       </c>
       <c r="D279" t="s">
         <v>634</v>
@@ -15832,13 +15832,13 @@
         <v>35</v>
       </c>
       <c r="F279" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J279" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L279" s="1" t="s">
         <v>1147</v>
-      </c>
-      <c r="L279" s="1" t="s">
-        <v>1148</v>
       </c>
       <c r="R279" t="s">
         <v>30</v>
@@ -15858,13 +15858,13 @@
     </row>
     <row r="280" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B280" t="s">
         <v>1126</v>
       </c>
-      <c r="B280" t="s">
-        <v>1127</v>
-      </c>
       <c r="D280" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E280" t="s">
         <v>79</v>
@@ -15873,10 +15873,10 @@
         <v>80</v>
       </c>
       <c r="J280" t="s">
+        <v>1148</v>
+      </c>
+      <c r="L280" s="1" t="s">
         <v>1149</v>
-      </c>
-      <c r="L280" s="1" t="s">
-        <v>1150</v>
       </c>
       <c r="R280" t="s">
         <v>30</v>
@@ -15896,13 +15896,13 @@
     </row>
     <row r="281" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B281" t="s">
         <v>1126</v>
       </c>
-      <c r="B281" t="s">
-        <v>1127</v>
-      </c>
       <c r="D281" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E281" t="s">
         <v>79</v>
@@ -15911,10 +15911,10 @@
         <v>80</v>
       </c>
       <c r="J281" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L281" s="1" t="s">
         <v>1151</v>
-      </c>
-      <c r="L281" s="1" t="s">
-        <v>1152</v>
       </c>
       <c r="R281" t="s">
         <v>30</v>
@@ -15937,10 +15937,10 @@
         <v>315</v>
       </c>
       <c r="B282" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D282" t="s">
         <v>1153</v>
-      </c>
-      <c r="D282" t="s">
-        <v>1154</v>
       </c>
       <c r="E282" t="s">
         <v>79</v>
@@ -15949,10 +15949,10 @@
         <v>80</v>
       </c>
       <c r="J282" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L282" s="1" t="s">
         <v>1155</v>
-      </c>
-      <c r="L282" s="1" t="s">
-        <v>1156</v>
       </c>
       <c r="R282" t="s">
         <v>30</v>
@@ -15961,7 +15961,7 @@
         <v>202</v>
       </c>
       <c r="T282" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="U282" t="s">
         <v>116</v>
@@ -15975,7 +15975,7 @@
         <v>315</v>
       </c>
       <c r="B283" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D283" t="s">
         <v>321</v>
@@ -15987,10 +15987,10 @@
         <v>80</v>
       </c>
       <c r="J283" t="s">
+        <v>1156</v>
+      </c>
+      <c r="L283" s="1" t="s">
         <v>1157</v>
-      </c>
-      <c r="L283" s="1" t="s">
-        <v>1158</v>
       </c>
       <c r="R283" s="2" t="s">
         <v>171</v>
@@ -15999,7 +15999,7 @@
         <v>171</v>
       </c>
       <c r="T283" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="U283" t="s">
         <v>396</v>
@@ -16013,7 +16013,7 @@
         <v>315</v>
       </c>
       <c r="B284" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D284">
         <v>1864</v>
@@ -16025,10 +16025,10 @@
         <v>145</v>
       </c>
       <c r="J284" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L284" s="1" t="s">
         <v>1160</v>
-      </c>
-      <c r="L284" s="1" t="s">
-        <v>1161</v>
       </c>
       <c r="R284" t="s">
         <v>30</v>
@@ -16051,22 +16051,22 @@
         <v>315</v>
       </c>
       <c r="B285" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D285" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E285" t="s">
         <v>79</v>
       </c>
       <c r="F285" t="s">
+        <v>1162</v>
+      </c>
+      <c r="J285" t="s">
         <v>1163</v>
       </c>
-      <c r="J285" t="s">
+      <c r="L285" s="1" t="s">
         <v>1164</v>
-      </c>
-      <c r="L285" s="1" t="s">
-        <v>1165</v>
       </c>
       <c r="R285" t="s">
         <v>30</v>
@@ -16078,7 +16078,7 @@
         <v>70</v>
       </c>
       <c r="U285" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="W285">
         <v>3</v>
@@ -16086,10 +16086,10 @@
     </row>
     <row r="286" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B286" t="s">
         <v>1166</v>
-      </c>
-      <c r="B286" t="s">
-        <v>1167</v>
       </c>
       <c r="D286" t="s">
         <v>192</v>
@@ -16101,11 +16101,11 @@
         <v>80</v>
       </c>
       <c r="J286" t="s">
+        <v>1167</v>
+      </c>
+      <c r="L286" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="L286" s="1" t="s">
-        <v>1169</v>
-      </c>
       <c r="R286" t="s">
         <v>30</v>
       </c>
@@ -16113,7 +16113,7 @@
         <v>31</v>
       </c>
       <c r="T286" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="U286" t="s">
         <v>374</v>
@@ -16124,10 +16124,10 @@
     </row>
     <row r="287" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B287" t="s">
         <v>1166</v>
-      </c>
-      <c r="B287" t="s">
-        <v>1167</v>
       </c>
       <c r="D287" t="s">
         <v>695</v>
@@ -16139,10 +16139,10 @@
         <v>80</v>
       </c>
       <c r="J287" t="s">
+        <v>1169</v>
+      </c>
+      <c r="L287" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="L287" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="R287" t="s">
         <v>30</v>
@@ -16154,7 +16154,7 @@
         <v>374</v>
       </c>
       <c r="U287" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="W287">
         <v>2</v>
@@ -16162,10 +16162,10 @@
     </row>
     <row r="288" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B288" t="s">
         <v>1166</v>
-      </c>
-      <c r="B288" t="s">
-        <v>1167</v>
       </c>
       <c r="D288" t="s">
         <v>317</v>
@@ -16174,22 +16174,22 @@
         <v>79</v>
       </c>
       <c r="F288" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="J288" t="s">
+        <v>1171</v>
+      </c>
+      <c r="L288" s="1" t="s">
         <v>1172</v>
       </c>
-      <c r="L288" s="1" t="s">
+      <c r="R288" t="s">
+        <v>30</v>
+      </c>
+      <c r="S288" t="s">
+        <v>31</v>
+      </c>
+      <c r="T288" t="s">
         <v>1173</v>
-      </c>
-      <c r="R288" t="s">
-        <v>30</v>
-      </c>
-      <c r="S288" t="s">
-        <v>31</v>
-      </c>
-      <c r="T288" t="s">
-        <v>1174</v>
       </c>
       <c r="U288" t="s">
         <v>374</v>
@@ -16200,13 +16200,13 @@
     </row>
     <row r="289" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B289" t="s">
         <v>1166</v>
       </c>
-      <c r="B289" t="s">
-        <v>1167</v>
-      </c>
       <c r="D289" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E289" t="s">
         <v>100</v>
@@ -16215,10 +16215,10 @@
         <v>101</v>
       </c>
       <c r="J289" t="s">
+        <v>1175</v>
+      </c>
+      <c r="L289" s="1" t="s">
         <v>1176</v>
-      </c>
-      <c r="L289" s="1" t="s">
-        <v>1177</v>
       </c>
       <c r="R289" t="s">
         <v>30</v>
@@ -16238,10 +16238,10 @@
     </row>
     <row r="290" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B290" t="s">
         <v>1166</v>
-      </c>
-      <c r="B290" t="s">
-        <v>1167</v>
       </c>
       <c r="D290" t="s">
         <v>260</v>
@@ -16253,10 +16253,10 @@
         <v>467</v>
       </c>
       <c r="J290" t="s">
+        <v>1177</v>
+      </c>
+      <c r="L290" s="1" t="s">
         <v>1178</v>
-      </c>
-      <c r="L290" s="1" t="s">
-        <v>1179</v>
       </c>
       <c r="R290" t="s">
         <v>30</v>
@@ -16276,10 +16276,10 @@
     </row>
     <row r="291" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B291" t="s">
         <v>1166</v>
-      </c>
-      <c r="B291" t="s">
-        <v>1167</v>
       </c>
       <c r="D291">
         <v>1879</v>
@@ -16291,10 +16291,10 @@
         <v>80</v>
       </c>
       <c r="J291" t="s">
+        <v>1179</v>
+      </c>
+      <c r="L291" s="1" t="s">
         <v>1180</v>
-      </c>
-      <c r="L291" s="1" t="s">
-        <v>1181</v>
       </c>
       <c r="R291" t="s">
         <v>30</v>
@@ -16314,10 +16314,10 @@
     </row>
     <row r="292" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B292" t="s">
         <v>1166</v>
-      </c>
-      <c r="B292" t="s">
-        <v>1167</v>
       </c>
       <c r="D292">
         <v>1881</v>
@@ -16329,10 +16329,10 @@
         <v>56</v>
       </c>
       <c r="J292" t="s">
+        <v>1181</v>
+      </c>
+      <c r="L292" s="1" t="s">
         <v>1182</v>
-      </c>
-      <c r="L292" s="1" t="s">
-        <v>1183</v>
       </c>
       <c r="R292" t="s">
         <v>30</v>
@@ -16352,10 +16352,10 @@
     </row>
     <row r="293" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B293" t="s">
         <v>1166</v>
-      </c>
-      <c r="B293" t="s">
-        <v>1167</v>
       </c>
       <c r="D293">
         <v>1891</v>
@@ -16364,14 +16364,14 @@
         <v>79</v>
       </c>
       <c r="F293" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="J293" t="s">
+        <v>1183</v>
+      </c>
+      <c r="L293" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="L293" s="1" t="s">
-        <v>1185</v>
-      </c>
       <c r="R293" t="s">
         <v>30</v>
       </c>
@@ -16379,10 +16379,10 @@
         <v>31</v>
       </c>
       <c r="T293" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="U293" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="W293">
         <v>2</v>
@@ -16390,10 +16390,10 @@
     </row>
     <row r="294" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B294" t="s">
         <v>1186</v>
-      </c>
-      <c r="B294" t="s">
-        <v>1187</v>
       </c>
       <c r="D294" t="s">
         <v>61</v>
@@ -16405,16 +16405,16 @@
         <v>56</v>
       </c>
       <c r="J294" t="s">
+        <v>1187</v>
+      </c>
+      <c r="L294" s="1" t="s">
         <v>1188</v>
-      </c>
-      <c r="L294" s="1" t="s">
-        <v>1189</v>
       </c>
       <c r="R294" s="2" t="s">
         <v>171</v>
       </c>
       <c r="S294" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="T294" t="s">
         <v>441</v>
@@ -16428,34 +16428,34 @@
     </row>
     <row r="295" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B295" t="s">
         <v>1186</v>
-      </c>
-      <c r="B295" t="s">
-        <v>1187</v>
       </c>
       <c r="D295">
         <v>1899</v>
       </c>
       <c r="E295" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F295" t="s">
         <v>1191</v>
-      </c>
-      <c r="F295" t="s">
-        <v>1192</v>
       </c>
       <c r="J295" t="s">
         <v>102</v>
       </c>
       <c r="L295" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="R295" t="s">
+        <v>30</v>
+      </c>
+      <c r="S295" t="s">
         <v>1193</v>
       </c>
-      <c r="R295" t="s">
-        <v>30</v>
-      </c>
-      <c r="S295" t="s">
+      <c r="T295" t="s">
         <v>1194</v>
-      </c>
-      <c r="T295" t="s">
-        <v>1195</v>
       </c>
       <c r="U295" t="s">
         <v>181</v>
@@ -16466,10 +16466,10 @@
     </row>
     <row r="296" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B296" t="s">
         <v>1186</v>
-      </c>
-      <c r="B296" t="s">
-        <v>1187</v>
       </c>
       <c r="D296">
         <v>1896</v>
@@ -16478,25 +16478,25 @@
         <v>55</v>
       </c>
       <c r="F296" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G296" t="s">
         <v>1196</v>
       </c>
-      <c r="G296" t="s">
+      <c r="J296" t="s">
         <v>1197</v>
       </c>
-      <c r="J296" t="s">
+      <c r="L296" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="L296" s="1" t="s">
+      <c r="R296" t="s">
+        <v>30</v>
+      </c>
+      <c r="S296" t="s">
+        <v>1193</v>
+      </c>
+      <c r="T296" t="s">
         <v>1199</v>
-      </c>
-      <c r="R296" t="s">
-        <v>30</v>
-      </c>
-      <c r="S296" t="s">
-        <v>1194</v>
-      </c>
-      <c r="T296" t="s">
-        <v>1200</v>
       </c>
       <c r="U296" t="s">
         <v>519</v>
@@ -16507,10 +16507,10 @@
     </row>
     <row r="297" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B297" t="s">
         <v>1186</v>
-      </c>
-      <c r="B297" t="s">
-        <v>1187</v>
       </c>
       <c r="D297">
         <v>1896</v>
@@ -16525,16 +16525,16 @@
         <v>64</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="R297" t="s">
         <v>30</v>
       </c>
       <c r="S297" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="T297" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="U297" t="s">
         <v>519</v>
@@ -16545,31 +16545,31 @@
     </row>
     <row r="298" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B298" t="s">
         <v>1202</v>
-      </c>
-      <c r="B298" t="s">
-        <v>1203</v>
       </c>
       <c r="D298" t="s">
         <v>352</v>
       </c>
       <c r="E298" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F298" t="s">
         <v>1204</v>
       </c>
-      <c r="F298" t="s">
+      <c r="J298" t="s">
         <v>1205</v>
       </c>
-      <c r="J298" t="s">
+      <c r="L298" s="6" t="s">
+        <v>1592</v>
+      </c>
+      <c r="R298" t="s">
+        <v>30</v>
+      </c>
+      <c r="S298" t="s">
         <v>1206</v>
-      </c>
-      <c r="L298" s="6" t="s">
-        <v>1594</v>
-      </c>
-      <c r="R298" t="s">
-        <v>30</v>
-      </c>
-      <c r="S298" t="s">
-        <v>1207</v>
       </c>
       <c r="T298" t="s">
         <v>154</v>
@@ -16583,25 +16583,25 @@
     </row>
     <row r="299" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B299" t="s">
         <v>1202</v>
-      </c>
-      <c r="B299" t="s">
-        <v>1203</v>
       </c>
       <c r="D299" t="s">
         <v>61</v>
       </c>
       <c r="E299" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="F299" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J299" t="s">
         <v>1208</v>
       </c>
-      <c r="J299" t="s">
+      <c r="L299" s="1" t="s">
         <v>1209</v>
-      </c>
-      <c r="L299" s="1" t="s">
-        <v>1210</v>
       </c>
       <c r="R299" t="s">
         <v>30</v>
@@ -16621,25 +16621,25 @@
     </row>
     <row r="300" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B300" t="s">
         <v>1202</v>
-      </c>
-      <c r="B300" t="s">
-        <v>1203</v>
       </c>
       <c r="D300">
         <v>1894</v>
       </c>
       <c r="E300" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F300" t="s">
         <v>1204</v>
       </c>
-      <c r="F300" t="s">
-        <v>1205</v>
-      </c>
       <c r="J300" t="s">
+        <v>1210</v>
+      </c>
+      <c r="L300" s="1" t="s">
         <v>1211</v>
-      </c>
-      <c r="L300" s="1" t="s">
-        <v>1212</v>
       </c>
       <c r="R300" t="s">
         <v>30</v>
@@ -16659,37 +16659,37 @@
     </row>
     <row r="301" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B301" t="s">
         <v>1202</v>
       </c>
-      <c r="B301" t="s">
+      <c r="D301" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E301" t="s">
         <v>1203</v>
       </c>
-      <c r="D301" t="s">
+      <c r="F301" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J301" t="s">
         <v>1213</v>
       </c>
-      <c r="E301" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F301" t="s">
-        <v>1205</v>
-      </c>
-      <c r="J301" t="s">
+      <c r="L301" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="L301" s="1" t="s">
+      <c r="R301" t="s">
+        <v>30</v>
+      </c>
+      <c r="S301" t="s">
+        <v>31</v>
+      </c>
+      <c r="T301" t="s">
         <v>1215</v>
       </c>
-      <c r="R301" t="s">
-        <v>30</v>
-      </c>
-      <c r="S301" t="s">
-        <v>31</v>
-      </c>
-      <c r="T301" t="s">
+      <c r="U301" t="s">
         <v>1216</v>
-      </c>
-      <c r="U301" t="s">
-        <v>1217</v>
       </c>
       <c r="W301">
         <v>1</v>
@@ -16697,10 +16697,10 @@
     </row>
     <row r="302" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B302" t="s">
         <v>1218</v>
-      </c>
-      <c r="B302" t="s">
-        <v>1219</v>
       </c>
       <c r="D302">
         <v>1867</v>
@@ -16712,22 +16712,22 @@
         <v>145</v>
       </c>
       <c r="J302" t="s">
+        <v>1219</v>
+      </c>
+      <c r="L302" s="1" t="s">
         <v>1220</v>
       </c>
-      <c r="L302" s="1" t="s">
+      <c r="R302" t="s">
+        <v>30</v>
+      </c>
+      <c r="S302" t="s">
+        <v>31</v>
+      </c>
+      <c r="T302" t="s">
         <v>1221</v>
       </c>
-      <c r="R302" t="s">
-        <v>30</v>
-      </c>
-      <c r="S302" t="s">
-        <v>31</v>
-      </c>
-      <c r="T302" t="s">
-        <v>1222</v>
-      </c>
       <c r="U302" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="W302">
         <v>2</v>
@@ -16735,10 +16735,10 @@
     </row>
     <row r="303" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B303" t="s">
         <v>1218</v>
-      </c>
-      <c r="B303" t="s">
-        <v>1219</v>
       </c>
       <c r="D303" t="s">
         <v>365</v>
@@ -16750,10 +16750,10 @@
         <v>80</v>
       </c>
       <c r="J303" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L303" s="1" t="s">
         <v>1223</v>
-      </c>
-      <c r="L303" s="1" t="s">
-        <v>1224</v>
       </c>
       <c r="R303" t="s">
         <v>30</v>
@@ -16773,10 +16773,10 @@
     </row>
     <row r="304" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B304" t="s">
         <v>1218</v>
-      </c>
-      <c r="B304" t="s">
-        <v>1219</v>
       </c>
       <c r="D304" t="s">
         <v>330</v>
@@ -16788,10 +16788,10 @@
         <v>80</v>
       </c>
       <c r="J304" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L304" s="1" t="s">
         <v>1225</v>
-      </c>
-      <c r="L304" s="1" t="s">
-        <v>1226</v>
       </c>
       <c r="R304" t="s">
         <v>30</v>
@@ -16811,10 +16811,10 @@
     </row>
     <row r="305" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B305" t="s">
         <v>1218</v>
-      </c>
-      <c r="B305" t="s">
-        <v>1219</v>
       </c>
       <c r="D305">
         <v>1881</v>
@@ -16826,10 +16826,10 @@
         <v>80</v>
       </c>
       <c r="J305" t="s">
+        <v>1227</v>
+      </c>
+      <c r="L305" s="1" t="s">
         <v>1228</v>
-      </c>
-      <c r="L305" s="1" t="s">
-        <v>1229</v>
       </c>
       <c r="R305" t="s">
         <v>30</v>
@@ -16849,13 +16849,13 @@
     </row>
     <row r="306" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B306" t="s">
         <v>1218</v>
       </c>
-      <c r="B306" t="s">
-        <v>1219</v>
-      </c>
       <c r="D306" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="E306" t="s">
         <v>176</v>
@@ -16864,10 +16864,10 @@
         <v>467</v>
       </c>
       <c r="J306" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L306" s="1" t="s">
         <v>1230</v>
-      </c>
-      <c r="L306" s="1" t="s">
-        <v>1231</v>
       </c>
       <c r="R306" t="s">
         <v>30</v>
@@ -16887,25 +16887,25 @@
     </row>
     <row r="307" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B307" t="s">
         <v>1218</v>
-      </c>
-      <c r="B307" t="s">
-        <v>1219</v>
       </c>
       <c r="D307">
         <v>1898</v>
       </c>
       <c r="E307" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="F307" t="s">
         <v>340</v>
       </c>
       <c r="J307" t="s">
+        <v>1232</v>
+      </c>
+      <c r="L307" s="1" t="s">
         <v>1233</v>
-      </c>
-      <c r="L307" s="1" t="s">
-        <v>1234</v>
       </c>
       <c r="R307" t="s">
         <v>30</v>
@@ -16925,10 +16925,10 @@
     </row>
     <row r="308" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B308" t="s">
         <v>1218</v>
-      </c>
-      <c r="B308" t="s">
-        <v>1219</v>
       </c>
       <c r="D308">
         <v>1867</v>
@@ -16937,13 +16937,13 @@
         <v>144</v>
       </c>
       <c r="F308" t="s">
+        <v>1234</v>
+      </c>
+      <c r="J308" t="s">
         <v>1235</v>
       </c>
-      <c r="J308" t="s">
+      <c r="L308" s="1" t="s">
         <v>1236</v>
-      </c>
-      <c r="L308" s="1" t="s">
-        <v>1237</v>
       </c>
       <c r="R308" t="s">
         <v>30</v>
@@ -16963,25 +16963,25 @@
     </row>
     <row r="309" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B309" t="s">
         <v>1218</v>
-      </c>
-      <c r="B309" t="s">
-        <v>1219</v>
       </c>
       <c r="D309">
         <v>1896</v>
       </c>
       <c r="E309" t="s">
+        <v>1237</v>
+      </c>
+      <c r="F309" t="s">
         <v>1238</v>
       </c>
-      <c r="F309" t="s">
+      <c r="J309" t="s">
         <v>1239</v>
       </c>
-      <c r="J309" t="s">
+      <c r="L309" s="1" t="s">
         <v>1240</v>
-      </c>
-      <c r="L309" s="1" t="s">
-        <v>1241</v>
       </c>
       <c r="R309" t="s">
         <v>30</v>
@@ -17004,7 +17004,7 @@
         <v>236</v>
       </c>
       <c r="B310" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D310" t="s">
         <v>34</v>
@@ -17016,10 +17016,10 @@
         <v>80</v>
       </c>
       <c r="J310" t="s">
+        <v>1242</v>
+      </c>
+      <c r="L310" s="1" t="s">
         <v>1243</v>
-      </c>
-      <c r="L310" s="1" t="s">
-        <v>1244</v>
       </c>
       <c r="R310" t="s">
         <v>30</v>
@@ -17042,7 +17042,7 @@
         <v>236</v>
       </c>
       <c r="B311" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D311" t="s">
         <v>199</v>
@@ -17054,10 +17054,10 @@
         <v>80</v>
       </c>
       <c r="J311" t="s">
+        <v>1244</v>
+      </c>
+      <c r="L311" s="1" t="s">
         <v>1245</v>
-      </c>
-      <c r="L311" s="1" t="s">
-        <v>1246</v>
       </c>
       <c r="R311" t="s">
         <v>30</v>
@@ -17080,7 +17080,7 @@
         <v>236</v>
       </c>
       <c r="B312" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D312">
         <v>1879</v>
@@ -17092,10 +17092,10 @@
         <v>80</v>
       </c>
       <c r="J312" t="s">
+        <v>1246</v>
+      </c>
+      <c r="L312" s="1" t="s">
         <v>1247</v>
-      </c>
-      <c r="L312" s="1" t="s">
-        <v>1248</v>
       </c>
       <c r="R312" t="s">
         <v>30</v>
@@ -17118,34 +17118,34 @@
         <v>236</v>
       </c>
       <c r="B313" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D313" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="E313" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="F313" t="s">
         <v>340</v>
       </c>
       <c r="J313" t="s">
+        <v>1249</v>
+      </c>
+      <c r="L313" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="L313" s="1" t="s">
+      <c r="R313" t="s">
+        <v>30</v>
+      </c>
+      <c r="S313" t="s">
+        <v>31</v>
+      </c>
+      <c r="T313" t="s">
         <v>1251</v>
       </c>
-      <c r="R313" t="s">
-        <v>30</v>
-      </c>
-      <c r="S313" t="s">
-        <v>31</v>
-      </c>
-      <c r="T313" t="s">
+      <c r="U313" t="s">
         <v>1252</v>
-      </c>
-      <c r="U313" t="s">
-        <v>1253</v>
       </c>
       <c r="W313">
         <v>3</v>
@@ -17153,10 +17153,10 @@
     </row>
     <row r="314" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B314" t="s">
         <v>1254</v>
-      </c>
-      <c r="B314" t="s">
-        <v>1255</v>
       </c>
       <c r="D314" t="s">
         <v>34</v>
@@ -17168,10 +17168,10 @@
         <v>80</v>
       </c>
       <c r="J314" t="s">
+        <v>1255</v>
+      </c>
+      <c r="L314" s="1" t="s">
         <v>1256</v>
-      </c>
-      <c r="L314" s="1" t="s">
-        <v>1257</v>
       </c>
       <c r="R314" t="s">
         <v>30</v>
@@ -17191,13 +17191,13 @@
     </row>
     <row r="315" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B315" t="s">
         <v>1254</v>
       </c>
-      <c r="B315" t="s">
-        <v>1255</v>
-      </c>
       <c r="D315" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E315" t="s">
         <v>79</v>
@@ -17206,10 +17206,10 @@
         <v>80</v>
       </c>
       <c r="J315" t="s">
+        <v>1257</v>
+      </c>
+      <c r="L315" s="1" t="s">
         <v>1258</v>
-      </c>
-      <c r="L315" s="1" t="s">
-        <v>1259</v>
       </c>
       <c r="R315" t="s">
         <v>30</v>
@@ -17229,10 +17229,10 @@
     </row>
     <row r="316" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B316" t="s">
         <v>1254</v>
-      </c>
-      <c r="B316" t="s">
-        <v>1255</v>
       </c>
       <c r="D316">
         <v>1910</v>
@@ -17244,10 +17244,10 @@
         <v>531</v>
       </c>
       <c r="J316" t="s">
+        <v>1259</v>
+      </c>
+      <c r="L316" s="1" t="s">
         <v>1260</v>
-      </c>
-      <c r="L316" s="1" t="s">
-        <v>1261</v>
       </c>
       <c r="R316" t="s">
         <v>30</v>
@@ -17267,10 +17267,10 @@
     </row>
     <row r="317" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B317" t="s">
         <v>1254</v>
-      </c>
-      <c r="B317" t="s">
-        <v>1255</v>
       </c>
       <c r="D317">
         <v>1890</v>
@@ -17282,10 +17282,10 @@
         <v>112</v>
       </c>
       <c r="J317" t="s">
+        <v>1261</v>
+      </c>
+      <c r="L317" s="1" t="s">
         <v>1262</v>
-      </c>
-      <c r="L317" s="1" t="s">
-        <v>1263</v>
       </c>
       <c r="R317" t="s">
         <v>30</v>
@@ -17305,10 +17305,10 @@
     </row>
     <row r="318" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B318" t="s">
         <v>1264</v>
-      </c>
-      <c r="B318" t="s">
-        <v>1265</v>
       </c>
       <c r="D318" t="s">
         <v>695</v>
@@ -17320,10 +17320,10 @@
         <v>381</v>
       </c>
       <c r="J318" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L318" s="1" t="s">
         <v>1266</v>
-      </c>
-      <c r="L318" s="1" t="s">
-        <v>1267</v>
       </c>
       <c r="R318" t="s">
         <v>30</v>
@@ -17343,10 +17343,10 @@
     </row>
     <row r="319" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B319" t="s">
         <v>1264</v>
-      </c>
-      <c r="B319" t="s">
-        <v>1265</v>
       </c>
       <c r="D319" t="s">
         <v>321</v>
@@ -17358,10 +17358,10 @@
         <v>80</v>
       </c>
       <c r="J319" t="s">
+        <v>1267</v>
+      </c>
+      <c r="L319" s="1" t="s">
         <v>1268</v>
-      </c>
-      <c r="L319" s="1" t="s">
-        <v>1269</v>
       </c>
       <c r="R319" t="s">
         <v>30</v>
@@ -17373,7 +17373,7 @@
         <v>248</v>
       </c>
       <c r="U319" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="W319">
         <v>1</v>
@@ -17381,10 +17381,10 @@
     </row>
     <row r="320" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B320" t="s">
         <v>1264</v>
-      </c>
-      <c r="B320" t="s">
-        <v>1265</v>
       </c>
       <c r="D320" t="s">
         <v>321</v>
@@ -17396,10 +17396,10 @@
         <v>80</v>
       </c>
       <c r="J320" t="s">
+        <v>1270</v>
+      </c>
+      <c r="L320" s="1" t="s">
         <v>1271</v>
-      </c>
-      <c r="L320" s="1" t="s">
-        <v>1272</v>
       </c>
       <c r="R320" t="s">
         <v>30</v>
@@ -17419,10 +17419,10 @@
     </row>
     <row r="321" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B321" t="s">
         <v>1264</v>
-      </c>
-      <c r="B321" t="s">
-        <v>1265</v>
       </c>
       <c r="D321" t="s">
         <v>321</v>
@@ -17434,10 +17434,10 @@
         <v>80</v>
       </c>
       <c r="J321" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L321" s="1" t="s">
         <v>1273</v>
-      </c>
-      <c r="L321" s="1" t="s">
-        <v>1274</v>
       </c>
       <c r="R321" t="s">
         <v>30</v>
@@ -17457,10 +17457,10 @@
     </row>
     <row r="322" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B322" t="s">
         <v>1264</v>
-      </c>
-      <c r="B322" t="s">
-        <v>1265</v>
       </c>
       <c r="D322" t="s">
         <v>349</v>
@@ -17472,11 +17472,11 @@
         <v>145</v>
       </c>
       <c r="J322" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L322" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="L322" s="1" t="s">
-        <v>1276</v>
-      </c>
       <c r="R322" t="s">
         <v>30</v>
       </c>
@@ -17484,7 +17484,7 @@
         <v>31</v>
       </c>
       <c r="T322" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="U322" t="s">
         <v>303</v>
@@ -17495,13 +17495,13 @@
     </row>
     <row r="323" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B323" t="s">
         <v>1264</v>
       </c>
-      <c r="B323" t="s">
-        <v>1265</v>
-      </c>
       <c r="D323" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="E323" t="s">
         <v>111</v>
@@ -17510,10 +17510,10 @@
         <v>570</v>
       </c>
       <c r="J323" t="s">
+        <v>1277</v>
+      </c>
+      <c r="L323" s="1" t="s">
         <v>1278</v>
-      </c>
-      <c r="L323" s="1" t="s">
-        <v>1279</v>
       </c>
       <c r="R323" t="s">
         <v>30</v>
@@ -17525,7 +17525,7 @@
         <v>314</v>
       </c>
       <c r="U323" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="W323">
         <v>1</v>
@@ -17533,10 +17533,10 @@
     </row>
     <row r="324" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B324" t="s">
         <v>1264</v>
-      </c>
-      <c r="B324" t="s">
-        <v>1265</v>
       </c>
       <c r="D324" t="s">
         <v>34</v>
@@ -17548,11 +17548,11 @@
         <v>101</v>
       </c>
       <c r="J324" t="s">
+        <v>1280</v>
+      </c>
+      <c r="L324" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="L324" s="1" t="s">
-        <v>1282</v>
-      </c>
       <c r="R324" t="s">
         <v>30</v>
       </c>
@@ -17560,7 +17560,7 @@
         <v>31</v>
       </c>
       <c r="T324" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="U324" t="s">
         <v>324</v>
@@ -17571,10 +17571,10 @@
     </row>
     <row r="325" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B325" t="s">
         <v>1264</v>
-      </c>
-      <c r="B325" t="s">
-        <v>1265</v>
       </c>
       <c r="D325" t="s">
         <v>199</v>
@@ -17586,13 +17586,13 @@
         <v>80</v>
       </c>
       <c r="J325" t="s">
+        <v>1282</v>
+      </c>
+      <c r="L325" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="L325" s="1" t="s">
+      <c r="M325" t="s">
         <v>1284</v>
-      </c>
-      <c r="M325" t="s">
-        <v>1285</v>
       </c>
       <c r="R325" t="s">
         <v>30</v>
@@ -17612,10 +17612,10 @@
     </row>
     <row r="326" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B326" t="s">
         <v>1264</v>
-      </c>
-      <c r="B326" t="s">
-        <v>1265</v>
       </c>
       <c r="D326" t="s">
         <v>199</v>
@@ -17627,13 +17627,13 @@
         <v>80</v>
       </c>
       <c r="J326" t="s">
+        <v>1285</v>
+      </c>
+      <c r="L326" s="1" t="s">
         <v>1286</v>
       </c>
-      <c r="L326" s="1" t="s">
+      <c r="M326" t="s">
         <v>1287</v>
-      </c>
-      <c r="M326" t="s">
-        <v>1288</v>
       </c>
       <c r="R326" t="s">
         <v>30</v>
@@ -17653,13 +17653,13 @@
     </row>
     <row r="327" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B327" t="s">
         <v>1264</v>
       </c>
-      <c r="B327" t="s">
-        <v>1265</v>
-      </c>
       <c r="D327" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="E327" t="s">
         <v>71</v>
@@ -17671,7 +17671,7 @@
         <v>401</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="R327" t="s">
         <v>30</v>
@@ -17680,7 +17680,7 @@
         <v>31</v>
       </c>
       <c r="T327" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="U327" t="s">
         <v>415</v>
@@ -17691,10 +17691,10 @@
     </row>
     <row r="328" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B328" t="s">
         <v>1264</v>
-      </c>
-      <c r="B328" t="s">
-        <v>1265</v>
       </c>
       <c r="D328" t="s">
         <v>634</v>
@@ -17706,10 +17706,10 @@
         <v>80</v>
       </c>
       <c r="J328" t="s">
+        <v>1290</v>
+      </c>
+      <c r="L328" s="1" t="s">
         <v>1291</v>
-      </c>
-      <c r="L328" s="1" t="s">
-        <v>1292</v>
       </c>
       <c r="R328" t="s">
         <v>30</v>
@@ -17729,10 +17729,10 @@
     </row>
     <row r="329" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B329" t="s">
         <v>1264</v>
-      </c>
-      <c r="B329" t="s">
-        <v>1265</v>
       </c>
       <c r="D329">
         <v>1877</v>
@@ -17744,10 +17744,10 @@
         <v>145</v>
       </c>
       <c r="J329" t="s">
+        <v>1292</v>
+      </c>
+      <c r="L329" s="1" t="s">
         <v>1293</v>
-      </c>
-      <c r="L329" s="1" t="s">
-        <v>1294</v>
       </c>
       <c r="R329" t="s">
         <v>30</v>
@@ -17767,13 +17767,13 @@
     </row>
     <row r="330" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B330" t="s">
         <v>1295</v>
       </c>
-      <c r="B330" t="s">
+      <c r="D330" t="s">
         <v>1296</v>
-      </c>
-      <c r="D330" t="s">
-        <v>1297</v>
       </c>
       <c r="E330" t="s">
         <v>26</v>
@@ -17782,10 +17782,10 @@
         <v>27</v>
       </c>
       <c r="J330" t="s">
+        <v>1297</v>
+      </c>
+      <c r="L330" s="1" t="s">
         <v>1298</v>
-      </c>
-      <c r="L330" s="1" t="s">
-        <v>1299</v>
       </c>
       <c r="R330" t="s">
         <v>30</v>
@@ -17805,13 +17805,13 @@
     </row>
     <row r="331" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B331" t="s">
         <v>1295</v>
       </c>
-      <c r="B331" t="s">
-        <v>1296</v>
-      </c>
       <c r="D331" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="E331" t="s">
         <v>26</v>
@@ -17820,22 +17820,22 @@
         <v>27</v>
       </c>
       <c r="J331" t="s">
+        <v>1300</v>
+      </c>
+      <c r="L331" s="1" t="s">
         <v>1301</v>
       </c>
-      <c r="L331" s="1" t="s">
+      <c r="R331" t="s">
+        <v>30</v>
+      </c>
+      <c r="S331" t="s">
+        <v>31</v>
+      </c>
+      <c r="T331" t="s">
         <v>1302</v>
       </c>
-      <c r="R331" t="s">
-        <v>30</v>
-      </c>
-      <c r="S331" t="s">
-        <v>31</v>
-      </c>
-      <c r="T331" t="s">
+      <c r="U331" t="s">
         <v>1303</v>
-      </c>
-      <c r="U331" t="s">
-        <v>1304</v>
       </c>
       <c r="W331">
         <v>3</v>
@@ -17843,13 +17843,13 @@
     </row>
     <row r="332" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B332" t="s">
         <v>1295</v>
       </c>
-      <c r="B332" t="s">
-        <v>1296</v>
-      </c>
       <c r="D332" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="E332" t="s">
         <v>35</v>
@@ -17858,11 +17858,11 @@
         <v>36</v>
       </c>
       <c r="J332" t="s">
+        <v>1305</v>
+      </c>
+      <c r="L332" s="1" t="s">
         <v>1306</v>
       </c>
-      <c r="L332" s="1" t="s">
-        <v>1307</v>
-      </c>
       <c r="R332" t="s">
         <v>30</v>
       </c>
@@ -17870,7 +17870,7 @@
         <v>31</v>
       </c>
       <c r="T332" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="U332" t="s">
         <v>618</v>
@@ -17881,13 +17881,13 @@
     </row>
     <row r="333" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B333" t="s">
         <v>1295</v>
       </c>
-      <c r="B333" t="s">
-        <v>1296</v>
-      </c>
       <c r="D333" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="E333" t="s">
         <v>35</v>
@@ -17896,10 +17896,10 @@
         <v>36</v>
       </c>
       <c r="J333" t="s">
+        <v>1308</v>
+      </c>
+      <c r="L333" s="1" t="s">
         <v>1309</v>
-      </c>
-      <c r="L333" s="1" t="s">
-        <v>1310</v>
       </c>
       <c r="R333" t="s">
         <v>30</v>
@@ -17919,13 +17919,13 @@
     </row>
     <row r="334" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B334" t="s">
         <v>1311</v>
       </c>
-      <c r="B334" t="s">
+      <c r="D334" t="s">
         <v>1312</v>
-      </c>
-      <c r="D334" t="s">
-        <v>1313</v>
       </c>
       <c r="E334" t="s">
         <v>176</v>
@@ -17934,11 +17934,11 @@
         <v>177</v>
       </c>
       <c r="J334" t="s">
+        <v>1313</v>
+      </c>
+      <c r="L334" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="L334" s="1" t="s">
-        <v>1315</v>
-      </c>
       <c r="R334" t="s">
         <v>30</v>
       </c>
@@ -17946,10 +17946,10 @@
         <v>31</v>
       </c>
       <c r="T334" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="U334" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="W334">
         <v>3</v>
@@ -17957,10 +17957,10 @@
     </row>
     <row r="335" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B335" t="s">
         <v>1311</v>
-      </c>
-      <c r="B335" t="s">
-        <v>1312</v>
       </c>
       <c r="D335" t="s">
         <v>695</v>
@@ -17972,10 +17972,10 @@
         <v>177</v>
       </c>
       <c r="J335" t="s">
+        <v>1315</v>
+      </c>
+      <c r="L335" s="1" t="s">
         <v>1316</v>
-      </c>
-      <c r="L335" s="1" t="s">
-        <v>1317</v>
       </c>
       <c r="R335" t="s">
         <v>30</v>
@@ -17995,13 +17995,13 @@
     </row>
     <row r="336" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B336" t="s">
         <v>1311</v>
       </c>
-      <c r="B336" t="s">
-        <v>1312</v>
-      </c>
       <c r="D336" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="E336" t="s">
         <v>176</v>
@@ -18010,10 +18010,10 @@
         <v>177</v>
       </c>
       <c r="J336" t="s">
+        <v>1317</v>
+      </c>
+      <c r="L336" s="1" t="s">
         <v>1318</v>
-      </c>
-      <c r="L336" s="1" t="s">
-        <v>1319</v>
       </c>
       <c r="R336" t="s">
         <v>30</v>
@@ -18033,10 +18033,10 @@
     </row>
     <row r="337" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B337" t="s">
         <v>1311</v>
-      </c>
-      <c r="B337" t="s">
-        <v>1312</v>
       </c>
       <c r="D337" t="s">
         <v>524</v>
@@ -18048,10 +18048,10 @@
         <v>177</v>
       </c>
       <c r="J337" t="s">
+        <v>1319</v>
+      </c>
+      <c r="L337" s="1" t="s">
         <v>1320</v>
-      </c>
-      <c r="L337" s="1" t="s">
-        <v>1321</v>
       </c>
       <c r="R337" t="s">
         <v>30</v>
@@ -18074,10 +18074,10 @@
         <v>405</v>
       </c>
       <c r="B338" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D338" t="s">
         <v>1322</v>
-      </c>
-      <c r="D338" t="s">
-        <v>1323</v>
       </c>
       <c r="E338" t="s">
         <v>79</v>
@@ -18086,10 +18086,10 @@
         <v>408</v>
       </c>
       <c r="J338" t="s">
+        <v>1323</v>
+      </c>
+      <c r="L338" s="1" t="s">
         <v>1324</v>
-      </c>
-      <c r="L338" s="1" t="s">
-        <v>1325</v>
       </c>
       <c r="R338" t="s">
         <v>30</v>
@@ -18112,7 +18112,7 @@
         <v>405</v>
       </c>
       <c r="B339" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="D339" t="s">
         <v>535</v>
@@ -18124,11 +18124,11 @@
         <v>408</v>
       </c>
       <c r="J339" t="s">
+        <v>1325</v>
+      </c>
+      <c r="L339" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="L339" s="1" t="s">
-        <v>1327</v>
-      </c>
       <c r="R339" t="s">
         <v>30</v>
       </c>
@@ -18136,7 +18136,7 @@
         <v>31</v>
       </c>
       <c r="T339" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="U339" t="s">
         <v>109</v>
@@ -18150,10 +18150,10 @@
         <v>405</v>
       </c>
       <c r="B340" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="D340" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="E340" t="s">
         <v>79</v>
@@ -18162,22 +18162,22 @@
         <v>408</v>
       </c>
       <c r="J340" t="s">
+        <v>1328</v>
+      </c>
+      <c r="L340" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="L340" s="1" t="s">
+      <c r="R340" t="s">
+        <v>30</v>
+      </c>
+      <c r="S340" t="s">
+        <v>31</v>
+      </c>
+      <c r="T340" t="s">
         <v>1330</v>
       </c>
-      <c r="R340" t="s">
-        <v>30</v>
-      </c>
-      <c r="S340" t="s">
-        <v>31</v>
-      </c>
-      <c r="T340" t="s">
-        <v>1331</v>
-      </c>
       <c r="U340" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="W340">
         <v>3</v>
@@ -18188,10 +18188,10 @@
         <v>405</v>
       </c>
       <c r="B341" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="D341" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="E341" t="s">
         <v>79</v>
@@ -18200,11 +18200,11 @@
         <v>408</v>
       </c>
       <c r="J341" t="s">
+        <v>1332</v>
+      </c>
+      <c r="L341" s="1" t="s">
         <v>1333</v>
       </c>
-      <c r="L341" s="1" t="s">
-        <v>1334</v>
-      </c>
       <c r="R341" t="s">
         <v>30</v>
       </c>
@@ -18212,7 +18212,7 @@
         <v>31</v>
       </c>
       <c r="T341" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="U341" t="s">
         <v>631</v>
@@ -18223,13 +18223,13 @@
     </row>
     <row r="342" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B342" t="s">
         <v>1335</v>
       </c>
-      <c r="B342" t="s">
+      <c r="D342" t="s">
         <v>1336</v>
-      </c>
-      <c r="D342" t="s">
-        <v>1337</v>
       </c>
       <c r="E342" t="s">
         <v>144</v>
@@ -18238,19 +18238,19 @@
         <v>145</v>
       </c>
       <c r="J342" t="s">
+        <v>1337</v>
+      </c>
+      <c r="L342" s="1" t="s">
         <v>1338</v>
       </c>
-      <c r="L342" s="1" t="s">
+      <c r="R342" t="s">
+        <v>30</v>
+      </c>
+      <c r="S342" t="s">
+        <v>31</v>
+      </c>
+      <c r="T342" t="s">
         <v>1339</v>
-      </c>
-      <c r="R342" t="s">
-        <v>30</v>
-      </c>
-      <c r="S342" t="s">
-        <v>31</v>
-      </c>
-      <c r="T342" t="s">
-        <v>1340</v>
       </c>
       <c r="U342" t="s">
         <v>99</v>
@@ -18261,10 +18261,10 @@
     </row>
     <row r="343" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B343" t="s">
         <v>1335</v>
-      </c>
-      <c r="B343" t="s">
-        <v>1336</v>
       </c>
       <c r="D343" t="s">
         <v>377</v>
@@ -18276,10 +18276,10 @@
         <v>177</v>
       </c>
       <c r="J343" t="s">
+        <v>1340</v>
+      </c>
+      <c r="L343" s="1" t="s">
         <v>1341</v>
-      </c>
-      <c r="L343" s="1" t="s">
-        <v>1342</v>
       </c>
       <c r="R343" t="s">
         <v>30</v>
@@ -18291,7 +18291,7 @@
         <v>548</v>
       </c>
       <c r="U343" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="W343">
         <v>3</v>
@@ -18299,10 +18299,10 @@
     </row>
     <row r="344" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B344" t="s">
         <v>1335</v>
-      </c>
-      <c r="B344" t="s">
-        <v>1336</v>
       </c>
       <c r="D344">
         <v>1882</v>
@@ -18314,22 +18314,22 @@
         <v>675</v>
       </c>
       <c r="J344" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L344" s="1" t="s">
         <v>1343</v>
       </c>
-      <c r="L344" s="1" t="s">
+      <c r="R344" t="s">
+        <v>30</v>
+      </c>
+      <c r="S344" t="s">
+        <v>31</v>
+      </c>
+      <c r="T344" t="s">
         <v>1344</v>
       </c>
-      <c r="R344" t="s">
-        <v>30</v>
-      </c>
-      <c r="S344" t="s">
-        <v>31</v>
-      </c>
-      <c r="T344" t="s">
+      <c r="U344" t="s">
         <v>1345</v>
-      </c>
-      <c r="U344" t="s">
-        <v>1346</v>
       </c>
       <c r="W344">
         <v>3</v>
@@ -18337,10 +18337,10 @@
     </row>
     <row r="345" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B345" t="s">
         <v>1335</v>
-      </c>
-      <c r="B345" t="s">
-        <v>1336</v>
       </c>
       <c r="D345">
         <v>1882</v>
@@ -18349,14 +18349,14 @@
         <v>674</v>
       </c>
       <c r="F345" t="s">
+        <v>1346</v>
+      </c>
+      <c r="J345" t="s">
         <v>1347</v>
       </c>
-      <c r="J345" t="s">
+      <c r="L345" s="1" t="s">
         <v>1348</v>
       </c>
-      <c r="L345" s="1" t="s">
-        <v>1349</v>
-      </c>
       <c r="R345" t="s">
         <v>30</v>
       </c>
@@ -18364,10 +18364,10 @@
         <v>31</v>
       </c>
       <c r="T345" t="s">
+        <v>823</v>
+      </c>
+      <c r="U345" t="s">
         <v>824</v>
-      </c>
-      <c r="U345" t="s">
-        <v>825</v>
       </c>
       <c r="W345">
         <v>3</v>
@@ -18378,7 +18378,7 @@
         <v>360</v>
       </c>
       <c r="B346" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D346" t="s">
         <v>54</v>
@@ -18390,10 +18390,10 @@
         <v>80</v>
       </c>
       <c r="J346" t="s">
+        <v>1350</v>
+      </c>
+      <c r="L346" s="1" t="s">
         <v>1351</v>
-      </c>
-      <c r="L346" s="1" t="s">
-        <v>1352</v>
       </c>
       <c r="R346" t="s">
         <v>30</v>
@@ -18416,7 +18416,7 @@
         <v>360</v>
       </c>
       <c r="B347" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D347" t="s">
         <v>222</v>
@@ -18428,10 +18428,10 @@
         <v>80</v>
       </c>
       <c r="J347" t="s">
+        <v>1352</v>
+      </c>
+      <c r="L347" s="1" t="s">
         <v>1353</v>
-      </c>
-      <c r="L347" s="1" t="s">
-        <v>1354</v>
       </c>
       <c r="R347" t="s">
         <v>30</v>
@@ -18454,22 +18454,22 @@
         <v>360</v>
       </c>
       <c r="B348" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D348" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E348" t="s">
         <v>1355</v>
-      </c>
-      <c r="E348" t="s">
-        <v>1356</v>
       </c>
       <c r="F348" t="s">
         <v>340</v>
       </c>
       <c r="J348" t="s">
+        <v>1356</v>
+      </c>
+      <c r="L348" s="1" t="s">
         <v>1357</v>
-      </c>
-      <c r="L348" s="1" t="s">
-        <v>1358</v>
       </c>
       <c r="R348" t="s">
         <v>30</v>
@@ -18492,7 +18492,7 @@
         <v>360</v>
       </c>
       <c r="B349" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D349">
         <v>1892</v>
@@ -18504,10 +18504,10 @@
         <v>80</v>
       </c>
       <c r="J349" t="s">
+        <v>1358</v>
+      </c>
+      <c r="L349" s="1" t="s">
         <v>1359</v>
-      </c>
-      <c r="L349" s="1" t="s">
-        <v>1360</v>
       </c>
       <c r="R349" t="s">
         <v>30</v>
@@ -18527,10 +18527,10 @@
     </row>
     <row r="350" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B350" t="s">
         <v>1361</v>
-      </c>
-      <c r="B350" t="s">
-        <v>1362</v>
       </c>
       <c r="D350" t="s">
         <v>293</v>
@@ -18542,19 +18542,19 @@
         <v>467</v>
       </c>
       <c r="J350" t="s">
+        <v>1362</v>
+      </c>
+      <c r="L350" s="1" t="s">
         <v>1363</v>
       </c>
-      <c r="L350" s="1" t="s">
+      <c r="R350" t="s">
+        <v>30</v>
+      </c>
+      <c r="S350" t="s">
+        <v>31</v>
+      </c>
+      <c r="T350" t="s">
         <v>1364</v>
-      </c>
-      <c r="R350" t="s">
-        <v>30</v>
-      </c>
-      <c r="S350" t="s">
-        <v>31</v>
-      </c>
-      <c r="T350" t="s">
-        <v>1365</v>
       </c>
       <c r="U350" t="s">
         <v>263</v>
@@ -18565,13 +18565,13 @@
     </row>
     <row r="351" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B351" t="s">
         <v>1361</v>
       </c>
-      <c r="B351" t="s">
-        <v>1362</v>
-      </c>
       <c r="D351" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E351" t="s">
         <v>100</v>
@@ -18580,10 +18580,10 @@
         <v>101</v>
       </c>
       <c r="J351" t="s">
+        <v>1365</v>
+      </c>
+      <c r="L351" s="1" t="s">
         <v>1366</v>
-      </c>
-      <c r="L351" s="1" t="s">
-        <v>1367</v>
       </c>
       <c r="R351" t="s">
         <v>30</v>
@@ -18595,7 +18595,7 @@
         <v>40</v>
       </c>
       <c r="U351" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="W351">
         <v>2</v>
@@ -18603,13 +18603,13 @@
     </row>
     <row r="352" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B352" t="s">
         <v>1361</v>
       </c>
-      <c r="B352" t="s">
-        <v>1362</v>
-      </c>
       <c r="D352" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E352" t="s">
         <v>176</v>
@@ -18618,11 +18618,11 @@
         <v>381</v>
       </c>
       <c r="J352" t="s">
+        <v>1368</v>
+      </c>
+      <c r="L352" s="1" t="s">
         <v>1369</v>
       </c>
-      <c r="L352" s="1" t="s">
-        <v>1370</v>
-      </c>
       <c r="R352" t="s">
         <v>30</v>
       </c>
@@ -18630,7 +18630,7 @@
         <v>31</v>
       </c>
       <c r="T352" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="U352" t="s">
         <v>66</v>
@@ -18641,26 +18641,26 @@
     </row>
     <row r="353" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B353" t="s">
         <v>1361</v>
       </c>
-      <c r="B353" t="s">
-        <v>1362</v>
-      </c>
       <c r="D353" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E353" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F353" t="s">
         <v>1371</v>
       </c>
-      <c r="F353" t="s">
+      <c r="J353" t="s">
         <v>1372</v>
       </c>
-      <c r="J353" t="s">
+      <c r="L353" s="1" t="s">
         <v>1373</v>
       </c>
-      <c r="L353" s="1" t="s">
-        <v>1374</v>
-      </c>
       <c r="R353" t="s">
         <v>30</v>
       </c>
@@ -18668,7 +18668,7 @@
         <v>31</v>
       </c>
       <c r="T353" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="U353" t="s">
         <v>659</v>
@@ -18679,10 +18679,10 @@
     </row>
     <row r="354" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B354" t="s">
         <v>1361</v>
-      </c>
-      <c r="B354" t="s">
-        <v>1362</v>
       </c>
       <c r="D354" t="s">
         <v>238</v>
@@ -18694,10 +18694,10 @@
         <v>80</v>
       </c>
       <c r="J354" t="s">
+        <v>1374</v>
+      </c>
+      <c r="L354" s="1" t="s">
         <v>1375</v>
-      </c>
-      <c r="L354" s="1" t="s">
-        <v>1376</v>
       </c>
       <c r="R354" t="s">
         <v>30</v>
@@ -18717,25 +18717,25 @@
     </row>
     <row r="355" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B355" t="s">
         <v>1361</v>
       </c>
-      <c r="B355" t="s">
-        <v>1362</v>
-      </c>
       <c r="D355" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="E355" t="s">
         <v>71</v>
       </c>
       <c r="F355" t="s">
+        <v>1377</v>
+      </c>
+      <c r="J355" t="s">
         <v>1378</v>
       </c>
-      <c r="J355" t="s">
+      <c r="L355" s="1" t="s">
         <v>1379</v>
-      </c>
-      <c r="L355" s="1" t="s">
-        <v>1380</v>
       </c>
       <c r="R355" t="s">
         <v>30</v>
@@ -18755,10 +18755,10 @@
     </row>
     <row r="356" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B356" t="s">
         <v>1361</v>
-      </c>
-      <c r="B356" t="s">
-        <v>1362</v>
       </c>
       <c r="D356" t="s">
         <v>660</v>
@@ -18770,10 +18770,10 @@
         <v>145</v>
       </c>
       <c r="J356" t="s">
+        <v>1380</v>
+      </c>
+      <c r="L356" s="1" t="s">
         <v>1381</v>
-      </c>
-      <c r="L356" s="1" t="s">
-        <v>1382</v>
       </c>
       <c r="R356" t="s">
         <v>30</v>
@@ -18793,10 +18793,10 @@
     </row>
     <row r="357" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B357" t="s">
         <v>1361</v>
-      </c>
-      <c r="B357" t="s">
-        <v>1362</v>
       </c>
       <c r="D357">
         <v>1890</v>
@@ -18808,10 +18808,10 @@
         <v>371</v>
       </c>
       <c r="J357" t="s">
+        <v>1382</v>
+      </c>
+      <c r="L357" s="1" t="s">
         <v>1383</v>
-      </c>
-      <c r="L357" s="1" t="s">
-        <v>1384</v>
       </c>
       <c r="R357" t="s">
         <v>30</v>
@@ -18834,10 +18834,10 @@
         <v>360</v>
       </c>
       <c r="B358" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="D358" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E358" t="s">
         <v>144</v>
@@ -18846,10 +18846,10 @@
         <v>371</v>
       </c>
       <c r="J358" t="s">
+        <v>1385</v>
+      </c>
+      <c r="L358" s="1" t="s">
         <v>1386</v>
-      </c>
-      <c r="L358" s="1" t="s">
-        <v>1387</v>
       </c>
       <c r="R358" t="s">
         <v>30</v>
@@ -18872,22 +18872,22 @@
         <v>360</v>
       </c>
       <c r="B359" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="D359" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E359" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F359" t="s">
         <v>1388</v>
       </c>
-      <c r="F359" t="s">
+      <c r="J359" t="s">
         <v>1389</v>
       </c>
-      <c r="J359" t="s">
+      <c r="L359" s="1" t="s">
         <v>1390</v>
-      </c>
-      <c r="L359" s="1" t="s">
-        <v>1391</v>
       </c>
       <c r="R359" t="s">
         <v>30</v>
@@ -18910,7 +18910,7 @@
         <v>360</v>
       </c>
       <c r="B360" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="D360">
         <v>1892</v>
@@ -18922,10 +18922,10 @@
         <v>80</v>
       </c>
       <c r="J360" t="s">
+        <v>1391</v>
+      </c>
+      <c r="L360" s="1" t="s">
         <v>1392</v>
-      </c>
-      <c r="L360" s="1" t="s">
-        <v>1393</v>
       </c>
       <c r="R360" t="s">
         <v>30</v>
@@ -18948,7 +18948,7 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="D361">
         <v>1895</v>
@@ -18960,10 +18960,10 @@
         <v>80</v>
       </c>
       <c r="J361" t="s">
+        <v>1393</v>
+      </c>
+      <c r="L361" s="1" t="s">
         <v>1394</v>
-      </c>
-      <c r="L361" s="1" t="s">
-        <v>1395</v>
       </c>
       <c r="R361" t="s">
         <v>30</v>
@@ -18983,10 +18983,10 @@
     </row>
     <row r="362" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B362" t="s">
         <v>1396</v>
-      </c>
-      <c r="B362" t="s">
-        <v>1397</v>
       </c>
       <c r="D362" t="s">
         <v>317</v>
@@ -18998,10 +18998,10 @@
         <v>80</v>
       </c>
       <c r="J362" t="s">
+        <v>1397</v>
+      </c>
+      <c r="L362" s="1" t="s">
         <v>1398</v>
-      </c>
-      <c r="L362" s="1" t="s">
-        <v>1399</v>
       </c>
       <c r="R362" t="s">
         <v>30</v>
@@ -19021,25 +19021,25 @@
     </row>
     <row r="363" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B363" t="s">
         <v>1396</v>
-      </c>
-      <c r="B363" t="s">
-        <v>1397</v>
       </c>
       <c r="D363" t="s">
         <v>321</v>
       </c>
       <c r="E363" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F363" t="s">
         <v>340</v>
       </c>
       <c r="J363" t="s">
+        <v>1400</v>
+      </c>
+      <c r="L363" s="1" t="s">
         <v>1401</v>
-      </c>
-      <c r="L363" s="1" t="s">
-        <v>1402</v>
       </c>
       <c r="R363" t="s">
         <v>30</v>
@@ -19059,10 +19059,10 @@
     </row>
     <row r="364" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B364" t="s">
         <v>1396</v>
-      </c>
-      <c r="B364" t="s">
-        <v>1397</v>
       </c>
       <c r="D364" t="s">
         <v>321</v>
@@ -19074,10 +19074,10 @@
         <v>145</v>
       </c>
       <c r="J364" t="s">
+        <v>1402</v>
+      </c>
+      <c r="L364" s="1" t="s">
         <v>1403</v>
-      </c>
-      <c r="L364" s="1" t="s">
-        <v>1404</v>
       </c>
       <c r="R364" t="s">
         <v>30</v>
@@ -19097,10 +19097,10 @@
     </row>
     <row r="365" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B365" t="s">
         <v>1396</v>
-      </c>
-      <c r="B365" t="s">
-        <v>1397</v>
       </c>
       <c r="D365" t="s">
         <v>321</v>
@@ -19109,13 +19109,13 @@
         <v>611</v>
       </c>
       <c r="F365" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="J365" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="L365" s="1" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="R365" t="s">
         <v>30</v>
@@ -19135,13 +19135,13 @@
     </row>
     <row r="366" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B366" t="s">
         <v>1396</v>
       </c>
-      <c r="B366" t="s">
-        <v>1397</v>
-      </c>
       <c r="D366" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E366" t="s">
         <v>79</v>
@@ -19150,10 +19150,10 @@
         <v>80</v>
       </c>
       <c r="J366" t="s">
+        <v>1405</v>
+      </c>
+      <c r="L366" s="1" t="s">
         <v>1406</v>
-      </c>
-      <c r="L366" s="1" t="s">
-        <v>1407</v>
       </c>
       <c r="R366" t="s">
         <v>30</v>
@@ -19173,10 +19173,10 @@
     </row>
     <row r="367" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B367" t="s">
         <v>1396</v>
-      </c>
-      <c r="B367" t="s">
-        <v>1397</v>
       </c>
       <c r="D367">
         <v>1872</v>
@@ -19188,10 +19188,10 @@
         <v>145</v>
       </c>
       <c r="J367" t="s">
+        <v>1407</v>
+      </c>
+      <c r="L367" s="1" t="s">
         <v>1408</v>
-      </c>
-      <c r="L367" s="1" t="s">
-        <v>1409</v>
       </c>
       <c r="R367" t="s">
         <v>30</v>
@@ -19211,10 +19211,10 @@
     </row>
     <row r="368" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B368" t="s">
         <v>1396</v>
-      </c>
-      <c r="B368" t="s">
-        <v>1397</v>
       </c>
       <c r="D368">
         <v>1870</v>
@@ -19226,10 +19226,10 @@
         <v>80</v>
       </c>
       <c r="J368" t="s">
+        <v>1409</v>
+      </c>
+      <c r="L368" s="1" t="s">
         <v>1410</v>
-      </c>
-      <c r="L368" s="1" t="s">
-        <v>1411</v>
       </c>
       <c r="R368" t="s">
         <v>30</v>
@@ -19249,10 +19249,10 @@
     </row>
     <row r="369" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B369" t="s">
         <v>1396</v>
-      </c>
-      <c r="B369" t="s">
-        <v>1397</v>
       </c>
       <c r="D369">
         <v>1873</v>
@@ -19264,10 +19264,10 @@
         <v>80</v>
       </c>
       <c r="J369" t="s">
+        <v>1411</v>
+      </c>
+      <c r="L369" s="1" t="s">
         <v>1412</v>
-      </c>
-      <c r="L369" s="1" t="s">
-        <v>1413</v>
       </c>
       <c r="R369" t="s">
         <v>30</v>
@@ -19287,10 +19287,10 @@
     </row>
     <row r="370" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B370" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="D370" t="s">
         <v>695</v>
@@ -19302,11 +19302,11 @@
         <v>177</v>
       </c>
       <c r="J370" t="s">
+        <v>1414</v>
+      </c>
+      <c r="L370" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="L370" s="1" t="s">
-        <v>1416</v>
-      </c>
       <c r="R370" t="s">
         <v>30</v>
       </c>
@@ -19314,7 +19314,7 @@
         <v>31</v>
       </c>
       <c r="T370" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="U370" t="s">
         <v>314</v>
@@ -19325,25 +19325,25 @@
     </row>
     <row r="371" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B371" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="D371" t="s">
         <v>330</v>
       </c>
       <c r="E371" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F371" t="s">
         <v>1417</v>
       </c>
-      <c r="F371" t="s">
+      <c r="J371" t="s">
         <v>1418</v>
       </c>
-      <c r="J371" t="s">
+      <c r="L371" s="1" t="s">
         <v>1419</v>
-      </c>
-      <c r="L371" s="1" t="s">
-        <v>1420</v>
       </c>
       <c r="R371" t="s">
         <v>30</v>
@@ -19363,10 +19363,10 @@
     </row>
     <row r="372" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B372" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="D372">
         <v>1873</v>
@@ -19375,13 +19375,13 @@
         <v>176</v>
       </c>
       <c r="F372" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J372" t="s">
         <v>1421</v>
       </c>
-      <c r="J372" t="s">
+      <c r="L372" s="1" t="s">
         <v>1422</v>
-      </c>
-      <c r="L372" s="1" t="s">
-        <v>1423</v>
       </c>
       <c r="R372" t="s">
         <v>30</v>
@@ -19401,10 +19401,10 @@
     </row>
     <row r="373" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B373" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="D373">
         <v>1876</v>
@@ -19416,10 +19416,10 @@
         <v>177</v>
       </c>
       <c r="J373" t="s">
+        <v>1423</v>
+      </c>
+      <c r="L373" s="1" t="s">
         <v>1424</v>
-      </c>
-      <c r="L373" s="1" t="s">
-        <v>1425</v>
       </c>
       <c r="R373" t="s">
         <v>30</v>
@@ -19439,10 +19439,10 @@
     </row>
     <row r="374" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B374" t="s">
         <v>1426</v>
-      </c>
-      <c r="B374" t="s">
-        <v>1427</v>
       </c>
       <c r="D374">
         <v>1829</v>
@@ -19454,10 +19454,10 @@
         <v>467</v>
       </c>
       <c r="J374" t="s">
+        <v>1427</v>
+      </c>
+      <c r="L374" s="1" t="s">
         <v>1428</v>
-      </c>
-      <c r="L374" s="1" t="s">
-        <v>1429</v>
       </c>
       <c r="R374" t="s">
         <v>30</v>
@@ -19469,7 +19469,7 @@
         <v>59</v>
       </c>
       <c r="U374" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="W374">
         <v>2</v>
@@ -19477,13 +19477,13 @@
     </row>
     <row r="375" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B375" t="s">
         <v>1426</v>
       </c>
-      <c r="B375" t="s">
-        <v>1427</v>
-      </c>
       <c r="D375" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="E375" t="s">
         <v>176</v>
@@ -19492,10 +19492,10 @@
         <v>467</v>
       </c>
       <c r="J375" t="s">
+        <v>1430</v>
+      </c>
+      <c r="L375" s="1" t="s">
         <v>1431</v>
-      </c>
-      <c r="L375" s="1" t="s">
-        <v>1432</v>
       </c>
       <c r="R375" t="s">
         <v>30</v>
@@ -19515,10 +19515,10 @@
     </row>
     <row r="376" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B376" t="s">
         <v>1426</v>
-      </c>
-      <c r="B376" t="s">
-        <v>1427</v>
       </c>
       <c r="D376">
         <v>1837</v>
@@ -19530,10 +19530,10 @@
         <v>177</v>
       </c>
       <c r="J376" t="s">
+        <v>1432</v>
+      </c>
+      <c r="L376" s="1" t="s">
         <v>1433</v>
-      </c>
-      <c r="L376" s="1" t="s">
-        <v>1434</v>
       </c>
       <c r="R376" t="s">
         <v>30</v>
@@ -19553,13 +19553,13 @@
     </row>
     <row r="377" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B377" t="s">
         <v>1426</v>
       </c>
-      <c r="B377" t="s">
-        <v>1427</v>
-      </c>
       <c r="D377" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E377" t="s">
         <v>674</v>
@@ -19568,10 +19568,10 @@
         <v>675</v>
       </c>
       <c r="J377" t="s">
+        <v>1434</v>
+      </c>
+      <c r="L377" s="1" t="s">
         <v>1435</v>
-      </c>
-      <c r="L377" s="1" t="s">
-        <v>1436</v>
       </c>
       <c r="R377" t="s">
         <v>30</v>
@@ -19591,10 +19591,10 @@
     </row>
     <row r="378" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B378" t="s">
         <v>1426</v>
-      </c>
-      <c r="B378" t="s">
-        <v>1427</v>
       </c>
       <c r="D378" t="s">
         <v>448</v>
@@ -19606,10 +19606,10 @@
         <v>177</v>
       </c>
       <c r="J378" t="s">
+        <v>1436</v>
+      </c>
+      <c r="L378" s="1" t="s">
         <v>1437</v>
-      </c>
-      <c r="L378" s="1" t="s">
-        <v>1438</v>
       </c>
       <c r="R378" t="s">
         <v>30</v>
@@ -19629,13 +19629,13 @@
     </row>
     <row r="379" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B379" t="s">
         <v>1426</v>
       </c>
-      <c r="B379" t="s">
-        <v>1427</v>
-      </c>
       <c r="D379" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="E379" t="s">
         <v>176</v>
@@ -19644,10 +19644,10 @@
         <v>467</v>
       </c>
       <c r="J379" t="s">
+        <v>1439</v>
+      </c>
+      <c r="L379" s="1" t="s">
         <v>1440</v>
-      </c>
-      <c r="L379" s="1" t="s">
-        <v>1441</v>
       </c>
       <c r="R379" t="s">
         <v>30</v>
@@ -19667,10 +19667,10 @@
     </row>
     <row r="380" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B380" t="s">
         <v>1426</v>
-      </c>
-      <c r="B380" t="s">
-        <v>1427</v>
       </c>
       <c r="D380">
         <v>1815</v>
@@ -19682,10 +19682,10 @@
         <v>467</v>
       </c>
       <c r="J380" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L380" s="1" t="s">
         <v>1442</v>
-      </c>
-      <c r="L380" s="1" t="s">
-        <v>1443</v>
       </c>
       <c r="R380" t="s">
         <v>30</v>
@@ -19705,10 +19705,10 @@
     </row>
     <row r="381" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B381" t="s">
         <v>1426</v>
-      </c>
-      <c r="B381" t="s">
-        <v>1427</v>
       </c>
       <c r="D381">
         <v>1817</v>
@@ -19720,11 +19720,11 @@
         <v>467</v>
       </c>
       <c r="J381" t="s">
+        <v>1443</v>
+      </c>
+      <c r="L381" s="1" t="s">
         <v>1444</v>
       </c>
-      <c r="L381" s="1" t="s">
-        <v>1445</v>
-      </c>
       <c r="R381" t="s">
         <v>30</v>
       </c>
@@ -19732,10 +19732,10 @@
         <v>31</v>
       </c>
       <c r="T381" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="U381" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="W381">
         <v>2</v>
@@ -19743,13 +19743,13 @@
     </row>
     <row r="382" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B382" t="s">
         <v>1446</v>
       </c>
-      <c r="B382" t="s">
-        <v>1447</v>
-      </c>
       <c r="D382" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="E382" t="s">
         <v>239</v>
@@ -19758,16 +19758,16 @@
         <v>663</v>
       </c>
       <c r="J382" t="s">
+        <v>1447</v>
+      </c>
+      <c r="L382" s="1" t="s">
         <v>1448</v>
       </c>
-      <c r="L382" s="1" t="s">
+      <c r="R382" t="s">
+        <v>30</v>
+      </c>
+      <c r="S382" t="s">
         <v>1449</v>
-      </c>
-      <c r="R382" t="s">
-        <v>30</v>
-      </c>
-      <c r="S382" t="s">
-        <v>1450</v>
       </c>
       <c r="T382" t="s">
         <v>109</v>
@@ -19781,13 +19781,13 @@
     </row>
     <row r="383" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B383" t="s">
         <v>1446</v>
       </c>
-      <c r="B383" t="s">
-        <v>1447</v>
-      </c>
       <c r="D383" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E383" t="s">
         <v>79</v>
@@ -19796,16 +19796,16 @@
         <v>80</v>
       </c>
       <c r="J383" t="s">
+        <v>1450</v>
+      </c>
+      <c r="L383" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="L383" s="1" t="s">
+      <c r="R383" t="s">
+        <v>30</v>
+      </c>
+      <c r="S383" t="s">
         <v>1452</v>
-      </c>
-      <c r="R383" t="s">
-        <v>30</v>
-      </c>
-      <c r="S383" t="s">
-        <v>1453</v>
       </c>
       <c r="T383" t="s">
         <v>391</v>
@@ -19819,25 +19819,25 @@
     </row>
     <row r="384" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B384" t="s">
         <v>1446</v>
-      </c>
-      <c r="B384" t="s">
-        <v>1447</v>
       </c>
       <c r="D384">
         <v>1893</v>
       </c>
       <c r="E384" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F384" t="s">
         <v>1454</v>
       </c>
-      <c r="F384" t="s">
+      <c r="J384" t="s">
         <v>1455</v>
       </c>
-      <c r="J384" t="s">
+      <c r="L384" s="1" t="s">
         <v>1456</v>
-      </c>
-      <c r="L384" s="1" t="s">
-        <v>1457</v>
       </c>
       <c r="R384" t="s">
         <v>30</v>
@@ -19857,10 +19857,10 @@
     </row>
     <row r="385" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B385" t="s">
         <v>1446</v>
-      </c>
-      <c r="B385" t="s">
-        <v>1447</v>
       </c>
       <c r="D385">
         <v>1899</v>
@@ -19872,10 +19872,10 @@
         <v>80</v>
       </c>
       <c r="J385" t="s">
+        <v>1457</v>
+      </c>
+      <c r="L385" s="6" t="s">
         <v>1458</v>
-      </c>
-      <c r="L385" s="6" t="s">
-        <v>1459</v>
       </c>
       <c r="R385" t="s">
         <v>30</v>
@@ -19895,10 +19895,10 @@
     </row>
     <row r="386" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B386" t="s">
         <v>1460</v>
-      </c>
-      <c r="B386" t="s">
-        <v>1461</v>
       </c>
       <c r="D386" t="s">
         <v>377</v>
@@ -19907,13 +19907,13 @@
         <v>130</v>
       </c>
       <c r="F386" t="s">
+        <v>1461</v>
+      </c>
+      <c r="J386" t="s">
         <v>1462</v>
       </c>
-      <c r="J386" t="s">
+      <c r="L386" s="1" t="s">
         <v>1463</v>
-      </c>
-      <c r="L386" s="1" t="s">
-        <v>1464</v>
       </c>
       <c r="R386" t="s">
         <v>30</v>
@@ -19933,10 +19933,10 @@
     </row>
     <row r="387" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B387" t="s">
         <v>1460</v>
-      </c>
-      <c r="B387" t="s">
-        <v>1461</v>
       </c>
       <c r="D387" t="s">
         <v>54</v>
@@ -19945,13 +19945,13 @@
         <v>130</v>
       </c>
       <c r="F387" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="J387" t="s">
+        <v>1464</v>
+      </c>
+      <c r="L387" s="1" t="s">
         <v>1465</v>
-      </c>
-      <c r="L387" s="1" t="s">
-        <v>1466</v>
       </c>
       <c r="R387" t="s">
         <v>30</v>
@@ -19971,10 +19971,10 @@
     </row>
     <row r="388" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B388" t="s">
         <v>1460</v>
-      </c>
-      <c r="B388" t="s">
-        <v>1461</v>
       </c>
       <c r="D388" t="s">
         <v>54</v>
@@ -19983,13 +19983,13 @@
         <v>130</v>
       </c>
       <c r="F388" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="J388" t="s">
+        <v>1466</v>
+      </c>
+      <c r="L388" s="1" t="s">
         <v>1467</v>
-      </c>
-      <c r="L388" s="1" t="s">
-        <v>1468</v>
       </c>
       <c r="R388" t="s">
         <v>30</v>
@@ -20009,25 +20009,25 @@
     </row>
     <row r="389" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B389" t="s">
         <v>1460</v>
-      </c>
-      <c r="B389" t="s">
-        <v>1461</v>
       </c>
       <c r="D389" t="s">
         <v>54</v>
       </c>
       <c r="E389" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F389" t="s">
         <v>1469</v>
       </c>
-      <c r="F389" t="s">
+      <c r="J389" t="s">
         <v>1470</v>
       </c>
-      <c r="J389" t="s">
-        <v>1471</v>
-      </c>
-      <c r="L389" s="1" t="s">
-        <v>1472</v>
+      <c r="L389" s="6" t="s">
+        <v>1595</v>
       </c>
       <c r="R389" t="s">
         <v>30</v>
@@ -20047,10 +20047,10 @@
     </row>
     <row r="390" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B390" t="s">
         <v>1460</v>
-      </c>
-      <c r="B390" t="s">
-        <v>1461</v>
       </c>
       <c r="D390" t="s">
         <v>222</v>
@@ -20062,10 +20062,10 @@
         <v>371</v>
       </c>
       <c r="J390" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="L390" s="1" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="R390" t="s">
         <v>30</v>
@@ -20085,10 +20085,10 @@
     </row>
     <row r="391" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B391" t="s">
         <v>1460</v>
-      </c>
-      <c r="B391" t="s">
-        <v>1461</v>
       </c>
       <c r="D391" t="s">
         <v>222</v>
@@ -20100,10 +20100,10 @@
         <v>381</v>
       </c>
       <c r="J391" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="L391" s="1" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="R391" t="s">
         <v>30</v>
@@ -20123,10 +20123,10 @@
     </row>
     <row r="392" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B392" t="s">
         <v>1460</v>
-      </c>
-      <c r="B392" t="s">
-        <v>1461</v>
       </c>
       <c r="D392" t="s">
         <v>222</v>
@@ -20138,10 +20138,10 @@
         <v>63</v>
       </c>
       <c r="J392" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="L392" s="1" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="R392" t="s">
         <v>30</v>
@@ -20161,25 +20161,25 @@
     </row>
     <row r="393" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B393" t="s">
         <v>1460</v>
       </c>
-      <c r="B393" t="s">
-        <v>1461</v>
-      </c>
       <c r="D393" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E393" t="s">
         <v>130</v>
       </c>
       <c r="F393" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="J393" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="L393" s="1" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="R393" t="s">
         <v>30</v>
@@ -20191,7 +20191,7 @@
         <v>252</v>
       </c>
       <c r="U393" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="W393">
         <v>1</v>
@@ -20199,13 +20199,13 @@
     </row>
     <row r="394" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B394" t="s">
         <v>1460</v>
       </c>
-      <c r="B394" t="s">
-        <v>1461</v>
-      </c>
       <c r="D394" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E394" t="s">
         <v>79</v>
@@ -20214,10 +20214,10 @@
         <v>80</v>
       </c>
       <c r="J394" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="L394" s="1" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="R394" t="s">
         <v>30</v>
@@ -20226,7 +20226,7 @@
         <v>31</v>
       </c>
       <c r="T394" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="U394" t="s">
         <v>129</v>
@@ -20237,10 +20237,10 @@
     </row>
     <row r="395" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B395" t="s">
         <v>1460</v>
-      </c>
-      <c r="B395" t="s">
-        <v>1461</v>
       </c>
       <c r="D395">
         <v>1890</v>
@@ -20252,10 +20252,10 @@
         <v>80</v>
       </c>
       <c r="J395" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="L395" s="1" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="R395" t="s">
         <v>30</v>
@@ -20275,10 +20275,10 @@
     </row>
     <row r="396" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B396" t="s">
         <v>1460</v>
-      </c>
-      <c r="B396" t="s">
-        <v>1461</v>
       </c>
       <c r="D396">
         <v>1890</v>
@@ -20287,13 +20287,13 @@
         <v>130</v>
       </c>
       <c r="F396" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="J396" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="L396" s="1" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="R396" t="s">
         <v>30</v>
@@ -20313,13 +20313,13 @@
     </row>
     <row r="397" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B397" t="s">
         <v>1460</v>
       </c>
-      <c r="B397" t="s">
-        <v>1461</v>
-      </c>
       <c r="D397" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E397" t="s">
         <v>79</v>
@@ -20328,10 +20328,10 @@
         <v>80</v>
       </c>
       <c r="J397" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="L397" s="1" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="R397" t="s">
         <v>30</v>
@@ -20351,10 +20351,10 @@
     </row>
     <row r="398" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="B398" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="D398" t="s">
         <v>61</v>
@@ -20366,22 +20366,22 @@
         <v>326</v>
       </c>
       <c r="J398" t="s">
+        <v>1489</v>
+      </c>
+      <c r="L398" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="R398" t="s">
+        <v>30</v>
+      </c>
+      <c r="S398" t="s">
+        <v>31</v>
+      </c>
+      <c r="T398" t="s">
         <v>1491</v>
       </c>
-      <c r="L398" s="1" t="s">
-        <v>1492</v>
-      </c>
-      <c r="R398" t="s">
-        <v>30</v>
-      </c>
-      <c r="S398" t="s">
-        <v>31</v>
-      </c>
-      <c r="T398" t="s">
-        <v>1493</v>
-      </c>
       <c r="U398" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="W398">
         <v>3</v>
@@ -20389,25 +20389,25 @@
     </row>
     <row r="399" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="B399" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="D399" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E399" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F399" t="s">
         <v>309</v>
       </c>
       <c r="J399" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="L399" s="1" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="R399" t="s">
         <v>30</v>
@@ -20416,7 +20416,7 @@
         <v>31</v>
       </c>
       <c r="T399" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="U399" t="s">
         <v>89</v>
@@ -20427,25 +20427,25 @@
     </row>
     <row r="400" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="B400" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="D400">
         <v>1890</v>
       </c>
       <c r="E400" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F400" t="s">
         <v>1371</v>
       </c>
-      <c r="F400" t="s">
-        <v>1372</v>
-      </c>
       <c r="J400" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="L400" s="1" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="R400" t="s">
         <v>30</v>
@@ -20465,10 +20465,10 @@
     </row>
     <row r="401" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="B401" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="D401">
         <v>1892</v>
@@ -20480,10 +20480,10 @@
         <v>467</v>
       </c>
       <c r="J401" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="L401" s="1" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="R401" t="s">
         <v>30</v>
@@ -20503,13 +20503,13 @@
     </row>
     <row r="402" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="B402" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="D402" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E402" t="s">
         <v>35</v>
@@ -20518,10 +20518,10 @@
         <v>36</v>
       </c>
       <c r="J402" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="L402" s="1" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="R402" t="s">
         <v>30</v>
@@ -20533,7 +20533,7 @@
         <v>282</v>
       </c>
       <c r="U402" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="W402">
         <v>3</v>
@@ -20541,13 +20541,13 @@
     </row>
     <row r="403" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="B403" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="D403" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="E403" t="s">
         <v>35</v>
@@ -20556,22 +20556,22 @@
         <v>36</v>
       </c>
       <c r="J403" t="s">
+        <v>1504</v>
+      </c>
+      <c r="L403" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="R403" t="s">
+        <v>30</v>
+      </c>
+      <c r="S403" t="s">
+        <v>31</v>
+      </c>
+      <c r="T403" t="s">
         <v>1506</v>
       </c>
-      <c r="L403" s="1" t="s">
+      <c r="U403" t="s">
         <v>1507</v>
-      </c>
-      <c r="R403" t="s">
-        <v>30</v>
-      </c>
-      <c r="S403" t="s">
-        <v>31</v>
-      </c>
-      <c r="T403" t="s">
-        <v>1508</v>
-      </c>
-      <c r="U403" t="s">
-        <v>1509</v>
       </c>
       <c r="W403">
         <v>3</v>
@@ -20579,10 +20579,10 @@
     </row>
     <row r="404" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="B404" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="D404">
         <v>1895</v>
@@ -20594,10 +20594,10 @@
         <v>36</v>
       </c>
       <c r="J404" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="L404" s="1" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="R404" t="s">
         <v>30</v>
@@ -20609,7 +20609,7 @@
         <v>297</v>
       </c>
       <c r="U404" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="W404">
         <v>3</v>
@@ -20617,10 +20617,10 @@
     </row>
     <row r="405" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="B405" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="D405">
         <v>1899</v>
@@ -20632,22 +20632,22 @@
         <v>36</v>
       </c>
       <c r="J405" t="s">
+        <v>1510</v>
+      </c>
+      <c r="L405" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="R405" t="s">
+        <v>30</v>
+      </c>
+      <c r="S405" t="s">
+        <v>31</v>
+      </c>
+      <c r="T405" t="s">
         <v>1512</v>
       </c>
-      <c r="L405" s="1" t="s">
-        <v>1513</v>
-      </c>
-      <c r="R405" t="s">
-        <v>30</v>
-      </c>
-      <c r="S405" t="s">
-        <v>31</v>
-      </c>
-      <c r="T405" t="s">
-        <v>1514</v>
-      </c>
       <c r="U405" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="W405">
         <v>3</v>
@@ -20655,10 +20655,10 @@
     </row>
     <row r="406" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B406" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D406" t="s">
         <v>634</v>
@@ -20670,10 +20670,10 @@
         <v>371</v>
       </c>
       <c r="J406" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="L406" s="1" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="R406" t="s">
         <v>30</v>
@@ -20682,7 +20682,7 @@
         <v>637</v>
       </c>
       <c r="T406" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="U406" t="s">
         <v>374</v>
@@ -20693,10 +20693,10 @@
     </row>
     <row r="407" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B407" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D407" t="s">
         <v>352</v>
@@ -20708,10 +20708,10 @@
         <v>371</v>
       </c>
       <c r="J407" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="L407" s="1" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="R407" t="s">
         <v>30</v>
@@ -20723,7 +20723,7 @@
         <v>374</v>
       </c>
       <c r="U407" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="W407">
         <v>2</v>
@@ -20731,10 +20731,10 @@
     </row>
     <row r="408" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B408" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D408" t="s">
         <v>61</v>
@@ -20746,10 +20746,10 @@
         <v>80</v>
       </c>
       <c r="J408" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="L408" s="1" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="R408" t="s">
         <v>30</v>
@@ -20758,7 +20758,7 @@
         <v>644</v>
       </c>
       <c r="T408" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="U408" t="s">
         <v>121</v>
@@ -20769,10 +20769,10 @@
     </row>
     <row r="409" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B409" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D409" t="s">
         <v>61</v>
@@ -20784,10 +20784,10 @@
         <v>80</v>
       </c>
       <c r="J409" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="L409" s="1" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="R409" t="s">
         <v>30</v>
@@ -20807,10 +20807,10 @@
     </row>
     <row r="410" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B410" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D410" t="s">
         <v>61</v>
@@ -20822,10 +20822,10 @@
         <v>80</v>
       </c>
       <c r="J410" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="L410" s="1" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="R410" t="s">
         <v>30</v>
@@ -20834,7 +20834,7 @@
         <v>644</v>
       </c>
       <c r="T410" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="U410" t="s">
         <v>75</v>
@@ -20845,10 +20845,10 @@
     </row>
     <row r="411" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B411" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D411">
         <v>1891</v>
@@ -20860,10 +20860,10 @@
         <v>80</v>
       </c>
       <c r="J411" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="L411" s="1" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="R411" t="s">
         <v>30</v>
@@ -20883,10 +20883,10 @@
     </row>
     <row r="412" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B412" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D412">
         <v>1890</v>
@@ -20898,10 +20898,10 @@
         <v>80</v>
       </c>
       <c r="J412" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="L412" s="1" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="R412" t="s">
         <v>30</v>
@@ -20921,10 +20921,10 @@
     </row>
     <row r="413" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B413" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D413">
         <v>1895</v>
@@ -20936,22 +20936,22 @@
         <v>145</v>
       </c>
       <c r="J413" t="s">
+        <v>1529</v>
+      </c>
+      <c r="L413" s="1" t="s">
+        <v>1530</v>
+      </c>
+      <c r="R413" t="s">
+        <v>30</v>
+      </c>
+      <c r="S413" t="s">
         <v>1531</v>
       </c>
-      <c r="L413" s="1" t="s">
+      <c r="T413" t="s">
         <v>1532</v>
       </c>
-      <c r="R413" t="s">
-        <v>30</v>
-      </c>
-      <c r="S413" t="s">
+      <c r="U413" t="s">
         <v>1533</v>
-      </c>
-      <c r="T413" t="s">
-        <v>1534</v>
-      </c>
-      <c r="U413" t="s">
-        <v>1535</v>
       </c>
       <c r="W413">
         <v>2</v>
@@ -20959,10 +20959,10 @@
     </row>
     <row r="414" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="B414" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="D414" t="s">
         <v>54</v>
@@ -20974,19 +20974,19 @@
         <v>177</v>
       </c>
       <c r="J414" t="s">
+        <v>1536</v>
+      </c>
+      <c r="L414" s="1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="R414" t="s">
+        <v>30</v>
+      </c>
+      <c r="S414" t="s">
+        <v>31</v>
+      </c>
+      <c r="T414" t="s">
         <v>1538</v>
-      </c>
-      <c r="L414" s="1" t="s">
-        <v>1539</v>
-      </c>
-      <c r="R414" t="s">
-        <v>30</v>
-      </c>
-      <c r="S414" t="s">
-        <v>31</v>
-      </c>
-      <c r="T414" t="s">
-        <v>1540</v>
       </c>
       <c r="U414" t="s">
         <v>554</v>
@@ -20997,25 +20997,25 @@
     </row>
     <row r="415" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="B415" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="D415">
         <v>1896</v>
       </c>
       <c r="E415" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F415" t="s">
+        <v>1238</v>
+      </c>
+      <c r="J415" t="s">
+        <v>1540</v>
+      </c>
+      <c r="L415" s="1" t="s">
         <v>1541</v>
-      </c>
-      <c r="F415" t="s">
-        <v>1239</v>
-      </c>
-      <c r="J415" t="s">
-        <v>1542</v>
-      </c>
-      <c r="L415" s="1" t="s">
-        <v>1543</v>
       </c>
       <c r="R415" t="s">
         <v>30</v>
@@ -21035,10 +21035,10 @@
     </row>
     <row r="416" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="B416" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="D416">
         <v>1894</v>
@@ -21050,10 +21050,10 @@
         <v>56</v>
       </c>
       <c r="J416" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="L416" s="1" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="R416" t="s">
         <v>30</v>
@@ -21062,7 +21062,7 @@
         <v>31</v>
       </c>
       <c r="T416" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="U416" t="s">
         <v>129</v>
@@ -21073,10 +21073,10 @@
     </row>
     <row r="417" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="B417" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="D417">
         <v>1895</v>
@@ -21088,10 +21088,10 @@
         <v>56</v>
       </c>
       <c r="J417" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="L417" s="1" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="R417" t="s">
         <v>30</v>
@@ -21103,7 +21103,7 @@
         <v>658</v>
       </c>
       <c r="U417" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="W417">
         <v>3</v>
@@ -21111,13 +21111,13 @@
     </row>
     <row r="418" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B418" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D418" t="s">
         <v>1547</v>
-      </c>
-      <c r="B418" t="s">
-        <v>1548</v>
-      </c>
-      <c r="D418" t="s">
-        <v>1549</v>
       </c>
       <c r="E418" t="s">
         <v>111</v>
@@ -21126,10 +21126,10 @@
         <v>112</v>
       </c>
       <c r="J418" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="L418" s="1" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="R418" t="s">
         <v>30</v>
@@ -21149,13 +21149,13 @@
     </row>
     <row r="419" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="B419" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="D419" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E419" t="s">
         <v>79</v>
@@ -21164,10 +21164,10 @@
         <v>80</v>
       </c>
       <c r="J419" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="L419" s="1" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="R419" t="s">
         <v>30</v>
@@ -21187,10 +21187,10 @@
     </row>
     <row r="420" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="B420" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="D420">
         <v>1875</v>
@@ -21202,16 +21202,16 @@
         <v>437</v>
       </c>
       <c r="J420" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="L420" s="1" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="R420" t="s">
         <v>30</v>
       </c>
       <c r="S420" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="T420" t="s">
         <v>115</v>
@@ -21225,25 +21225,25 @@
     </row>
     <row r="421" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="B421" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="D421" t="s">
+        <v>1554</v>
+      </c>
+      <c r="E421" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F421" t="s">
         <v>1556</v>
       </c>
-      <c r="E421" t="s">
+      <c r="J421" t="s">
         <v>1557</v>
       </c>
-      <c r="F421" t="s">
+      <c r="L421" s="1" t="s">
         <v>1558</v>
-      </c>
-      <c r="J421" t="s">
-        <v>1559</v>
-      </c>
-      <c r="L421" s="1" t="s">
-        <v>1560</v>
       </c>
       <c r="R421" t="s">
         <v>30</v>
@@ -21648,41 +21648,41 @@
     <hyperlink ref="L386" r:id="rId383" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
     <hyperlink ref="L387" r:id="rId384" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
     <hyperlink ref="L388" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="L389" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="L390" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="L391" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="L392" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="L393" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="L394" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="L395" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="L396" r:id="rId393" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="L397" r:id="rId394" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="L398" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="L399" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="L400" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="L401" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="L402" r:id="rId399" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="L403" r:id="rId400" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="L404" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="L405" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="L406" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="L407" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="L408" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="L409" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="L410" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="L411" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="L412" r:id="rId409" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="L413" r:id="rId410" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="L414" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="L415" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="L416" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="L417" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="L418" r:id="rId415" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="L419" r:id="rId416" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="L420" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="L421" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="L262" r:id="rId419" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/Jean-Fran%C3%A7ois_Millet_-_The_Sower_-_Google_Art_Project.jpg/960px-Jean-Fran%C3%A7ois_Millet_-_The_Sower_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AD55A34B-4E25-4396-B911-838D251D201A}"/>
-    <hyperlink ref="L298" r:id="rId420" xr:uid="{DDE94C4E-CF54-4E41-BCDD-0E2DF2D957BF}"/>
+    <hyperlink ref="L390" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="L391" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="L392" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="L393" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="L394" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="L395" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="L396" r:id="rId392" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="L397" r:id="rId393" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="L398" r:id="rId394" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="L399" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="L400" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="L401" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="L402" r:id="rId398" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="L403" r:id="rId399" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="L404" r:id="rId400" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="L405" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="L406" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="L407" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="L408" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="L409" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="L410" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="L411" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="L412" r:id="rId408" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="L413" r:id="rId409" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="L414" r:id="rId410" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="L415" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="L416" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="L417" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="L418" r:id="rId414" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="L419" r:id="rId415" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="L420" r:id="rId416" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="L421" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="L262" r:id="rId418" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/Jean-Fran%C3%A7ois_Millet_-_The_Sower_-_Google_Art_Project.jpg/960px-Jean-Fran%C3%A7ois_Millet_-_The_Sower_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AD55A34B-4E25-4396-B911-838D251D201A}"/>
+    <hyperlink ref="L298" r:id="rId419" xr:uid="{DDE94C4E-CF54-4E41-BCDD-0E2DF2D957BF}"/>
+    <hyperlink ref="L389" r:id="rId420" xr:uid="{866FB934-71A2-4526-80D9-C78373652DF4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -6211,8 +6211,10 @@
       <c r="R26" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="S26" t="s">
-        <v>172</v>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aquarelle, graphite et encre sur papier</t>
+        </is>
       </c>
       <c r="T26" t="s">
         <v>173</v>
@@ -6290,8 +6292,10 @@
       <c r="R28" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="S28" t="s">
-        <v>172</v>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aquarelle, graphite et encre sur papier</t>
+        </is>
       </c>
       <c r="T28" t="s">
         <v>173</v>
@@ -6331,8 +6335,10 @@
       <c r="R29" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="S29" t="s">
-        <v>172</v>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aquarelle, graphite et encre sur papier</t>
+        </is>
       </c>
       <c r="T29" t="s">
         <v>188</v>
@@ -15843,8 +15849,10 @@
       <c r="R279" t="s">
         <v>30</v>
       </c>
-      <c r="S279" t="s">
-        <v>31</v>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huile sur toile</t>
+        </is>
       </c>
       <c r="T279" t="s">
         <v>116</v>
@@ -15995,8 +16003,10 @@
       <c r="R283" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="S283" t="s">
-        <v>171</v>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aquarelle sur papier</t>
+        </is>
       </c>
       <c r="T283" t="s">
         <v>1158</v>
@@ -16413,8 +16423,10 @@
       <c r="R294" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="S294" t="s">
-        <v>1189</v>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aquarelle et gouache sur papier</t>
+        </is>
       </c>
       <c r="T294" t="s">
         <v>441</v>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -5194,10 +5194,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W421"/>
+  <dimension ref="A1:X421"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="24" max="24" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
@@ -5269,6 +5270,11 @@
       </c>
       <c r="W1" t="s">
         <v>22</v>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artiste associé</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
